--- a/tonghop.xlsx
+++ b/tonghop.xlsx
@@ -13,7 +13,7 @@
 </file>
 
 <file path=xl/sharedStrings.xml><?xml version="1.0" encoding="utf-8"?>
-<sst xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" count="45" uniqueCount="3">
+<sst xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" count="63" uniqueCount="3">
   <si>
     <t>N = 40</t>
   </si>
@@ -86,162 +86,162 @@
     </row>
     <row r="10">
       <c r="B10" t="n" s="0">
-        <v>9.81362429068405E-42</v>
+        <v>2.9177517341774225E-42</v>
       </c>
       <c r="C10" t="n" s="0">
-        <v>3.361151824300803E-41</v>
+        <v>7.089653071007392E-42</v>
       </c>
       <c r="D10" t="n" s="0">
-        <v>2.8641251833428423</v>
+        <v>2.2131917145449553</v>
       </c>
       <c r="E10" t="n" s="0">
-        <v>3.1449210724492405</v>
+        <v>5.178013628769972</v>
       </c>
       <c r="F10" t="n" s="0">
-        <v>1.6092111552395564E-31</v>
+        <v>1.724454052270313E-31</v>
       </c>
       <c r="G10" t="n" s="0">
-        <v>4.89766532996706E-31</v>
+        <v>3.490619011033126E-31</v>
       </c>
     </row>
     <row r="11">
       <c r="B11" t="n" s="0">
-        <v>5.004707992415383E-25</v>
+        <v>1.0276298862925235E-24</v>
       </c>
       <c r="C11" t="n" s="0">
-        <v>6.724916374361237E-25</v>
+        <v>3.049141996396935E-24</v>
       </c>
       <c r="D11" t="n" s="0">
-        <v>1.4051602951325874</v>
+        <v>1.454504096797602</v>
       </c>
       <c r="E11" t="n" s="0">
-        <v>1.0968572961696383</v>
+        <v>1.7880175461906482</v>
       </c>
       <c r="F11" t="n" s="0">
-        <v>7.905532314668865E-19</v>
+        <v>7.70012145688017E-19</v>
       </c>
       <c r="G11" t="n" s="0">
-        <v>9.61747181270983E-19</v>
+        <v>7.888619733545883E-19</v>
       </c>
     </row>
     <row r="12">
       <c r="B12" t="n" s="0">
-        <v>2.3886786954333466E-18</v>
+        <v>1.8526002261762448E-17</v>
       </c>
       <c r="C12" t="n" s="0">
-        <v>9.205912042312339E-18</v>
+        <v>9.960138280350122E-17</v>
       </c>
       <c r="D12" t="n" s="0">
-        <v>343.2857497536533</v>
+        <v>224.6661711797245</v>
       </c>
       <c r="E12" t="n" s="0">
-        <v>740.1205158352815</v>
+        <v>250.58130789597507</v>
       </c>
       <c r="F12" t="n" s="0">
-        <v>1.604967706709874E-14</v>
+        <v>1.3671916693888264E-13</v>
       </c>
       <c r="G12" t="n" s="0">
-        <v>3.916880700852916E-14</v>
+        <v>5.595571762905442E-13</v>
       </c>
     </row>
     <row r="13">
       <c r="B13" t="n" s="0">
-        <v>1.6653816980282426E-13</v>
+        <v>1.0607411328021336E-13</v>
       </c>
       <c r="C13" t="n" s="0">
-        <v>2.6674041582009146E-13</v>
+        <v>1.2908875993460818E-13</v>
       </c>
       <c r="D13" t="n" s="0">
-        <v>2.5058759148443945</v>
+        <v>3.684960789305568</v>
       </c>
       <c r="E13" t="n" s="0">
-        <v>2.0580071313367982</v>
+        <v>6.762120840002016</v>
       </c>
       <c r="F13" t="n" s="0">
-        <v>5.767338472516947E-10</v>
+        <v>4.349289616484926E-10</v>
       </c>
       <c r="G13" t="n" s="0">
-        <v>1.467425971097447E-9</v>
+        <v>7.448081397331155E-10</v>
       </c>
     </row>
     <row r="14">
       <c r="B14" t="n" s="0">
-        <v>6.896208615852859</v>
+        <v>6.966797840015383</v>
       </c>
       <c r="C14" t="n" s="0">
-        <v>0.509466027374127</v>
+        <v>0.5363160884258577</v>
       </c>
       <c r="D14" t="n" s="0">
-        <v>209.06166785389394</v>
+        <v>5596.967481243784</v>
       </c>
       <c r="E14" t="n" s="0">
-        <v>286.83874804952933</v>
+        <v>19344.626969838264</v>
       </c>
       <c r="F14" t="n" s="0">
-        <v>6.338347546214894</v>
+        <v>6.241684912162886</v>
       </c>
       <c r="G14" t="n" s="0">
-        <v>0.3218499441345193</v>
+        <v>0.25434322500567635</v>
       </c>
     </row>
     <row r="15">
       <c r="B15" t="n" s="0">
-        <v>3.418591151775146E-6</v>
+        <v>0.008333033692900544</v>
       </c>
       <c r="C15" t="n" s="0">
-        <v>1.3199165755746752E-6</v>
+        <v>0.04562781688610472</v>
       </c>
       <c r="D15" t="n" s="0">
-        <v>10.370568107410946</v>
+        <v>7.491703175796101</v>
       </c>
       <c r="E15" t="n" s="0">
-        <v>47.682506013871006</v>
+        <v>18.333566454128015</v>
       </c>
       <c r="F15" t="n" s="0">
-        <v>3.93724834784541E-6</v>
+        <v>5.002207093377064E-6</v>
       </c>
       <c r="G15" t="n" s="0">
-        <v>1.9890598887963447E-6</v>
+        <v>2.948276877432131E-6</v>
       </c>
     </row>
     <row r="16">
       <c r="B16" t="n" s="0">
-        <v>0.47803884410159375</v>
+        <v>0.5394220925013808</v>
       </c>
       <c r="C16" t="n" s="0">
-        <v>0.30869427416523315</v>
+        <v>0.28431630217448756</v>
       </c>
       <c r="D16" t="n" s="0">
-        <v>0.030332053732468202</v>
+        <v>0.029771540100975356</v>
       </c>
       <c r="E16" t="n" s="0">
-        <v>0.022606531658903792</v>
+        <v>0.02834745446404371</v>
       </c>
       <c r="F16" t="n" s="0">
-        <v>0.4786925609674597</v>
+        <v>0.4571970554841536</v>
       </c>
       <c r="G16" t="n" s="0">
-        <v>0.27954169816224766</v>
+        <v>0.2889649034038536</v>
       </c>
     </row>
     <row r="17">
       <c r="B17" t="n" s="0">
-        <v>-659.36114917496</v>
+        <v>-611.174938030123</v>
       </c>
       <c r="C17" t="n" s="0">
-        <v>121.27182389875391</v>
+        <v>153.73190148520112</v>
       </c>
       <c r="D17" t="n" s="0">
-        <v>-2914.6818154067546</v>
+        <v>-2893.486413627907</v>
       </c>
       <c r="E17" t="n" s="0">
-        <v>484.2755654532459</v>
+        <v>403.1176254836665</v>
       </c>
       <c r="F17" t="n" s="0">
-        <v>-2581.4978054474764</v>
+        <v>-2556.2319453525074</v>
       </c>
       <c r="G17" t="n" s="0">
-        <v>351.9133029670419</v>
+        <v>330.2041947785638</v>
       </c>
     </row>
     <row r="18">
@@ -252,318 +252,318 @@
         <v>0.0</v>
       </c>
       <c r="D18" t="n" s="0">
-        <v>31.16537813770562</v>
+        <v>28.362379246292335</v>
       </c>
       <c r="E18" t="n" s="0">
-        <v>14.688846464999498</v>
+        <v>14.387861409370057</v>
       </c>
       <c r="F18" t="n" s="0">
-        <v>0.0</v>
+        <v>4.144832625267251E-16</v>
       </c>
       <c r="G18" t="n" s="0">
-        <v>0.0</v>
+        <v>1.7256080763143042E-15</v>
       </c>
     </row>
     <row r="19">
       <c r="B19" t="n" s="0">
-        <v>3.641531520770513E-15</v>
+        <v>3.4046839421838135E-15</v>
       </c>
       <c r="C19" t="n" s="0">
-        <v>1.0840344679840707E-15</v>
+        <v>1.3466526446473342E-15</v>
       </c>
       <c r="D19" t="n" s="0">
-        <v>3.9126361059709756</v>
+        <v>3.177974736807275</v>
       </c>
       <c r="E19" t="n" s="0">
-        <v>4.331872900478235</v>
+        <v>2.4807037405367973</v>
       </c>
       <c r="F19" t="n" s="0">
-        <v>6.8389738316909644E-15</v>
+        <v>7.431092778157715E-15</v>
       </c>
       <c r="G19" t="n" s="0">
-        <v>2.1680689359681413E-15</v>
+        <v>2.8731395141844268E-15</v>
       </c>
     </row>
     <row r="20">
       <c r="B20" t="n" s="0">
-        <v>0.009355815899494475</v>
+        <v>0.008318953226763244</v>
       </c>
       <c r="C20" t="n" s="0">
-        <v>0.011048384233869842</v>
+        <v>0.010193810432926829</v>
       </c>
       <c r="D20" t="n" s="0">
-        <v>0.4965105332910325</v>
+        <v>0.46424115720296355</v>
       </c>
       <c r="E20" t="n" s="0">
-        <v>0.34038771568142046</v>
+        <v>0.3038035190587179</v>
       </c>
       <c r="F20" t="n" s="0">
-        <v>0.006917053967802382</v>
+        <v>0.01017833001643839</v>
       </c>
       <c r="G20" t="n" s="0">
-        <v>0.008261169443653437</v>
+        <v>0.016075103840624848</v>
       </c>
     </row>
     <row r="21">
       <c r="B21" t="n" s="0">
-        <v>0.0032629849362122722</v>
+        <v>0.005339819468094124</v>
       </c>
       <c r="C21" t="n" s="0">
-        <v>0.0074173867450130215</v>
+        <v>0.010449406698155719</v>
       </c>
       <c r="D21" t="n" s="0">
-        <v>2.1406083253907826</v>
+        <v>1.938606493806445</v>
       </c>
       <c r="E21" t="n" s="0">
-        <v>3.7313099968073598</v>
+        <v>1.778542332717744</v>
       </c>
       <c r="F21" t="n" s="0">
-        <v>6.708935512090463E-4</v>
+        <v>3.394652849368371E-6</v>
       </c>
       <c r="G21" t="n" s="0">
-        <v>0.0036540691013980772</v>
+        <v>2.3662041523315276E-6</v>
       </c>
     </row>
     <row r="22">
       <c r="B22" t="n" s="0">
-        <v>0.01213327412330909</v>
+        <v>0.01617509140956585</v>
       </c>
       <c r="C22" t="n" s="0">
-        <v>0.048793114068164396</v>
+        <v>0.041908587178452486</v>
       </c>
       <c r="D22" t="n" s="0">
-        <v>0.9549306453024619</v>
+        <v>1.7601071735540819</v>
       </c>
       <c r="E22" t="n" s="0">
-        <v>1.949743692679735</v>
+        <v>3.914136932321208</v>
       </c>
       <c r="F22" t="n" s="0">
-        <v>0.006559240651184046</v>
+        <v>2.5504320041164948E-5</v>
       </c>
       <c r="G22" t="n" s="0">
-        <v>0.025620240626401402</v>
+        <v>1.7556825717330505E-5</v>
       </c>
     </row>
     <row r="23">
       <c r="B23" t="n" s="0">
-        <v>7.641006518420377</v>
+        <v>9.321614363840341</v>
       </c>
       <c r="C23" t="n" s="0">
-        <v>4.474501751527129</v>
+        <v>4.132998401597906</v>
       </c>
       <c r="D23" t="n" s="0">
-        <v>0.9933826609434998</v>
+        <v>0.5969512887758069</v>
       </c>
       <c r="E23" t="n" s="0">
-        <v>1.5414038744592573</v>
+        <v>1.0948597398062632</v>
       </c>
       <c r="F23" t="n" s="0">
-        <v>0.16620140455918517</v>
+        <v>0.4980739997587698</v>
       </c>
       <c r="G23" t="n" s="0">
-        <v>0.4596675827525284</v>
+        <v>0.8576429151689016</v>
       </c>
     </row>
     <row r="24">
       <c r="B24" t="n" s="0">
-        <v>4.851439931564325E-4</v>
+        <v>5.071046864729419E-4</v>
       </c>
       <c r="C24" t="n" s="0">
-        <v>1.281972946418297E-4</v>
+        <v>2.4284193845324406E-4</v>
       </c>
       <c r="D24" t="n" s="0">
-        <v>0.0062047147220433705</v>
+        <v>0.006646706505048757</v>
       </c>
       <c r="E24" t="n" s="0">
-        <v>0.008121308506072109</v>
+        <v>0.008401845767439277</v>
       </c>
       <c r="F24" t="n" s="0">
-        <v>3.1691498562194854E-4</v>
+        <v>3.597552966743655E-4</v>
       </c>
       <c r="G24" t="n" s="0">
-        <v>2.5579917990260454E-5</v>
+        <v>2.3518084000811746E-4</v>
       </c>
     </row>
     <row r="25">
       <c r="B25" t="n" s="0">
-        <v>-1.031628384747976</v>
+        <v>-1.0316283776263817</v>
       </c>
       <c r="C25" t="n" s="0">
-        <v>8.169860778140706E-8</v>
+        <v>8.527769332519992E-8</v>
       </c>
       <c r="D25" t="n" s="0">
-        <v>-1.0316284534898466</v>
+        <v>-1.0316284534663454</v>
       </c>
       <c r="E25" t="n" s="0">
-        <v>1.5955510587602435E-13</v>
+        <v>1.288684039502953E-10</v>
       </c>
       <c r="F25" t="n" s="0">
-        <v>-1.0316283365958094</v>
+        <v>-1.0316283829263748</v>
       </c>
       <c r="G25" t="n" s="0">
-        <v>1.6057204559107025E-7</v>
+        <v>6.758898388035616E-8</v>
       </c>
     </row>
     <row r="26">
       <c r="B26" t="n" s="0">
-        <v>0.3978888189235601</v>
+        <v>0.3978884908729379</v>
       </c>
       <c r="C26" t="n" s="0">
-        <v>1.3801924494954916E-6</v>
+        <v>8.880305698560583E-7</v>
       </c>
       <c r="D26" t="n" s="0">
-        <v>0.397887357729741</v>
+        <v>0.39788735772973877</v>
       </c>
       <c r="E26" t="n" s="0">
-        <v>1.556721547335102E-14</v>
+        <v>2.9257389466589586E-15</v>
       </c>
       <c r="F26" t="n" s="0">
-        <v>0.397889041322802</v>
+        <v>0.3978898860528747</v>
       </c>
       <c r="G26" t="n" s="0">
-        <v>2.0502810458781845E-6</v>
+        <v>4.3593914417514265E-6</v>
       </c>
     </row>
     <row r="27">
       <c r="B27" t="n" s="0">
-        <v>3.0008671462336705</v>
+        <v>3.0008907188891665</v>
       </c>
       <c r="C27" t="n" s="0">
-        <v>0.0017571963580759482</v>
+        <v>0.0022227405692715066</v>
       </c>
       <c r="D27" t="n" s="0">
-        <v>3.0000000077417943</v>
+        <v>2.9999999999999125</v>
       </c>
       <c r="E27" t="n" s="0">
-        <v>4.2404003613993165E-8</v>
+        <v>7.42920327257848E-15</v>
       </c>
       <c r="F27" t="n" s="0">
-        <v>3.0000490719185295</v>
+        <v>3.000029031210531</v>
       </c>
       <c r="G27" t="n" s="0">
-        <v>8.880351707411086E-5</v>
+        <v>4.0487927392878346E-5</v>
       </c>
     </row>
     <row r="28">
       <c r="B28" t="n" s="0">
-        <v>-3.8618432336684925</v>
+        <v>-3.861220769942824</v>
       </c>
       <c r="C28" t="n" s="0">
-        <v>9.767559035457989E-4</v>
+        <v>0.001840863511305315</v>
       </c>
       <c r="D28" t="n" s="0">
-        <v>-3.8626919722215507</v>
+        <v>-3.8607971066960953</v>
       </c>
       <c r="E28" t="n" s="0">
-        <v>2.077993298434464E-4</v>
+        <v>0.009910303284647827</v>
       </c>
       <c r="F28" t="n" s="0">
-        <v>-3.8625635984229976</v>
+        <v>-3.8626275516717135</v>
       </c>
       <c r="G28" t="n" s="0">
-        <v>3.96407251143115E-4</v>
+        <v>2.0234624687636593E-4</v>
       </c>
     </row>
     <row r="29">
       <c r="B29" t="n" s="0">
-        <v>-3.321974607042488</v>
+        <v>-3.3219743546827103</v>
       </c>
       <c r="C29" t="n" s="0">
-        <v>1.875496818488766E-5</v>
+        <v>2.0123054782094338E-5</v>
       </c>
       <c r="D29" t="n" s="0">
-        <v>-3.2095738045716478</v>
+        <v>-3.25219621624131</v>
       </c>
       <c r="E29" t="n" s="0">
-        <v>0.18297645469284413</v>
+        <v>0.09235360697808004</v>
       </c>
       <c r="F29" t="n" s="0">
-        <v>-3.3219694579474197</v>
+        <v>-3.3219715635844267</v>
       </c>
       <c r="G29" t="n" s="0">
-        <v>2.1669514223522357E-5</v>
+        <v>1.6468153376083595E-5</v>
       </c>
     </row>
     <row r="30">
       <c r="B30" t="n" s="0">
-        <v>-10.151685006867076</v>
+        <v>-10.151876610777917</v>
       </c>
       <c r="C30" t="n" s="0">
-        <v>0.0010220123114191835</v>
+        <v>5.011551331872219E-4</v>
       </c>
       <c r="D30" t="n" s="0">
-        <v>-7.376573830628411</v>
+        <v>-7.293880151702999</v>
       </c>
       <c r="E30" t="n" s="0">
-        <v>2.910944917321862</v>
+        <v>2.7872243471395115</v>
       </c>
       <c r="F30" t="n" s="0">
-        <v>-10.151674931702868</v>
+        <v>-9.983171636887015</v>
       </c>
       <c r="G30" t="n" s="0">
-        <v>0.001414336558295026</v>
+        <v>0.9224694251014163</v>
       </c>
     </row>
     <row r="31">
       <c r="B31" t="n" s="0">
-        <v>-10.401579255538703</v>
+        <v>-10.1789955375105</v>
       </c>
       <c r="C31" t="n" s="0">
-        <v>9.304719892030189E-4</v>
+        <v>1.2191196529184254</v>
       </c>
       <c r="D31" t="n" s="0">
-        <v>-7.624843612221154</v>
+        <v>-7.334027911838926</v>
       </c>
       <c r="E31" t="n" s="0">
-        <v>3.114301261693909</v>
+        <v>2.7624552737467964</v>
       </c>
       <c r="F31" t="n" s="0">
-        <v>-10.225186510810968</v>
+        <v>-10.049523923262825</v>
       </c>
       <c r="G31" t="n" s="0">
-        <v>0.9627430213373406</v>
+        <v>1.3384536681122108</v>
       </c>
     </row>
     <row r="32">
       <c r="B32" t="n" s="0">
-        <v>-10.53481049515502</v>
+        <v>-10.535124793802646</v>
       </c>
       <c r="C32" t="n" s="0">
-        <v>8.012968584440353E-4</v>
+        <v>9.97593699718798E-4</v>
       </c>
       <c r="D32" t="n" s="0">
-        <v>-6.278723007996278</v>
+        <v>-7.56755310086818</v>
       </c>
       <c r="E32" t="n" s="0">
-        <v>2.7881527111296407</v>
+        <v>3.327355022128981</v>
       </c>
       <c r="F32" t="n" s="0">
-        <v>-10.177445437232812</v>
+        <v>-10.356370715860681</v>
       </c>
       <c r="G32" t="n" s="0">
-        <v>1.3603432209348878</v>
+        <v>0.9786255171131002</v>
       </c>
     </row>
     <row r="39">
       <c r="B39" t="n" s="0">
-        <v>2.8719490663203402E-11</v>
+        <v>5.31674280364282E-10</v>
       </c>
       <c r="E39" t="n" s="0">
         <v>2.8719490663203402E-11</v>
       </c>
       <c r="H39" t="n" s="0">
-        <v>2.8719490663203402E-11</v>
+        <v>5.31674280364282E-10</v>
       </c>
     </row>
     <row r="40">
       <c r="B40" t="n" s="0">
-        <v>2.8719490663203402E-11</v>
+        <v>5.31674280364282E-10</v>
       </c>
       <c r="E40" t="n" s="0">
         <v>2.8719490663203402E-11</v>
       </c>
       <c r="H40" t="n" s="0">
-        <v>2.8719490663203402E-11</v>
+        <v>5.31674280364282E-10</v>
       </c>
     </row>
     <row r="41">
@@ -571,7 +571,7 @@
         <v>2.8719490663203402E-11</v>
       </c>
       <c r="E41" t="n" s="0">
-        <v>6.373034178451358E-11</v>
+        <v>5.7729863008733963E-11</v>
       </c>
       <c r="H41" t="n" s="0">
         <v>2.8719490663203402E-11</v>
@@ -590,13 +590,13 @@
     </row>
     <row r="43">
       <c r="B43" t="n" s="0">
-        <v>5.31674280364282E-10</v>
+        <v>8.487224956448446E-10</v>
       </c>
       <c r="E43" t="n" s="0">
-        <v>6.067192022543983E-6</v>
+        <v>4.619232489580079E-7</v>
       </c>
       <c r="H43" t="n" s="0">
-        <v>5.840569474989402E-10</v>
+        <v>3.6574283634182565E-9</v>
       </c>
     </row>
     <row r="44">
@@ -604,26 +604,26 @@
         <v>2.8719490663203402E-11</v>
       </c>
       <c r="E44" t="n" s="0">
-        <v>0.39117045199768496</v>
+        <v>0.0037585319247780517</v>
       </c>
       <c r="H44" t="n" s="0">
-        <v>2.8719490663203402E-11</v>
+        <v>8.562993904900892E-11</v>
       </c>
     </row>
     <row r="45">
       <c r="B45" t="n" s="0">
-        <v>6.414635193082751E-10</v>
+        <v>7.03394552480195E-11</v>
       </c>
       <c r="E45" t="n" s="0">
-        <v>0.8941460645782623</v>
+        <v>0.26117582460728006</v>
       </c>
       <c r="H45" t="n" s="0">
-        <v>9.444947151237936E-11</v>
+        <v>4.838863000512779E-10</v>
       </c>
     </row>
     <row r="46">
       <c r="B46" t="n" s="0">
-        <v>0.0047454249600479975</v>
+        <v>0.0015568790292720205</v>
       </c>
       <c r="E46" t="n" s="0">
         <v>2.8719490663203402E-11</v>
@@ -637,7 +637,7 @@
         <v>2.8719490663203402E-11</v>
       </c>
       <c r="E47" t="n" s="0">
-        <v>1.0</v>
+        <v>0.6573804271100814</v>
       </c>
       <c r="H47" t="n" s="0">
         <v>2.8719490663203402E-11</v>
@@ -645,13 +645,13 @@
     </row>
     <row r="48">
       <c r="B48" t="n" s="0">
-        <v>3.643171050266978E-10</v>
+        <v>2.8719490663203402E-11</v>
       </c>
       <c r="E48" t="n" s="0">
-        <v>4.275281031924089E-7</v>
+        <v>8.351995916556194E-8</v>
       </c>
       <c r="H48" t="n" s="0">
-        <v>1.0936695631099071E-10</v>
+        <v>2.8719490663203402E-11</v>
       </c>
     </row>
     <row r="49">
@@ -659,7 +659,7 @@
         <v>2.8719490663203402E-11</v>
       </c>
       <c r="E49" t="n" s="0">
-        <v>0.6897609572758945</v>
+        <v>0.7787839689422887</v>
       </c>
       <c r="H49" t="n" s="0">
         <v>2.8719490663203402E-11</v>
@@ -667,57 +667,57 @@
     </row>
     <row r="50">
       <c r="B50" t="n" s="0">
-        <v>3.8787144759013784E-11</v>
+        <v>2.8719490663203402E-11</v>
       </c>
       <c r="E50" t="n" s="0">
-        <v>0.09775105544859974</v>
+        <v>0.5444075540129325</v>
       </c>
       <c r="H50" t="n" s="0">
-        <v>1.2657957728370648E-10</v>
+        <v>5.7729863008733963E-11</v>
       </c>
     </row>
     <row r="51">
       <c r="B51" t="n" s="0">
-        <v>7.03394552480195E-11</v>
+        <v>2.8719490663203402E-11</v>
       </c>
       <c r="E51" t="n" s="0">
-        <v>0.10078263179832236</v>
+        <v>0.08909163442771983</v>
       </c>
       <c r="H51" t="n" s="0">
-        <v>1.8647261589758743E-10</v>
+        <v>3.011893711871355E-10</v>
       </c>
     </row>
     <row r="52">
       <c r="B52" t="n" s="0">
-        <v>0.05099234896566832</v>
+        <v>8.339303300103502E-4</v>
       </c>
       <c r="E52" t="n" s="0">
-        <v>3.8787144759013784E-11</v>
+        <v>3.011893711871355E-10</v>
       </c>
       <c r="H52" t="n" s="0">
-        <v>5.224845695592977E-9</v>
+        <v>2.260390486287696E-10</v>
       </c>
     </row>
     <row r="53">
       <c r="B53" t="n" s="0">
-        <v>2.8719490663203402E-11</v>
+        <v>7.761734689605519E-11</v>
       </c>
       <c r="E53" t="n" s="0">
-        <v>6.812005340813848E-9</v>
+        <v>1.3690186798427894E-8</v>
       </c>
       <c r="H53" t="n" s="0">
-        <v>9.444947151237936E-11</v>
+        <v>7.761734689605519E-11</v>
       </c>
     </row>
     <row r="54">
       <c r="B54" t="n" s="0">
-        <v>2.8719490663203402E-11</v>
+        <v>3.175217248668002E-11</v>
       </c>
       <c r="E54" t="n" s="0">
-        <v>0.344044940644476</v>
+        <v>0.8130052876119973</v>
       </c>
       <c r="H54" t="n" s="0">
-        <v>2.8719490663203402E-11</v>
+        <v>3.175217248668002E-11</v>
       </c>
     </row>
     <row r="55">
@@ -725,7 +725,7 @@
         <v>2.8719490663203402E-11</v>
       </c>
       <c r="E55" t="n" s="0">
-        <v>0.9293151249146342</v>
+        <v>0.4246622046508919</v>
       </c>
       <c r="H55" t="n" s="0">
         <v>2.8719490663203402E-11</v>
@@ -736,65 +736,65 @@
         <v>2.8719490663203402E-11</v>
       </c>
       <c r="E56" t="n" s="0">
-        <v>0.847587480259332</v>
+        <v>0.8708108045360416</v>
       </c>
       <c r="H56" t="n" s="0">
-        <v>3.8787144759013784E-11</v>
+        <v>2.8719490663203402E-11</v>
       </c>
     </row>
     <row r="57">
       <c r="B57" t="n" s="0">
-        <v>1.2857816253298126E-4</v>
+        <v>0.0021038931094179507</v>
       </c>
       <c r="E57" t="n" s="0">
-        <v>4.58482304215622E-4</v>
+        <v>2.1104831763424417E-7</v>
       </c>
       <c r="H57" t="n" s="0">
-        <v>1.3057305617737233E-7</v>
+        <v>3.6599799289507135E-7</v>
       </c>
     </row>
     <row r="58">
       <c r="B58" t="n" s="0">
-        <v>2.9212595033341424E-4</v>
+        <v>0.01729890096036322</v>
       </c>
       <c r="E58" t="n" s="0">
-        <v>0.47791970420909236</v>
+        <v>0.39938939501369475</v>
       </c>
       <c r="H58" t="n" s="0">
-        <v>2.320278143607131E-4</v>
+        <v>0.014119268503564276</v>
       </c>
     </row>
     <row r="59">
       <c r="B59" t="n" s="0">
-        <v>0.6467245773434842</v>
+        <v>0.8130052876119973</v>
       </c>
       <c r="E59" t="n" s="0">
-        <v>0.6256305639654388</v>
+        <v>0.9528424295801989</v>
       </c>
       <c r="H59" t="n" s="0">
-        <v>0.6467245773434842</v>
+        <v>0.6573804271100814</v>
       </c>
     </row>
     <row r="60">
       <c r="B60" t="n" s="0">
-        <v>0.7227197915710599</v>
+        <v>0.5542678363243183</v>
       </c>
       <c r="E60" t="n" s="0">
-        <v>0.03578267558370112</v>
+        <v>0.882465683286275</v>
       </c>
       <c r="H60" t="n" s="0">
-        <v>0.6256305639654388</v>
+        <v>0.48713803171001935</v>
       </c>
     </row>
     <row r="61">
       <c r="B61" t="n" s="0">
-        <v>0.01009698661285167</v>
+        <v>0.7901470561745595</v>
       </c>
       <c r="E61" t="n" s="0">
-        <v>0.1646090619494488</v>
+        <v>0.9646228051136888</v>
       </c>
       <c r="H61" t="n" s="0">
-        <v>0.0019045321644495508</v>
+        <v>0.678900536466896</v>
       </c>
     </row>
   </sheetData>
@@ -809,738 +809,738 @@
   <sheetData>
     <row r="6">
       <c r="C6" t="n" s="0">
-        <v>1.1512866511916149E-42</v>
+        <v>4.0504039776101785E-44</v>
       </c>
       <c r="D6" t="n" s="0">
-        <v>3.659778158913924E-43</v>
+        <v>1.9692804454414784E-42</v>
       </c>
       <c r="E6" t="n" s="0">
-        <v>7.946245640868671E-41</v>
+        <v>2.3515900997804525E-42</v>
       </c>
       <c r="F6" t="n" s="0">
-        <v>6.299485685850304E-46</v>
+        <v>2.6158838728718237E-44</v>
       </c>
       <c r="G6" t="n" s="0">
-        <v>3.809465994540623E-43</v>
+        <v>2.418797133699933E-44</v>
       </c>
       <c r="H6" t="n" s="0">
-        <v>6.344573877187998E-43</v>
+        <v>4.287890362038066E-43</v>
       </c>
       <c r="I6" t="n" s="0">
-        <v>9.46693794063556E-44</v>
+        <v>6.63313300764729E-44</v>
       </c>
       <c r="J6" t="n" s="0">
-        <v>1.4071248465878353E-41</v>
+        <v>1.0215065588534016E-42</v>
       </c>
       <c r="K6" t="n" s="0">
-        <v>1.2385404380668103E-44</v>
+        <v>4.924865117939057E-43</v>
       </c>
       <c r="L6" t="n" s="0">
-        <v>1.0541687684889608E-43</v>
+        <v>1.9935380796085695E-43</v>
       </c>
       <c r="M6" t="n" s="0">
-        <v>4.69598111882626E-43</v>
+        <v>4.349872829483617E-43</v>
       </c>
       <c r="N6" t="n" s="0">
-        <v>3.7383093408321303E-42</v>
+        <v>7.930477840859395E-44</v>
       </c>
       <c r="O6" t="n" s="0">
-        <v>2.1285666098221158E-45</v>
+        <v>3.273965830576057E-44</v>
       </c>
       <c r="P6" t="n" s="0">
-        <v>6.422692418843085E-43</v>
+        <v>5.8490196986366235E-43</v>
       </c>
       <c r="Q6" t="n" s="0">
-        <v>2.546347207928075E-44</v>
+        <v>2.696354089533025E-43</v>
       </c>
       <c r="R6" t="n" s="0">
-        <v>2.814780039116741E-42</v>
+        <v>1.0177095952537297E-41</v>
       </c>
       <c r="S6" t="n" s="0">
-        <v>2.3500563953877646E-43</v>
+        <v>2.363765482193166E-44</v>
       </c>
       <c r="T6" t="n" s="0">
-        <v>1.6003671816840798E-41</v>
+        <v>6.584961293650075E-42</v>
       </c>
       <c r="U6" t="n" s="0">
-        <v>8.706167098030259E-44</v>
+        <v>1.1667457668638267E-43</v>
       </c>
       <c r="V6" t="n" s="0">
-        <v>1.6986382821210618E-40</v>
+        <v>9.457575468889791E-42</v>
       </c>
       <c r="W6" t="n" s="0">
-        <v>1.3746863069963865E-43</v>
+        <v>1.8960450344156734E-43</v>
       </c>
       <c r="X6" t="n" s="0">
-        <v>3.2317709540765582E-43</v>
+        <v>2.3400250285841756E-45</v>
       </c>
       <c r="Y6" t="n" s="0">
-        <v>1.2072692154988953E-43</v>
+        <v>9.766069855634474E-43</v>
       </c>
       <c r="Z6" t="n" s="0">
-        <v>1.0251847860133533E-42</v>
+        <v>4.2538599310127785E-44</v>
       </c>
       <c r="AA6" t="n" s="0">
-        <v>7.4256939244741E-44</v>
+        <v>2.4105711900022287E-42</v>
       </c>
       <c r="AB6" t="n" s="0">
-        <v>3.1964437702650556E-43</v>
+        <v>2.56501847588795E-43</v>
       </c>
       <c r="AC6" t="n" s="0">
-        <v>2.786817031199663E-43</v>
+        <v>1.1682574895141437E-41</v>
       </c>
       <c r="AD6" t="n" s="0">
-        <v>1.8393276380107418E-42</v>
+        <v>3.6345162718959566E-41</v>
       </c>
       <c r="AE6" t="n" s="0">
-        <v>7.424961193947627E-44</v>
+        <v>6.592246367693923E-43</v>
       </c>
       <c r="AF6" t="n" s="0">
-        <v>5.441996761309645E-44</v>
+        <v>5.857239385001771E-43</v>
       </c>
     </row>
     <row r="7">
       <c r="C7" t="n" s="0">
-        <v>6.408523410791984E-25</v>
+        <v>1.0358863111334551E-25</v>
       </c>
       <c r="D7" t="n" s="0">
-        <v>2.4521819340784446E-25</v>
+        <v>1.8837344786191837E-25</v>
       </c>
       <c r="E7" t="n" s="0">
-        <v>3.290481123478651E-24</v>
+        <v>3.5771009732602587E-25</v>
       </c>
       <c r="F7" t="n" s="0">
-        <v>1.5974972780722214E-25</v>
+        <v>1.4753824353899852E-26</v>
       </c>
       <c r="G7" t="n" s="0">
-        <v>3.301221555074112E-25</v>
+        <v>1.6750814000495968E-23</v>
       </c>
       <c r="H7" t="n" s="0">
-        <v>2.939522674218518E-25</v>
+        <v>1.5407688027576398E-25</v>
       </c>
       <c r="I7" t="n" s="0">
-        <v>1.4845238099003971E-24</v>
+        <v>3.4528999480798853E-25</v>
       </c>
       <c r="J7" t="n" s="0">
-        <v>1.2461290592193092E-24</v>
+        <v>1.8856780758407942E-24</v>
       </c>
       <c r="K7" t="n" s="0">
-        <v>5.123519845371257E-26</v>
+        <v>8.531163591558164E-26</v>
       </c>
       <c r="L7" t="n" s="0">
-        <v>1.0271251225778073E-26</v>
+        <v>1.579621913450988E-24</v>
       </c>
       <c r="M7" t="n" s="0">
-        <v>1.2770288011227483E-25</v>
+        <v>1.1430916706189086E-24</v>
       </c>
       <c r="N7" t="n" s="0">
-        <v>4.223157825099105E-25</v>
+        <v>3.6325483070224905E-26</v>
       </c>
       <c r="O7" t="n" s="0">
-        <v>1.1106250703845529E-25</v>
+        <v>3.6293548754551545E-25</v>
       </c>
       <c r="P7" t="n" s="0">
-        <v>1.0223061814363595E-25</v>
+        <v>2.8216619151408644E-26</v>
       </c>
       <c r="Q7" t="n" s="0">
-        <v>4.4051178219545665E-25</v>
+        <v>2.855406248731793E-24</v>
       </c>
       <c r="R7" t="n" s="0">
-        <v>6.989815679611673E-26</v>
+        <v>1.9749838076493865E-25</v>
       </c>
       <c r="S7" t="n" s="0">
-        <v>6.803260354691194E-26</v>
+        <v>2.1142027146792752E-26</v>
       </c>
       <c r="T7" t="n" s="0">
-        <v>1.1365885938613055E-24</v>
+        <v>6.631203190345066E-26</v>
       </c>
       <c r="U7" t="n" s="0">
-        <v>1.696818461088017E-25</v>
+        <v>5.607824529001428E-25</v>
       </c>
       <c r="V7" t="n" s="0">
-        <v>2.7849037523386906E-25</v>
+        <v>1.5463236877873837E-24</v>
       </c>
       <c r="W7" t="n" s="0">
-        <v>5.978614843587686E-26</v>
+        <v>9.416815615206929E-26</v>
       </c>
       <c r="X7" t="n" s="0">
-        <v>7.792215709505517E-25</v>
+        <v>1.2419807717954459E-24</v>
       </c>
       <c r="Y7" t="n" s="0">
-        <v>1.393321063989652E-24</v>
+        <v>7.298354663534371E-26</v>
       </c>
       <c r="Z7" t="n" s="0">
-        <v>1.599804052807417E-25</v>
+        <v>9.640718681497593E-26</v>
       </c>
       <c r="AA7" t="n" s="0">
-        <v>3.574431650831428E-25</v>
+        <v>4.870188259996254E-26</v>
       </c>
       <c r="AB7" t="n" s="0">
-        <v>1.1382447078228067E-25</v>
+        <v>2.6075650757479174E-26</v>
       </c>
       <c r="AC7" t="n" s="0">
-        <v>5.818185159358316E-26</v>
+        <v>6.07902672492792E-25</v>
       </c>
       <c r="AD7" t="n" s="0">
-        <v>1.692097694295222E-25</v>
+        <v>1.3657754895559114E-25</v>
       </c>
       <c r="AE7" t="n" s="0">
-        <v>5.615099903153665E-25</v>
+        <v>1.8498677871536001E-25</v>
       </c>
       <c r="AF7" t="n" s="0">
-        <v>6.82595268337315E-25</v>
+        <v>3.585980279385654E-26</v>
       </c>
     </row>
     <row r="8">
       <c r="C8" t="n" s="0">
-        <v>4.2119943841899027E-19</v>
+        <v>1.0507171292818545E-20</v>
       </c>
       <c r="D8" t="n" s="0">
-        <v>4.381395850893789E-21</v>
+        <v>3.8372839305341436E-20</v>
       </c>
       <c r="E8" t="n" s="0">
-        <v>6.260116244893611E-20</v>
+        <v>3.3908618872074443E-18</v>
       </c>
       <c r="F8" t="n" s="0">
-        <v>4.127908274221612E-19</v>
+        <v>8.586950133791081E-20</v>
       </c>
       <c r="G8" t="n" s="0">
-        <v>4.23880329472124E-20</v>
+        <v>1.54530155496427E-18</v>
       </c>
       <c r="H8" t="n" s="0">
-        <v>2.0135682448613218E-21</v>
+        <v>7.358887828791903E-20</v>
       </c>
       <c r="I8" t="n" s="0">
-        <v>2.3450740046003317E-17</v>
+        <v>8.855137730067429E-22</v>
       </c>
       <c r="J8" t="n" s="0">
-        <v>5.015880020345873E-19</v>
+        <v>7.7562774621362E-21</v>
       </c>
       <c r="K8" t="n" s="0">
-        <v>3.788527377761701E-21</v>
+        <v>4.968388160853927E-20</v>
       </c>
       <c r="L8" t="n" s="0">
-        <v>8.507413310659972E-21</v>
+        <v>3.347680157939785E-19</v>
       </c>
       <c r="M8" t="n" s="0">
-        <v>2.3257499629544677E-22</v>
+        <v>9.327968754670595E-20</v>
       </c>
       <c r="N8" t="n" s="0">
-        <v>1.9982042119186253E-20</v>
+        <v>2.3967035673983163E-21</v>
       </c>
       <c r="O8" t="n" s="0">
-        <v>8.547627136873204E-22</v>
+        <v>2.387166808790487E-19</v>
       </c>
       <c r="P8" t="n" s="0">
-        <v>4.5585529208248963E-17</v>
+        <v>5.9474831564375456E-21</v>
       </c>
       <c r="Q8" t="n" s="0">
-        <v>9.167255110133983E-21</v>
+        <v>3.2998947300696776E-21</v>
       </c>
       <c r="R8" t="n" s="0">
-        <v>5.1852263904429206E-21</v>
+        <v>6.155149174870284E-20</v>
       </c>
       <c r="S8" t="n" s="0">
-        <v>1.3460035491694067E-20</v>
+        <v>5.084700242489853E-19</v>
       </c>
       <c r="T8" t="n" s="0">
-        <v>1.8812898194277958E-19</v>
+        <v>7.187815667020594E-21</v>
       </c>
       <c r="U8" t="n" s="0">
-        <v>3.134810358381362E-22</v>
+        <v>7.127633678245827E-21</v>
       </c>
       <c r="V8" t="n" s="0">
-        <v>2.0876615500301524E-20</v>
+        <v>1.8730704495507578E-20</v>
       </c>
       <c r="W8" t="n" s="0">
-        <v>3.1909963288340687E-25</v>
+        <v>8.033244995729626E-21</v>
       </c>
       <c r="X8" t="n" s="0">
-        <v>4.592637959886433E-19</v>
+        <v>5.458649932025686E-16</v>
       </c>
       <c r="Y8" t="n" s="0">
-        <v>1.898116269190685E-21</v>
+        <v>3.299639295948034E-20</v>
       </c>
       <c r="Z8" t="n" s="0">
-        <v>5.279073167376671E-22</v>
+        <v>5.511490129604247E-20</v>
       </c>
       <c r="AA8" t="n" s="0">
-        <v>1.255410643761298E-20</v>
+        <v>2.0677081313923373E-20</v>
       </c>
       <c r="AB8" t="n" s="0">
-        <v>1.3762140652270731E-19</v>
+        <v>2.3963287714598974E-18</v>
       </c>
       <c r="AC8" t="n" s="0">
-        <v>1.12986531615161E-19</v>
+        <v>3.1803208660553714E-19</v>
       </c>
       <c r="AD8" t="n" s="0">
-        <v>1.6342023743341606E-19</v>
+        <v>8.042124410922859E-22</v>
       </c>
       <c r="AE8" t="n" s="0">
-        <v>2.1636986731404723E-23</v>
+        <v>4.565605863497307E-19</v>
       </c>
       <c r="AF8" t="n" s="0">
-        <v>1.8338207721860253E-20</v>
+        <v>1.422237321317478E-19</v>
       </c>
     </row>
     <row r="9">
       <c r="C9" t="n" s="0">
-        <v>1.5332331759264717E-13</v>
+        <v>6.583634640700722E-14</v>
       </c>
       <c r="D9" t="n" s="0">
-        <v>1.6952656834731834E-13</v>
+        <v>6.340174720230707E-14</v>
       </c>
       <c r="E9" t="n" s="0">
-        <v>7.247656527264659E-14</v>
+        <v>1.781465975163364E-14</v>
       </c>
       <c r="F9" t="n" s="0">
-        <v>1.5359914389456466E-13</v>
+        <v>5.618318246985251E-13</v>
       </c>
       <c r="G9" t="n" s="0">
-        <v>2.8052180216272812E-14</v>
+        <v>1.7160332006956292E-14</v>
       </c>
       <c r="H9" t="n" s="0">
-        <v>5.134837327178973E-14</v>
+        <v>3.333435575750976E-13</v>
       </c>
       <c r="I9" t="n" s="0">
-        <v>6.425974398251122E-14</v>
+        <v>6.832384127576501E-15</v>
       </c>
       <c r="J9" t="n" s="0">
-        <v>1.8979586407189767E-14</v>
+        <v>8.419816585805622E-14</v>
       </c>
       <c r="K9" t="n" s="0">
-        <v>5.427684796244129E-14</v>
+        <v>2.5657872541708155E-14</v>
       </c>
       <c r="L9" t="n" s="0">
-        <v>1.431568925687446E-13</v>
+        <v>1.0852617194033278E-15</v>
       </c>
       <c r="M9" t="n" s="0">
-        <v>1.228946401774097E-13</v>
+        <v>2.187017722902648E-14</v>
       </c>
       <c r="N9" t="n" s="0">
-        <v>4.0967739404460235E-13</v>
+        <v>9.595420516930221E-14</v>
       </c>
       <c r="O9" t="n" s="0">
-        <v>4.1919833368676395E-14</v>
+        <v>2.3160548136649567E-13</v>
       </c>
       <c r="P9" t="n" s="0">
-        <v>3.142341168807123E-14</v>
+        <v>3.7191530909215886E-14</v>
       </c>
       <c r="Q9" t="n" s="0">
-        <v>5.375595390397804E-14</v>
+        <v>1.9127710564115328E-14</v>
       </c>
       <c r="R9" t="n" s="0">
-        <v>2.4242884433918382E-14</v>
+        <v>2.2873039619340626E-13</v>
       </c>
       <c r="S9" t="n" s="0">
-        <v>2.3056759113389285E-13</v>
+        <v>4.987726963995796E-14</v>
       </c>
       <c r="T9" t="n" s="0">
-        <v>7.859115819878838E-14</v>
+        <v>7.029403325280555E-15</v>
       </c>
       <c r="U9" t="n" s="0">
-        <v>5.748097079830666E-13</v>
+        <v>3.1199464337711383E-13</v>
       </c>
       <c r="V9" t="n" s="0">
-        <v>1.0618447131832111E-13</v>
+        <v>8.065928186514006E-14</v>
       </c>
       <c r="W9" t="n" s="0">
-        <v>8.942460627157211E-14</v>
+        <v>4.8498590074885546E-14</v>
       </c>
       <c r="X9" t="n" s="0">
-        <v>1.3880888661962904E-12</v>
+        <v>2.169903984873692E-13</v>
       </c>
       <c r="Y9" t="n" s="0">
-        <v>3.364500669161378E-14</v>
+        <v>2.2027957955922428E-13</v>
       </c>
       <c r="Z9" t="n" s="0">
-        <v>1.0717239297777807E-13</v>
+        <v>9.40545748957236E-14</v>
       </c>
       <c r="AA9" t="n" s="0">
-        <v>4.5072585843845496E-13</v>
+        <v>2.5105695221599392E-15</v>
       </c>
       <c r="AB9" t="n" s="0">
-        <v>9.764949569508154E-14</v>
+        <v>5.940801424077945E-14</v>
       </c>
       <c r="AC9" t="n" s="0">
-        <v>4.313434863833767E-14</v>
+        <v>4.39450541025149E-15</v>
       </c>
       <c r="AD9" t="n" s="0">
-        <v>1.7438716762231163E-13</v>
+        <v>2.065245722682202E-14</v>
       </c>
       <c r="AE9" t="n" s="0">
-        <v>1.5786482565702117E-14</v>
+        <v>1.9918745772903004E-13</v>
       </c>
       <c r="AF9" t="n" s="0">
-        <v>1.3064603220733639E-14</v>
+        <v>5.504499973283005E-14</v>
       </c>
     </row>
     <row r="10">
       <c r="C10" t="n" s="0">
-        <v>7.200134668164904</v>
+        <v>7.199828480144287</v>
       </c>
       <c r="D10" t="n" s="0">
-        <v>7.20628531513611</v>
+        <v>7.178293242136341</v>
       </c>
       <c r="E10" t="n" s="0">
-        <v>7.210018262091892</v>
+        <v>8.095848013617994</v>
       </c>
       <c r="F10" t="n" s="0">
-        <v>6.4688738876273835</v>
+        <v>6.244369359561979</v>
       </c>
       <c r="G10" t="n" s="0">
-        <v>7.220292712285139</v>
+        <v>6.227583134347169</v>
       </c>
       <c r="H10" t="n" s="0">
-        <v>7.227274449823552</v>
+        <v>8.075693967709409</v>
       </c>
       <c r="I10" t="n" s="0">
-        <v>6.267786775189085</v>
+        <v>7.167094216756297</v>
       </c>
       <c r="J10" t="n" s="0">
-        <v>7.204714097492949</v>
+        <v>7.209206002071522</v>
       </c>
       <c r="K10" t="n" s="0">
-        <v>6.265130306517316</v>
+        <v>7.254340355764442</v>
       </c>
       <c r="L10" t="n" s="0">
-        <v>7.189152298895733</v>
+        <v>7.1940991862738874</v>
       </c>
       <c r="M10" t="n" s="0">
-        <v>7.214930617266358</v>
+        <v>7.207721310446335</v>
       </c>
       <c r="N10" t="n" s="0">
-        <v>7.224435541064554</v>
+        <v>6.21974798795357</v>
       </c>
       <c r="O10" t="n" s="0">
-        <v>8.086724697504009</v>
+        <v>6.239899026276603</v>
       </c>
       <c r="P10" t="n" s="0">
-        <v>6.241450162770054</v>
+        <v>7.204900897090583</v>
       </c>
       <c r="Q10" t="n" s="0">
-        <v>6.317284176050533</v>
+        <v>7.198549435830479</v>
       </c>
       <c r="R10" t="n" s="0">
-        <v>7.1997137383742915</v>
+        <v>6.240664582077894</v>
       </c>
       <c r="S10" t="n" s="0">
-        <v>7.195540269809567</v>
+        <v>7.21662998408571</v>
       </c>
       <c r="T10" t="n" s="0">
-        <v>6.242295075528572</v>
+        <v>6.244776368626668</v>
       </c>
       <c r="U10" t="n" s="0">
-        <v>7.213666088179973</v>
+        <v>7.198499532724648</v>
       </c>
       <c r="V10" t="n" s="0">
-        <v>7.22473588727871</v>
+        <v>7.063521613589119</v>
       </c>
       <c r="W10" t="n" s="0">
-        <v>7.223539592542423</v>
+        <v>6.222269171265593</v>
       </c>
       <c r="X10" t="n" s="0">
-        <v>7.207559959109711</v>
+        <v>7.2151575955444605</v>
       </c>
       <c r="Y10" t="n" s="0">
-        <v>6.229911674791709</v>
+        <v>7.194260876286108</v>
       </c>
       <c r="Z10" t="n" s="0">
-        <v>7.230676452083707</v>
+        <v>7.202143841955615</v>
       </c>
       <c r="AA10" t="n" s="0">
-        <v>6.233571316043496</v>
+        <v>6.248405306147009</v>
       </c>
       <c r="AB10" t="n" s="0">
-        <v>6.262172876527679</v>
+        <v>7.227094834650545</v>
       </c>
       <c r="AC10" t="n" s="0">
-        <v>6.215225369653043</v>
+        <v>7.188449340834771</v>
       </c>
       <c r="AD10" t="n" s="0">
-        <v>7.198391188460727</v>
+        <v>6.2289981738066444</v>
       </c>
       <c r="AE10" t="n" s="0">
-        <v>7.20696147449249</v>
+        <v>7.206402785095885</v>
       </c>
       <c r="AF10" t="n" s="0">
-        <v>6.257809544830107</v>
+        <v>7.189486577789872</v>
       </c>
     </row>
     <row r="11">
       <c r="C11" t="n" s="0">
-        <v>2.7887770699797275E-6</v>
+        <v>2.3115288111142375E-6</v>
       </c>
       <c r="D11" t="n" s="0">
-        <v>3.0657851087110847E-6</v>
+        <v>1.3280315410858965E-6</v>
       </c>
       <c r="E11" t="n" s="0">
-        <v>2.5894522193156633E-6</v>
+        <v>1.8885341918134206E-6</v>
       </c>
       <c r="F11" t="n" s="0">
-        <v>4.94601774384329E-6</v>
+        <v>1.4357425524903834E-6</v>
       </c>
       <c r="G11" t="n" s="0">
-        <v>1.9471732067743365E-6</v>
+        <v>1.8288390509651322E-6</v>
       </c>
       <c r="H11" t="n" s="0">
-        <v>2.3180334916301774E-6</v>
+        <v>3.244316617621278E-6</v>
       </c>
       <c r="I11" t="n" s="0">
-        <v>4.8664493568086535E-6</v>
+        <v>2.890669090557664E-6</v>
       </c>
       <c r="J11" t="n" s="0">
-        <v>2.984428025667112E-6</v>
+        <v>9.619666181742128E-7</v>
       </c>
       <c r="K11" t="n" s="0">
-        <v>1.3654330996433346E-6</v>
+        <v>3.5930070481841127E-6</v>
       </c>
       <c r="L11" t="n" s="0">
-        <v>3.0708967569000083E-6</v>
+        <v>3.6829554920587126E-6</v>
       </c>
       <c r="M11" t="n" s="0">
-        <v>1.7880789410553998E-6</v>
+        <v>5.095493974333735E-6</v>
       </c>
       <c r="N11" t="n" s="0">
-        <v>5.628161337019925E-6</v>
+        <v>2.715199715081345E-6</v>
       </c>
       <c r="O11" t="n" s="0">
-        <v>3.842992602473993E-6</v>
+        <v>1.4928310101591816E-6</v>
       </c>
       <c r="P11" t="n" s="0">
-        <v>6.278186246862216E-7</v>
+        <v>2.9614736812290344E-6</v>
       </c>
       <c r="Q11" t="n" s="0">
-        <v>2.9443943307687736E-6</v>
+        <v>1.3815664197875893E-6</v>
       </c>
       <c r="R11" t="n" s="0">
-        <v>3.705505296296432E-6</v>
+        <v>1.6367317345039681E-6</v>
       </c>
       <c r="S11" t="n" s="0">
-        <v>5.542726861850052E-6</v>
+        <v>2.959383378731379E-6</v>
       </c>
       <c r="T11" t="n" s="0">
-        <v>2.3688432501691568E-6</v>
+        <v>2.8791547978992594E-6</v>
       </c>
       <c r="U11" t="n" s="0">
-        <v>3.7036967958146137E-6</v>
+        <v>1.7998559032934556E-6</v>
       </c>
       <c r="V11" t="n" s="0">
-        <v>3.3154490106543217E-6</v>
+        <v>3.3342674697629845E-6</v>
       </c>
       <c r="W11" t="n" s="0">
-        <v>3.92594874997328E-6</v>
+        <v>2.3090472776901194E-6</v>
       </c>
       <c r="X11" t="n" s="0">
-        <v>3.0508031433195078E-6</v>
+        <v>2.1018023814895E-6</v>
       </c>
       <c r="Y11" t="n" s="0">
-        <v>1.2039864630532866E-6</v>
+        <v>3.828034127815628E-6</v>
       </c>
       <c r="Z11" t="n" s="0">
-        <v>3.1867377809681847E-6</v>
+        <v>2.285878185282311E-6</v>
       </c>
       <c r="AA11" t="n" s="0">
-        <v>4.651668067079001E-6</v>
+        <v>2.861413470392461E-6</v>
       </c>
       <c r="AB11" t="n" s="0">
-        <v>5.318133497344103E-6</v>
+        <v>0.24991641767182274</v>
       </c>
       <c r="AC11" t="n" s="0">
-        <v>5.145027429386578E-6</v>
+        <v>6.583502329466844E-6</v>
       </c>
       <c r="AD11" t="n" s="0">
-        <v>4.152337295184914E-6</v>
+        <v>1.2044946045180324E-6</v>
       </c>
       <c r="AE11" t="n" s="0">
-        <v>4.428309005564887E-6</v>
+        <v>1.463717316106484E-6</v>
       </c>
       <c r="AF11" t="n" s="0">
-        <v>4.084669991318358E-6</v>
+        <v>2.5336764019933183E-6</v>
       </c>
     </row>
     <row r="12">
       <c r="C12" t="n" s="0">
-        <v>0.15509802148168905</v>
+        <v>0.36094933964106474</v>
       </c>
       <c r="D12" t="n" s="0">
-        <v>0.0427332966815838</v>
+        <v>0.010353239556894434</v>
       </c>
       <c r="E12" t="n" s="0">
-        <v>0.6808557367163656</v>
+        <v>0.5464953687491122</v>
       </c>
       <c r="F12" t="n" s="0">
-        <v>0.8629553095411694</v>
+        <v>0.09214151590550033</v>
       </c>
       <c r="G12" t="n" s="0">
-        <v>0.7192294786053531</v>
+        <v>0.8484503279205856</v>
       </c>
       <c r="H12" t="n" s="0">
-        <v>0.2288181578809778</v>
+        <v>0.675796579025408</v>
       </c>
       <c r="I12" t="n" s="0">
-        <v>0.7553306072657874</v>
+        <v>0.6662508950290851</v>
       </c>
       <c r="J12" t="n" s="0">
-        <v>0.2873654843221109</v>
+        <v>0.39630753406089275</v>
       </c>
       <c r="K12" t="n" s="0">
-        <v>0.1796502768168604</v>
+        <v>0.7044702029780602</v>
       </c>
       <c r="L12" t="n" s="0">
-        <v>0.054917876890460696</v>
+        <v>0.6068356771274604</v>
       </c>
       <c r="M12" t="n" s="0">
-        <v>0.6668858633540151</v>
+        <v>0.7209478058713163</v>
       </c>
       <c r="N12" t="n" s="0">
-        <v>0.11786831552592004</v>
+        <v>0.2598892623780069</v>
       </c>
       <c r="O12" t="n" s="0">
-        <v>0.22109455874634787</v>
+        <v>0.04622703732288259</v>
       </c>
       <c r="P12" t="n" s="0">
-        <v>0.24364736946257573</v>
+        <v>0.3645918563130879</v>
       </c>
       <c r="Q12" t="n" s="0">
-        <v>0.26725149884308697</v>
+        <v>0.34379165831193376</v>
       </c>
       <c r="R12" t="n" s="0">
-        <v>0.6323481347430354</v>
+        <v>0.8269818860590407</v>
       </c>
       <c r="S12" t="n" s="0">
-        <v>0.9948919082331452</v>
+        <v>0.8475963721720838</v>
       </c>
       <c r="T12" t="n" s="0">
-        <v>0.4608983977005652</v>
+        <v>0.360399242455493</v>
       </c>
       <c r="U12" t="n" s="0">
-        <v>0.4178788913299069</v>
+        <v>0.5098082473810908</v>
       </c>
       <c r="V12" t="n" s="0">
-        <v>0.8690552332549225</v>
+        <v>0.5544960112563373</v>
       </c>
       <c r="W12" t="n" s="0">
-        <v>0.833553602843077</v>
+        <v>0.9601843382056012</v>
       </c>
       <c r="X12" t="n" s="0">
-        <v>0.09166632710926893</v>
+        <v>0.5877599085960742</v>
       </c>
       <c r="Y12" t="n" s="0">
-        <v>0.7585501459150096</v>
+        <v>0.9988782616423314</v>
       </c>
       <c r="Z12" t="n" s="0">
-        <v>0.5687679171227458</v>
+        <v>0.8895433905142158</v>
       </c>
       <c r="AA12" t="n" s="0">
-        <v>0.20338392371331337</v>
+        <v>0.5261280567133026</v>
       </c>
       <c r="AB12" t="n" s="0">
-        <v>0.23060591281517784</v>
+        <v>0.21509320898156797</v>
       </c>
       <c r="AC12" t="n" s="0">
-        <v>0.9724441793310259</v>
+        <v>0.8940516337963816</v>
       </c>
       <c r="AD12" t="n" s="0">
-        <v>0.616796134236474</v>
+        <v>0.3793633449872676</v>
       </c>
       <c r="AE12" t="n" s="0">
-        <v>0.2824241369880327</v>
+        <v>0.14653819397508708</v>
       </c>
       <c r="AF12" t="n" s="0">
-        <v>0.9241986255778107</v>
+        <v>0.8423423781142586</v>
       </c>
     </row>
     <row r="13">
       <c r="C13" t="n" s="0">
-        <v>-714.275635993808</v>
+        <v>-703.6135931731403</v>
       </c>
       <c r="D13" t="n" s="0">
-        <v>-678.3219598778352</v>
+        <v>-712.2158389490218</v>
       </c>
       <c r="E13" t="n" s="0">
-        <v>-718.3353844200728</v>
+        <v>-814.8156253192672</v>
       </c>
       <c r="F13" t="n" s="0">
-        <v>-639.7266875214359</v>
+        <v>-590.3145356030544</v>
       </c>
       <c r="G13" t="n" s="0">
-        <v>-786.1760943368149</v>
+        <v>-678.3262114069846</v>
       </c>
       <c r="H13" t="n" s="0">
-        <v>-511.6062847140629</v>
+        <v>-553.299516406415</v>
       </c>
       <c r="I13" t="n" s="0">
-        <v>-554.5556213240649</v>
+        <v>-463.94311878188887</v>
       </c>
       <c r="J13" t="n" s="0">
-        <v>-504.5553230560035</v>
+        <v>-874.8238767386823</v>
       </c>
       <c r="K13" t="n" s="0">
-        <v>-813.245628651206</v>
+        <v>-300.2085033900014</v>
       </c>
       <c r="L13" t="n" s="0">
-        <v>-816.894004865823</v>
+        <v>-517.7090027589529</v>
       </c>
       <c r="M13" t="n" s="0">
-        <v>-800.2565299319646</v>
+        <v>-333.4905693694159</v>
       </c>
       <c r="N13" t="n" s="0">
-        <v>-614.3202830589282</v>
+        <v>-636.3261712768634</v>
       </c>
       <c r="O13" t="n" s="0">
-        <v>-526.7934663226298</v>
+        <v>-851.606283018068</v>
       </c>
       <c r="P13" t="n" s="0">
-        <v>-759.7842676088267</v>
+        <v>-506.1290742362311</v>
       </c>
       <c r="Q13" t="n" s="0">
-        <v>-774.3022497559733</v>
+        <v>-593.2533956352021</v>
       </c>
       <c r="R13" t="n" s="0">
-        <v>-659.3760121869213</v>
+        <v>-555.7925138651148</v>
       </c>
       <c r="S13" t="n" s="0">
-        <v>-532.6414623442057</v>
+        <v>-576.9563881190031</v>
       </c>
       <c r="T13" t="n" s="0">
-        <v>-716.3580181430056</v>
+        <v>-661.000074487246</v>
       </c>
       <c r="U13" t="n" s="0">
-        <v>-875.1457670934024</v>
+        <v>-800.4298952207176</v>
       </c>
       <c r="V13" t="n" s="0">
-        <v>-761.302528028229</v>
+        <v>-817.3470981851282</v>
       </c>
       <c r="W13" t="n" s="0">
-        <v>-670.051828775846</v>
+        <v>-534.096289066191</v>
       </c>
       <c r="X13" t="n" s="0">
-        <v>-538.0692931907639</v>
+        <v>-437.4927685619014</v>
       </c>
       <c r="Y13" t="n" s="0">
-        <v>-621.0228621430565</v>
+        <v>-497.5028170166676</v>
       </c>
       <c r="Z13" t="n" s="0">
-        <v>-711.8649436717784</v>
+        <v>-357.3139730894207</v>
       </c>
       <c r="AA13" t="n" s="0">
-        <v>-854.987559199641</v>
+        <v>-764.4481494275005</v>
       </c>
       <c r="AB13" t="n" s="0">
-        <v>-556.5628073946204</v>
+        <v>-776.5926768515407</v>
       </c>
       <c r="AC13" t="n" s="0">
-        <v>-492.6904508029767</v>
+        <v>-596.4332686128461</v>
       </c>
       <c r="AD13" t="n" s="0">
-        <v>-548.7432397248284</v>
+        <v>-497.14743154663466</v>
       </c>
       <c r="AE13" t="n" s="0">
-        <v>-447.44303542544026</v>
+        <v>-618.0806360601521</v>
       </c>
       <c r="AF13" t="n" s="0">
-        <v>-581.4252456846385</v>
+        <v>-714.5388447304409</v>
       </c>
     </row>
     <row r="14">
@@ -1637,7 +1637,7 @@
     </row>
     <row r="15">
       <c r="C15" t="n" s="0">
-        <v>3.9968028886505635E-15</v>
+        <v>4.440892098500626E-16</v>
       </c>
       <c r="D15" t="n" s="0">
         <v>3.9968028886505635E-15</v>
@@ -1652,7 +1652,7 @@
         <v>3.9968028886505635E-15</v>
       </c>
       <c r="H15" t="n" s="0">
-        <v>4.440892098500626E-16</v>
+        <v>3.9968028886505635E-15</v>
       </c>
       <c r="I15" t="n" s="0">
         <v>3.9968028886505635E-15</v>
@@ -1676,7 +1676,7 @@
         <v>3.9968028886505635E-15</v>
       </c>
       <c r="P15" t="n" s="0">
-        <v>4.440892098500626E-16</v>
+        <v>3.9968028886505635E-15</v>
       </c>
       <c r="Q15" t="n" s="0">
         <v>3.9968028886505635E-15</v>
@@ -1685,7 +1685,7 @@
         <v>3.9968028886505635E-15</v>
       </c>
       <c r="S15" t="n" s="0">
-        <v>3.9968028886505635E-15</v>
+        <v>4.440892098500626E-16</v>
       </c>
       <c r="T15" t="n" s="0">
         <v>3.9968028886505635E-15</v>
@@ -1694,10 +1694,10 @@
         <v>3.9968028886505635E-15</v>
       </c>
       <c r="V15" t="n" s="0">
-        <v>3.9968028886505635E-15</v>
+        <v>4.440892098500626E-16</v>
       </c>
       <c r="W15" t="n" s="0">
-        <v>3.9968028886505635E-15</v>
+        <v>4.440892098500626E-16</v>
       </c>
       <c r="X15" t="n" s="0">
         <v>3.9968028886505635E-15</v>
@@ -1715,10 +1715,10 @@
         <v>3.9968028886505635E-15</v>
       </c>
       <c r="AC15" t="n" s="0">
+        <v>4.440892098500626E-16</v>
+      </c>
+      <c r="AD15" t="n" s="0">
         <v>3.9968028886505635E-15</v>
-      </c>
-      <c r="AD15" t="n" s="0">
-        <v>4.440892098500626E-16</v>
       </c>
       <c r="AE15" t="n" s="0">
         <v>3.9968028886505635E-15</v>
@@ -1729,88 +1729,88 @@
     </row>
     <row r="16">
       <c r="C16" t="n" s="0">
-        <v>0.0100790672155745</v>
+        <v>0.020726652218240438</v>
       </c>
       <c r="D16" t="n" s="0">
-        <v>0.03161738634495015</v>
+        <v>0.02751925803702493</v>
       </c>
       <c r="E16" t="n" s="0">
         <v>0.0</v>
       </c>
       <c r="F16" t="n" s="0">
-        <v>0.019992055064085412</v>
+        <v>0.01362438537396371</v>
       </c>
       <c r="G16" t="n" s="0">
-        <v>0.02187314173810795</v>
+        <v>0.027072681983937863</v>
       </c>
       <c r="H16" t="n" s="0">
         <v>0.0</v>
       </c>
       <c r="I16" t="n" s="0">
-        <v>0.008094795236356589</v>
+        <v>0.010016136405594511</v>
       </c>
       <c r="J16" t="n" s="0">
         <v>0.0</v>
       </c>
       <c r="K16" t="n" s="0">
-        <v>0.0</v>
+        <v>0.012549619724383732</v>
       </c>
       <c r="L16" t="n" s="0">
         <v>0.0</v>
       </c>
       <c r="M16" t="n" s="0">
-        <v>0.02972271785825631</v>
+        <v>0.0</v>
       </c>
       <c r="N16" t="n" s="0">
-        <v>0.028173026667246637</v>
+        <v>0.0</v>
       </c>
       <c r="O16" t="n" s="0">
-        <v>0.0</v>
+        <v>2.220446049250313E-16</v>
       </c>
       <c r="P16" t="n" s="0">
-        <v>0.014140266396380108</v>
+        <v>0.018460744276876384</v>
       </c>
       <c r="Q16" t="n" s="0">
-        <v>0.0</v>
+        <v>0.012799209742982987</v>
       </c>
       <c r="R16" t="n" s="0">
         <v>0.0</v>
       </c>
       <c r="S16" t="n" s="0">
-        <v>0.012750336875235191</v>
+        <v>0.0</v>
       </c>
       <c r="T16" t="n" s="0">
-        <v>0.0</v>
+        <v>0.027635662511823034</v>
       </c>
       <c r="U16" t="n" s="0">
-        <v>0.0</v>
+        <v>0.017495390751423368</v>
       </c>
       <c r="V16" t="n" s="0">
-        <v>0.0</v>
+        <v>0.00790106043318084</v>
       </c>
       <c r="W16" t="n" s="0">
-        <v>0.0</v>
+        <v>0.007683489472449234</v>
       </c>
       <c r="X16" t="n" s="0">
-        <v>0.013479926680116883</v>
+        <v>0.0</v>
       </c>
       <c r="Y16" t="n" s="0">
-        <v>0.017353502247808295</v>
+        <v>0.0</v>
       </c>
       <c r="Z16" t="n" s="0">
-        <v>0.024695212680549083</v>
+        <v>0.0</v>
       </c>
       <c r="AA16" t="n" s="0">
-        <v>0.0</v>
+        <v>0.030022500082655168</v>
       </c>
       <c r="AB16" t="n" s="0">
-        <v>0.007603698078390342</v>
+        <v>0.0</v>
       </c>
       <c r="AC16" t="n" s="0">
-        <v>0.02711506914438111</v>
+        <v>0.008289525993616653</v>
       </c>
       <c r="AD16" t="n" s="0">
-        <v>0.01398427475739572</v>
+        <v>0.0077722797947442634</v>
       </c>
       <c r="AE16" t="n" s="0">
         <v>0.0</v>
@@ -1821,2364 +1821,2364 @@
     </row>
     <row r="17">
       <c r="C17" t="n" s="0">
-        <v>4.673522085748415E-6</v>
+        <v>2.9557310460511897E-6</v>
       </c>
       <c r="D17" t="n" s="0">
-        <v>0.0196652726192565</v>
+        <v>0.019698597466991187</v>
       </c>
       <c r="E17" t="n" s="0">
-        <v>1.328322299024377E-7</v>
+        <v>0.02018879292299204</v>
       </c>
       <c r="F17" t="n" s="0">
-        <v>0.019675637032783716</v>
+        <v>1.3932774201946313E-6</v>
       </c>
       <c r="G17" t="n" s="0">
-        <v>1.6093618807566164E-6</v>
+        <v>2.1703094470407125E-6</v>
       </c>
       <c r="H17" t="n" s="0">
-        <v>4.648731900491025E-6</v>
+        <v>0.019634524132461726</v>
       </c>
       <c r="I17" t="n" s="0">
-        <v>1.0175989845316323E-6</v>
+        <v>1.5727450988778138E-6</v>
       </c>
       <c r="J17" t="n" s="0">
-        <v>1.8188157266903983E-6</v>
+        <v>1.7061409515448777E-6</v>
       </c>
       <c r="K17" t="n" s="0">
-        <v>2.0618393109949283E-6</v>
+        <v>1.9214281135900183E-6</v>
       </c>
       <c r="L17" t="n" s="0">
-        <v>2.5289414063560585E-6</v>
+        <v>0.02078206376857101</v>
       </c>
       <c r="M17" t="n" s="0">
-        <v>0.019481498866148934</v>
+        <v>4.377500940528361E-6</v>
       </c>
       <c r="N17" t="n" s="0">
-        <v>5.136985794676421E-6</v>
+        <v>9.383232952665451E-7</v>
       </c>
       <c r="O17" t="n" s="0">
-        <v>1.990878863392706E-6</v>
+        <v>4.273921323835039E-6</v>
       </c>
       <c r="P17" t="n" s="0">
-        <v>1.226478010960371E-6</v>
+        <v>0.01986900508987571</v>
       </c>
       <c r="Q17" t="n" s="0">
-        <v>6.339025039661623E-7</v>
+        <v>1.144929174300102E-6</v>
       </c>
       <c r="R17" t="n" s="0">
-        <v>2.3189266352466264E-6</v>
+        <v>1.4820233215358472E-6</v>
       </c>
       <c r="S17" t="n" s="0">
-        <v>2.5035251423041706E-6</v>
+        <v>9.739789446861028E-7</v>
       </c>
       <c r="T17" t="n" s="0">
-        <v>2.6446891891321138E-6</v>
+        <v>3.0467573307457124E-6</v>
       </c>
       <c r="U17" t="n" s="0">
-        <v>1.5442719128062078E-6</v>
+        <v>1.8078963109303E-6</v>
       </c>
       <c r="V17" t="n" s="0">
-        <v>2.7275770052703342E-6</v>
+        <v>9.942872219973496E-7</v>
       </c>
       <c r="W17" t="n" s="0">
-        <v>0.020094938069876646</v>
+        <v>1.2402427517829695E-6</v>
       </c>
       <c r="X17" t="n" s="0">
-        <v>0.01891386070421684</v>
+        <v>2.13553406101372E-6</v>
       </c>
       <c r="Y17" t="n" s="0">
-        <v>4.5730278032596345E-6</v>
+        <v>3.631960148695182E-6</v>
       </c>
       <c r="Z17" t="n" s="0">
-        <v>8.675181363955285E-7</v>
+        <v>1.9270362997531673E-6</v>
       </c>
       <c r="AA17" t="n" s="0">
-        <v>3.4419576605240482E-6</v>
+        <v>8.956501300815643E-7</v>
       </c>
       <c r="AB17" t="n" s="0">
-        <v>2.049998230001748E-6</v>
+        <v>8.643115538428187E-7</v>
       </c>
       <c r="AC17" t="n" s="0">
-        <v>3.0282479287196425E-6</v>
+        <v>5.828718622155996E-6</v>
       </c>
       <c r="AD17" t="n" s="0">
-        <v>2.0229870908162568E-6</v>
+        <v>0.04037231475852319</v>
       </c>
       <c r="AE17" t="n" s="0">
-        <v>1.352405907427833E-6</v>
+        <v>0.019600789557589045</v>
       </c>
       <c r="AF17" t="n" s="0">
-        <v>1.785772745161634E-6</v>
+        <v>1.2136423113544147E-6</v>
       </c>
     </row>
     <row r="18">
       <c r="C18" t="n" s="0">
-        <v>3.5157157737585633E-6</v>
+        <v>6.644466672456853E-6</v>
       </c>
       <c r="D18" t="n" s="0">
-        <v>1.831840271446833E-5</v>
+        <v>2.294525418501707E-5</v>
       </c>
       <c r="E18" t="n" s="0">
-        <v>1.3280086564901612E-5</v>
+        <v>3.3282223680453965E-5</v>
       </c>
       <c r="F18" t="n" s="0">
-        <v>2.043497248210292E-5</v>
+        <v>9.29188889166696E-6</v>
       </c>
       <c r="G18" t="n" s="0">
-        <v>7.836889699698174E-6</v>
+        <v>5.225788887273666E-6</v>
       </c>
       <c r="H18" t="n" s="0">
-        <v>6.5280864573522765E-6</v>
+        <v>0.1212121432409654</v>
       </c>
       <c r="I18" t="n" s="0">
-        <v>2.3703948497114448E-5</v>
+        <v>4.88820709023335E-6</v>
       </c>
       <c r="J18" t="n" s="0">
-        <v>1.2973920692969038E-5</v>
+        <v>6.342609399993257E-6</v>
       </c>
       <c r="K18" t="n" s="0">
-        <v>2.453523957198961E-5</v>
+        <v>1.0773619517215121E-5</v>
       </c>
       <c r="L18" t="n" s="0">
-        <v>4.779167367749562E-6</v>
+        <v>1.4644693021460311E-5</v>
       </c>
       <c r="M18" t="n" s="0">
-        <v>1.0373015962880913E-5</v>
+        <v>6.188859241629281E-6</v>
       </c>
       <c r="N18" t="n" s="0">
-        <v>1.6685077931509045E-5</v>
+        <v>1.2722027593482557E-5</v>
       </c>
       <c r="O18" t="n" s="0">
-        <v>1.2956772158400787E-5</v>
+        <v>1.216574878824967E-5</v>
       </c>
       <c r="P18" t="n" s="0">
-        <v>4.676718461671728E-6</v>
+        <v>1.2752183444751122E-5</v>
       </c>
       <c r="Q18" t="n" s="0">
-        <v>0.24241516685239675</v>
+        <v>3.60626420965105E-5</v>
       </c>
       <c r="R18" t="n" s="0">
-        <v>1.1930376394703357E-5</v>
+        <v>0.12122336625355137</v>
       </c>
       <c r="S18" t="n" s="0">
-        <v>1.1759017165401635E-5</v>
+        <v>0.12123982134676276</v>
       </c>
       <c r="T18" t="n" s="0">
-        <v>1.472072591430968E-5</v>
+        <v>9.116663941109733E-6</v>
       </c>
       <c r="U18" t="n" s="0">
-        <v>6.939434982996611E-6</v>
+        <v>1.2018867440556362E-5</v>
       </c>
       <c r="V18" t="n" s="0">
-        <v>1.7441705003216536E-5</v>
+        <v>2.550670053128207E-6</v>
       </c>
       <c r="W18" t="n" s="0">
-        <v>7.133349214198899E-6</v>
+        <v>1.3259153830109285E-5</v>
       </c>
       <c r="X18" t="n" s="0">
-        <v>9.718516682225746E-6</v>
+        <v>8.7605819900575E-6</v>
       </c>
       <c r="Y18" t="n" s="0">
-        <v>1.5290538705658187E-5</v>
+        <v>1.5190591558126711E-5</v>
       </c>
       <c r="Z18" t="n" s="0">
-        <v>2.7390873432155334E-5</v>
+        <v>8.471061895056365E-6</v>
       </c>
       <c r="AA18" t="n" s="0">
-        <v>1.7869926853001407E-5</v>
+        <v>4.749108016578851E-6</v>
       </c>
       <c r="AB18" t="n" s="0">
-        <v>1.6639028462553526E-5</v>
+        <v>1.5473172773112036E-5</v>
       </c>
       <c r="AC18" t="n" s="0">
-        <v>8.738200621334461E-6</v>
+        <v>2.5353921658779823E-5</v>
       </c>
       <c r="AD18" t="n" s="0">
-        <v>7.664311554433788E-6</v>
+        <v>3.5753087259668785E-5</v>
       </c>
       <c r="AE18" t="n" s="0">
-        <v>1.1886139448076338E-5</v>
+        <v>0.12122697176664757</v>
       </c>
       <c r="AF18" t="n" s="0">
-        <v>0.12121733668810508</v>
+        <v>5.812586121829314E-6</v>
       </c>
     </row>
     <row r="19">
       <c r="C19" t="n" s="0">
-        <v>9.803897741079606</v>
+        <v>11.718699111327835</v>
       </c>
       <c r="D19" t="n" s="0">
-        <v>10.763166845651908</v>
+        <v>11.718699111328078</v>
       </c>
       <c r="E19" t="n" s="0">
-        <v>10.763166846132064</v>
+        <v>11.718699111328078</v>
       </c>
       <c r="F19" t="n" s="0">
-        <v>1.992030891891068</v>
+        <v>11.718699111327783</v>
       </c>
       <c r="G19" t="n" s="0">
-        <v>1.9920308918588832</v>
+        <v>11.718699111328077</v>
       </c>
       <c r="H19" t="n" s="0">
-        <v>11.718699111328082</v>
+        <v>1.9920308918568623</v>
       </c>
       <c r="I19" t="n" s="0">
-        <v>1.9920324862770211</v>
+        <v>11.71869911132808</v>
       </c>
       <c r="J19" t="n" s="0">
-        <v>10.763166845903413</v>
+        <v>11.718699111327785</v>
       </c>
       <c r="K19" t="n" s="0">
-        <v>1.9920308918715115</v>
+        <v>11.718699111327831</v>
       </c>
       <c r="L19" t="n" s="0">
+        <v>11.718699111328078</v>
+      </c>
+      <c r="M19" t="n" s="0">
         <v>11.718699111327785</v>
       </c>
-      <c r="M19" t="n" s="0">
-        <v>1.9920308918587886</v>
-      </c>
       <c r="N19" t="n" s="0">
-        <v>9.803897741018199</v>
+        <v>11.718699111327835</v>
       </c>
       <c r="O19" t="n" s="0">
-        <v>10.763166846131998</v>
+        <v>11.718699111328027</v>
       </c>
       <c r="P19" t="n" s="0">
-        <v>11.718699111327831</v>
+        <v>11.718699111327783</v>
       </c>
       <c r="Q19" t="n" s="0">
-        <v>6.903335554603642</v>
+        <v>11.718699111327837</v>
       </c>
       <c r="R19" t="n" s="0">
-        <v>11.718699111327831</v>
+        <v>1.992030891928731</v>
       </c>
       <c r="S19" t="n" s="0">
-        <v>1.992030891913482</v>
+        <v>1.99203089200362</v>
       </c>
       <c r="T19" t="n" s="0">
+        <v>10.76316686492513</v>
+      </c>
+      <c r="U19" t="n" s="0">
+        <v>11.718699111328029</v>
+      </c>
+      <c r="V19" t="n" s="0">
+        <v>10.763166846130746</v>
+      </c>
+      <c r="W19" t="n" s="0">
+        <v>1.9920308921591203</v>
+      </c>
+      <c r="X19" t="n" s="0">
         <v>11.718699111327785</v>
       </c>
-      <c r="U19" t="n" s="0">
-        <v>1.9920308918690193</v>
-      </c>
-      <c r="V19" t="n" s="0">
-        <v>1.9920309148770095</v>
-      </c>
-      <c r="W19" t="n" s="0">
-        <v>10.763166846131686</v>
-      </c>
-      <c r="X19" t="n" s="0">
-        <v>11.718699111328027</v>
-      </c>
       <c r="Y19" t="n" s="0">
-        <v>11.718699111327831</v>
+        <v>1.992031555769788</v>
       </c>
       <c r="Z19" t="n" s="0">
-        <v>11.718699111328029</v>
+        <v>11.718699111328077</v>
       </c>
       <c r="AA19" t="n" s="0">
+        <v>11.71869911132803</v>
+      </c>
+      <c r="AB19" t="n" s="0">
+        <v>9.803898069691941</v>
+      </c>
+      <c r="AC19" t="n" s="0">
         <v>11.718699111328078</v>
       </c>
-      <c r="AB19" t="n" s="0">
-        <v>1.9920308919703407</v>
-      </c>
-      <c r="AC19" t="n" s="0">
-        <v>9.80389774414984</v>
-      </c>
       <c r="AD19" t="n" s="0">
-        <v>1.9920308918663472</v>
+        <v>11.718699111327787</v>
       </c>
       <c r="AE19" t="n" s="0">
-        <v>11.718699111327831</v>
+        <v>1.9920308918648941</v>
       </c>
       <c r="AF19" t="n" s="0">
-        <v>1.9920308922763883</v>
+        <v>1.9920308923207546</v>
       </c>
     </row>
     <row r="20">
       <c r="C20" t="n" s="0">
-        <v>3.0933547152294953E-4</v>
+        <v>3.308141221756041E-4</v>
       </c>
       <c r="D20" t="n" s="0">
-        <v>6.415111425701822E-4</v>
+        <v>5.321442580302001E-4</v>
       </c>
       <c r="E20" t="n" s="0">
-        <v>4.463092639533402E-4</v>
+        <v>6.393590219175385E-4</v>
       </c>
       <c r="F20" t="n" s="0">
-        <v>5.093820102934946E-4</v>
+        <v>6.560638283179053E-4</v>
       </c>
       <c r="G20" t="n" s="0">
-        <v>3.2542000608071805E-4</v>
+        <v>3.810118813918065E-4</v>
       </c>
       <c r="H20" t="n" s="0">
-        <v>4.4318996150984264E-4</v>
+        <v>3.53200041054643E-4</v>
       </c>
       <c r="I20" t="n" s="0">
-        <v>5.219086080965231E-4</v>
+        <v>6.115918555343183E-4</v>
       </c>
       <c r="J20" t="n" s="0">
-        <v>4.521046303542972E-4</v>
+        <v>5.622372125219533E-4</v>
       </c>
       <c r="K20" t="n" s="0">
-        <v>6.770739715080113E-4</v>
+        <v>3.140103326669789E-4</v>
       </c>
       <c r="L20" t="n" s="0">
-        <v>4.071066026893185E-4</v>
+        <v>5.298453388181491E-4</v>
       </c>
       <c r="M20" t="n" s="0">
-        <v>3.0827740002674147E-4</v>
+        <v>4.648137982993812E-4</v>
       </c>
       <c r="N20" t="n" s="0">
-        <v>5.999489246428031E-4</v>
+        <v>3.324289725979609E-4</v>
       </c>
       <c r="O20" t="n" s="0">
-        <v>6.372126389498986E-4</v>
+        <v>3.729100131269546E-4</v>
       </c>
       <c r="P20" t="n" s="0">
-        <v>5.760728446686207E-4</v>
+        <v>0.0016136398611190097</v>
       </c>
       <c r="Q20" t="n" s="0">
-        <v>4.626747857351084E-4</v>
+        <v>5.608711199356443E-4</v>
       </c>
       <c r="R20" t="n" s="0">
-        <v>5.921852967547031E-4</v>
+        <v>3.132128108509449E-4</v>
       </c>
       <c r="S20" t="n" s="0">
-        <v>6.952901633939257E-4</v>
+        <v>3.284693862185457E-4</v>
       </c>
       <c r="T20" t="n" s="0">
-        <v>4.0945330413257535E-4</v>
+        <v>3.958992036964926E-4</v>
       </c>
       <c r="U20" t="n" s="0">
-        <v>3.115949698758263E-4</v>
+        <v>6.774000552202004E-4</v>
       </c>
       <c r="V20" t="n" s="0">
-        <v>3.3073450073475765E-4</v>
+        <v>6.458742909817348E-4</v>
       </c>
       <c r="W20" t="n" s="0">
-        <v>5.854941430057244E-4</v>
+        <v>3.6920103609033053E-4</v>
       </c>
       <c r="X20" t="n" s="0">
-        <v>3.1048536457629704E-4</v>
+        <v>4.513162936158967E-4</v>
       </c>
       <c r="Y20" t="n" s="0">
-        <v>4.1157224589565634E-4</v>
+        <v>3.152744274430148E-4</v>
       </c>
       <c r="Z20" t="n" s="0">
-        <v>3.1208164648642496E-4</v>
+        <v>4.3119212430924313E-4</v>
       </c>
       <c r="AA20" t="n" s="0">
-        <v>3.4995795962821524E-4</v>
+        <v>3.481650857165793E-4</v>
       </c>
       <c r="AB20" t="n" s="0">
-        <v>6.435324785915229E-4</v>
+        <v>5.194735290048788E-4</v>
       </c>
       <c r="AC20" t="n" s="0">
-        <v>5.983994871919517E-4</v>
+        <v>4.155164084669077E-4</v>
       </c>
       <c r="AD20" t="n" s="0">
-        <v>5.817382051596394E-4</v>
+        <v>5.444240033677388E-4</v>
       </c>
       <c r="AE20" t="n" s="0">
-        <v>5.052276791899124E-4</v>
+        <v>7.063854957197401E-4</v>
       </c>
       <c r="AF20" t="n" s="0">
-        <v>5.990440874739891E-4</v>
+        <v>4.963947859779636E-4</v>
       </c>
     </row>
     <row r="21">
       <c r="C21" t="n" s="0">
-        <v>-1.0316281524712292</v>
+        <v>-1.0316284263518218</v>
       </c>
       <c r="D21" t="n" s="0">
-        <v>-1.0316284516154384</v>
+        <v>-1.031628449564669</v>
       </c>
       <c r="E21" t="n" s="0">
-        <v>-1.0316283531374077</v>
+        <v>-1.0316284530619815</v>
       </c>
       <c r="F21" t="n" s="0">
-        <v>-1.03162839400356</v>
+        <v>-1.0316282242395531</v>
       </c>
       <c r="G21" t="n" s="0">
-        <v>-1.031628416544944</v>
+        <v>-1.0316282419058425</v>
       </c>
       <c r="H21" t="n" s="0">
-        <v>-1.0316284397757574</v>
+        <v>-1.0316283949982912</v>
       </c>
       <c r="I21" t="n" s="0">
-        <v>-1.0316284497308152</v>
+        <v>-1.031628443545232</v>
       </c>
       <c r="J21" t="n" s="0">
-        <v>-1.0316284398021651</v>
+        <v>-1.031628433350038</v>
       </c>
       <c r="K21" t="n" s="0">
-        <v>-1.0316284440030692</v>
+        <v>-1.031628392912847</v>
       </c>
       <c r="L21" t="n" s="0">
-        <v>-1.0316284438363237</v>
+        <v>-1.0316281743039102</v>
       </c>
       <c r="M21" t="n" s="0">
-        <v>-1.0316283067228602</v>
+        <v>-1.0316283063421405</v>
       </c>
       <c r="N21" t="n" s="0">
-        <v>-1.0316284010037409</v>
+        <v>-1.0316284452151405</v>
       </c>
       <c r="O21" t="n" s="0">
-        <v>-1.0316282431159054</v>
+        <v>-1.0316284038569263</v>
       </c>
       <c r="P21" t="n" s="0">
-        <v>-1.0316284505806999</v>
+        <v>-1.0316283715940715</v>
       </c>
       <c r="Q21" t="n" s="0">
-        <v>-1.0316284444404993</v>
+        <v>-1.0316284484209182</v>
       </c>
       <c r="R21" t="n" s="0">
-        <v>-1.0316283328917875</v>
+        <v>-1.0316283699116666</v>
       </c>
       <c r="S21" t="n" s="0">
-        <v>-1.0316284487036564</v>
+        <v>-1.0316283581854373</v>
       </c>
       <c r="T21" t="n" s="0">
-        <v>-1.0316281588628557</v>
+        <v>-1.0316282754993538</v>
       </c>
       <c r="U21" t="n" s="0">
-        <v>-1.0316284254155874</v>
+        <v>-1.0316284511115539</v>
       </c>
       <c r="V21" t="n" s="0">
-        <v>-1.0316283173771563</v>
+        <v>-1.0316281599929185</v>
       </c>
       <c r="W21" t="n" s="0">
-        <v>-1.0316284311803863</v>
+        <v>-1.0316284258841704</v>
       </c>
       <c r="X21" t="n" s="0">
-        <v>-1.0316283535547262</v>
+        <v>-1.0316284505444768</v>
       </c>
       <c r="Y21" t="n" s="0">
-        <v>-1.03162841900561</v>
+        <v>-1.0316284387612487</v>
       </c>
       <c r="Z21" t="n" s="0">
-        <v>-1.0316283240508162</v>
+        <v>-1.0316283833432611</v>
       </c>
       <c r="AA21" t="n" s="0">
-        <v>-1.0316284416510793</v>
+        <v>-1.0316284348086204</v>
       </c>
       <c r="AB21" t="n" s="0">
-        <v>-1.0316283976814127</v>
+        <v>-1.0316284378845075</v>
       </c>
       <c r="AC21" t="n" s="0">
-        <v>-1.0316284496993937</v>
+        <v>-1.0316283775795727</v>
       </c>
       <c r="AD21" t="n" s="0">
-        <v>-1.0316283918545435</v>
+        <v>-1.0316283087301998</v>
       </c>
       <c r="AE21" t="n" s="0">
-        <v>-1.0316283935327042</v>
+        <v>-1.0316284306163628</v>
       </c>
       <c r="AF21" t="n" s="0">
-        <v>-1.0316284261931459</v>
+        <v>-1.03162841627472</v>
       </c>
     </row>
     <row r="22">
       <c r="C22" t="n" s="0">
-        <v>0.397892139741705</v>
+        <v>0.39788797707428003</v>
       </c>
       <c r="D22" t="n" s="0">
-        <v>0.39788808761432826</v>
+        <v>0.3978879351320508</v>
       </c>
       <c r="E22" t="n" s="0">
-        <v>0.3978876243533005</v>
+        <v>0.39789025476846795</v>
       </c>
       <c r="F22" t="n" s="0">
-        <v>0.3978879101281283</v>
+        <v>0.39788757812946507</v>
       </c>
       <c r="G22" t="n" s="0">
-        <v>0.3978882905200365</v>
+        <v>0.39788835425905056</v>
       </c>
       <c r="H22" t="n" s="0">
-        <v>0.397888134714778</v>
+        <v>0.3978880272458678</v>
       </c>
       <c r="I22" t="n" s="0">
-        <v>0.3978916080838868</v>
+        <v>0.39788791504110854</v>
       </c>
       <c r="J22" t="n" s="0">
-        <v>0.3978907676151522</v>
+        <v>0.39788744482496163</v>
       </c>
       <c r="K22" t="n" s="0">
-        <v>0.39788787777483314</v>
+        <v>0.3978876575960193</v>
       </c>
       <c r="L22" t="n" s="0">
-        <v>0.3978885987906011</v>
+        <v>0.39788845029085884</v>
       </c>
       <c r="M22" t="n" s="0">
-        <v>0.39788761132544437</v>
+        <v>0.3978895810163561</v>
       </c>
       <c r="N22" t="n" s="0">
-        <v>0.39788801869280377</v>
+        <v>0.39788805203681754</v>
       </c>
       <c r="O22" t="n" s="0">
-        <v>0.397888602175378</v>
+        <v>0.3978895915617109</v>
       </c>
       <c r="P22" t="n" s="0">
-        <v>0.39788873688098114</v>
+        <v>0.39788800794813106</v>
       </c>
       <c r="Q22" t="n" s="0">
-        <v>0.397887440126965</v>
+        <v>0.3978895174064281</v>
       </c>
       <c r="R22" t="n" s="0">
-        <v>0.39788901149511346</v>
+        <v>0.39788809499527744</v>
       </c>
       <c r="S22" t="n" s="0">
-        <v>0.39788871672854675</v>
+        <v>0.3978893825054577</v>
       </c>
       <c r="T22" t="n" s="0">
-        <v>0.3978885320006711</v>
+        <v>0.3978883736527177</v>
       </c>
       <c r="U22" t="n" s="0">
-        <v>0.3978896432283783</v>
+        <v>0.39788769430320237</v>
       </c>
       <c r="V22" t="n" s="0">
-        <v>0.3978895805260283</v>
+        <v>0.39788847922022974</v>
       </c>
       <c r="W22" t="n" s="0">
-        <v>0.39788883189384805</v>
+        <v>0.3978874429619914</v>
       </c>
       <c r="X22" t="n" s="0">
-        <v>0.39788758754199804</v>
+        <v>0.39788789445121964</v>
       </c>
       <c r="Y22" t="n" s="0">
-        <v>0.3978875180159829</v>
+        <v>0.3978876551044923</v>
       </c>
       <c r="Z22" t="n" s="0">
-        <v>0.39788785816424443</v>
+        <v>0.39788957345994547</v>
       </c>
       <c r="AA22" t="n" s="0">
-        <v>0.39788890062620474</v>
+        <v>0.39789013253149896</v>
       </c>
       <c r="AB22" t="n" s="0">
-        <v>0.39788740251510646</v>
+        <v>0.39788962451630994</v>
       </c>
       <c r="AC22" t="n" s="0">
-        <v>0.39788883857826285</v>
+        <v>0.3978882710115972</v>
       </c>
       <c r="AD22" t="n" s="0">
-        <v>0.3978907964698486</v>
+        <v>0.3978899429494991</v>
       </c>
       <c r="AE22" t="n" s="0">
-        <v>0.39789219886819716</v>
+        <v>0.39788747360025667</v>
       </c>
       <c r="AF22" t="n" s="0">
-        <v>0.39788770251604966</v>
+        <v>0.3978883465928682</v>
       </c>
     </row>
     <row r="23">
       <c r="C23" t="n" s="0">
-        <v>3.002676646491116</v>
+        <v>3.0000019170254206</v>
       </c>
       <c r="D23" t="n" s="0">
-        <v>3.0000002573336957</v>
+        <v>3.0000000728128144</v>
       </c>
       <c r="E23" t="n" s="0">
-        <v>3.0003887013343635</v>
+        <v>3.008483879441659</v>
       </c>
       <c r="F23" t="n" s="0">
-        <v>3.0000000198155794</v>
+        <v>3.0027721500318156</v>
       </c>
       <c r="G23" t="n" s="0">
-        <v>3.0000018902366947</v>
+        <v>3.00041109449307</v>
       </c>
       <c r="H23" t="n" s="0">
-        <v>3.005240854414511</v>
+        <v>3.000309515362189</v>
       </c>
       <c r="I23" t="n" s="0">
-        <v>3.000016392681802</v>
+        <v>3.000480919367947</v>
       </c>
       <c r="J23" t="n" s="0">
-        <v>3.0000380142692267</v>
+        <v>3.0000000845081787</v>
       </c>
       <c r="K23" t="n" s="0">
-        <v>3.0000225058812697</v>
+        <v>3.003855684452125</v>
       </c>
       <c r="L23" t="n" s="0">
-        <v>3.000002251811419</v>
+        <v>3.0000049622654257</v>
       </c>
       <c r="M23" t="n" s="0">
-        <v>3.000000319663611</v>
+        <v>3.000003845579098</v>
       </c>
       <c r="N23" t="n" s="0">
-        <v>3.000135898109459</v>
+        <v>3.0000000034321674</v>
       </c>
       <c r="O23" t="n" s="0">
-        <v>3.0000008184986546</v>
+        <v>3.0000000731718246</v>
       </c>
       <c r="P23" t="n" s="0">
-        <v>3.0000007979165466</v>
+        <v>3.0000000610024093</v>
       </c>
       <c r="Q23" t="n" s="0">
-        <v>3.0000072685078214</v>
+        <v>3.0000001044985174</v>
       </c>
       <c r="R23" t="n" s="0">
-        <v>3.000000100260824</v>
+        <v>3.0000004565264766</v>
       </c>
       <c r="S23" t="n" s="0">
-        <v>3.000053498806209</v>
+        <v>3.0000000974457253</v>
       </c>
       <c r="T23" t="n" s="0">
-        <v>3.000033892524381</v>
+        <v>3.000001550476281</v>
       </c>
       <c r="U23" t="n" s="0">
-        <v>3.000002381865118</v>
+        <v>3.0000213266005558</v>
       </c>
       <c r="V23" t="n" s="0">
-        <v>3.0000180058160826</v>
+        <v>3.0011758719829937</v>
       </c>
       <c r="W23" t="n" s="0">
-        <v>3.0000003713508994</v>
+        <v>3.0000968902262373</v>
       </c>
       <c r="X23" t="n" s="0">
-        <v>3.0000048491782114</v>
+        <v>3.0000665179015806</v>
       </c>
       <c r="Y23" t="n" s="0">
-        <v>3.0000000177741777</v>
+        <v>3.0000205604788004</v>
       </c>
       <c r="Z23" t="n" s="0">
-        <v>3.001026732753191</v>
+        <v>3.0000197934825574</v>
       </c>
       <c r="AA23" t="n" s="0">
-        <v>3.0000173212501746</v>
+        <v>3.0005392143699203</v>
       </c>
       <c r="AB23" t="n" s="0">
-        <v>3.000003337885849</v>
+        <v>3.0000542560430645</v>
       </c>
       <c r="AC23" t="n" s="0">
-        <v>3.0044425668763886</v>
+        <v>3.000000018247829</v>
       </c>
       <c r="AD23" t="n" s="0">
-        <v>3.004430211480351</v>
+        <v>3.0000018595574156</v>
       </c>
       <c r="AE23" t="n" s="0">
-        <v>3.005861759302792</v>
+        <v>3.000010515819072</v>
       </c>
       <c r="AF23" t="n" s="0">
-        <v>3.001586702919677</v>
+        <v>3.0083882700718054</v>
       </c>
     </row>
     <row r="24">
       <c r="C24" t="n" s="0">
-        <v>-3.8599912632246225</v>
+        <v>-3.8593640134645737</v>
       </c>
       <c r="D24" t="n" s="0">
-        <v>-3.8627605384351575</v>
+        <v>-3.8616773549351793</v>
       </c>
       <c r="E24" t="n" s="0">
-        <v>-3.8615997973033025</v>
+        <v>-3.8624231236412885</v>
       </c>
       <c r="F24" t="n" s="0">
-        <v>-3.861620017075684</v>
+        <v>-3.8594495545449186</v>
       </c>
       <c r="G24" t="n" s="0">
-        <v>-3.8621186396429943</v>
+        <v>-3.8627611313777557</v>
       </c>
       <c r="H24" t="n" s="0">
-        <v>-3.862599879196451</v>
+        <v>-3.8617736611966738</v>
       </c>
       <c r="I24" t="n" s="0">
-        <v>-3.8620575344800177</v>
+        <v>-3.8625889232438295</v>
       </c>
       <c r="J24" t="n" s="0">
-        <v>-3.862745093111545</v>
+        <v>-3.862772675524142</v>
       </c>
       <c r="K24" t="n" s="0">
-        <v>-3.862742583847763</v>
+        <v>-3.8619898375375956</v>
       </c>
       <c r="L24" t="n" s="0">
-        <v>-3.86133862557974</v>
+        <v>-3.862305249092522</v>
       </c>
       <c r="M24" t="n" s="0">
-        <v>-3.861761265463778</v>
+        <v>-3.8573715354102758</v>
       </c>
       <c r="N24" t="n" s="0">
-        <v>-3.86176727191338</v>
+        <v>-3.861684205164668</v>
       </c>
       <c r="O24" t="n" s="0">
-        <v>-3.8625216830082914</v>
+        <v>-3.8540511177254473</v>
       </c>
       <c r="P24" t="n" s="0">
-        <v>-3.8588608179304114</v>
+        <v>-3.8625040190730093</v>
       </c>
       <c r="Q24" t="n" s="0">
-        <v>-3.8624996138293355</v>
+        <v>-3.8620355540075018</v>
       </c>
       <c r="R24" t="n" s="0">
-        <v>-3.862581715876788</v>
+        <v>-3.862620813804444</v>
       </c>
       <c r="S24" t="n" s="0">
-        <v>-3.8623296712999813</v>
+        <v>-3.861827057559541</v>
       </c>
       <c r="T24" t="n" s="0">
-        <v>-3.8626821436762473</v>
+        <v>-3.8602581743424396</v>
       </c>
       <c r="U24" t="n" s="0">
-        <v>-3.8623636284917344</v>
+        <v>-3.860612437170033</v>
       </c>
       <c r="V24" t="n" s="0">
-        <v>-3.8613621454467357</v>
+        <v>-3.860847534849916</v>
       </c>
       <c r="W24" t="n" s="0">
-        <v>-3.8614599701594976</v>
+        <v>-3.8614949889606134</v>
       </c>
       <c r="X24" t="n" s="0">
-        <v>-3.8627730007926036</v>
+        <v>-3.861820495968553</v>
       </c>
       <c r="Y24" t="n" s="0">
-        <v>-3.8607953761703615</v>
+        <v>-3.8618583332163654</v>
       </c>
       <c r="Z24" t="n" s="0">
-        <v>-3.8627809017663113</v>
+        <v>-3.8623986630919145</v>
       </c>
       <c r="AA24" t="n" s="0">
-        <v>-3.8627764888615155</v>
+        <v>-3.860210149700899</v>
       </c>
       <c r="AB24" t="n" s="0">
-        <v>-3.8610817332245264</v>
+        <v>-3.861311041577796</v>
       </c>
       <c r="AC24" t="n" s="0">
-        <v>-3.8619175009461983</v>
+        <v>-3.862537486330038</v>
       </c>
       <c r="AD24" t="n" s="0">
-        <v>-3.8608598602947315</v>
+        <v>-3.859936186146784</v>
       </c>
       <c r="AE24" t="n" s="0">
-        <v>-3.862472022179446</v>
+        <v>-3.8626685235346856</v>
       </c>
       <c r="AF24" t="n" s="0">
-        <v>-3.860076226825624</v>
+        <v>-3.8614692560913584</v>
       </c>
     </row>
     <row r="25">
       <c r="C25" t="n" s="0">
-        <v>-3.3219715684412883</v>
+        <v>-3.3219737939660945</v>
       </c>
       <c r="D25" t="n" s="0">
-        <v>-3.321901551865567</v>
+        <v>-3.321947751958625</v>
       </c>
       <c r="E25" t="n" s="0">
-        <v>-3.3219798923276693</v>
+        <v>-3.3218881422658053</v>
       </c>
       <c r="F25" t="n" s="0">
-        <v>-3.321979973634273</v>
+        <v>-3.321980887696234</v>
       </c>
       <c r="G25" t="n" s="0">
-        <v>-3.321978613771237</v>
+        <v>-3.321985586249143</v>
       </c>
       <c r="H25" t="n" s="0">
-        <v>-3.3219770663733446</v>
+        <v>-3.3219799021582754</v>
       </c>
       <c r="I25" t="n" s="0">
-        <v>-3.321987030891525</v>
+        <v>-3.3219603886498836</v>
       </c>
       <c r="J25" t="n" s="0">
-        <v>-3.3219422016083673</v>
+        <v>-3.3219785106239414</v>
       </c>
       <c r="K25" t="n" s="0">
-        <v>-3.3219861376672495</v>
+        <v>-3.3219584822044164</v>
       </c>
       <c r="L25" t="n" s="0">
-        <v>-3.3219792011395315</v>
+        <v>-3.321983474654059</v>
       </c>
       <c r="M25" t="n" s="0">
-        <v>-3.3219912488618606</v>
+        <v>-3.3219874233894475</v>
       </c>
       <c r="N25" t="n" s="0">
-        <v>-3.321967624051529</v>
+        <v>-3.3219833213953014</v>
       </c>
       <c r="O25" t="n" s="0">
-        <v>-3.3219599319364046</v>
+        <v>-3.3219860486804604</v>
       </c>
       <c r="P25" t="n" s="0">
-        <v>-3.321984846931347</v>
+        <v>-3.321984773975808</v>
       </c>
       <c r="Q25" t="n" s="0">
-        <v>-3.3219572194560705</v>
+        <v>-3.321981969690482</v>
       </c>
       <c r="R25" t="n" s="0">
-        <v>-3.3219771452363664</v>
+        <v>-3.3219905413928927</v>
       </c>
       <c r="S25" t="n" s="0">
-        <v>-3.3219730743064635</v>
+        <v>-3.3219822547779243</v>
       </c>
       <c r="T25" t="n" s="0">
-        <v>-3.3219763444198693</v>
+        <v>-3.3219768811260626</v>
       </c>
       <c r="U25" t="n" s="0">
-        <v>-3.3219894074372434</v>
+        <v>-3.3219508258588077</v>
       </c>
       <c r="V25" t="n" s="0">
-        <v>-3.321978285324742</v>
+        <v>-3.321989654655154</v>
       </c>
       <c r="W25" t="n" s="0">
-        <v>-3.3219637594837947</v>
+        <v>-3.321993692738126</v>
       </c>
       <c r="X25" t="n" s="0">
-        <v>-3.321984104212151</v>
+        <v>-3.3219752838225136</v>
       </c>
       <c r="Y25" t="n" s="0">
-        <v>-3.321987001890665</v>
+        <v>-3.321988538860228</v>
       </c>
       <c r="Z25" t="n" s="0">
-        <v>-3.3219818637642278</v>
+        <v>-3.3219719438998268</v>
       </c>
       <c r="AA25" t="n" s="0">
-        <v>-3.3219877679525167</v>
+        <v>-3.3219643351186017</v>
       </c>
       <c r="AB25" t="n" s="0">
-        <v>-3.321991188815615</v>
+        <v>-3.3219667701292854</v>
       </c>
       <c r="AC25" t="n" s="0">
-        <v>-3.3219805719219035</v>
+        <v>-3.3219881713778006</v>
       </c>
       <c r="AD25" t="n" s="0">
-        <v>-3.3219943412231734</v>
+        <v>-3.3219800071159633</v>
       </c>
       <c r="AE25" t="n" s="0">
-        <v>-3.3219454174371084</v>
+        <v>-3.3219652330236706</v>
       </c>
       <c r="AF25" t="n" s="0">
-        <v>-3.3219838288915526</v>
+        <v>-3.321986049026484</v>
       </c>
     </row>
     <row r="26">
       <c r="C26" t="n" s="0">
-        <v>-10.150706562895612</v>
+        <v>-10.1526262138922</v>
       </c>
       <c r="D26" t="n" s="0">
-        <v>-10.15177488535799</v>
+        <v>-10.15117747284005</v>
       </c>
       <c r="E26" t="n" s="0">
-        <v>-10.152234647889276</v>
+        <v>-10.151120609869785</v>
       </c>
       <c r="F26" t="n" s="0">
-        <v>-10.151457826811214</v>
+        <v>-10.15201690506811</v>
       </c>
       <c r="G26" t="n" s="0">
-        <v>-10.152220093401468</v>
+        <v>-10.151645158273977</v>
       </c>
       <c r="H26" t="n" s="0">
-        <v>-10.15115441072535</v>
+        <v>-10.15131214348625</v>
       </c>
       <c r="I26" t="n" s="0">
-        <v>-10.152348412519284</v>
+        <v>-10.152938297711597</v>
       </c>
       <c r="J26" t="n" s="0">
-        <v>-10.152590954255478</v>
+        <v>-10.151088194288002</v>
       </c>
       <c r="K26" t="n" s="0">
-        <v>-10.151897974406236</v>
+        <v>-10.152154131639634</v>
       </c>
       <c r="L26" t="n" s="0">
-        <v>-10.152089510697893</v>
+        <v>-10.152088258124785</v>
       </c>
       <c r="M26" t="n" s="0">
-        <v>-10.150859442987688</v>
+        <v>-10.151313121913095</v>
       </c>
       <c r="N26" t="n" s="0">
-        <v>-10.152732378359076</v>
+        <v>-10.152276640553406</v>
       </c>
       <c r="O26" t="n" s="0">
-        <v>-10.152405096537429</v>
+        <v>-10.15213685919788</v>
       </c>
       <c r="P26" t="n" s="0">
-        <v>-10.151167359849584</v>
+        <v>-10.152100185464343</v>
       </c>
       <c r="Q26" t="n" s="0">
-        <v>-10.152145345189313</v>
+        <v>-10.151560423681339</v>
       </c>
       <c r="R26" t="n" s="0">
-        <v>-10.15149196112672</v>
+        <v>-10.151299391841254</v>
       </c>
       <c r="S26" t="n" s="0">
-        <v>-10.147839747493627</v>
+        <v>-10.15257212813111</v>
       </c>
       <c r="T26" t="n" s="0">
-        <v>-10.15309543781159</v>
+        <v>-10.151462088551373</v>
       </c>
       <c r="U26" t="n" s="0">
-        <v>-10.151577258710407</v>
+        <v>-10.151535980121976</v>
       </c>
       <c r="V26" t="n" s="0">
-        <v>-10.150968404759725</v>
+        <v>-10.152128194830048</v>
       </c>
       <c r="W26" t="n" s="0">
-        <v>-10.152418285001454</v>
+        <v>-10.151815518103286</v>
       </c>
       <c r="X26" t="n" s="0">
-        <v>-10.15197092853605</v>
+        <v>-10.15212835970336</v>
       </c>
       <c r="Y26" t="n" s="0">
-        <v>-10.151658569370289</v>
+        <v>-10.152118120906396</v>
       </c>
       <c r="Z26" t="n" s="0">
-        <v>-10.15152856495055</v>
+        <v>-10.151279765615916</v>
       </c>
       <c r="AA26" t="n" s="0">
-        <v>-10.15264407224326</v>
+        <v>-10.151421337060661</v>
       </c>
       <c r="AB26" t="n" s="0">
-        <v>-10.150468283133415</v>
+        <v>-10.152400615468192</v>
       </c>
       <c r="AC26" t="n" s="0">
-        <v>-10.152672023671602</v>
+        <v>-10.151978070065324</v>
       </c>
       <c r="AD26" t="n" s="0">
-        <v>-10.152562115579649</v>
+        <v>-10.152603685328955</v>
       </c>
       <c r="AE26" t="n" s="0">
-        <v>-10.15160764166226</v>
+        <v>-10.152035673845264</v>
       </c>
       <c r="AF26" t="n" s="0">
-        <v>-10.150262010078793</v>
+        <v>-10.151964777759874</v>
       </c>
     </row>
     <row r="27">
       <c r="C27" t="n" s="0">
-        <v>-10.401256625330095</v>
+        <v>-10.400556045790152</v>
       </c>
       <c r="D27" t="n" s="0">
-        <v>-10.401293221906187</v>
+        <v>-10.401025497046854</v>
       </c>
       <c r="E27" t="n" s="0">
-        <v>-10.402209486673796</v>
+        <v>-10.402159561445702</v>
       </c>
       <c r="F27" t="n" s="0">
-        <v>-10.402143015373907</v>
+        <v>-10.402272804636388</v>
       </c>
       <c r="G27" t="n" s="0">
-        <v>-10.402429352107713</v>
+        <v>-10.401924242841808</v>
       </c>
       <c r="H27" t="n" s="0">
-        <v>-10.401392811008924</v>
+        <v>-10.400881089661452</v>
       </c>
       <c r="I27" t="n" s="0">
-        <v>-10.402108164050963</v>
+        <v>-10.401306463905605</v>
       </c>
       <c r="J27" t="n" s="0">
-        <v>-10.401757651264953</v>
+        <v>-10.402689398056083</v>
       </c>
       <c r="K27" t="n" s="0">
-        <v>-10.401945776760995</v>
+        <v>-10.401060454396541</v>
       </c>
       <c r="L27" t="n" s="0">
-        <v>-10.402330392010978</v>
+        <v>-10.400701954064482</v>
       </c>
       <c r="M27" t="n" s="0">
-        <v>-10.400535993507702</v>
+        <v>-10.401931368690338</v>
       </c>
       <c r="N27" t="n" s="0">
-        <v>-10.40169653483259</v>
+        <v>-10.400922583492777</v>
       </c>
       <c r="O27" t="n" s="0">
-        <v>-10.399961296782067</v>
+        <v>-10.40257771201838</v>
       </c>
       <c r="P27" t="n" s="0">
-        <v>-10.400953473737221</v>
+        <v>-10.401850022776998</v>
       </c>
       <c r="Q27" t="n" s="0">
-        <v>-10.402334168250674</v>
+        <v>-3.7241832444079055</v>
       </c>
       <c r="R27" t="n" s="0">
-        <v>-10.401335590133577</v>
+        <v>-10.402227309141644</v>
       </c>
       <c r="S27" t="n" s="0">
-        <v>-10.40214810054117</v>
+        <v>-10.399792817640932</v>
       </c>
       <c r="T27" t="n" s="0">
-        <v>-10.402338216697919</v>
+        <v>-10.40031064397445</v>
       </c>
       <c r="U27" t="n" s="0">
-        <v>-10.401145574155002</v>
+        <v>-10.40175245551955</v>
       </c>
       <c r="V27" t="n" s="0">
-        <v>-10.402523583189208</v>
+        <v>-10.401271901935367</v>
       </c>
       <c r="W27" t="n" s="0">
-        <v>-10.4024203135367</v>
+        <v>-10.401872186656528</v>
       </c>
       <c r="X27" t="n" s="0">
-        <v>-10.400676281216153</v>
+        <v>-10.402127845368526</v>
       </c>
       <c r="Y27" t="n" s="0">
-        <v>-10.402695430399875</v>
+        <v>-10.401883894274924</v>
       </c>
       <c r="Z27" t="n" s="0">
-        <v>-10.40179722947111</v>
+        <v>-10.402241448083327</v>
       </c>
       <c r="AA27" t="n" s="0">
-        <v>-10.402018399789476</v>
+        <v>-10.402726014626172</v>
       </c>
       <c r="AB27" t="n" s="0">
-        <v>-10.401603957764138</v>
+        <v>-10.401604721294873</v>
       </c>
       <c r="AC27" t="n" s="0">
-        <v>-10.3987720358565</v>
+        <v>-10.402113078487414</v>
       </c>
       <c r="AD27" t="n" s="0">
-        <v>-10.4017874751531</v>
+        <v>-10.401689689195987</v>
       </c>
       <c r="AE27" t="n" s="0">
-        <v>-10.399502087489758</v>
+        <v>-10.402078786133657</v>
       </c>
       <c r="AF27" t="n" s="0">
-        <v>-10.402265427168574</v>
+        <v>-10.40013088975027</v>
       </c>
     </row>
     <row r="28">
       <c r="C28" t="n" s="0">
-        <v>-10.534827889708426</v>
+        <v>-10.53133439222762</v>
       </c>
       <c r="D28" t="n" s="0">
-        <v>-10.53468919438118</v>
+        <v>-10.535413083747844</v>
       </c>
       <c r="E28" t="n" s="0">
-        <v>-10.534091274778795</v>
+        <v>-10.53541989249725</v>
       </c>
       <c r="F28" t="n" s="0">
-        <v>-10.535421897875958</v>
+        <v>-10.535576211300125</v>
       </c>
       <c r="G28" t="n" s="0">
-        <v>-10.53500433245413</v>
+        <v>-10.535766233574419</v>
       </c>
       <c r="H28" t="n" s="0">
-        <v>-10.534932399681125</v>
+        <v>-10.53532632691462</v>
       </c>
       <c r="I28" t="n" s="0">
-        <v>-10.535217178692006</v>
+        <v>-10.534881536656833</v>
       </c>
       <c r="J28" t="n" s="0">
-        <v>-10.535703865107013</v>
+        <v>-10.535570523492105</v>
       </c>
       <c r="K28" t="n" s="0">
-        <v>-10.536048775384389</v>
+        <v>-10.53494918930863</v>
       </c>
       <c r="L28" t="n" s="0">
-        <v>-10.534903590880244</v>
+        <v>-10.533925372476903</v>
       </c>
       <c r="M28" t="n" s="0">
-        <v>-10.534530942774067</v>
+        <v>-10.534954569678082</v>
       </c>
       <c r="N28" t="n" s="0">
-        <v>-10.535529576056012</v>
+        <v>-10.535089193764628</v>
       </c>
       <c r="O28" t="n" s="0">
-        <v>-10.53568104075203</v>
+        <v>-10.536273680360013</v>
       </c>
       <c r="P28" t="n" s="0">
-        <v>-10.532563566381068</v>
+        <v>-10.53619188868565</v>
       </c>
       <c r="Q28" t="n" s="0">
-        <v>-10.535749260436017</v>
+        <v>-10.533506514341704</v>
       </c>
       <c r="R28" t="n" s="0">
-        <v>-10.536119655968072</v>
+        <v>-10.535844429438862</v>
       </c>
       <c r="S28" t="n" s="0">
-        <v>-10.533325613910334</v>
+        <v>-10.535554105961575</v>
       </c>
       <c r="T28" t="n" s="0">
-        <v>-10.535749346079891</v>
+        <v>-10.534207102750823</v>
       </c>
       <c r="U28" t="n" s="0">
-        <v>-10.53422138451843</v>
+        <v>-10.535601444732906</v>
       </c>
       <c r="V28" t="n" s="0">
-        <v>-10.53484195355643</v>
+        <v>-10.534433371785273</v>
       </c>
       <c r="W28" t="n" s="0">
-        <v>-10.534523288620832</v>
+        <v>-10.536024747845241</v>
       </c>
       <c r="X28" t="n" s="0">
-        <v>-10.533672314074893</v>
+        <v>-10.535577580542494</v>
       </c>
       <c r="Y28" t="n" s="0">
-        <v>-10.534964687148284</v>
+        <v>-10.535122204398512</v>
       </c>
       <c r="Z28" t="n" s="0">
-        <v>-10.534104029509932</v>
+        <v>-10.536031805846932</v>
       </c>
       <c r="AA28" t="n" s="0">
-        <v>-10.534514480364923</v>
+        <v>-10.535089577519503</v>
       </c>
       <c r="AB28" t="n" s="0">
-        <v>-10.535044792003285</v>
+        <v>-10.53616714483023</v>
       </c>
       <c r="AC28" t="n" s="0">
-        <v>-10.534762113455658</v>
+        <v>-10.533980200770332</v>
       </c>
       <c r="AD28" t="n" s="0">
-        <v>-10.534180405624943</v>
+        <v>-10.535137710827412</v>
       </c>
       <c r="AE28" t="n" s="0">
-        <v>-10.5350563862544</v>
+        <v>-10.53508133809258</v>
       </c>
       <c r="AF28" t="n" s="0">
-        <v>-10.534339618217839</v>
+        <v>-10.535712439710247</v>
       </c>
     </row>
     <row r="35">
       <c r="C35" t="n" s="0">
-        <v>1.8119914151376761</v>
+        <v>0.0</v>
       </c>
       <c r="D35" t="n" s="0">
-        <v>5.849112079866011</v>
+        <v>0.599046796331471</v>
       </c>
       <c r="E35" t="n" s="0">
-        <v>5.482430521603653</v>
+        <v>0.00978130564227977</v>
       </c>
       <c r="F35" t="n" s="0">
-        <v>0.42913581877718676</v>
+        <v>7.646489833955252</v>
       </c>
       <c r="G35" t="n" s="0">
-        <v>3.749511322299803</v>
+        <v>0.2318665090100453</v>
       </c>
       <c r="H35" t="n" s="0">
-        <v>0.722587244035823</v>
+        <v>0.06796564290922934</v>
       </c>
       <c r="I35" t="n" s="0">
-        <v>3.6368380567485064</v>
+        <v>0.024991160586661544</v>
       </c>
       <c r="J35" t="n" s="0">
-        <v>1.1381998970751939</v>
+        <v>8.177981816669291E-5</v>
       </c>
       <c r="K35" t="n" s="0">
-        <v>0.48716269097717096</v>
+        <v>1.052850184661432</v>
       </c>
       <c r="L35" t="n" s="0">
-        <v>7.753800726865793E-4</v>
+        <v>0.37300010159121016</v>
       </c>
       <c r="M35" t="n" s="0">
-        <v>5.115356601468488</v>
+        <v>1.4904713756353192</v>
       </c>
       <c r="N35" t="n" s="0">
-        <v>0.24064579582154905</v>
+        <v>0.42707079383026914</v>
       </c>
       <c r="O35" t="n" s="0">
-        <v>5.1705109622855</v>
+        <v>15.645441095047138</v>
       </c>
       <c r="P35" t="n" s="0">
-        <v>0.10230178659637545</v>
+        <v>23.781608225713427</v>
       </c>
       <c r="Q35" t="n" s="0">
-        <v>1.0727260869907676E-4</v>
+        <v>0.00829438213521632</v>
       </c>
       <c r="R35" t="n" s="0">
-        <v>0.07293652269658243</v>
+        <v>0.32397576017389806</v>
       </c>
       <c r="S35" t="n" s="0">
-        <v>11.394931764962164</v>
+        <v>0.6733308745567371</v>
       </c>
       <c r="T35" t="n" s="0">
-        <v>3.487220958269776</v>
+        <v>4.85993872499944</v>
       </c>
       <c r="U35" t="n" s="0">
-        <v>8.298877534810796</v>
+        <v>0.2342583492235334</v>
       </c>
       <c r="V35" t="n" s="0">
-        <v>0.759788211049591</v>
+        <v>0.014674935054912438</v>
       </c>
       <c r="W35" t="n" s="0">
-        <v>0.8417082723258668</v>
+        <v>0.024884126257188447</v>
       </c>
       <c r="X35" t="n" s="0">
-        <v>0.14167889844023004</v>
+        <v>0.03299565342098555</v>
       </c>
       <c r="Y35" t="n" s="0">
-        <v>4.2889866588012255</v>
+        <v>0.011583523233529893</v>
       </c>
       <c r="Z35" t="n" s="0">
-        <v>0.3694382556846705</v>
+        <v>4.60746383687426</v>
       </c>
       <c r="AA35" t="n" s="0">
-        <v>2.682242152553594</v>
+        <v>0.44534581321194155</v>
       </c>
       <c r="AB35" t="n" s="0">
-        <v>10.629155739026423</v>
+        <v>2.1530059436054687</v>
       </c>
       <c r="AC35" t="n" s="0">
-        <v>4.835845083090114</v>
+        <v>0.10006109897424735</v>
       </c>
       <c r="AD35" t="n" s="0">
-        <v>2.4459240271080183</v>
+        <v>0.14801576550285947</v>
       </c>
       <c r="AE35" t="n" s="0">
-        <v>0.1263999116186898</v>
+        <v>0.3244748778641354</v>
       </c>
       <c r="AF35" t="n" s="0">
-        <v>1.6119546644731821</v>
+        <v>1.082782966528391</v>
       </c>
     </row>
     <row r="36">
       <c r="C36" t="n" s="0">
-        <v>0.027282833613965978</v>
+        <v>0.8357682652491949</v>
       </c>
       <c r="D36" t="n" s="0">
-        <v>0.27435058396029244</v>
+        <v>2.566120989277514</v>
       </c>
       <c r="E36" t="n" s="0">
-        <v>1.063983847377874</v>
+        <v>0.6275093441524688</v>
       </c>
       <c r="F36" t="n" s="0">
-        <v>1.9986929968454008</v>
+        <v>0.0</v>
       </c>
       <c r="G36" t="n" s="0">
-        <v>4.55035506573416</v>
+        <v>1.2932576382088121</v>
       </c>
       <c r="H36" t="n" s="0">
-        <v>2.6192941794166558</v>
+        <v>0.01047537647584968</v>
       </c>
       <c r="I36" t="n" s="0">
-        <v>0.18884576599968372</v>
+        <v>1.6048030099762196</v>
       </c>
       <c r="J36" t="n" s="0">
-        <v>1.1037710110741423</v>
+        <v>1.2542702986308696</v>
       </c>
       <c r="K36" t="n" s="0">
-        <v>0.724103549861323</v>
+        <v>0.681228467269563</v>
       </c>
       <c r="L36" t="n" s="0">
-        <v>0.4206969800007777</v>
+        <v>1.555193864337885</v>
       </c>
       <c r="M36" t="n" s="0">
-        <v>0.5068383293433583</v>
+        <v>1.6043803902322382</v>
       </c>
       <c r="N36" t="n" s="0">
-        <v>2.139199670676419</v>
+        <v>0.07808562631292383</v>
       </c>
       <c r="O36" t="n" s="0">
-        <v>1.506039140544649</v>
+        <v>0.6100397442430031</v>
       </c>
       <c r="P36" t="n" s="0">
-        <v>2.1778148123188545</v>
+        <v>0.5125159791246228</v>
       </c>
       <c r="Q36" t="n" s="0">
-        <v>1.3582593297412908</v>
+        <v>0.4107275323874584</v>
       </c>
       <c r="R36" t="n" s="0">
-        <v>0.24590503917192183</v>
+        <v>0.8170788470128869</v>
       </c>
       <c r="S36" t="n" s="0">
-        <v>1.1600903227068455</v>
+        <v>1.2226204830050882</v>
       </c>
       <c r="T36" t="n" s="0">
-        <v>2.6412054081242413</v>
+        <v>2.0833718045512937</v>
       </c>
       <c r="U36" t="n" s="0">
-        <v>0.24822253942845815</v>
+        <v>1.302230439017739</v>
       </c>
       <c r="V36" t="n" s="0">
-        <v>1.1101318294310203</v>
+        <v>2.6282859531953613</v>
       </c>
       <c r="W36" t="n" s="0">
-        <v>0.40596314884491946</v>
+        <v>1.5041682962559997</v>
       </c>
       <c r="X36" t="n" s="0">
-        <v>2.196868673344203</v>
+        <v>9.744732634166164</v>
       </c>
       <c r="Y36" t="n" s="0">
-        <v>0.5535661497468093</v>
+        <v>3.2785737058786917</v>
       </c>
       <c r="Z36" t="n" s="0">
-        <v>1.1996879138386005</v>
+        <v>0.21643705091532772</v>
       </c>
       <c r="AA36" t="n" s="0">
-        <v>0.12181878943113209</v>
+        <v>0.71344309200947</v>
       </c>
       <c r="AB36" t="n" s="0">
-        <v>3.413611687794298</v>
+        <v>0.1705331787891404</v>
       </c>
       <c r="AC36" t="n" s="0">
-        <v>1.5120710080190132</v>
+        <v>0.3156805355837304</v>
       </c>
       <c r="AD36" t="n" s="0">
-        <v>1.7355508895186162</v>
+        <v>2.53644240615696</v>
       </c>
       <c r="AE36" t="n" s="0">
-        <v>2.6718960789407937</v>
+        <v>1.3793924432658142</v>
       </c>
       <c r="AF36" t="n" s="0">
-        <v>2.278691279127908</v>
+        <v>2.077755508245765</v>
       </c>
     </row>
     <row r="37">
       <c r="C37" t="n" s="0">
-        <v>42.77898225455749</v>
+        <v>61.73028596214628</v>
       </c>
       <c r="D37" t="n" s="0">
-        <v>470.416208668403</v>
+        <v>537.4863791514063</v>
       </c>
       <c r="E37" t="n" s="0">
-        <v>4.860407406624084</v>
+        <v>19.941320850087454</v>
       </c>
       <c r="F37" t="n" s="0">
-        <v>14.911680786735193</v>
+        <v>13.834038123150407</v>
       </c>
       <c r="G37" t="n" s="0">
-        <v>362.9755629223475</v>
+        <v>798.8396478811235</v>
       </c>
       <c r="H37" t="n" s="0">
-        <v>76.915811500264</v>
+        <v>4.275661187551887</v>
       </c>
       <c r="I37" t="n" s="0">
-        <v>124.06735919964808</v>
+        <v>18.1527890990586</v>
       </c>
       <c r="J37" t="n" s="0">
-        <v>81.52522063058281</v>
+        <v>447.2051880949384</v>
       </c>
       <c r="K37" t="n" s="0">
-        <v>122.8702941398679</v>
+        <v>30.11640436863266</v>
       </c>
       <c r="L37" t="n" s="0">
-        <v>66.98663888541181</v>
+        <v>372.8669861723456</v>
       </c>
       <c r="M37" t="n" s="0">
-        <v>1.8972255279363015</v>
+        <v>187.54502974195526</v>
       </c>
       <c r="N37" t="n" s="0">
-        <v>76.8363385308887</v>
+        <v>134.77195863258837</v>
       </c>
       <c r="O37" t="n" s="0">
-        <v>100.54219990087994</v>
+        <v>791.0392821121773</v>
       </c>
       <c r="P37" t="n" s="0">
-        <v>86.57954115356573</v>
+        <v>679.8856797900952</v>
       </c>
       <c r="Q37" t="n" s="0">
-        <v>486.28481265077033</v>
+        <v>170.77301581489843</v>
       </c>
       <c r="R37" t="n" s="0">
-        <v>198.60718760729694</v>
+        <v>6.828568112280416</v>
       </c>
       <c r="S37" t="n" s="0">
-        <v>197.0110733107607</v>
+        <v>157.47610546954797</v>
       </c>
       <c r="T37" t="n" s="0">
-        <v>192.2833308387801</v>
+        <v>13.569582473110513</v>
       </c>
       <c r="U37" t="n" s="0">
-        <v>53.60996309317056</v>
+        <v>16.432068982755048</v>
       </c>
       <c r="V37" t="n" s="0">
-        <v>317.8289793768126</v>
+        <v>61.071302242352786</v>
       </c>
       <c r="W37" t="n" s="0">
-        <v>822.270894899805</v>
+        <v>148.15155005301443</v>
       </c>
       <c r="X37" t="n" s="0">
-        <v>392.66665791749614</v>
+        <v>427.161126082574</v>
       </c>
       <c r="Y37" t="n" s="0">
-        <v>137.68595561008843</v>
+        <v>21.798343249137698</v>
       </c>
       <c r="Z37" t="n" s="0">
-        <v>4009.0887651270637</v>
+        <v>92.34848660872609</v>
       </c>
       <c r="AA37" t="n" s="0">
-        <v>1176.9373614225997</v>
+        <v>22.381715673956506</v>
       </c>
       <c r="AB37" t="n" s="0">
-        <v>65.1433184319396</v>
+        <v>413.0863151161313</v>
       </c>
       <c r="AC37" t="n" s="0">
-        <v>73.8073907297289</v>
+        <v>61.97530048272989</v>
       </c>
       <c r="AD37" t="n" s="0">
-        <v>22.758380390386172</v>
+        <v>571.4356049457781</v>
       </c>
       <c r="AE37" t="n" s="0">
-        <v>50.25912250071536</v>
+        <v>80.20381612616528</v>
       </c>
       <c r="AF37" t="n" s="0">
-        <v>468.16582719447456</v>
+        <v>377.60158279131923</v>
       </c>
     </row>
     <row r="38">
       <c r="C38" t="n" s="0">
-        <v>1.8212642710331381</v>
+        <v>0.10866210376565849</v>
       </c>
       <c r="D38" t="n" s="0">
-        <v>2.979316308296124</v>
+        <v>1.7993099195251303</v>
       </c>
       <c r="E38" t="n" s="0">
-        <v>0.7896143905193138</v>
+        <v>0.2483646362420102</v>
       </c>
       <c r="F38" t="n" s="0">
-        <v>2.3853534358711626</v>
+        <v>3.169250218482064</v>
       </c>
       <c r="G38" t="n" s="0">
-        <v>0.8356635673532827</v>
+        <v>0.9162773124838972</v>
       </c>
       <c r="H38" t="n" s="0">
-        <v>1.0071718034553925</v>
+        <v>3.684919868908623</v>
       </c>
       <c r="I38" t="n" s="0">
-        <v>3.365714176445589</v>
+        <v>2.384374445696592</v>
       </c>
       <c r="J38" t="n" s="0">
-        <v>1.2730619583659541</v>
+        <v>0.8609565373486494</v>
       </c>
       <c r="K38" t="n" s="0">
-        <v>0.5575889348771903</v>
+        <v>0.5396180120326644</v>
       </c>
       <c r="L38" t="n" s="0">
-        <v>1.4736406521041305</v>
+        <v>0.9836328043932974</v>
       </c>
       <c r="M38" t="n" s="0">
-        <v>4.970696651433543</v>
+        <v>1.113411593264128</v>
       </c>
       <c r="N38" t="n" s="0">
-        <v>1.8315071838923558</v>
+        <v>1.6617760948223723</v>
       </c>
       <c r="O38" t="n" s="0">
-        <v>7.5362362273344425</v>
+        <v>3.80373765331139</v>
       </c>
       <c r="P38" t="n" s="0">
-        <v>6.484705953014411</v>
+        <v>1.9030837105902585</v>
       </c>
       <c r="Q38" t="n" s="0">
-        <v>0.15675283961232409</v>
+        <v>5.712329538085621</v>
       </c>
       <c r="R38" t="n" s="0">
-        <v>2.761590590116682</v>
+        <v>3.0380578043697244</v>
       </c>
       <c r="S38" t="n" s="0">
-        <v>4.931535568138743</v>
+        <v>0.6490164145196993</v>
       </c>
       <c r="T38" t="n" s="0">
-        <v>2.6913771989915327</v>
+        <v>3.694553106251484</v>
       </c>
       <c r="U38" t="n" s="0">
-        <v>1.189389977337882</v>
+        <v>1.7847417059878141</v>
       </c>
       <c r="V38" t="n" s="0">
-        <v>1.0803318165901605</v>
+        <v>0.5294911676595127</v>
       </c>
       <c r="W38" t="n" s="0">
-        <v>0.3078985148134037</v>
+        <v>37.41324711601858</v>
       </c>
       <c r="X38" t="n" s="0">
-        <v>0.40314649691969334</v>
+        <v>1.2931056369834355</v>
       </c>
       <c r="Y38" t="n" s="0">
-        <v>2.6179587382740936</v>
+        <v>3.5654770919377436</v>
       </c>
       <c r="Z38" t="n" s="0">
-        <v>1.3056215654176346</v>
+        <v>3.558000302695369</v>
       </c>
       <c r="AA38" t="n" s="0">
-        <v>4.313301628750901</v>
+        <v>3.7987736534639116</v>
       </c>
       <c r="AB38" t="n" s="0">
-        <v>3.9749590022256513</v>
+        <v>3.1692415961224474</v>
       </c>
       <c r="AC38" t="n" s="0">
-        <v>2.024294206438504</v>
+        <v>12.185699745920306</v>
       </c>
       <c r="AD38" t="n" s="0">
-        <v>1.097165117434997</v>
+        <v>2.428823194587413</v>
       </c>
       <c r="AE38" t="n" s="0">
-        <v>7.483504349249286</v>
+        <v>1.7920048939158182</v>
       </c>
       <c r="AF38" t="n" s="0">
-        <v>1.5259143210243329</v>
+        <v>2.7588857997814427</v>
       </c>
     </row>
     <row r="39">
       <c r="C39" t="n" s="0">
-        <v>79.06253131030226</v>
+        <v>433.9234461630173</v>
       </c>
       <c r="D39" t="n" s="0">
-        <v>4.4741133242530635</v>
+        <v>71.69892176131893</v>
       </c>
       <c r="E39" t="n" s="0">
-        <v>14.058925774332824</v>
+        <v>591.2233114829548</v>
       </c>
       <c r="F39" t="n" s="0">
-        <v>72.19697748334768</v>
+        <v>1003.4344626681235</v>
       </c>
       <c r="G39" t="n" s="0">
-        <v>8.101347554850301</v>
+        <v>177.667113461112</v>
       </c>
       <c r="H39" t="n" s="0">
-        <v>340.4519732305905</v>
+        <v>355.65880140621886</v>
       </c>
       <c r="I39" t="n" s="0">
-        <v>330.21270075227045</v>
+        <v>3541.7477623187315</v>
       </c>
       <c r="J39" t="n" s="0">
-        <v>359.2877236511052</v>
+        <v>39.279959402645</v>
       </c>
       <c r="K39" t="n" s="0">
-        <v>1155.368742178981</v>
+        <v>408.82321269688373</v>
       </c>
       <c r="L39" t="n" s="0">
-        <v>851.2501406379349</v>
+        <v>354.7183423316107</v>
       </c>
       <c r="M39" t="n" s="0">
-        <v>58.212937393263516</v>
+        <v>337.4448504797361</v>
       </c>
       <c r="N39" t="n" s="0">
-        <v>77.4064187224125</v>
+        <v>60143.46849373258</v>
       </c>
       <c r="O39" t="n" s="0">
-        <v>9.082471877459563</v>
+        <v>15.381024620830406</v>
       </c>
       <c r="P39" t="n" s="0">
-        <v>94.96143039117995</v>
+        <v>17.660221946580908</v>
       </c>
       <c r="Q39" t="n" s="0">
-        <v>80.82885667500582</v>
+        <v>82.3548722183325</v>
       </c>
       <c r="R39" t="n" s="0">
-        <v>10.420000859256763</v>
+        <v>195.37379189330278</v>
       </c>
       <c r="S39" t="n" s="0">
-        <v>9.476901581659597</v>
+        <v>7343.73233279091</v>
       </c>
       <c r="T39" t="n" s="0">
-        <v>282.68935493603357</v>
+        <v>14.250576571896497</v>
       </c>
       <c r="U39" t="n" s="0">
-        <v>75.78232445613126</v>
+        <v>75.78486515071278</v>
       </c>
       <c r="V39" t="n" s="0">
-        <v>98.06240785480173</v>
+        <v>6.332077572344925</v>
       </c>
       <c r="W39" t="n" s="0">
-        <v>97.11667667370638</v>
+        <v>137.27130563613593</v>
       </c>
       <c r="X39" t="n" s="0">
-        <v>8.063578487891371</v>
+        <v>776.5809185171751</v>
       </c>
       <c r="Y39" t="n" s="0">
-        <v>119.09129684211145</v>
+        <v>114.19922555627778</v>
       </c>
       <c r="Z39" t="n" s="0">
-        <v>158.48503837084735</v>
+        <v>5.592432351206208</v>
       </c>
       <c r="AA39" t="n" s="0">
-        <v>8.753951418203604</v>
+        <v>41.414140868594345</v>
       </c>
       <c r="AB39" t="n" s="0">
-        <v>588.0402950688994</v>
+        <v>77.40669513701924</v>
       </c>
       <c r="AC39" t="n" s="0">
-        <v>129.4292384499682</v>
+        <v>90024.07783901035</v>
       </c>
       <c r="AD39" t="n" s="0">
-        <v>136.3100804200691</v>
+        <v>719.2676950344169</v>
       </c>
       <c r="AE39" t="n" s="0">
-        <v>828.6513733367648</v>
+        <v>8.991504312951449</v>
       </c>
       <c r="AF39" t="n" s="0">
-        <v>186.52022590318413</v>
+        <v>794.2642402195604</v>
       </c>
     </row>
     <row r="40">
       <c r="C40" t="n" s="0">
-        <v>0.05076310545294178</v>
+        <v>0.001050459211524898</v>
       </c>
       <c r="D40" t="n" s="0">
-        <v>0.020005070145156064</v>
+        <v>0.12129018642788494</v>
       </c>
       <c r="E40" t="n" s="0">
-        <v>0.009770925284742032</v>
+        <v>6.835766286770169</v>
       </c>
       <c r="F40" t="n" s="0">
-        <v>0.5332294410751098</v>
+        <v>0.1282302560403405</v>
       </c>
       <c r="G40" t="n" s="0">
-        <v>2.9221016251844274</v>
+        <v>92.72472183053817</v>
       </c>
       <c r="H40" t="n" s="0">
-        <v>1.0320823836559698</v>
+        <v>0.8185556518096406</v>
       </c>
       <c r="I40" t="n" s="0">
-        <v>0.14844233589175207</v>
+        <v>6.457891117457592</v>
       </c>
       <c r="J40" t="n" s="0">
-        <v>0.5165033996828803</v>
+        <v>0.46927362815507273</v>
       </c>
       <c r="K40" t="n" s="0">
-        <v>0.5046099498725239</v>
+        <v>3.2567263133952125</v>
       </c>
       <c r="L40" t="n" s="0">
-        <v>0.007159310015644808</v>
+        <v>0.006066181323125096</v>
       </c>
       <c r="M40" t="n" s="0">
-        <v>0.27274942928730084</v>
+        <v>19.74532865397739</v>
       </c>
       <c r="N40" t="n" s="0">
-        <v>2.1171148092620893</v>
+        <v>0.009125362051576168</v>
       </c>
       <c r="O40" t="n" s="0">
-        <v>0.006458784329743774</v>
+        <v>0.00854631821173381</v>
       </c>
       <c r="P40" t="n" s="0">
-        <v>0.0191135122447228</v>
+        <v>2.3615982482400444</v>
       </c>
       <c r="Q40" t="n" s="0">
-        <v>3.8292001874606083E-4</v>
+        <v>0.04769630075074054</v>
       </c>
       <c r="R40" t="n" s="0">
-        <v>0.6042899588198243</v>
+        <v>1.165157616025273E-4</v>
       </c>
       <c r="S40" t="n" s="0">
-        <v>6.500371789995288</v>
+        <v>7.317989225141959</v>
       </c>
       <c r="T40" t="n" s="0">
-        <v>0.7743777221208556</v>
+        <v>38.657335492269894</v>
       </c>
       <c r="U40" t="n" s="0">
-        <v>0.01444978603041229</v>
+        <v>0.5851978410147505</v>
       </c>
       <c r="V40" t="n" s="0">
-        <v>0.8900985067537196</v>
+        <v>0.026222549259227724</v>
       </c>
       <c r="W40" t="n" s="0">
-        <v>0.128560372101217</v>
+        <v>2.1463104036983593</v>
       </c>
       <c r="X40" t="n" s="0">
-        <v>0.05357235106694243</v>
+        <v>0.04508835502217038</v>
       </c>
       <c r="Y40" t="n" s="0">
-        <v>0.058103915225405756</v>
+        <v>2.379080017264442</v>
       </c>
       <c r="Z40" t="n" s="0">
-        <v>2.096008487554586</v>
+        <v>0.06112556691724906</v>
       </c>
       <c r="AA40" t="n" s="0">
-        <v>0.13237013111525786</v>
+        <v>5.709265332594632</v>
       </c>
       <c r="AB40" t="n" s="0">
-        <v>14.306761883113362</v>
+        <v>1.194933692346662</v>
       </c>
       <c r="AC40" t="n" s="0">
-        <v>1.4530769759473183</v>
+        <v>2.9511258716391997</v>
       </c>
       <c r="AD40" t="n" s="0">
-        <v>262.1068563409714</v>
+        <v>2.5886626601442804</v>
       </c>
       <c r="AE40" t="n" s="0">
-        <v>0.008559017713537384</v>
+        <v>26.995217231056753</v>
       </c>
       <c r="AF40" t="n" s="0">
-        <v>13.829098982395506</v>
+        <v>1.1015577253916207</v>
       </c>
     </row>
     <row r="41">
       <c r="C41" t="n" s="0">
-        <v>0.0031596088252383984</v>
+        <v>0.02287513860022234</v>
       </c>
       <c r="D41" t="n" s="0">
-        <v>0.052815404786779346</v>
+        <v>0.012247070896703197</v>
       </c>
       <c r="E41" t="n" s="0">
-        <v>0.053440790225830107</v>
+        <v>0.044669108447092876</v>
       </c>
       <c r="F41" t="n" s="0">
-        <v>0.009808480377992292</v>
+        <v>0.024247886894749018</v>
       </c>
       <c r="G41" t="n" s="0">
-        <v>0.016286787534050006</v>
+        <v>0.12960985304533448</v>
       </c>
       <c r="H41" t="n" s="0">
-        <v>0.0488977990534668</v>
+        <v>0.008685402516252157</v>
       </c>
       <c r="I41" t="n" s="0">
-        <v>0.020732320251191677</v>
+        <v>0.01835054596930677</v>
       </c>
       <c r="J41" t="n" s="0">
-        <v>0.05440105372951403</v>
+        <v>0.0897872258948621</v>
       </c>
       <c r="K41" t="n" s="0">
-        <v>0.022736645530088414</v>
+        <v>0.02063860858825806</v>
       </c>
       <c r="L41" t="n" s="0">
-        <v>0.02184578773280025</v>
+        <v>0.01290681233021936</v>
       </c>
       <c r="M41" t="n" s="0">
-        <v>0.10615217188602993</v>
+        <v>0.0251964759300237</v>
       </c>
       <c r="N41" t="n" s="0">
-        <v>0.027097729313866264</v>
+        <v>0.006592149709161664</v>
       </c>
       <c r="O41" t="n" s="0">
-        <v>0.018593047709798697</v>
+        <v>0.028623697836319385</v>
       </c>
       <c r="P41" t="n" s="0">
-        <v>0.05501009590954649</v>
+        <v>0.08158440741291516</v>
       </c>
       <c r="Q41" t="n" s="0">
-        <v>0.005140794677313993</v>
+        <v>0.030652866545217584</v>
       </c>
       <c r="R41" t="n" s="0">
-        <v>0.029285934588903835</v>
+        <v>0.002753705655429602</v>
       </c>
       <c r="S41" t="n" s="0">
-        <v>0.01926185448977063</v>
+        <v>0.015304857415657213</v>
       </c>
       <c r="T41" t="n" s="0">
-        <v>0.011392116931507767</v>
+        <v>0.005438263975530283</v>
       </c>
       <c r="U41" t="n" s="0">
-        <v>0.039535790904041204</v>
+        <v>0.03203082580591533</v>
       </c>
       <c r="V41" t="n" s="0">
-        <v>0.00685010893538043</v>
+        <v>0.050814398304587644</v>
       </c>
       <c r="W41" t="n" s="0">
-        <v>0.031112787230613486</v>
+        <v>0.035044323716539934</v>
       </c>
       <c r="X41" t="n" s="0">
-        <v>0.03801592820488249</v>
+        <v>0.0421258139096476</v>
       </c>
       <c r="Y41" t="n" s="0">
-        <v>0.022547546167688042</v>
+        <v>0.0020257820548093405</v>
       </c>
       <c r="Z41" t="n" s="0">
-        <v>0.014703271031465294</v>
+        <v>0.00953065355039209</v>
       </c>
       <c r="AA41" t="n" s="0">
-        <v>0.0286058246797449</v>
+        <v>0.010473190411627722</v>
       </c>
       <c r="AB41" t="n" s="0">
-        <v>0.007337294780555152</v>
+        <v>0.01868995328722091</v>
       </c>
       <c r="AC41" t="n" s="0">
-        <v>0.05195147574029538</v>
+        <v>0.05245742627720575</v>
       </c>
       <c r="AD41" t="n" s="0">
-        <v>0.030792793958226032</v>
+        <v>0.028973808880591964</v>
       </c>
       <c r="AE41" t="n" s="0">
-        <v>0.05998195209269402</v>
+        <v>0.024814143274558078</v>
       </c>
       <c r="AF41" t="n" s="0">
-        <v>0.0024684146947708124</v>
+        <v>0.006001805892909054</v>
       </c>
     </row>
     <row r="42">
       <c r="C42" t="n" s="0">
-        <v>-3400.5394465826776</v>
+        <v>-2465.762957239392</v>
       </c>
       <c r="D42" t="n" s="0">
-        <v>-2639.71603080197</v>
+        <v>-3654.699989605351</v>
       </c>
       <c r="E42" t="n" s="0">
-        <v>-3417.41104847686</v>
+        <v>-3055.970635066969</v>
       </c>
       <c r="F42" t="n" s="0">
-        <v>-3655.322295972883</v>
+        <v>-3234.8486530975806</v>
       </c>
       <c r="G42" t="n" s="0">
-        <v>-3773.432798291795</v>
+        <v>-2191.4510458839995</v>
       </c>
       <c r="H42" t="n" s="0">
-        <v>-2842.9629687376823</v>
+        <v>-3169.3853879880553</v>
       </c>
       <c r="I42" t="n" s="0">
-        <v>-2456.6015876184065</v>
+        <v>-3022.9754771774838</v>
       </c>
       <c r="J42" t="n" s="0">
-        <v>-2276.9701442520586</v>
+        <v>-3080.500991696796</v>
       </c>
       <c r="K42" t="n" s="0">
-        <v>-2744.7448302524385</v>
+        <v>-2566.581594385449</v>
       </c>
       <c r="L42" t="n" s="0">
-        <v>-2874.849364542817</v>
+        <v>-2190.836332009986</v>
       </c>
       <c r="M42" t="n" s="0">
-        <v>-3257.309001395397</v>
+        <v>-2821.6878666341604</v>
       </c>
       <c r="N42" t="n" s="0">
-        <v>-3723.091338249856</v>
+        <v>-3180.998550296456</v>
       </c>
       <c r="O42" t="n" s="0">
-        <v>-2439.9747084731393</v>
+        <v>-2724.5244221530515</v>
       </c>
       <c r="P42" t="n" s="0">
-        <v>-2543.3108993651617</v>
+        <v>-2879.4218838464526</v>
       </c>
       <c r="Q42" t="n" s="0">
-        <v>-2547.510948725861</v>
+        <v>-2488.7200016003676</v>
       </c>
       <c r="R42" t="n" s="0">
-        <v>-2861.8630937145517</v>
+        <v>-3047.2420810892736</v>
       </c>
       <c r="S42" t="n" s="0">
-        <v>-3896.962519971217</v>
+        <v>-3704.385070979473</v>
       </c>
       <c r="T42" t="n" s="0">
-        <v>-2800.1539340254044</v>
+        <v>-3215.016964956191</v>
       </c>
       <c r="U42" t="n" s="0">
-        <v>-2189.980112413031</v>
+        <v>-2930.716289386485</v>
       </c>
       <c r="V42" t="n" s="0">
-        <v>-2942.8381845288427</v>
+        <v>-2961.394126892737</v>
       </c>
       <c r="W42" t="n" s="0">
-        <v>-3159.9062174291666</v>
+        <v>-2353.5627059860335</v>
       </c>
       <c r="X42" t="n" s="0">
-        <v>-2704.855949772581</v>
+        <v>-2521.19984062389</v>
       </c>
       <c r="Y42" t="n" s="0">
-        <v>-2363.346312734541</v>
+        <v>-2681.729597115605</v>
       </c>
       <c r="Z42" t="n" s="0">
-        <v>-2729.434090129888</v>
+        <v>-2709.0448378535307</v>
       </c>
       <c r="AA42" t="n" s="0">
-        <v>-2065.722543789698</v>
+        <v>-2683.3576985918066</v>
       </c>
       <c r="AB42" t="n" s="0">
-        <v>-2794.7673018388236</v>
+        <v>-3185.7802933545936</v>
       </c>
       <c r="AC42" t="n" s="0">
-        <v>-3357.7238607033114</v>
+        <v>-3000.8882578231537</v>
       </c>
       <c r="AD42" t="n" s="0">
-        <v>-3099.042159222895</v>
+        <v>-2448.14356973517</v>
       </c>
       <c r="AE42" t="n" s="0">
-        <v>-3178.539928799371</v>
+        <v>-2924.4205792433986</v>
       </c>
       <c r="AF42" t="n" s="0">
-        <v>-2701.570841390323</v>
+        <v>-3709.3447065243045</v>
       </c>
     </row>
     <row r="43">
       <c r="C43" t="n" s="0">
-        <v>41.660131466104474</v>
+        <v>54.811141062345015</v>
       </c>
       <c r="D43" t="n" s="0">
-        <v>24.90682468480422</v>
+        <v>24.197786714821575</v>
       </c>
       <c r="E43" t="n" s="0">
-        <v>9.968923730894058</v>
+        <v>17.027882998081445</v>
       </c>
       <c r="F43" t="n" s="0">
-        <v>39.02296470025024</v>
+        <v>62.04518925047246</v>
       </c>
       <c r="G43" t="n" s="0">
-        <v>12.033066056314185</v>
+        <v>34.49915925014152</v>
       </c>
       <c r="H43" t="n" s="0">
-        <v>12.23649930230616</v>
+        <v>22.83208575583484</v>
       </c>
       <c r="I43" t="n" s="0">
-        <v>40.87057054698889</v>
+        <v>40.95311630217947</v>
       </c>
       <c r="J43" t="n" s="0">
-        <v>22.698418967704818</v>
+        <v>11.958657200425993</v>
       </c>
       <c r="K43" t="n" s="0">
-        <v>8.098326002754987</v>
+        <v>16.352081997152972</v>
       </c>
       <c r="L43" t="n" s="0">
-        <v>61.72743496288193</v>
+        <v>13.807049135382709</v>
       </c>
       <c r="M43" t="n" s="0">
-        <v>27.906995381934856</v>
+        <v>35.85234373297179</v>
       </c>
       <c r="N43" t="n" s="0">
-        <v>40.62945692132716</v>
+        <v>42.78346897933184</v>
       </c>
       <c r="O43" t="n" s="0">
-        <v>41.92772635085915</v>
+        <v>34.07902691690832</v>
       </c>
       <c r="P43" t="n" s="0">
-        <v>33.71744649632683</v>
+        <v>33.61017856274533</v>
       </c>
       <c r="Q43" t="n" s="0">
-        <v>66.34125021414864</v>
+        <v>29.848758077847414</v>
       </c>
       <c r="R43" t="n" s="0">
-        <v>29.84911263125025</v>
+        <v>46.763241050883295</v>
       </c>
       <c r="S43" t="n" s="0">
-        <v>35.84837489633697</v>
+        <v>27.867810116843437</v>
       </c>
       <c r="T43" t="n" s="0">
-        <v>24.326862416163152</v>
+        <v>22.494758046020905</v>
       </c>
       <c r="U43" t="n" s="0">
-        <v>47.31422939843995</v>
+        <v>8.50473583045927</v>
       </c>
       <c r="V43" t="n" s="0">
-        <v>30.172701969383958</v>
+        <v>22.902477761179036</v>
       </c>
       <c r="W43" t="n" s="0">
-        <v>41.97090860986784</v>
+        <v>31.0862736577823</v>
       </c>
       <c r="X43" t="n" s="0">
-        <v>19.078331103137277</v>
+        <v>16.08430714718896</v>
       </c>
       <c r="Y43" t="n" s="0">
-        <v>26.53688614896366</v>
+        <v>36.44672089773354</v>
       </c>
       <c r="Z43" t="n" s="0">
-        <v>11.115124043957929</v>
+        <v>24.9016119437648</v>
       </c>
       <c r="AA43" t="n" s="0">
-        <v>41.97326944677569</v>
+        <v>6.898297724218139</v>
       </c>
       <c r="AB43" t="n" s="0">
-        <v>30.8911917694427</v>
+        <v>52.84974986266727</v>
       </c>
       <c r="AC43" t="n" s="0">
-        <v>34.826054447922374</v>
+        <v>10.68049643519734</v>
       </c>
       <c r="AD43" t="n" s="0">
-        <v>37.44863858672088</v>
+        <v>12.87422917507559</v>
       </c>
       <c r="AE43" t="n" s="0">
-        <v>6.895407914457698</v>
+        <v>17.958966524568694</v>
       </c>
       <c r="AF43" t="n" s="0">
-        <v>32.96821496274761</v>
+        <v>37.89977527854439</v>
       </c>
     </row>
     <row r="44">
       <c r="C44" t="n" s="0">
-        <v>1.6470393649636645</v>
+        <v>9.023728233818922</v>
       </c>
       <c r="D44" t="n" s="0">
-        <v>2.317045654857314</v>
+        <v>2.3527356410854527</v>
       </c>
       <c r="E44" t="n" s="0">
-        <v>8.788716181028093</v>
+        <v>3.9960850736601903</v>
       </c>
       <c r="F44" t="n" s="0">
-        <v>1.3342910747095726</v>
+        <v>3.048011141367138</v>
       </c>
       <c r="G44" t="n" s="0">
-        <v>0.006141212494921167</v>
+        <v>2.0572684574132976</v>
       </c>
       <c r="H44" t="n" s="0">
-        <v>2.5993817756050572</v>
+        <v>1.6708069110622046</v>
       </c>
       <c r="I44" t="n" s="0">
-        <v>19.21274289485431</v>
+        <v>1.2294159193973084</v>
       </c>
       <c r="J44" t="n" s="0">
-        <v>4.651180341162956</v>
+        <v>6.889232773420309</v>
       </c>
       <c r="K44" t="n" s="0">
-        <v>3.026948643201312</v>
+        <v>8.908026388847265</v>
       </c>
       <c r="L44" t="n" s="0">
-        <v>3.7817046175693467</v>
+        <v>2.317038897321581</v>
       </c>
       <c r="M44" t="n" s="0">
-        <v>18.101143205494555</v>
+        <v>3.736114337110678</v>
       </c>
       <c r="N44" t="n" s="0">
-        <v>2.329314449037988</v>
+        <v>3.4961725091155356</v>
       </c>
       <c r="O44" t="n" s="0">
-        <v>3.1776932663428004</v>
+        <v>3.6125402581870536</v>
       </c>
       <c r="P44" t="n" s="0">
-        <v>2.815794849336261</v>
+        <v>1.6473382161974226</v>
       </c>
       <c r="Q44" t="n" s="0">
-        <v>1.7425057949275744</v>
+        <v>1.737361271162055</v>
       </c>
       <c r="R44" t="n" s="0">
-        <v>3.9968028886505635E-15</v>
+        <v>1.346846960122225</v>
       </c>
       <c r="S44" t="n" s="0">
-        <v>3.1855924438303522</v>
+        <v>1.7076857739691715</v>
       </c>
       <c r="T44" t="n" s="0">
-        <v>4.192039103278034</v>
+        <v>2.3187761144026493</v>
       </c>
       <c r="U44" t="n" s="0">
-        <v>3.246805878398036</v>
+        <v>1.1633614361660283</v>
       </c>
       <c r="V44" t="n" s="0">
-        <v>2.920505959055188</v>
+        <v>2.655048036993574</v>
       </c>
       <c r="W44" t="n" s="0">
-        <v>2.407759973776852</v>
+        <v>1.3692729795530885</v>
       </c>
       <c r="X44" t="n" s="0">
-        <v>2.923501628725156</v>
+        <v>2.3168693485541856</v>
       </c>
       <c r="Y44" t="n" s="0">
-        <v>2.5800294866239075</v>
+        <v>1.155691968323414</v>
       </c>
       <c r="Z44" t="n" s="0">
-        <v>4.575010559620992</v>
+        <v>3.6379052395191107</v>
       </c>
       <c r="AA44" t="n" s="0">
-        <v>2.6174218304029933</v>
+        <v>2.5812967159539153</v>
       </c>
       <c r="AB44" t="n" s="0">
-        <v>4.0536614596227025</v>
+        <v>1.7266971825714674</v>
       </c>
       <c r="AC44" t="n" s="0">
-        <v>2.361388501291661</v>
+        <v>0.0182078775404233</v>
       </c>
       <c r="AD44" t="n" s="0">
-        <v>4.080342925744905</v>
+        <v>2.823593185231584</v>
       </c>
       <c r="AE44" t="n" s="0">
-        <v>2.6434431873673465</v>
+        <v>4.557186375940695</v>
       </c>
       <c r="AF44" t="n" s="0">
-        <v>0.05993691580539151</v>
+        <v>10.238926880210292</v>
       </c>
     </row>
     <row r="45">
       <c r="C45" t="n" s="0">
-        <v>0.3595773686880295</v>
+        <v>0.2925089419475809</v>
       </c>
       <c r="D45" t="n" s="0">
-        <v>0.7094030790173335</v>
+        <v>0.4141374989229759</v>
       </c>
       <c r="E45" t="n" s="0">
-        <v>0.5334145399906959</v>
+        <v>0.406730676320484</v>
       </c>
       <c r="F45" t="n" s="0">
-        <v>0.2613097500831165</v>
+        <v>0.3486485692145842</v>
       </c>
       <c r="G45" t="n" s="0">
-        <v>0.22425960052369465</v>
+        <v>0.17448308824629655</v>
       </c>
       <c r="H45" t="n" s="0">
-        <v>0.36254268130001543</v>
+        <v>0.19265524554493474</v>
       </c>
       <c r="I45" t="n" s="0">
-        <v>0.3300149789493778</v>
+        <v>0.6567655388294871</v>
       </c>
       <c r="J45" t="n" s="0">
-        <v>0.5187671104053216</v>
+        <v>0.17661546132796457</v>
       </c>
       <c r="K45" t="n" s="0">
-        <v>0.44223617905341495</v>
+        <v>0.6837337737756088</v>
       </c>
       <c r="L45" t="n" s="0">
-        <v>0.36396115071241264</v>
+        <v>0.2529479238567378</v>
       </c>
       <c r="M45" t="n" s="0">
-        <v>0.6564221115415798</v>
+        <v>1.0450634482479162</v>
       </c>
       <c r="N45" t="n" s="0">
-        <v>0.563193387080481</v>
+        <v>0.6340303221781517</v>
       </c>
       <c r="O45" t="n" s="0">
-        <v>0.38446107292460696</v>
+        <v>0.5297366594567389</v>
       </c>
       <c r="P45" t="n" s="0">
-        <v>0.34150709057707385</v>
+        <v>0.2656939132259182</v>
       </c>
       <c r="Q45" t="n" s="0">
-        <v>0.26419783677440845</v>
+        <v>0.11811368611773254</v>
       </c>
       <c r="R45" t="n" s="0">
-        <v>0.4179288717786396</v>
+        <v>0.19206465918400295</v>
       </c>
       <c r="S45" t="n" s="0">
-        <v>0.9449499103210425</v>
+        <v>0.23561330760683052</v>
       </c>
       <c r="T45" t="n" s="0">
-        <v>0.6454131793717893</v>
+        <v>1.2372451059816516</v>
       </c>
       <c r="U45" t="n" s="0">
-        <v>2.050217326465447</v>
+        <v>0.7399361278961335</v>
       </c>
       <c r="V45" t="n" s="0">
-        <v>0.08071326183421212</v>
+        <v>0.2982395444767091</v>
       </c>
       <c r="W45" t="n" s="0">
-        <v>0.467609876373666</v>
+        <v>0.23727547971426632</v>
       </c>
       <c r="X45" t="n" s="0">
-        <v>0.40517949854512647</v>
+        <v>0.41754417301221836</v>
       </c>
       <c r="Y45" t="n" s="0">
-        <v>0.49421718153475414</v>
+        <v>1.0778436847686232</v>
       </c>
       <c r="Z45" t="n" s="0">
-        <v>0.6276658942662326</v>
+        <v>0.3862459565624943</v>
       </c>
       <c r="AA45" t="n" s="0">
-        <v>0.3597007587208465</v>
+        <v>0.3907228108505455</v>
       </c>
       <c r="AB45" t="n" s="0">
-        <v>0.39105909494687374</v>
+        <v>0.5253169928396422</v>
       </c>
       <c r="AC45" t="n" s="0">
-        <v>0.35531027686758265</v>
+        <v>1.0801666055816659</v>
       </c>
       <c r="AD45" t="n" s="0">
-        <v>0.3983981654163977</v>
+        <v>0.3026466744666695</v>
       </c>
       <c r="AE45" t="n" s="0">
-        <v>0.27785507655402897</v>
+        <v>0.3186481962614439</v>
       </c>
       <c r="AF45" t="n" s="0">
-        <v>0.6638296881127735</v>
+        <v>0.2958606496728938</v>
       </c>
     </row>
     <row r="46">
       <c r="C46" t="n" s="0">
-        <v>0.001041477484511747</v>
+        <v>5.836055122443988</v>
       </c>
       <c r="D46" t="n" s="0">
-        <v>0.8569523583102052</v>
+        <v>0.614863656021513</v>
       </c>
       <c r="E46" t="n" s="0">
-        <v>2.205877883377533</v>
+        <v>1.4962692846978802</v>
       </c>
       <c r="F46" t="n" s="0">
-        <v>1.9693031798319356</v>
+        <v>0.634891463422877</v>
       </c>
       <c r="G46" t="n" s="0">
-        <v>1.123888024641742</v>
+        <v>0.7573423306312483</v>
       </c>
       <c r="H46" t="n" s="0">
-        <v>1.0633352071584914</v>
+        <v>1.5231978621021849</v>
       </c>
       <c r="I46" t="n" s="0">
-        <v>1.739130151885821</v>
+        <v>1.3402230423011396</v>
       </c>
       <c r="J46" t="n" s="0">
-        <v>0.7512991711227345</v>
+        <v>0.7110841524483761</v>
       </c>
       <c r="K46" t="n" s="0">
-        <v>1.8123856141471189</v>
+        <v>6.490974571564942</v>
       </c>
       <c r="L46" t="n" s="0">
-        <v>1.062972878912544</v>
+        <v>0.30537161068248303</v>
       </c>
       <c r="M46" t="n" s="0">
-        <v>0.012206814599742839</v>
+        <v>1.7744868020145843</v>
       </c>
       <c r="N46" t="n" s="0">
-        <v>1.1131308810694582</v>
+        <v>2.396713443756705</v>
       </c>
       <c r="O46" t="n" s="0">
-        <v>1.3727137153879667</v>
+        <v>0.010954925084602522</v>
       </c>
       <c r="P46" t="n" s="0">
-        <v>1.0083136696695432</v>
+        <v>1.251940657119002</v>
       </c>
       <c r="Q46" t="n" s="0">
-        <v>0.57482589434681</v>
+        <v>0.0476435038935348</v>
       </c>
       <c r="R46" t="n" s="0">
-        <v>5.152747410342707</v>
+        <v>1.93093721253417</v>
       </c>
       <c r="S46" t="n" s="0">
-        <v>1.519529273158568</v>
+        <v>0.42897069144961053</v>
       </c>
       <c r="T46" t="n" s="0">
-        <v>2.541732918451719</v>
+        <v>1.0695537176881893</v>
       </c>
       <c r="U46" t="n" s="0">
-        <v>21.001061469285055</v>
+        <v>2.7589164185658883</v>
       </c>
       <c r="V46" t="n" s="0">
-        <v>1.6614275856739247</v>
+        <v>0.8093976493264152</v>
       </c>
       <c r="W46" t="n" s="0">
-        <v>0.004351012459193942</v>
+        <v>3.090976683025377</v>
       </c>
       <c r="X46" t="n" s="0">
-        <v>4.219518402877624</v>
+        <v>2.2213781731343714</v>
       </c>
       <c r="Y46" t="n" s="0">
-        <v>1.3236724785510905</v>
+        <v>3.1508310002690623</v>
       </c>
       <c r="Z46" t="n" s="0">
-        <v>1.543366971228465</v>
+        <v>1.9631092787728686</v>
       </c>
       <c r="AA46" t="n" s="0">
-        <v>1.7073480229280746</v>
+        <v>1.269096246210232</v>
       </c>
       <c r="AB46" t="n" s="0">
-        <v>1.9131695454967825</v>
+        <v>1.4328160310886822</v>
       </c>
       <c r="AC46" t="n" s="0">
-        <v>0.5892330635394297</v>
+        <v>5.319524080982067</v>
       </c>
       <c r="AD46" t="n" s="0">
-        <v>1.9070061904852795</v>
+        <v>0.40779863709038966</v>
       </c>
       <c r="AE46" t="n" s="0">
-        <v>0.18166563593473328</v>
+        <v>5.847515609218215</v>
       </c>
       <c r="AF46" t="n" s="0">
-        <v>2.285042859364684</v>
+        <v>1.2653609566527522</v>
       </c>
     </row>
     <row r="47">
       <c r="C47" t="n" s="0">
-        <v>0.4610599679286793</v>
+        <v>0.07739629202930588</v>
       </c>
       <c r="D47" t="n" s="0">
-        <v>0.27878924399501337</v>
+        <v>0.3424520748050811</v>
       </c>
       <c r="E47" t="n" s="0">
-        <v>0.06950705889138062</v>
+        <v>0.17828293603916726</v>
       </c>
       <c r="F47" t="n" s="0">
-        <v>0.4693522961212546</v>
+        <v>0.022939523282029074</v>
       </c>
       <c r="G47" t="n" s="0">
-        <v>0.5840781589480227</v>
+        <v>10.729055617045855</v>
       </c>
       <c r="H47" t="n" s="0">
-        <v>0.36031359890351755</v>
+        <v>2.629386418414438</v>
       </c>
       <c r="I47" t="n" s="0">
-        <v>0.22650670329369713</v>
+        <v>1.232905726261702</v>
       </c>
       <c r="J47" t="n" s="0">
-        <v>0.14805511722433848</v>
+        <v>0.41509136608903746</v>
       </c>
       <c r="K47" t="n" s="0">
-        <v>0.005738880721319307</v>
+        <v>0.8514432057223215</v>
       </c>
       <c r="L47" t="n" s="0">
-        <v>0.10128426476859227</v>
+        <v>3.0285805049172465</v>
       </c>
       <c r="M47" t="n" s="0">
-        <v>0.1421877460101488</v>
+        <v>0.1864344692854678</v>
       </c>
       <c r="N47" t="n" s="0">
-        <v>0.6776086663705474</v>
+        <v>0.17909874970720263</v>
       </c>
       <c r="O47" t="n" s="0">
-        <v>10.666983196137238</v>
+        <v>0.26790247539875583</v>
       </c>
       <c r="P47" t="n" s="0">
-        <v>2.670874941585639</v>
+        <v>0.5641947554363578</v>
       </c>
       <c r="Q47" t="n" s="0">
-        <v>1.5291953072649855</v>
+        <v>0.2273248221305237</v>
       </c>
       <c r="R47" t="n" s="0">
-        <v>1.127194981472643</v>
+        <v>0.11926905355128753</v>
       </c>
       <c r="S47" t="n" s="0">
-        <v>1.3093684167842685</v>
+        <v>17.278281934449243</v>
       </c>
       <c r="T47" t="n" s="0">
-        <v>0.7533727284052238</v>
+        <v>0.050712926450155564</v>
       </c>
       <c r="U47" t="n" s="0">
-        <v>0.07328040417741635</v>
+        <v>0.3425625557994661</v>
       </c>
       <c r="V47" t="n" s="0">
-        <v>0.20358947179144737</v>
+        <v>0.12022119114682364</v>
       </c>
       <c r="W47" t="n" s="0">
-        <v>2.026529478224478</v>
+        <v>0.6533763236746334</v>
       </c>
       <c r="X47" t="n" s="0">
-        <v>1.5891907092500914</v>
+        <v>10.04361694885449</v>
       </c>
       <c r="Y47" t="n" s="0">
-        <v>0.31614777268982563</v>
+        <v>1.5156895814500893</v>
       </c>
       <c r="Z47" t="n" s="0">
-        <v>0.8879490208449039</v>
+        <v>0.14483212692959743</v>
       </c>
       <c r="AA47" t="n" s="0">
-        <v>0.16586161206304084</v>
+        <v>0.23637538746049352</v>
       </c>
       <c r="AB47" t="n" s="0">
-        <v>0.1644539095702059</v>
+        <v>0.18017687354846892</v>
       </c>
       <c r="AC47" t="n" s="0">
-        <v>0.10775262111788769</v>
+        <v>0.04504735942664176</v>
       </c>
       <c r="AD47" t="n" s="0">
-        <v>1.2523076843809866</v>
+        <v>0.13902770577328954</v>
       </c>
       <c r="AE47" t="n" s="0">
-        <v>0.11918892377947743</v>
+        <v>0.3694228394034191</v>
       </c>
       <c r="AF47" t="n" s="0">
-        <v>0.16019647635759088</v>
+        <v>0.6321134621398654</v>
       </c>
     </row>
     <row r="48">
       <c r="C48" t="n" s="0">
-        <v>1.9920308918556293</v>
+        <v>0.0</v>
       </c>
       <c r="D48" t="n" s="0">
+        <v>0.998003748179203</v>
+      </c>
+      <c r="E48" t="n" s="0">
+        <v>0.9980037481792028</v>
+      </c>
+      <c r="F48" t="n" s="0">
+        <v>3.4649682406289974E-55</v>
+      </c>
+      <c r="G48" t="n" s="0">
+        <v>1.2868893973670072E-85</v>
+      </c>
+      <c r="H48" t="n" s="0">
         <v>1.9920308918556306</v>
       </c>
-      <c r="E48" t="n" s="0">
-        <v>2.9821051755564376</v>
-      </c>
-      <c r="F48" t="n" s="0">
-        <v>0.0</v>
-      </c>
-      <c r="G48" t="n" s="0">
-        <v>0.0</v>
-      </c>
-      <c r="H48" t="n" s="0">
-        <v>0.0</v>
-      </c>
       <c r="I48" t="n" s="0">
+        <v>0.9980037481792026</v>
+      </c>
+      <c r="J48" t="n" s="0">
+        <v>8.211056237818357E-67</v>
+      </c>
+      <c r="K48" t="n" s="0">
+        <v>0.0</v>
+      </c>
+      <c r="L48" t="n" s="0">
+        <v>0.0</v>
+      </c>
+      <c r="M48" t="n" s="0">
+        <v>0.0</v>
+      </c>
+      <c r="N48" t="n" s="0">
+        <v>1.28471022234132E-53</v>
+      </c>
+      <c r="O48" t="n" s="0">
+        <v>0.0</v>
+      </c>
+      <c r="P48" t="n" s="0">
+        <v>3.968251535733217</v>
+      </c>
+      <c r="Q48" t="n" s="0">
         <v>0.998003748179203</v>
       </c>
-      <c r="J48" t="n" s="0">
-        <v>0.998003748179203</v>
-      </c>
-      <c r="K48" t="n" s="0">
-        <v>1.9920308918556306</v>
-      </c>
-      <c r="L48" t="n" s="0">
-        <v>0.0</v>
-      </c>
-      <c r="M48" t="n" s="0">
-        <v>0.0</v>
-      </c>
-      <c r="N48" t="n" s="0">
-        <v>0.0</v>
-      </c>
-      <c r="O48" t="n" s="0">
-        <v>3.968251517879963</v>
-      </c>
-      <c r="P48" t="n" s="0">
-        <v>1.3069970442008667E-85</v>
-      </c>
-      <c r="Q48" t="n" s="0">
-        <v>3.968251517880211</v>
-      </c>
       <c r="R48" t="n" s="0">
-        <v>9.381423706805483E-83</v>
+        <v>2.9821051755564363</v>
       </c>
       <c r="S48" t="n" s="0">
-        <v>4.950489035327462</v>
+        <v>0.0</v>
       </c>
       <c r="T48" t="n" s="0">
-        <v>7.636743513971997E-76</v>
+        <v>0.0</v>
       </c>
       <c r="U48" t="n" s="0">
-        <v>1.9920308918556615</v>
+        <v>0.0</v>
       </c>
       <c r="V48" t="n" s="0">
-        <v>0.0</v>
+        <v>2.510486614325891E-77</v>
       </c>
       <c r="W48" t="n" s="0">
         <v>0.0</v>
@@ -4193,19 +4193,19 @@
         <v>0.0</v>
       </c>
       <c r="AA48" t="n" s="0">
-        <v>1.4658474541883567E-84</v>
+        <v>2.0107646833859488E-87</v>
       </c>
       <c r="AB48" t="n" s="0">
-        <v>3.1082489271148415E-78</v>
+        <v>2.982105175556438</v>
       </c>
       <c r="AC48" t="n" s="0">
-        <v>3.968251517879963</v>
+        <v>0.0</v>
       </c>
       <c r="AD48" t="n" s="0">
         <v>0.0</v>
       </c>
       <c r="AE48" t="n" s="0">
-        <v>0.0</v>
+        <v>1.9920308918556746</v>
       </c>
       <c r="AF48" t="n" s="0">
         <v>0.0</v>
@@ -4213,108 +4213,108 @@
     </row>
     <row r="49">
       <c r="C49" t="n" s="0">
-        <v>0.0014939647641664404</v>
+        <v>0.0023264483551068667</v>
       </c>
       <c r="D49" t="n" s="0">
-        <v>8.260403479432983E-4</v>
+        <v>0.0015143076432277342</v>
       </c>
       <c r="E49" t="n" s="0">
-        <v>7.832968608021464E-4</v>
+        <v>0.0016556336799688153</v>
       </c>
       <c r="F49" t="n" s="0">
-        <v>0.02036333934816068</v>
+        <v>0.02036358706686035</v>
       </c>
       <c r="G49" t="n" s="0">
+        <v>0.001655371334718708</v>
+      </c>
+      <c r="H49" t="n" s="0">
+        <v>0.00606921456989451</v>
+      </c>
+      <c r="I49" t="n" s="0">
         <v>0.020363339348068495</v>
       </c>
-      <c r="H49" t="n" s="0">
-        <v>9.13333045654494E-4</v>
-      </c>
-      <c r="I49" t="n" s="0">
-        <v>0.0018878181559469393</v>
-      </c>
       <c r="J49" t="n" s="0">
-        <v>0.0016553715148082515</v>
+        <v>9.158012202565507E-4</v>
       </c>
       <c r="K49" t="n" s="0">
-        <v>0.0012425622639537295</v>
+        <v>0.00148865923536384</v>
       </c>
       <c r="L49" t="n" s="0">
-        <v>0.020363339348119135</v>
+        <v>0.0016553752096103058</v>
       </c>
       <c r="M49" t="n" s="0">
-        <v>0.0014791897390482463</v>
+        <v>0.020363339498435808</v>
       </c>
       <c r="N49" t="n" s="0">
-        <v>8.149138054327766E-4</v>
+        <v>7.897922706148673E-4</v>
       </c>
       <c r="O49" t="n" s="0">
-        <v>0.002251949318339088</v>
+        <v>0.0014886592353638393</v>
       </c>
       <c r="P49" t="n" s="0">
-        <v>0.020363340148017894</v>
+        <v>0.020363339348068495</v>
       </c>
       <c r="Q49" t="n" s="0">
-        <v>8.022327526269968E-4</v>
+        <v>0.00165542987494791</v>
       </c>
       <c r="R49" t="n" s="0">
-        <v>0.0013751222012800316</v>
+        <v>0.019516530567148818</v>
       </c>
       <c r="S49" t="n" s="0">
-        <v>0.0014887148976191493</v>
+        <v>0.02036338648689962</v>
       </c>
       <c r="T49" t="n" s="0">
-        <v>9.439393546162079E-4</v>
+        <v>7.846800988823895E-4</v>
       </c>
       <c r="U49" t="n" s="0">
-        <v>0.0016553713347187107</v>
+        <v>0.0022519493183390878</v>
       </c>
       <c r="V49" t="n" s="0">
-        <v>0.001488659235363839</v>
+        <v>7.83001020923254E-4</v>
       </c>
       <c r="W49" t="n" s="0">
-        <v>5.611232109582008E-4</v>
+        <v>8.318411134808196E-4</v>
       </c>
       <c r="X49" t="n" s="0">
-        <v>0.0016553723170428052</v>
+        <v>0.001655754332286074</v>
       </c>
       <c r="Y49" t="n" s="0">
-        <v>0.007389886878663718</v>
+        <v>0.020363341306371747</v>
       </c>
       <c r="Z49" t="n" s="0">
-        <v>0.0016553790596360158</v>
+        <v>0.001758902818078667</v>
       </c>
       <c r="AA49" t="n" s="0">
-        <v>0.02036669552096372</v>
+        <v>7.864156670159089E-4</v>
       </c>
       <c r="AB49" t="n" s="0">
-        <v>0.02036337359002775</v>
+        <v>0.0022519493183390886</v>
       </c>
       <c r="AC49" t="n" s="0">
-        <v>0.0016559766084041645</v>
+        <v>0.0016553713347187118</v>
       </c>
       <c r="AD49" t="n" s="0">
-        <v>0.008333703114662368</v>
+        <v>0.0011295759081899927</v>
       </c>
       <c r="AE49" t="n" s="0">
-        <v>0.020363376014597645</v>
+        <v>0.002236858622181302</v>
       </c>
       <c r="AF49" t="n" s="0">
-        <v>0.0012407175616581613</v>
+        <v>0.020363339348100196</v>
       </c>
     </row>
     <row r="50">
       <c r="C50" t="n" s="0">
+        <v>-1.0316284534898779</v>
+      </c>
+      <c r="D50" t="n" s="0">
         <v>-1.0316284534898776</v>
       </c>
-      <c r="D50" t="n" s="0">
+      <c r="E50" t="n" s="0">
+        <v>-1.0316284534898776</v>
+      </c>
+      <c r="F50" t="n" s="0">
         <v>-1.0316284534898779</v>
-      </c>
-      <c r="E50" t="n" s="0">
-        <v>-1.0316284534898779</v>
-      </c>
-      <c r="F50" t="n" s="0">
-        <v>-1.0316284534898776</v>
       </c>
       <c r="G50" t="n" s="0">
         <v>-1.0316284534898776</v>
@@ -4323,22 +4323,22 @@
         <v>-1.0316284534898776</v>
       </c>
       <c r="I50" t="n" s="0">
-        <v>-1.0316284534898779</v>
+        <v>-1.0316284534898776</v>
       </c>
       <c r="J50" t="n" s="0">
         <v>-1.0316284534898776</v>
       </c>
       <c r="K50" t="n" s="0">
+        <v>-1.0316284534898779</v>
+      </c>
+      <c r="L50" t="n" s="0">
         <v>-1.0316284534898776</v>
-      </c>
-      <c r="L50" t="n" s="0">
-        <v>-1.0316284534898779</v>
       </c>
       <c r="M50" t="n" s="0">
         <v>-1.0316284534898776</v>
       </c>
       <c r="N50" t="n" s="0">
-        <v>-1.0316284534898776</v>
+        <v>-1.031628453489764</v>
       </c>
       <c r="O50" t="n" s="0">
         <v>-1.0316284534898776</v>
@@ -4347,28 +4347,28 @@
         <v>-1.0316284534898776</v>
       </c>
       <c r="Q50" t="n" s="0">
-        <v>-1.031628453489835</v>
+        <v>-1.0316284534898776</v>
       </c>
       <c r="R50" t="n" s="0">
         <v>-1.0316284534898776</v>
       </c>
       <c r="S50" t="n" s="0">
-        <v>-1.0316284534898768</v>
+        <v>-1.0316284534898776</v>
       </c>
       <c r="T50" t="n" s="0">
-        <v>-1.0316284534890032</v>
+        <v>-1.0316284534898779</v>
       </c>
       <c r="U50" t="n" s="0">
         <v>-1.0316284534898779</v>
       </c>
       <c r="V50" t="n" s="0">
+        <v>-1.0316284534898776</v>
+      </c>
+      <c r="W50" t="n" s="0">
+        <v>-1.0316284534898776</v>
+      </c>
+      <c r="X50" t="n" s="0">
         <v>-1.0316284534898779</v>
-      </c>
-      <c r="W50" t="n" s="0">
-        <v>-1.0316284534898779</v>
-      </c>
-      <c r="X50" t="n" s="0">
-        <v>-1.0316284534898743</v>
       </c>
       <c r="Y50" t="n" s="0">
         <v>-1.0316284534898779</v>
@@ -4377,22 +4377,22 @@
         <v>-1.0316284534898776</v>
       </c>
       <c r="AA50" t="n" s="0">
+        <v>-1.0316284534898776</v>
+      </c>
+      <c r="AB50" t="n" s="0">
         <v>-1.0316284534898779</v>
       </c>
-      <c r="AB50" t="n" s="0">
-        <v>-1.0316284534898776</v>
-      </c>
       <c r="AC50" t="n" s="0">
-        <v>-1.0316284534898776</v>
+        <v>-1.0316284527840325</v>
       </c>
       <c r="AD50" t="n" s="0">
         <v>-1.0316284534898776</v>
       </c>
       <c r="AE50" t="n" s="0">
+        <v>-1.0316284534898776</v>
+      </c>
+      <c r="AF50" t="n" s="0">
         <v>-1.0316284534898779</v>
-      </c>
-      <c r="AF50" t="n" s="0">
-        <v>-1.0316284534898776</v>
       </c>
     </row>
     <row r="51">
@@ -4406,7 +4406,7 @@
         <v>0.39788735772973816</v>
       </c>
       <c r="F51" t="n" s="0">
-        <v>0.39788735772973816</v>
+        <v>0.39788735772975414</v>
       </c>
       <c r="G51" t="n" s="0">
         <v>0.39788735772973816</v>
@@ -4475,10 +4475,10 @@
         <v>0.39788735772973816</v>
       </c>
       <c r="AC51" t="n" s="0">
-        <v>0.3978873577298234</v>
+        <v>0.39788735772973816</v>
       </c>
       <c r="AD51" t="n" s="0">
-        <v>0.39788735772973816</v>
+        <v>0.39788735772973993</v>
       </c>
       <c r="AE51" t="n" s="0">
         <v>0.39788735772973816</v>
@@ -4492,1287 +4492,1287 @@
         <v>2.999999999999904</v>
       </c>
       <c r="D52" t="n" s="0">
-        <v>2.999999999999911</v>
+        <v>2.9999999999999045</v>
       </c>
       <c r="E52" t="n" s="0">
-        <v>2.999999999999912</v>
+        <v>2.9999999999999116</v>
       </c>
       <c r="F52" t="n" s="0">
+        <v>2.999999999999924</v>
+      </c>
+      <c r="G52" t="n" s="0">
+        <v>2.9999999999999116</v>
+      </c>
+      <c r="H52" t="n" s="0">
+        <v>2.999999999999908</v>
+      </c>
+      <c r="I52" t="n" s="0">
+        <v>2.999999999999916</v>
+      </c>
+      <c r="J52" t="n" s="0">
+        <v>2.9999999999999054</v>
+      </c>
+      <c r="K52" t="n" s="0">
+        <v>2.999999999999904</v>
+      </c>
+      <c r="L52" t="n" s="0">
+        <v>2.999999999999904</v>
+      </c>
+      <c r="M52" t="n" s="0">
+        <v>2.9999999999999303</v>
+      </c>
+      <c r="N52" t="n" s="0">
+        <v>2.9999999999999067</v>
+      </c>
+      <c r="O52" t="n" s="0">
+        <v>2.9999999999999196</v>
+      </c>
+      <c r="P52" t="n" s="0">
         <v>2.999999999999906</v>
       </c>
-      <c r="G52" t="n" s="0">
-        <v>2.999999999999912</v>
-      </c>
-      <c r="H52" t="n" s="0">
-        <v>2.9999999999999045</v>
-      </c>
-      <c r="I52" t="n" s="0">
-        <v>2.9999999999999116</v>
-      </c>
-      <c r="J52" t="n" s="0">
-        <v>2.999999999999904</v>
-      </c>
-      <c r="K52" t="n" s="0">
-        <v>2.999999999999907</v>
-      </c>
-      <c r="L52" t="n" s="0">
-        <v>2.9999999999999205</v>
-      </c>
-      <c r="M52" t="n" s="0">
-        <v>3.0000000000000355</v>
-      </c>
-      <c r="N52" t="n" s="0">
-        <v>2.999999999999911</v>
-      </c>
-      <c r="O52" t="n" s="0">
-        <v>2.999999999999906</v>
-      </c>
-      <c r="P52" t="n" s="0">
-        <v>2.9999999999999205</v>
-      </c>
       <c r="Q52" t="n" s="0">
-        <v>2.9999999999999107</v>
+        <v>2.9999999999999156</v>
       </c>
       <c r="R52" t="n" s="0">
-        <v>2.999999999999935</v>
+        <v>2.99999999999993</v>
       </c>
       <c r="S52" t="n" s="0">
         <v>2.999999999999911</v>
       </c>
       <c r="T52" t="n" s="0">
+        <v>2.9999999999999045</v>
+      </c>
+      <c r="U52" t="n" s="0">
+        <v>2.999999999999912</v>
+      </c>
+      <c r="V52" t="n" s="0">
+        <v>2.9999999999999245</v>
+      </c>
+      <c r="W52" t="n" s="0">
+        <v>2.9999999999999054</v>
+      </c>
+      <c r="X52" t="n" s="0">
+        <v>2.9999999999999085</v>
+      </c>
+      <c r="Y52" t="n" s="0">
         <v>2.999999999999911</v>
       </c>
-      <c r="U52" t="n" s="0">
-        <v>3.0000002322562107</v>
-      </c>
-      <c r="V52" t="n" s="0">
+      <c r="Z52" t="n" s="0">
+        <v>2.9999999999999116</v>
+      </c>
+      <c r="AA52" t="n" s="0">
+        <v>2.999999999999913</v>
+      </c>
+      <c r="AB52" t="n" s="0">
+        <v>2.999999999999913</v>
+      </c>
+      <c r="AC52" t="n" s="0">
         <v>2.999999999999904</v>
       </c>
-      <c r="W52" t="n" s="0">
-        <v>2.999999999999925</v>
-      </c>
-      <c r="X52" t="n" s="0">
-        <v>2.9999999999999045</v>
-      </c>
-      <c r="Y52" t="n" s="0">
-        <v>2.9999999999999303</v>
-      </c>
-      <c r="Z52" t="n" s="0">
-        <v>2.9999999999999147</v>
-      </c>
-      <c r="AA52" t="n" s="0">
-        <v>2.9999999999999045</v>
-      </c>
-      <c r="AB52" t="n" s="0">
-        <v>2.999999999999907</v>
-      </c>
-      <c r="AC52" t="n" s="0">
-        <v>2.999999999999906</v>
-      </c>
       <c r="AD52" t="n" s="0">
-        <v>2.9999999999999547</v>
+        <v>2.999999999999913</v>
       </c>
       <c r="AE52" t="n" s="0">
         <v>2.9999999999999116</v>
       </c>
       <c r="AF52" t="n" s="0">
-        <v>2.9999999999999143</v>
+        <v>2.9999999999999116</v>
       </c>
     </row>
     <row r="53">
       <c r="C53" t="n" s="0">
-        <v>-3.8627670637238163</v>
+        <v>-3.8627821477948068</v>
       </c>
       <c r="D53" t="n" s="0">
-        <v>-3.862561576149235</v>
+        <v>-3.8627385662637157</v>
       </c>
       <c r="E53" t="n" s="0">
-        <v>-3.862747837965121</v>
+        <v>-3.862691569231342</v>
       </c>
       <c r="F53" t="n" s="0">
-        <v>-3.8619958434843187</v>
+        <v>-3.8627588408953786</v>
       </c>
       <c r="G53" t="n" s="0">
-        <v>-3.862782147820756</v>
+        <v>-3.86278214696114</v>
       </c>
       <c r="H53" t="n" s="0">
-        <v>-3.8627820919419684</v>
+        <v>-3.8627821477804223</v>
       </c>
       <c r="I53" t="n" s="0">
-        <v>-3.8627819007806545</v>
+        <v>-3.8627714445264854</v>
       </c>
       <c r="J53" t="n" s="0">
-        <v>-3.8627785252606173</v>
+        <v>-3.862782098334168</v>
       </c>
       <c r="K53" t="n" s="0">
-        <v>-3.8627485560405406</v>
+        <v>-3.8627819700933426</v>
       </c>
       <c r="L53" t="n" s="0">
-        <v>-3.862339600132734</v>
+        <v>-3.8626632095092717</v>
       </c>
       <c r="M53" t="n" s="0">
-        <v>-3.862782147820754</v>
+        <v>-3.862782147816266</v>
       </c>
       <c r="N53" t="n" s="0">
-        <v>-3.862706789210379</v>
+        <v>-3.862782147820733</v>
       </c>
       <c r="O53" t="n" s="0">
-        <v>-3.8627821475369233</v>
+        <v>-3.8627821440069363</v>
       </c>
       <c r="P53" t="n" s="0">
-        <v>-3.8627821413815795</v>
+        <v>-3.862782147634218</v>
       </c>
       <c r="Q53" t="n" s="0">
-        <v>-3.8627821478207545</v>
+        <v>-3.861392165351954</v>
       </c>
       <c r="R53" t="n" s="0">
-        <v>-3.862780477753253</v>
+        <v>-3.86155502401643</v>
       </c>
       <c r="S53" t="n" s="0">
-        <v>-3.8627810711911224</v>
+        <v>-3.8083862455324575</v>
       </c>
       <c r="T53" t="n" s="0">
-        <v>-3.8627783258189385</v>
+        <v>-3.862782147820752</v>
       </c>
       <c r="U53" t="n" s="0">
-        <v>-3.8627083970510316</v>
+        <v>-3.8627802718156437</v>
       </c>
       <c r="V53" t="n" s="0">
-        <v>-3.862782137875915</v>
+        <v>-3.8626274580602087</v>
       </c>
       <c r="W53" t="n" s="0">
-        <v>-3.862782147820506</v>
+        <v>-3.8627227896208756</v>
       </c>
       <c r="X53" t="n" s="0">
-        <v>-3.862782147820756</v>
+        <v>-3.862762468405114</v>
       </c>
       <c r="Y53" t="n" s="0">
-        <v>-3.8627821426208717</v>
+        <v>-3.862773300350014</v>
       </c>
       <c r="Z53" t="n" s="0">
-        <v>-3.862035139742507</v>
+        <v>-3.8627821478207554</v>
       </c>
       <c r="AA53" t="n" s="0">
-        <v>-3.8625342121047312</v>
+        <v>-3.8627797022116903</v>
       </c>
       <c r="AB53" t="n" s="0">
-        <v>-3.8627821465802143</v>
+        <v>-3.8627821478202717</v>
       </c>
       <c r="AC53" t="n" s="0">
-        <v>-3.862782147820547</v>
+        <v>-3.8627821478207554</v>
       </c>
       <c r="AD53" t="n" s="0">
-        <v>-3.8627671732637587</v>
+        <v>-3.86278214780729</v>
       </c>
       <c r="AE53" t="n" s="0">
-        <v>-3.862778948784634</v>
+        <v>-3.8627821478200284</v>
       </c>
       <c r="AF53" t="n" s="0">
-        <v>-3.862782033327571</v>
+        <v>-3.8607781599404065</v>
       </c>
     </row>
     <row r="54">
       <c r="C54" t="n" s="0">
-        <v>-3.321994491533448</v>
+        <v>-3.1797885992271495</v>
       </c>
       <c r="D54" t="n" s="0">
-        <v>-3.1917863210592206</v>
+        <v>-3.3219943434001995</v>
       </c>
       <c r="E54" t="n" s="0">
-        <v>-3.165316005208565</v>
+        <v>-3.099196274023126</v>
       </c>
       <c r="F54" t="n" s="0">
-        <v>-3.2011470831699964</v>
+        <v>-3.3192981599341964</v>
       </c>
       <c r="G54" t="n" s="0">
-        <v>-2.867248866995874</v>
+        <v>-3.321995171584125</v>
       </c>
       <c r="H54" t="n" s="0">
-        <v>-3.3219951032310178</v>
+        <v>-3.3219951705318054</v>
       </c>
       <c r="I54" t="n" s="0">
-        <v>-3.3219950203301454</v>
+        <v>-3.1884002735641634</v>
       </c>
       <c r="J54" t="n" s="0">
-        <v>-3.101090910983492</v>
+        <v>-3.3218521982369453</v>
       </c>
       <c r="K54" t="n" s="0">
-        <v>-3.321983374072152</v>
+        <v>-3.321995049305353</v>
       </c>
       <c r="L54" t="n" s="0">
-        <v>-3.32199202715313</v>
+        <v>-3.196905606443115</v>
       </c>
       <c r="M54" t="n" s="0">
-        <v>-2.3978807046674113</v>
+        <v>-3.3219950125284465</v>
       </c>
       <c r="N54" t="n" s="0">
-        <v>-3.1737454931387425</v>
+        <v>-3.3219891112471753</v>
       </c>
       <c r="O54" t="n" s="0">
-        <v>-3.315361454815753</v>
+        <v>-2.9519900529634833</v>
       </c>
       <c r="P54" t="n" s="0">
-        <v>-3.3219311617049607</v>
+        <v>-3.1652894409572743</v>
       </c>
       <c r="Q54" t="n" s="0">
-        <v>-3.1723891879009325</v>
+        <v>-3.199277690829759</v>
       </c>
       <c r="R54" t="n" s="0">
-        <v>-3.320244064635806</v>
+        <v>-3.32102790990015</v>
       </c>
       <c r="S54" t="n" s="0">
-        <v>-3.2023309473281127</v>
+        <v>-3.3219515052887947</v>
       </c>
       <c r="T54" t="n" s="0">
-        <v>-3.1739542736366713</v>
+        <v>-3.321994819632543</v>
       </c>
       <c r="U54" t="n" s="0">
-        <v>-3.3216629596890774</v>
+        <v>-3.318788457890237</v>
       </c>
       <c r="V54" t="n" s="0">
-        <v>-3.1943137121881504</v>
+        <v>-3.1921828376035988</v>
       </c>
       <c r="W54" t="n" s="0">
-        <v>-3.3219937217881106</v>
+        <v>-3.1901835659529043</v>
       </c>
       <c r="X54" t="n" s="0">
-        <v>-3.1996954058949973</v>
+        <v>-3.3219943765464572</v>
       </c>
       <c r="Y54" t="n" s="0">
-        <v>-3.193634616274213</v>
+        <v>-3.1676240119089503</v>
       </c>
       <c r="Z54" t="n" s="0">
-        <v>-3.1695065775785825</v>
+        <v>-3.1468862546054863</v>
       </c>
       <c r="AA54" t="n" s="0">
-        <v>-3.3183213495518644</v>
+        <v>-3.201524270371916</v>
       </c>
       <c r="AB54" t="n" s="0">
-        <v>-3.3219460303650523</v>
+        <v>-3.3218993110122517</v>
       </c>
       <c r="AC54" t="n" s="0">
-        <v>-3.3219951715639593</v>
+        <v>-3.321979700415459</v>
       </c>
       <c r="AD54" t="n" s="0">
-        <v>-3.32156542946268</v>
+        <v>-3.321755896209236</v>
       </c>
       <c r="AE54" t="n" s="0">
-        <v>-3.189682026108412</v>
+        <v>-3.321995171569946</v>
       </c>
       <c r="AF54" t="n" s="0">
-        <v>-3.1985106451188945</v>
+        <v>-3.2201362435550296</v>
       </c>
     </row>
     <row r="55">
       <c r="C55" t="n" s="0">
+        <v>-5.10077214028838</v>
+      </c>
+      <c r="D55" t="n" s="0">
+        <v>-5.100772140331986</v>
+      </c>
+      <c r="E55" t="n" s="0">
+        <v>-10.153055686708933</v>
+      </c>
+      <c r="F55" t="n" s="0">
+        <v>-10.153199679058229</v>
+      </c>
+      <c r="G55" t="n" s="0">
+        <v>-10.153199678897414</v>
+      </c>
+      <c r="H55" t="n" s="0">
+        <v>-5.100772140331986</v>
+      </c>
+      <c r="I55" t="n" s="0">
+        <v>-5.100772140328711</v>
+      </c>
+      <c r="J55" t="n" s="0">
+        <v>-10.153199672158268</v>
+      </c>
+      <c r="K55" t="n" s="0">
+        <v>-5.100772140331988</v>
+      </c>
+      <c r="L55" t="n" s="0">
+        <v>-10.153199679048083</v>
+      </c>
+      <c r="M55" t="n" s="0">
+        <v>-5.10077201546755</v>
+      </c>
+      <c r="N55" t="n" s="0">
+        <v>-5.100772136266641</v>
+      </c>
+      <c r="O55" t="n" s="0">
+        <v>-10.153199631566398</v>
+      </c>
+      <c r="P55" t="n" s="0">
+        <v>-5.100772140331987</v>
+      </c>
+      <c r="Q55" t="n" s="0">
+        <v>-5.10077206636211</v>
+      </c>
+      <c r="R55" t="n" s="0">
+        <v>-10.153199679058217</v>
+      </c>
+      <c r="S55" t="n" s="0">
+        <v>-10.153199679058229</v>
+      </c>
+      <c r="T55" t="n" s="0">
+        <v>-2.6304716684108937</v>
+      </c>
+      <c r="U55" t="n" s="0">
+        <v>-5.100772133605136</v>
+      </c>
+      <c r="V55" t="n" s="0">
+        <v>-5.100772140331988</v>
+      </c>
+      <c r="W55" t="n" s="0">
+        <v>-10.153199679058226</v>
+      </c>
+      <c r="X55" t="n" s="0">
+        <v>-10.153199678586075</v>
+      </c>
+      <c r="Y55" t="n" s="0">
         <v>-10.153199679058227</v>
       </c>
-      <c r="D55" t="n" s="0">
-        <v>-5.100770168193738</v>
-      </c>
-      <c r="E55" t="n" s="0">
+      <c r="Z55" t="n" s="0">
+        <v>-5.100772140331587</v>
+      </c>
+      <c r="AA55" t="n" s="0">
+        <v>-2.6304716683151286</v>
+      </c>
+      <c r="AB55" t="n" s="0">
+        <v>-5.100772140291469</v>
+      </c>
+      <c r="AC55" t="n" s="0">
+        <v>-10.153199679058227</v>
+      </c>
+      <c r="AD55" t="n" s="0">
+        <v>-5.100772140331473</v>
+      </c>
+      <c r="AE55" t="n" s="0">
         <v>-10.153199679058229</v>
       </c>
-      <c r="F55" t="n" s="0">
-        <v>-10.153199679058227</v>
-      </c>
-      <c r="G55" t="n" s="0">
-        <v>-10.153017883236569</v>
-      </c>
-      <c r="H55" t="n" s="0">
-        <v>-10.153199508009594</v>
-      </c>
-      <c r="I55" t="n" s="0">
-        <v>-5.1007721400594335</v>
-      </c>
-      <c r="J55" t="n" s="0">
-        <v>-10.14307315026306</v>
-      </c>
-      <c r="K55" t="n" s="0">
-        <v>-10.153199679058227</v>
-      </c>
-      <c r="L55" t="n" s="0">
-        <v>-2.630470255425536</v>
-      </c>
-      <c r="M55" t="n" s="0">
-        <v>-10.153199679058215</v>
-      </c>
-      <c r="N55" t="n" s="0">
-        <v>-5.055197728932868</v>
-      </c>
-      <c r="O55" t="n" s="0">
-        <v>-5.100772140331135</v>
-      </c>
-      <c r="P55" t="n" s="0">
-        <v>-5.100772140331753</v>
-      </c>
-      <c r="Q55" t="n" s="0">
-        <v>-10.153199679058226</v>
-      </c>
-      <c r="R55" t="n" s="0">
-        <v>-10.153199679058227</v>
-      </c>
-      <c r="S55" t="n" s="0">
-        <v>-10.153199675852708</v>
-      </c>
-      <c r="T55" t="n" s="0">
-        <v>-10.153199564336857</v>
-      </c>
-      <c r="U55" t="n" s="0">
-        <v>-10.15319967905767</v>
-      </c>
-      <c r="V55" t="n" s="0">
-        <v>-5.100772139515442</v>
-      </c>
-      <c r="W55" t="n" s="0">
-        <v>-10.153199550533506</v>
-      </c>
-      <c r="X55" t="n" s="0">
-        <v>-10.153199679056925</v>
-      </c>
-      <c r="Y55" t="n" s="0">
-        <v>-5.100772140331988</v>
-      </c>
-      <c r="Z55" t="n" s="0">
-        <v>-5.100772140331986</v>
-      </c>
-      <c r="AA55" t="n" s="0">
-        <v>-5.100772136346834</v>
-      </c>
-      <c r="AB55" t="n" s="0">
-        <v>-2.6304716684108937</v>
-      </c>
-      <c r="AC55" t="n" s="0">
-        <v>-5.100772140331988</v>
-      </c>
-      <c r="AD55" t="n" s="0">
-        <v>-2.63047166841038</v>
-      </c>
-      <c r="AE55" t="n" s="0">
-        <v>-5.100772140331988</v>
-      </c>
       <c r="AF55" t="n" s="0">
-        <v>-5.055197727811798</v>
+        <v>-10.153199679058229</v>
       </c>
     </row>
     <row r="56">
       <c r="C56" t="n" s="0">
-        <v>-5.128822755876281</v>
+        <v>-10.402916445645069</v>
       </c>
       <c r="D56" t="n" s="0">
+        <v>-10.402940566818664</v>
+      </c>
+      <c r="E56" t="n" s="0">
+        <v>-5.12882279696545</v>
+      </c>
+      <c r="F56" t="n" s="0">
+        <v>-5.1288227928618095</v>
+      </c>
+      <c r="G56" t="n" s="0">
+        <v>-10.40294056546987</v>
+      </c>
+      <c r="H56" t="n" s="0">
+        <v>-5.1288227969654026</v>
+      </c>
+      <c r="I56" t="n" s="0">
+        <v>-5.0876702231854045</v>
+      </c>
+      <c r="J56" t="n" s="0">
+        <v>-5.128822796965456</v>
+      </c>
+      <c r="K56" t="n" s="0">
+        <v>-5.128822796965455</v>
+      </c>
+      <c r="L56" t="n" s="0">
+        <v>-5.128800450609823</v>
+      </c>
+      <c r="M56" t="n" s="0">
+        <v>-10.402940482956405</v>
+      </c>
+      <c r="N56" t="n" s="0">
+        <v>-5.128822796965455</v>
+      </c>
+      <c r="O56" t="n" s="0">
+        <v>-5.1288227969652445</v>
+      </c>
+      <c r="P56" t="n" s="0">
+        <v>-10.402905985087811</v>
+      </c>
+      <c r="Q56" t="n" s="0">
         <v>-10.40294056681866</v>
       </c>
-      <c r="E56" t="n" s="0">
-        <v>-3.7243003465069995</v>
-      </c>
-      <c r="F56" t="n" s="0">
-        <v>-10.351972508578482</v>
-      </c>
-      <c r="G56" t="n" s="0">
-        <v>-10.402940566809805</v>
-      </c>
-      <c r="H56" t="n" s="0">
-        <v>-2.7658953371529833</v>
-      </c>
-      <c r="I56" t="n" s="0">
-        <v>-10.402940566818662</v>
-      </c>
-      <c r="J56" t="n" s="0">
-        <v>-5.128822082190909</v>
-      </c>
-      <c r="K56" t="n" s="0">
-        <v>-10.402453711224899</v>
-      </c>
-      <c r="L56" t="n" s="0">
-        <v>-5.128822796965454</v>
-      </c>
-      <c r="M56" t="n" s="0">
-        <v>-5.128822796965456</v>
-      </c>
-      <c r="N56" t="n" s="0">
-        <v>-10.372538477949115</v>
-      </c>
-      <c r="O56" t="n" s="0">
-        <v>-10.402940566818662</v>
-      </c>
-      <c r="P56" t="n" s="0">
-        <v>-5.12882032894864</v>
-      </c>
-      <c r="Q56" t="n" s="0">
-        <v>-1.837592927360792</v>
-      </c>
       <c r="R56" t="n" s="0">
-        <v>-10.40294056681866</v>
+        <v>-10.40294056681716</v>
       </c>
       <c r="S56" t="n" s="0">
-        <v>-2.765468352698561</v>
+        <v>-2.7658973277790255</v>
       </c>
       <c r="T56" t="n" s="0">
-        <v>-10.40294056052227</v>
+        <v>-10.402940424371582</v>
       </c>
       <c r="U56" t="n" s="0">
-        <v>-10.402900198764383</v>
+        <v>-5.12609135614498</v>
       </c>
       <c r="V56" t="n" s="0">
-        <v>-5.128822796965416</v>
+        <v>-10.402940566818659</v>
       </c>
       <c r="W56" t="n" s="0">
-        <v>-10.40294056659746</v>
+        <v>-10.40294056681816</v>
       </c>
       <c r="X56" t="n" s="0">
-        <v>-5.12783857682306</v>
+        <v>-5.128822493912207</v>
       </c>
       <c r="Y56" t="n" s="0">
-        <v>-10.402940566818666</v>
+        <v>-5.128822796965445</v>
       </c>
       <c r="Z56" t="n" s="0">
-        <v>-5.128822796965434</v>
+        <v>-10.402454168639242</v>
       </c>
       <c r="AA56" t="n" s="0">
-        <v>-10.40294056659042</v>
+        <v>-5.128822796965455</v>
       </c>
       <c r="AB56" t="n" s="0">
-        <v>-10.402940566625729</v>
+        <v>-5.128822701518603</v>
       </c>
       <c r="AC56" t="n" s="0">
-        <v>-5.128822796965455</v>
+        <v>-5.128822796861512</v>
       </c>
       <c r="AD56" t="n" s="0">
-        <v>-5.128822787825472</v>
+        <v>-10.402940566772143</v>
       </c>
       <c r="AE56" t="n" s="0">
-        <v>-10.402599761849178</v>
+        <v>-10.402940566818664</v>
       </c>
       <c r="AF56" t="n" s="0">
-        <v>-10.40294056681866</v>
+        <v>-5.128822796718973</v>
       </c>
     </row>
     <row r="57">
       <c r="C57" t="n" s="0">
-        <v>-1.6765531443344086</v>
+        <v>-10.536409816692048</v>
       </c>
       <c r="D57" t="n" s="0">
-        <v>-5.175646739650303</v>
+        <v>-5.175646741647882</v>
       </c>
       <c r="E57" t="n" s="0">
-        <v>-5.17564674164788</v>
+        <v>-9.969476039730315</v>
       </c>
       <c r="F57" t="n" s="0">
-        <v>-10.536409816692032</v>
+        <v>-2.8066189799828054</v>
       </c>
       <c r="G57" t="n" s="0">
-        <v>-5.175646741647884</v>
+        <v>-5.175646741647881</v>
       </c>
       <c r="H57" t="n" s="0">
-        <v>-5.175646740742729</v>
+        <v>-5.128480786627355</v>
       </c>
       <c r="I57" t="n" s="0">
-        <v>-5.1756467416463305</v>
+        <v>-2.341319178979983</v>
       </c>
       <c r="J57" t="n" s="0">
-        <v>-5.175646737888616</v>
+        <v>-5.136351319679044</v>
       </c>
       <c r="K57" t="n" s="0">
-        <v>-10.53640981651506</v>
+        <v>-3.8354268032089385</v>
       </c>
       <c r="L57" t="n" s="0">
-        <v>-5.1756467416478795</v>
+        <v>-1.8594803012174992</v>
       </c>
       <c r="M57" t="n" s="0">
-        <v>-10.536409816692043</v>
+        <v>-1.676553243486734</v>
       </c>
       <c r="N57" t="n" s="0">
-        <v>-5.175646741647879</v>
+        <v>-10.53640981669135</v>
       </c>
       <c r="O57" t="n" s="0">
-        <v>-10.536259658999457</v>
+        <v>-10.536409816692034</v>
       </c>
       <c r="P57" t="n" s="0">
-        <v>-2.4273352000741277</v>
+        <v>-10.536409816692046</v>
       </c>
       <c r="Q57" t="n" s="0">
+        <v>-10.536409815078715</v>
+      </c>
+      <c r="R57" t="n" s="0">
+        <v>-5.175646741647883</v>
+      </c>
+      <c r="S57" t="n" s="0">
+        <v>-5.175644154652529</v>
+      </c>
+      <c r="T57" t="n" s="0">
         <v>-10.536409816692046</v>
       </c>
-      <c r="R57" t="n" s="0">
-        <v>-1.6765532502392722</v>
-      </c>
-      <c r="S57" t="n" s="0">
-        <v>-5.175645553208794</v>
-      </c>
-      <c r="T57" t="n" s="0">
-        <v>-5.175646741647883</v>
-      </c>
       <c r="U57" t="n" s="0">
-        <v>-10.536409803827654</v>
+        <v>-10.536409816646858</v>
       </c>
       <c r="V57" t="n" s="0">
-        <v>-5.175646741644656</v>
+        <v>-10.536409816692046</v>
       </c>
       <c r="W57" t="n" s="0">
-        <v>-5.175646083162655</v>
+        <v>-10.536409742504631</v>
       </c>
       <c r="X57" t="n" s="0">
+        <v>-5.1756467416477925</v>
+      </c>
+      <c r="Y57" t="n" s="0">
+        <v>-5.1756467399927795</v>
+      </c>
+      <c r="Z57" t="n" s="0">
+        <v>-10.533625705698581</v>
+      </c>
+      <c r="AA57" t="n" s="0">
+        <v>-10.536409816690808</v>
+      </c>
+      <c r="AB57" t="n" s="0">
+        <v>-10.536409787720968</v>
+      </c>
+      <c r="AC57" t="n" s="0">
+        <v>-10.53640973074645</v>
+      </c>
+      <c r="AD57" t="n" s="0">
+        <v>-5.17564670233168</v>
+      </c>
+      <c r="AE57" t="n" s="0">
         <v>-10.536409816692045</v>
       </c>
-      <c r="Y57" t="n" s="0">
-        <v>-5.128480786627454</v>
-      </c>
-      <c r="Z57" t="n" s="0">
-        <v>-5.175646741626435</v>
-      </c>
-      <c r="AA57" t="n" s="0">
-        <v>-5.175646741580516</v>
-      </c>
-      <c r="AB57" t="n" s="0">
-        <v>-5.175646741647883</v>
-      </c>
-      <c r="AC57" t="n" s="0">
-        <v>-5.175646741490748</v>
-      </c>
-      <c r="AD57" t="n" s="0">
-        <v>-5.175646741647883</v>
-      </c>
-      <c r="AE57" t="n" s="0">
-        <v>-5.175646741647871</v>
-      </c>
       <c r="AF57" t="n" s="0">
-        <v>-10.53640981667794</v>
+        <v>-10.536408677633691</v>
       </c>
     </row>
     <row r="64">
       <c r="C64" t="n" s="0">
-        <v>1.9547832386329982E-33</v>
+        <v>8.763988796181985E-34</v>
       </c>
       <c r="D64" t="n" s="0">
-        <v>7.672480897738633E-33</v>
+        <v>4.153745084038235E-32</v>
       </c>
       <c r="E64" t="n" s="0">
-        <v>2.0434759254824222E-31</v>
+        <v>3.697320326895416E-34</v>
       </c>
       <c r="F64" t="n" s="0">
-        <v>4.625519954636297E-33</v>
+        <v>1.1073057165195085E-31</v>
       </c>
       <c r="G64" t="n" s="0">
-        <v>2.1068031514466566E-31</v>
+        <v>1.3011654676306686E-31</v>
       </c>
       <c r="H64" t="n" s="0">
-        <v>8.995356353958908E-32</v>
+        <v>1.679823904399776E-32</v>
       </c>
       <c r="I64" t="n" s="0">
-        <v>1.147376273865607E-32</v>
+        <v>1.8457393646530886E-33</v>
       </c>
       <c r="J64" t="n" s="0">
-        <v>2.103979526017725E-33</v>
+        <v>1.0473769380095707E-33</v>
       </c>
       <c r="K64" t="n" s="0">
-        <v>1.3975662176819205E-31</v>
+        <v>4.374416355402399E-34</v>
       </c>
       <c r="L64" t="n" s="0">
-        <v>1.339475085047795E-32</v>
+        <v>1.205787798394549E-33</v>
       </c>
       <c r="M64" t="n" s="0">
-        <v>1.033934704502039E-31</v>
+        <v>1.3343859655474314E-32</v>
       </c>
       <c r="N64" t="n" s="0">
-        <v>3.945779333576391E-31</v>
+        <v>2.883587969374623E-34</v>
       </c>
       <c r="O64" t="n" s="0">
-        <v>1.3312699866277665E-33</v>
+        <v>6.859983933276548E-31</v>
       </c>
       <c r="P64" t="n" s="0">
-        <v>7.719811162559364E-32</v>
+        <v>2.5885366957525653E-31</v>
       </c>
       <c r="Q64" t="n" s="0">
-        <v>2.0217866892376491E-35</v>
+        <v>1.2973976309232055E-33</v>
       </c>
       <c r="R64" t="n" s="0">
-        <v>2.1430431589045436E-32</v>
+        <v>2.056131289035809E-32</v>
       </c>
       <c r="S64" t="n" s="0">
-        <v>1.1489315906642853E-33</v>
+        <v>4.238577188634274E-31</v>
       </c>
       <c r="T64" t="n" s="0">
-        <v>3.295135730605171E-31</v>
+        <v>5.401607389656318E-31</v>
       </c>
       <c r="U64" t="n" s="0">
-        <v>1.2918662091955492E-34</v>
+        <v>1.5162712406517708E-33</v>
       </c>
       <c r="V64" t="n" s="0">
-        <v>1.0481208978892162E-31</v>
+        <v>8.781754412609867E-33</v>
       </c>
       <c r="W64" t="n" s="0">
-        <v>8.755186644001901E-32</v>
+        <v>5.2787231205129715E-33</v>
       </c>
       <c r="X64" t="n" s="0">
-        <v>5.721523273715327E-33</v>
+        <v>1.6370979326033515E-30</v>
       </c>
       <c r="Y64" t="n" s="0">
-        <v>4.159065913512035E-34</v>
+        <v>2.729038269292107E-33</v>
       </c>
       <c r="Z64" t="n" s="0">
-        <v>2.691299879909689E-30</v>
+        <v>3.984325550104111E-32</v>
       </c>
       <c r="AA64" t="n" s="0">
-        <v>2.848208889203442E-34</v>
+        <v>3.0450830694800747E-32</v>
       </c>
       <c r="AB64" t="n" s="0">
-        <v>2.1995651972464952E-32</v>
+        <v>6.1861529495238355E-31</v>
       </c>
       <c r="AC64" t="n" s="0">
-        <v>2.723201719667837E-33</v>
+        <v>1.6952904162496764E-33</v>
       </c>
       <c r="AD64" t="n" s="0">
-        <v>1.0716121292004376E-32</v>
+        <v>3.99092457720591E-34</v>
       </c>
       <c r="AE64" t="n" s="0">
-        <v>2.738916582921087E-31</v>
+        <v>5.649786237991872E-31</v>
       </c>
       <c r="AF64" t="n" s="0">
-        <v>1.3514249194854957E-32</v>
+        <v>1.2649314689171253E-32</v>
       </c>
     </row>
     <row r="65">
       <c r="C65" t="n" s="0">
-        <v>6.260783473750237E-20</v>
+        <v>2.1256670549092138E-19</v>
       </c>
       <c r="D65" t="n" s="0">
-        <v>9.748413423480769E-19</v>
+        <v>1.7765865148063064E-19</v>
       </c>
       <c r="E65" t="n" s="0">
-        <v>1.859033942604992E-18</v>
+        <v>1.0641888536011075E-18</v>
       </c>
       <c r="F65" t="n" s="0">
-        <v>2.2536474051957354E-19</v>
+        <v>9.453764315660267E-19</v>
       </c>
       <c r="G65" t="n" s="0">
-        <v>1.0495076198156626E-18</v>
+        <v>2.7316893712100016E-19</v>
       </c>
       <c r="H65" t="n" s="0">
-        <v>3.39574528138087E-19</v>
+        <v>1.1832530597170412E-18</v>
       </c>
       <c r="I65" t="n" s="0">
-        <v>3.19095580471405E-19</v>
+        <v>5.353942999543195E-19</v>
       </c>
       <c r="J65" t="n" s="0">
-        <v>2.256287591113569E-19</v>
+        <v>2.235516783301948E-18</v>
       </c>
       <c r="K65" t="n" s="0">
-        <v>5.020674665553766E-20</v>
+        <v>3.8709706765613204E-19</v>
       </c>
       <c r="L65" t="n" s="0">
-        <v>1.2907151328502272E-19</v>
+        <v>9.124252575995654E-20</v>
       </c>
       <c r="M65" t="n" s="0">
-        <v>7.727193611817127E-19</v>
+        <v>1.524458114255416E-19</v>
       </c>
       <c r="N65" t="n" s="0">
-        <v>1.4069148156356643E-18</v>
+        <v>6.717798972801967E-19</v>
       </c>
       <c r="O65" t="n" s="0">
-        <v>2.8834703850440393E-19</v>
+        <v>1.175292137602021E-18</v>
       </c>
       <c r="P65" t="n" s="0">
-        <v>4.5470270044332883E-20</v>
+        <v>1.779490838117816E-18</v>
       </c>
       <c r="Q65" t="n" s="0">
-        <v>8.079898322239498E-19</v>
+        <v>5.879129382388592E-19</v>
       </c>
       <c r="R65" t="n" s="0">
-        <v>5.002691056074781E-19</v>
+        <v>6.009195124335802E-19</v>
       </c>
       <c r="S65" t="n" s="0">
-        <v>2.1085397028979353E-18</v>
+        <v>6.419958821153185E-19</v>
       </c>
       <c r="T65" t="n" s="0">
-        <v>1.900588839728742E-19</v>
+        <v>1.9662592477139895E-19</v>
       </c>
       <c r="U65" t="n" s="0">
-        <v>5.172050977389888E-19</v>
+        <v>2.3366588515585193E-18</v>
       </c>
       <c r="V65" t="n" s="0">
-        <v>3.366754722761261E-19</v>
+        <v>5.103496904430391E-19</v>
       </c>
       <c r="W65" t="n" s="0">
-        <v>1.2957925137221514E-18</v>
+        <v>4.330825112301131E-19</v>
       </c>
       <c r="X65" t="n" s="0">
-        <v>3.940524195736618E-19</v>
+        <v>1.070596583565699E-18</v>
       </c>
       <c r="Y65" t="n" s="0">
-        <v>1.894720779624233E-18</v>
+        <v>7.33176286134247E-20</v>
       </c>
       <c r="Z65" t="n" s="0">
-        <v>4.873322233979167E-18</v>
+        <v>4.847888427054088E-20</v>
       </c>
       <c r="AA65" t="n" s="0">
-        <v>1.0685163988616257E-18</v>
+        <v>1.4289728598763873E-18</v>
       </c>
       <c r="AB65" t="n" s="0">
-        <v>4.0065626670215554E-19</v>
+        <v>3.3433181233634676E-18</v>
       </c>
       <c r="AC65" t="n" s="0">
-        <v>6.773799109222352E-19</v>
+        <v>3.4491592914725325E-19</v>
       </c>
       <c r="AD65" t="n" s="0">
-        <v>3.6072636530167765E-19</v>
+        <v>2.4845068162249387E-20</v>
       </c>
       <c r="AE65" t="n" s="0">
-        <v>4.756990839106409E-19</v>
+        <v>4.719079872352424E-19</v>
       </c>
       <c r="AF65" t="n" s="0">
-        <v>6.660878363836243E-20</v>
+        <v>1.0199399554075498E-19</v>
       </c>
     </row>
     <row r="66">
       <c r="C66" t="n" s="0">
-        <v>8.413387202230722E-17</v>
+        <v>6.605871869081475E-16</v>
       </c>
       <c r="D66" t="n" s="0">
-        <v>5.743559928517712E-16</v>
+        <v>1.5233729799095401E-15</v>
       </c>
       <c r="E66" t="n" s="0">
-        <v>4.4371882965236996E-16</v>
+        <v>5.273939528773727E-15</v>
       </c>
       <c r="F66" t="n" s="0">
-        <v>5.512896129360393E-17</v>
+        <v>3.0531959027709513E-12</v>
       </c>
       <c r="G66" t="n" s="0">
-        <v>5.689237163388572E-14</v>
+        <v>9.09785907601232E-15</v>
       </c>
       <c r="H66" t="n" s="0">
-        <v>4.8882712773328706E-15</v>
+        <v>1.4653225388152454E-14</v>
       </c>
       <c r="I66" t="n" s="0">
-        <v>2.8763652123554433E-16</v>
+        <v>6.764093820792378E-16</v>
       </c>
       <c r="J66" t="n" s="0">
-        <v>8.601001163770052E-16</v>
+        <v>1.7240412699590133E-17</v>
       </c>
       <c r="K66" t="n" s="0">
-        <v>6.627114757786712E-17</v>
+        <v>1.8688527991982387E-17</v>
       </c>
       <c r="L66" t="n" s="0">
-        <v>1.1200812572975936E-17</v>
+        <v>1.3835808790361687E-13</v>
       </c>
       <c r="M66" t="n" s="0">
-        <v>1.2038970029163439E-14</v>
+        <v>8.06733874974235E-15</v>
       </c>
       <c r="N66" t="n" s="0">
-        <v>6.678383917928748E-19</v>
+        <v>2.940602176417468E-15</v>
       </c>
       <c r="O66" t="n" s="0">
-        <v>1.8494971580272636E-14</v>
+        <v>2.111231794786704E-15</v>
       </c>
       <c r="P66" t="n" s="0">
-        <v>1.8999782415444736E-18</v>
+        <v>1.5029004466269316E-17</v>
       </c>
       <c r="Q66" t="n" s="0">
-        <v>1.999446229693308E-15</v>
+        <v>4.821257008796502E-13</v>
       </c>
       <c r="R66" t="n" s="0">
-        <v>5.875614306882267E-14</v>
+        <v>1.5196637830245524E-16</v>
       </c>
       <c r="S66" t="n" s="0">
-        <v>2.8466505699954717E-15</v>
+        <v>1.8458908389425497E-15</v>
       </c>
       <c r="T66" t="n" s="0">
-        <v>2.699584067986841E-16</v>
+        <v>3.776818274856867E-15</v>
       </c>
       <c r="U66" t="n" s="0">
-        <v>3.822086984332358E-14</v>
+        <v>1.037498912992873E-15</v>
       </c>
       <c r="V66" t="n" s="0">
-        <v>5.230350404635776E-14</v>
+        <v>2.415003033458549E-14</v>
       </c>
       <c r="W66" t="n" s="0">
-        <v>1.79696577910641E-16</v>
+        <v>1.472566667888571E-15</v>
       </c>
       <c r="X66" t="n" s="0">
-        <v>3.0044215718256826E-15</v>
+        <v>3.7934415197499395E-14</v>
       </c>
       <c r="Y66" t="n" s="0">
-        <v>2.606167833476891E-15</v>
+        <v>4.703059639605322E-17</v>
       </c>
       <c r="Z66" t="n" s="0">
-        <v>1.6518783003915401E-15</v>
+        <v>3.0670538983975326E-16</v>
       </c>
       <c r="AA66" t="n" s="0">
-        <v>8.558847014002995E-16</v>
+        <v>2.775769866515891E-16</v>
       </c>
       <c r="AB66" t="n" s="0">
-        <v>2.1058279314077454E-14</v>
+        <v>2.512107254209058E-13</v>
       </c>
       <c r="AC66" t="n" s="0">
-        <v>9.342021541206105E-17</v>
+        <v>3.52401806487338E-14</v>
       </c>
       <c r="AD66" t="n" s="0">
-        <v>2.087725847726022E-15</v>
+        <v>1.051775942367773E-15</v>
       </c>
       <c r="AE66" t="n" s="0">
-        <v>2.008540502564816E-13</v>
+        <v>1.914385857344756E-14</v>
       </c>
       <c r="AF66" t="n" s="0">
-        <v>2.5166383971595266E-18</v>
+        <v>5.1927522409122405E-15</v>
       </c>
     </row>
     <row r="67">
       <c r="C67" t="n" s="0">
-        <v>1.012376182298066E-10</v>
+        <v>1.0297029464855945E-10</v>
       </c>
       <c r="D67" t="n" s="0">
-        <v>2.4877829471526623E-10</v>
+        <v>6.273479836713235E-10</v>
       </c>
       <c r="E67" t="n" s="0">
-        <v>1.6957661292895193E-10</v>
+        <v>2.347010471590065E-11</v>
       </c>
       <c r="F67" t="n" s="0">
-        <v>1.2642050704227589E-10</v>
+        <v>7.719861016709201E-11</v>
       </c>
       <c r="G67" t="n" s="0">
-        <v>4.851455556436258E-11</v>
+        <v>3.2599281307612436E-10</v>
       </c>
       <c r="H67" t="n" s="0">
-        <v>1.021667959281206E-9</v>
+        <v>3.5575530384441424E-11</v>
       </c>
       <c r="I67" t="n" s="0">
-        <v>1.6161260484472044E-10</v>
+        <v>2.0023706557877836E-10</v>
       </c>
       <c r="J67" t="n" s="0">
-        <v>1.0289750659624268E-10</v>
+        <v>1.3269620226702663E-10</v>
       </c>
       <c r="K67" t="n" s="0">
-        <v>5.559860221282965E-11</v>
+        <v>7.272759673127675E-11</v>
       </c>
       <c r="L67" t="n" s="0">
-        <v>5.102412164122879E-11</v>
+        <v>4.396227098752599E-11</v>
       </c>
       <c r="M67" t="n" s="0">
-        <v>1.3029885068553798E-10</v>
+        <v>1.4297647250365349E-10</v>
       </c>
       <c r="N67" t="n" s="0">
-        <v>2.9080946909323217E-10</v>
+        <v>6.612306661771048E-12</v>
       </c>
       <c r="O67" t="n" s="0">
-        <v>3.331495773248434E-10</v>
+        <v>8.303779291082136E-11</v>
       </c>
       <c r="P67" t="n" s="0">
-        <v>1.7904837460643213E-10</v>
+        <v>3.662866656893887E-12</v>
       </c>
       <c r="Q67" t="n" s="0">
-        <v>3.167973653160629E-10</v>
+        <v>4.4882760417908055E-11</v>
       </c>
       <c r="R67" t="n" s="0">
-        <v>3.2883793100412443E-9</v>
+        <v>2.4792980090813934E-10</v>
       </c>
       <c r="S67" t="n" s="0">
-        <v>4.4603955734978326E-11</v>
+        <v>8.7854167583728E-12</v>
       </c>
       <c r="T67" t="n" s="0">
-        <v>3.102216730997892E-10</v>
+        <v>1.950905662059684E-9</v>
       </c>
       <c r="U67" t="n" s="0">
-        <v>6.170369882675207E-11</v>
+        <v>2.9400253643455644E-11</v>
       </c>
       <c r="V67" t="n" s="0">
-        <v>4.4122915340712445E-11</v>
+        <v>2.7249349990417708E-9</v>
       </c>
       <c r="W67" t="n" s="0">
-        <v>1.1868551144557483E-10</v>
+        <v>1.872055841168387E-11</v>
       </c>
       <c r="X67" t="n" s="0">
-        <v>6.294332756980983E-10</v>
+        <v>1.450444055070745E-9</v>
       </c>
       <c r="Y67" t="n" s="0">
-        <v>4.5233148510797584E-10</v>
+        <v>1.4228001098038216E-10</v>
       </c>
       <c r="Z67" t="n" s="0">
-        <v>1.8055546593847875E-11</v>
+        <v>4.458730473440449E-10</v>
       </c>
       <c r="AA67" t="n" s="0">
-        <v>1.0744264068342586E-11</v>
+        <v>2.9373858809898793E-10</v>
       </c>
       <c r="AB67" t="n" s="0">
-        <v>1.0650121224814473E-9</v>
+        <v>2.4178262967830265E-9</v>
       </c>
       <c r="AC67" t="n" s="0">
-        <v>1.439917575934183E-10</v>
+        <v>2.596180507431259E-11</v>
       </c>
       <c r="AD67" t="n" s="0">
-        <v>8.215855905591292E-11</v>
+        <v>1.262739638876668E-9</v>
       </c>
       <c r="AE67" t="n" s="0">
-        <v>6.781847283734148E-11</v>
+        <v>4.9279101964510076E-11</v>
       </c>
       <c r="AF67" t="n" s="0">
-        <v>7.627320849542405E-9</v>
+        <v>5.569894305990182E-11</v>
       </c>
     </row>
     <row r="68">
       <c r="C68" t="n" s="0">
-        <v>6.956621000725626</v>
+        <v>5.972490757223117</v>
       </c>
       <c r="D68" t="n" s="0">
-        <v>6.032367302058626</v>
+        <v>6.035823665923131</v>
       </c>
       <c r="E68" t="n" s="0">
-        <v>6.197427856838467</v>
+        <v>6.21295469651251</v>
       </c>
       <c r="F68" t="n" s="0">
-        <v>6.760856109170982</v>
+        <v>6.175235160864254</v>
       </c>
       <c r="G68" t="n" s="0">
-        <v>6.190978617893232</v>
+        <v>6.257438131142494</v>
       </c>
       <c r="H68" t="n" s="0">
-        <v>6.161623629909407</v>
+        <v>6.253294415016616</v>
       </c>
       <c r="I68" t="n" s="0">
-        <v>6.153061535598918</v>
+        <v>5.917046983415501</v>
       </c>
       <c r="J68" t="n" s="0">
-        <v>6.183664926035569</v>
+        <v>6.867567593299828</v>
       </c>
       <c r="K68" t="n" s="0">
-        <v>6.165708691510874</v>
+        <v>6.249510346951591</v>
       </c>
       <c r="L68" t="n" s="0">
-        <v>6.357624703151166</v>
+        <v>6.023155962006175</v>
       </c>
       <c r="M68" t="n" s="0">
-        <v>6.186860873444127</v>
+        <v>6.821959165540954</v>
       </c>
       <c r="N68" t="n" s="0">
-        <v>7.166459949492329</v>
+        <v>6.174306239850099</v>
       </c>
       <c r="O68" t="n" s="0">
-        <v>6.007538973390566</v>
+        <v>6.2700704748567695</v>
       </c>
       <c r="P68" t="n" s="0">
-        <v>6.152567603096639</v>
+        <v>6.610865429530984</v>
       </c>
       <c r="Q68" t="n" s="0">
-        <v>5.9689303060962775</v>
+        <v>5.920187539116461</v>
       </c>
       <c r="R68" t="n" s="0">
-        <v>6.248975946318273</v>
+        <v>6.271305271117733</v>
       </c>
       <c r="S68" t="n" s="0">
-        <v>6.021740697371023</v>
+        <v>5.987916463560315</v>
       </c>
       <c r="T68" t="n" s="0">
-        <v>6.295819247032284</v>
+        <v>6.412311664800362</v>
       </c>
       <c r="U68" t="n" s="0">
-        <v>6.403356981920837</v>
+        <v>6.244837095283026</v>
       </c>
       <c r="V68" t="n" s="0">
-        <v>6.327072766873629</v>
+        <v>6.176545877227348</v>
       </c>
       <c r="W68" t="n" s="0">
-        <v>6.21787515029751</v>
+        <v>6.898462613175606</v>
       </c>
       <c r="X68" t="n" s="0">
-        <v>6.708336537130506</v>
+        <v>6.176994010887304</v>
       </c>
       <c r="Y68" t="n" s="0">
-        <v>6.216140747069076</v>
+        <v>6.318370474673859</v>
       </c>
       <c r="Z68" t="n" s="0">
-        <v>6.4059665735101134</v>
+        <v>6.06112876549133</v>
       </c>
       <c r="AA68" t="n" s="0">
-        <v>7.2040557664612574</v>
+        <v>6.176507003789937</v>
       </c>
       <c r="AB68" t="n" s="0">
-        <v>6.030663103084268</v>
+        <v>6.182706894297343</v>
       </c>
       <c r="AC68" t="n" s="0">
-        <v>6.200044934041963</v>
+        <v>6.223261401502346</v>
       </c>
       <c r="AD68" t="n" s="0">
-        <v>6.263462246866745</v>
+        <v>6.091453348035877</v>
       </c>
       <c r="AE68" t="n" s="0">
-        <v>6.525027959447121</v>
+        <v>6.1662706345897496</v>
       </c>
       <c r="AF68" t="n" s="0">
-        <v>6.439595650609437</v>
+        <v>6.1005692852039335</v>
       </c>
     </row>
     <row r="69">
       <c r="C69" t="n" s="0">
-        <v>3.4382437008949755E-6</v>
+        <v>1.6652540288193454E-6</v>
       </c>
       <c r="D69" t="n" s="0">
-        <v>6.965772758922193E-7</v>
+        <v>2.5054705267079E-6</v>
       </c>
       <c r="E69" t="n" s="0">
-        <v>9.804884350205041E-6</v>
+        <v>4.877258872508315E-6</v>
       </c>
       <c r="F69" t="n" s="0">
-        <v>3.5419238789237317E-6</v>
+        <v>1.2701699536279117E-5</v>
       </c>
       <c r="G69" t="n" s="0">
-        <v>7.926561506957271E-7</v>
+        <v>4.8833133990093965E-6</v>
       </c>
       <c r="H69" t="n" s="0">
-        <v>3.549747652955448E-6</v>
+        <v>8.34602869267099E-6</v>
       </c>
       <c r="I69" t="n" s="0">
-        <v>2.201111477197821E-6</v>
+        <v>9.269239799107704E-6</v>
       </c>
       <c r="J69" t="n" s="0">
-        <v>1.6884491738928765E-6</v>
+        <v>1.3688909470819348E-6</v>
       </c>
       <c r="K69" t="n" s="0">
-        <v>2.581963802018477E-6</v>
+        <v>6.178384498468126E-6</v>
       </c>
       <c r="L69" t="n" s="0">
-        <v>2.4843621015405543E-6</v>
+        <v>4.0421453153446255E-6</v>
       </c>
       <c r="M69" t="n" s="0">
-        <v>4.187773911542959E-6</v>
+        <v>5.662549183384847E-6</v>
       </c>
       <c r="N69" t="n" s="0">
-        <v>4.873130049394541E-6</v>
+        <v>4.710034587222907E-6</v>
       </c>
       <c r="O69" t="n" s="0">
-        <v>3.7946084494161436E-6</v>
+        <v>8.689597224053006E-6</v>
       </c>
       <c r="P69" t="n" s="0">
-        <v>3.292478783143573E-6</v>
+        <v>6.4815552461844545E-6</v>
       </c>
       <c r="Q69" t="n" s="0">
-        <v>5.623580743419473E-6</v>
+        <v>9.970439084543108E-7</v>
       </c>
       <c r="R69" t="n" s="0">
-        <v>1.8383693565516423E-6</v>
+        <v>1.9732474717388477E-6</v>
       </c>
       <c r="S69" t="n" s="0">
-        <v>5.881635076028808E-6</v>
+        <v>5.242849371328457E-6</v>
       </c>
       <c r="T69" t="n" s="0">
-        <v>7.102617839162842E-6</v>
+        <v>7.110232049614823E-6</v>
       </c>
       <c r="U69" t="n" s="0">
-        <v>3.189302590411667E-6</v>
+        <v>7.759505703669881E-6</v>
       </c>
       <c r="V69" t="n" s="0">
-        <v>3.5954698564452243E-6</v>
+        <v>1.945093569762954E-6</v>
       </c>
       <c r="W69" t="n" s="0">
-        <v>4.1191068847893314E-6</v>
+        <v>5.583692865596999E-6</v>
       </c>
       <c r="X69" t="n" s="0">
-        <v>4.181190339323333E-6</v>
+        <v>1.0200419723108373E-6</v>
       </c>
       <c r="Y69" t="n" s="0">
-        <v>3.309806516964938E-6</v>
+        <v>1.415498711954016E-6</v>
       </c>
       <c r="Z69" t="n" s="0">
-        <v>5.574844517743944E-6</v>
+        <v>5.298549260077198E-6</v>
       </c>
       <c r="AA69" t="n" s="0">
-        <v>7.794061757183208E-6</v>
+        <v>5.2143048967666675E-6</v>
       </c>
       <c r="AB69" t="n" s="0">
-        <v>2.8423188795809734E-6</v>
+        <v>4.144308886302696E-6</v>
       </c>
       <c r="AC69" t="n" s="0">
-        <v>4.614485264069328E-6</v>
+        <v>4.373415923514594E-6</v>
       </c>
       <c r="AD69" t="n" s="0">
-        <v>2.161821056882673E-6</v>
+        <v>5.346041832089397E-6</v>
       </c>
       <c r="AE69" t="n" s="0">
-        <v>5.056570340733584E-6</v>
+        <v>1.3703768642999792E-6</v>
       </c>
       <c r="AF69" t="n" s="0">
-        <v>4.3043586583572645E-6</v>
+        <v>9.89058765698755E-6</v>
       </c>
     </row>
     <row r="70">
       <c r="C70" t="n" s="0">
-        <v>0.00326936393348934</v>
+        <v>0.49361724008535174</v>
       </c>
       <c r="D70" t="n" s="0">
-        <v>0.3283573919297923</v>
+        <v>0.23119958185905684</v>
       </c>
       <c r="E70" t="n" s="0">
-        <v>0.57472520304253</v>
+        <v>0.7243154095819372</v>
       </c>
       <c r="F70" t="n" s="0">
-        <v>0.675070954451504</v>
+        <v>0.0833503413351532</v>
       </c>
       <c r="G70" t="n" s="0">
-        <v>0.34555356081636934</v>
+        <v>0.6814880855121221</v>
       </c>
       <c r="H70" t="n" s="0">
-        <v>0.6090866866810533</v>
+        <v>0.06206982161201906</v>
       </c>
       <c r="I70" t="n" s="0">
-        <v>0.0552247714610991</v>
+        <v>0.5491036961730011</v>
       </c>
       <c r="J70" t="n" s="0">
-        <v>0.7105125651969265</v>
+        <v>0.25858412040544365</v>
       </c>
       <c r="K70" t="n" s="0">
-        <v>0.807800983005445</v>
+        <v>0.5939119855841909</v>
       </c>
       <c r="L70" t="n" s="0">
-        <v>0.7001765616470174</v>
+        <v>0.23064994629114782</v>
       </c>
       <c r="M70" t="n" s="0">
-        <v>0.12363853729571601</v>
+        <v>0.2502972080446277</v>
       </c>
       <c r="N70" t="n" s="0">
-        <v>0.19695912343132477</v>
+        <v>0.3554623573350111</v>
       </c>
       <c r="O70" t="n" s="0">
-        <v>0.42754542886681385</v>
+        <v>0.7572872255397355</v>
       </c>
       <c r="P70" t="n" s="0">
-        <v>0.3640744629131099</v>
+        <v>0.9052724369145781</v>
       </c>
       <c r="Q70" t="n" s="0">
-        <v>0.2882103727196576</v>
+        <v>0.8966974786299078</v>
       </c>
       <c r="R70" t="n" s="0">
-        <v>0.6414490385755139</v>
+        <v>0.9434391852450936</v>
       </c>
       <c r="S70" t="n" s="0">
-        <v>0.8127498221725864</v>
+        <v>0.23440183585271404</v>
       </c>
       <c r="T70" t="n" s="0">
-        <v>0.703381742939249</v>
+        <v>0.24164841128516698</v>
       </c>
       <c r="U70" t="n" s="0">
-        <v>0.2608272078118308</v>
+        <v>0.10269475070953533</v>
       </c>
       <c r="V70" t="n" s="0">
-        <v>0.20585146471215493</v>
+        <v>0.5681810268724953</v>
       </c>
       <c r="W70" t="n" s="0">
-        <v>0.09442931512276209</v>
+        <v>0.34532053853223793</v>
       </c>
       <c r="X70" t="n" s="0">
-        <v>0.6562962627318067</v>
+        <v>0.6655772447371753</v>
       </c>
       <c r="Y70" t="n" s="0">
-        <v>0.5952783379028763</v>
+        <v>0.1660878934347118</v>
       </c>
       <c r="Z70" t="n" s="0">
-        <v>0.8810845702626036</v>
+        <v>0.834429317428629</v>
       </c>
       <c r="AA70" t="n" s="0">
-        <v>0.8680237968103507</v>
+        <v>0.21569348804482105</v>
       </c>
       <c r="AB70" t="n" s="0">
-        <v>0.3321743934683849</v>
+        <v>0.0788896116598316</v>
       </c>
       <c r="AC70" t="n" s="0">
-        <v>0.8131786679209794</v>
+        <v>0.1673168478482005</v>
       </c>
       <c r="AD70" t="n" s="0">
-        <v>0.09845702803685198</v>
+        <v>0.9357508446278751</v>
       </c>
       <c r="AE70" t="n" s="0">
-        <v>0.30562675340020423</v>
+        <v>0.6059361801716852</v>
       </c>
       <c r="AF70" t="n" s="0">
-        <v>0.8817624597637904</v>
+        <v>0.537237553171153</v>
       </c>
     </row>
     <row r="71">
       <c r="C71" t="n" s="0">
-        <v>-2844.73467994208</v>
+        <v>-2799.604516017596</v>
       </c>
       <c r="D71" t="n" s="0">
-        <v>-2523.0090519669375</v>
+        <v>-3222.258822918483</v>
       </c>
       <c r="E71" t="n" s="0">
-        <v>-2379.4551409629917</v>
+        <v>-2257.900252698954</v>
       </c>
       <c r="F71" t="n" s="0">
-        <v>-2569.447479526034</v>
+        <v>-2794.8317846812297</v>
       </c>
       <c r="G71" t="n" s="0">
-        <v>-2924.732704168538</v>
+        <v>-2548.3960453371283</v>
       </c>
       <c r="H71" t="n" s="0">
-        <v>-2409.622445718276</v>
+        <v>-2694.326390742937</v>
       </c>
       <c r="I71" t="n" s="0">
-        <v>-2767.8228233301616</v>
+        <v>-2147.845513350392</v>
       </c>
       <c r="J71" t="n" s="0">
-        <v>-1990.342719904669</v>
+        <v>-2649.989985248471</v>
       </c>
       <c r="K71" t="n" s="0">
-        <v>-2353.592662309257</v>
+        <v>-2347.4867435165875</v>
       </c>
       <c r="L71" t="n" s="0">
-        <v>-2278.4391992785113</v>
+        <v>-2923.950851492366</v>
       </c>
       <c r="M71" t="n" s="0">
-        <v>-2688.741624362242</v>
+        <v>-2584.2760878237927</v>
       </c>
       <c r="N71" t="n" s="0">
-        <v>-2748.596402649481</v>
+        <v>-2491.135977384899</v>
       </c>
       <c r="O71" t="n" s="0">
-        <v>-2312.5210255311276</v>
+        <v>-2865.5738835182647</v>
       </c>
       <c r="P71" t="n" s="0">
-        <v>-2307.385293602286</v>
+        <v>-2472.3375721237294</v>
       </c>
       <c r="Q71" t="n" s="0">
-        <v>-2889.0454956675553</v>
+        <v>-1988.8889725850524</v>
       </c>
       <c r="R71" t="n" s="0">
-        <v>-2530.806732150868</v>
+        <v>-2725.413716503979</v>
       </c>
       <c r="S71" t="n" s="0">
-        <v>-2570.415807118396</v>
+        <v>-2344.476798119548</v>
       </c>
       <c r="T71" t="n" s="0">
-        <v>-2059.4977460550645</v>
+        <v>-1880.0181354981937</v>
       </c>
       <c r="U71" t="n" s="0">
-        <v>-2097.203971988346</v>
+        <v>-2728.691965672894</v>
       </c>
       <c r="V71" t="n" s="0">
-        <v>-3617.211778729505</v>
+        <v>-3143.1533021187215</v>
       </c>
       <c r="W71" t="n" s="0">
-        <v>-3163.26426566516</v>
+        <v>-2432.5662924331127</v>
       </c>
       <c r="X71" t="n" s="0">
-        <v>-2699.4741058602804</v>
+        <v>-2116.8388913068693</v>
       </c>
       <c r="Y71" t="n" s="0">
-        <v>-2630.123788025565</v>
+        <v>-2370.0498726836668</v>
       </c>
       <c r="Z71" t="n" s="0">
-        <v>-2570.468013421885</v>
+        <v>-2617.7451043781484</v>
       </c>
       <c r="AA71" t="n" s="0">
-        <v>-2629.955344284673</v>
+        <v>-2317.8755706086463</v>
       </c>
       <c r="AB71" t="n" s="0">
-        <v>-2214.884610511246</v>
+        <v>-2957.708743200958</v>
       </c>
       <c r="AC71" t="n" s="0">
-        <v>-3202.1435361721833</v>
+        <v>-2459.558002829079</v>
       </c>
       <c r="AD71" t="n" s="0">
-        <v>-2567.9222085668503</v>
+        <v>-2999.8987870472247</v>
       </c>
       <c r="AE71" t="n" s="0">
-        <v>-2333.6813671869745</v>
+        <v>-2193.9134212775634</v>
       </c>
       <c r="AF71" t="n" s="0">
-        <v>-2570.3921387671285</v>
+        <v>-2610.246357456742</v>
       </c>
     </row>
     <row r="72">
@@ -5840,7 +5840,7 @@
         <v>0.0</v>
       </c>
       <c r="X72" t="n" s="0">
-        <v>0.0</v>
+        <v>8.881784197001252E-15</v>
       </c>
       <c r="Y72" t="n" s="0">
         <v>0.0</v>
@@ -5855,7 +5855,7 @@
         <v>0.0</v>
       </c>
       <c r="AC72" t="n" s="0">
-        <v>0.0</v>
+        <v>3.552713678800501E-15</v>
       </c>
       <c r="AD72" t="n" s="0">
         <v>0.0</v>
@@ -5869,13 +5869,13 @@
     </row>
     <row r="73">
       <c r="C73" t="n" s="0">
+        <v>1.4654943925052066E-14</v>
+      </c>
+      <c r="D73" t="n" s="0">
         <v>7.549516567451064E-15</v>
       </c>
-      <c r="D73" t="n" s="0">
-        <v>3.9968028886505635E-15</v>
-      </c>
       <c r="E73" t="n" s="0">
-        <v>3.9968028886505635E-15</v>
+        <v>7.549516567451064E-15</v>
       </c>
       <c r="F73" t="n" s="0">
         <v>7.549516567451064E-15</v>
@@ -5893,19 +5893,19 @@
         <v>3.9968028886505635E-15</v>
       </c>
       <c r="K73" t="n" s="0">
-        <v>7.549516567451064E-15</v>
+        <v>3.9968028886505635E-15</v>
       </c>
       <c r="L73" t="n" s="0">
-        <v>7.549516567451064E-15</v>
+        <v>1.4654943925052066E-14</v>
       </c>
       <c r="M73" t="n" s="0">
         <v>7.549516567451064E-15</v>
       </c>
       <c r="N73" t="n" s="0">
+        <v>3.9968028886505635E-15</v>
+      </c>
+      <c r="O73" t="n" s="0">
         <v>7.549516567451064E-15</v>
-      </c>
-      <c r="O73" t="n" s="0">
-        <v>3.9968028886505635E-15</v>
       </c>
       <c r="P73" t="n" s="0">
         <v>7.549516567451064E-15</v>
@@ -5917,19 +5917,19 @@
         <v>7.549516567451064E-15</v>
       </c>
       <c r="S73" t="n" s="0">
+        <v>3.9968028886505635E-15</v>
+      </c>
+      <c r="T73" t="n" s="0">
         <v>7.549516567451064E-15</v>
-      </c>
-      <c r="T73" t="n" s="0">
-        <v>1.4654943925052066E-14</v>
       </c>
       <c r="U73" t="n" s="0">
         <v>7.549516567451064E-15</v>
       </c>
       <c r="V73" t="n" s="0">
+        <v>1.4654943925052066E-14</v>
+      </c>
+      <c r="W73" t="n" s="0">
         <v>7.549516567451064E-15</v>
-      </c>
-      <c r="W73" t="n" s="0">
-        <v>3.9968028886505635E-15</v>
       </c>
       <c r="X73" t="n" s="0">
         <v>7.549516567451064E-15</v>
@@ -5944,10 +5944,10 @@
         <v>3.9968028886505635E-15</v>
       </c>
       <c r="AB73" t="n" s="0">
+        <v>3.9968028886505635E-15</v>
+      </c>
+      <c r="AC73" t="n" s="0">
         <v>7.549516567451064E-15</v>
-      </c>
-      <c r="AC73" t="n" s="0">
-        <v>3.9968028886505635E-15</v>
       </c>
       <c r="AD73" t="n" s="0">
         <v>3.9968028886505635E-15</v>
@@ -5961,1198 +5961,1198 @@
     </row>
     <row r="74">
       <c r="C74" t="n" s="0">
-        <v>0.0</v>
+        <v>0.027901849723153904</v>
       </c>
       <c r="D74" t="n" s="0">
-        <v>0.0189594192708602</v>
+        <v>0.04196380768383379</v>
       </c>
       <c r="E74" t="n" s="0">
         <v>0.0</v>
       </c>
       <c r="F74" t="n" s="0">
-        <v>0.01365059970233895</v>
+        <v>0.0</v>
       </c>
       <c r="G74" t="n" s="0">
         <v>0.0</v>
       </c>
       <c r="H74" t="n" s="0">
-        <v>0.010211468549043312</v>
+        <v>0.029785760395028227</v>
       </c>
       <c r="I74" t="n" s="0">
-        <v>0.0</v>
+        <v>0.010152690321530988</v>
       </c>
       <c r="J74" t="n" s="0">
-        <v>0.02533369487877235</v>
+        <v>0.011241508641993359</v>
       </c>
       <c r="K74" t="n" s="0">
-        <v>0.02005563575445979</v>
+        <v>0.0</v>
       </c>
       <c r="L74" t="n" s="0">
         <v>0.0</v>
       </c>
       <c r="M74" t="n" s="0">
-        <v>0.009933130232577025</v>
+        <v>0.0</v>
       </c>
       <c r="N74" t="n" s="0">
-        <v>0.01867457355486235</v>
+        <v>0.0</v>
       </c>
       <c r="O74" t="n" s="0">
         <v>0.0</v>
       </c>
       <c r="P74" t="n" s="0">
-        <v>0.01617661406739057</v>
+        <v>0.010336092660694018</v>
       </c>
       <c r="Q74" t="n" s="0">
-        <v>0.010869963458771448</v>
+        <v>0.0</v>
       </c>
       <c r="R74" t="n" s="0">
         <v>0.0</v>
       </c>
       <c r="S74" t="n" s="0">
-        <v>0.0</v>
+        <v>0.020439302846542162</v>
       </c>
       <c r="T74" t="n" s="0">
-        <v>0.013181450234297731</v>
+        <v>0.0</v>
       </c>
       <c r="U74" t="n" s="0">
-        <v>0.0</v>
+        <v>0.016845918918379277</v>
       </c>
       <c r="V74" t="n" s="0">
-        <v>0.008031111785411937</v>
+        <v>0.01494827974538282</v>
       </c>
       <c r="W74" t="n" s="0">
-        <v>0.0</v>
+        <v>0.06541142105440789</v>
       </c>
       <c r="X74" t="n" s="0">
-        <v>0.0</v>
+        <v>0.03311401803400238</v>
       </c>
       <c r="Y74" t="n" s="0">
-        <v>0.015293007172346162</v>
+        <v>0.02320925046820288</v>
       </c>
       <c r="Z74" t="n" s="0">
         <v>0.0</v>
       </c>
       <c r="AA74" t="n" s="0">
-        <v>0.008435008650882203</v>
+        <v>0.0</v>
       </c>
       <c r="AB74" t="n" s="0">
         <v>0.0</v>
       </c>
       <c r="AC74" t="n" s="0">
-        <v>2.098370477376932E-9</v>
+        <v>0.0</v>
       </c>
       <c r="AD74" t="n" s="0">
-        <v>0.018705936317057748</v>
+        <v>0.0</v>
       </c>
       <c r="AE74" t="n" s="0">
         <v>0.0</v>
       </c>
       <c r="AF74" t="n" s="0">
-        <v>3.306629192678656E-9</v>
+        <v>0.0</v>
       </c>
     </row>
     <row r="75">
       <c r="C75" t="n" s="0">
-        <v>9.974523988458447E-6</v>
+        <v>5.1629622095320764E-6</v>
       </c>
       <c r="D75" t="n" s="0">
-        <v>3.871455442072983E-6</v>
+        <v>4.637371689388956E-6</v>
       </c>
       <c r="E75" t="n" s="0">
-        <v>2.6659122408747285E-6</v>
+        <v>2.806561798325501E-6</v>
       </c>
       <c r="F75" t="n" s="0">
-        <v>4.407265178486857E-6</v>
+        <v>5.3120120685525216E-6</v>
       </c>
       <c r="G75" t="n" s="0">
-        <v>2.467128090456288E-6</v>
+        <v>3.833184601927087E-6</v>
       </c>
       <c r="H75" t="n" s="0">
-        <v>0.020017912642242584</v>
+        <v>1.5378254166562356E-6</v>
       </c>
       <c r="I75" t="n" s="0">
-        <v>2.444332794637157E-6</v>
+        <v>2.937812619431583E-6</v>
       </c>
       <c r="J75" t="n" s="0">
-        <v>9.98964236462778E-7</v>
+        <v>2.0898442622597686E-6</v>
       </c>
       <c r="K75" t="n" s="0">
-        <v>6.522844119493085E-6</v>
+        <v>1.8349337678748169E-6</v>
       </c>
       <c r="L75" t="n" s="0">
-        <v>5.7866547236599685E-6</v>
+        <v>1.228143741085414E-5</v>
       </c>
       <c r="M75" t="n" s="0">
-        <v>2.784323622455724E-6</v>
+        <v>7.296907159831298E-6</v>
       </c>
       <c r="N75" t="n" s="0">
-        <v>4.843769132858631E-6</v>
+        <v>5.198701418705507E-6</v>
       </c>
       <c r="O75" t="n" s="0">
-        <v>2.7166201204644456E-6</v>
+        <v>5.694503817652004E-6</v>
       </c>
       <c r="P75" t="n" s="0">
-        <v>1.5969843241208625E-6</v>
+        <v>2.990848076756763E-6</v>
       </c>
       <c r="Q75" t="n" s="0">
-        <v>1.5580819236065342E-6</v>
+        <v>1.3196191371169635E-6</v>
       </c>
       <c r="R75" t="n" s="0">
-        <v>2.9771229916757204E-6</v>
+        <v>2.408894451513555E-6</v>
       </c>
       <c r="S75" t="n" s="0">
-        <v>3.533588138483098E-6</v>
+        <v>1.2550789513651805E-6</v>
       </c>
       <c r="T75" t="n" s="0">
-        <v>3.0245408659295614E-6</v>
+        <v>4.139165381950328E-6</v>
       </c>
       <c r="U75" t="n" s="0">
-        <v>3.6469556724051178E-6</v>
+        <v>1.9458005484899454E-6</v>
       </c>
       <c r="V75" t="n" s="0">
-        <v>3.0078965231739067E-6</v>
+        <v>2.5252902691799246E-6</v>
       </c>
       <c r="W75" t="n" s="0">
-        <v>3.2138193183982135E-6</v>
+        <v>6.2339542752055E-6</v>
       </c>
       <c r="X75" t="n" s="0">
-        <v>8.399679933253745E-6</v>
+        <v>2.524596270198845E-6</v>
       </c>
       <c r="Y75" t="n" s="0">
-        <v>1.6025073685844266E-6</v>
+        <v>2.7700864404094277E-6</v>
       </c>
       <c r="Z75" t="n" s="0">
-        <v>3.651268932466505E-6</v>
+        <v>2.1345091954759335E-6</v>
       </c>
       <c r="AA75" t="n" s="0">
-        <v>5.336982700289437E-6</v>
+        <v>2.989333434967027E-6</v>
       </c>
       <c r="AB75" t="n" s="0">
-        <v>2.160872040237843E-6</v>
+        <v>5.22586897209993E-7</v>
       </c>
       <c r="AC75" t="n" s="0">
-        <v>3.2817710646216325E-6</v>
+        <v>1.5039162885429497E-6</v>
       </c>
       <c r="AD75" t="n" s="0">
-        <v>4.756072639647077E-6</v>
+        <v>1.3409591861132002E-6</v>
       </c>
       <c r="AE75" t="n" s="0">
-        <v>1.8440201242631257E-6</v>
+        <v>2.572138634013269E-6</v>
       </c>
       <c r="AF75" t="n" s="0">
-        <v>5.817935777259954E-6</v>
+        <v>2.038749801550831E-6</v>
       </c>
     </row>
     <row r="76">
       <c r="C76" t="n" s="0">
-        <v>4.764580250041706E-6</v>
+        <v>2.797346590404133E-5</v>
       </c>
       <c r="D76" t="n" s="0">
-        <v>5.0705023676392535E-5</v>
+        <v>2.6540169652957434E-5</v>
       </c>
       <c r="E76" t="n" s="0">
-        <v>8.197805187797311E-6</v>
+        <v>3.551282365138881E-5</v>
       </c>
       <c r="F76" t="n" s="0">
-        <v>1.3568697083054673E-5</v>
+        <v>8.371503047686528E-6</v>
       </c>
       <c r="G76" t="n" s="0">
-        <v>2.982926473757277E-5</v>
+        <v>4.0178469877253916E-6</v>
       </c>
       <c r="H76" t="n" s="0">
-        <v>1.1986112525534541E-5</v>
+        <v>1.6017235167062367E-5</v>
       </c>
       <c r="I76" t="n" s="0">
-        <v>2.556424475943466E-5</v>
+        <v>2.445853207835664E-5</v>
       </c>
       <c r="J76" t="n" s="0">
-        <v>2.5506222214352902E-5</v>
+        <v>3.548543167862494E-5</v>
       </c>
       <c r="K76" t="n" s="0">
-        <v>2.265071523702333E-5</v>
+        <v>3.679136128380357E-5</v>
       </c>
       <c r="L76" t="n" s="0">
-        <v>5.216460800755741E-6</v>
+        <v>8.923931916863672E-6</v>
       </c>
       <c r="M76" t="n" s="0">
-        <v>6.478836926661508E-6</v>
+        <v>4.304670821217214E-5</v>
       </c>
       <c r="N76" t="n" s="0">
-        <v>1.9570824079485617E-5</v>
+        <v>2.2369467612302343E-5</v>
       </c>
       <c r="O76" t="n" s="0">
-        <v>2.8836446815952564E-5</v>
+        <v>1.541070064543011E-5</v>
       </c>
       <c r="P76" t="n" s="0">
-        <v>1.0654233808023476E-5</v>
+        <v>1.657440245644384E-5</v>
       </c>
       <c r="Q76" t="n" s="0">
-        <v>0.12123934611531165</v>
+        <v>7.738550911930053E-6</v>
       </c>
       <c r="R76" t="n" s="0">
-        <v>1.4848948916041815E-5</v>
+        <v>3.419178014533661E-5</v>
       </c>
       <c r="S76" t="n" s="0">
-        <v>1.9665524956278936E-5</v>
+        <v>9.634492726020915E-6</v>
       </c>
       <c r="T76" t="n" s="0">
-        <v>1.8016488645983958E-5</v>
+        <v>4.734166799109536E-5</v>
       </c>
       <c r="U76" t="n" s="0">
-        <v>0.07501481191067072</v>
+        <v>4.564076453553192E-5</v>
       </c>
       <c r="V76" t="n" s="0">
-        <v>1.0816518853211548E-5</v>
+        <v>1.7126600539032445E-5</v>
       </c>
       <c r="W76" t="n" s="0">
-        <v>3.6936455162657016E-5</v>
+        <v>3.289514052300408E-6</v>
       </c>
       <c r="X76" t="n" s="0">
-        <v>1.764922653989902E-5</v>
+        <v>3.8121994573135346E-5</v>
       </c>
       <c r="Y76" t="n" s="0">
-        <v>3.412131963898443E-5</v>
+        <v>1.3890211334446663E-5</v>
       </c>
       <c r="Z76" t="n" s="0">
-        <v>2.729991911499032E-5</v>
+        <v>7.682899457979357E-5</v>
       </c>
       <c r="AA76" t="n" s="0">
-        <v>8.319405440827058E-6</v>
+        <v>3.1821772928043815E-6</v>
       </c>
       <c r="AB76" t="n" s="0">
-        <v>4.389258895037289E-6</v>
+        <v>5.912072374543425E-5</v>
       </c>
       <c r="AC76" t="n" s="0">
-        <v>2.5856029462198202E-5</v>
+        <v>3.438328350736418E-5</v>
       </c>
       <c r="AD76" t="n" s="0">
-        <v>7.285249674239618E-6</v>
+        <v>1.1728111258434957E-5</v>
       </c>
       <c r="AE76" t="n" s="0">
-        <v>2.4964755617103576E-5</v>
+        <v>2.4173754085668346E-5</v>
       </c>
       <c r="AF76" t="n" s="0">
-        <v>9.362940519484369E-6</v>
+        <v>1.7243399661760017E-5</v>
       </c>
     </row>
     <row r="77">
       <c r="C77" t="n" s="0">
-        <v>1.377438118583247E-15</v>
+        <v>4.626103501988173E-16</v>
       </c>
       <c r="D77" t="n" s="0">
-        <v>8.637874235572762E-13</v>
+        <v>9.138223178565083E-15</v>
       </c>
       <c r="E77" t="n" s="0">
-        <v>0.9980037481892611</v>
+        <v>1.992030891954196</v>
       </c>
       <c r="F77" t="n" s="0">
-        <v>2.0734670850869773E-13</v>
+        <v>2.3876518653707124E-13</v>
       </c>
       <c r="G77" t="n" s="0">
-        <v>7.219929354718862E-13</v>
+        <v>1.992030891934186</v>
       </c>
       <c r="H77" t="n" s="0">
-        <v>4.176619584185763E-15</v>
+        <v>1.992030892266717</v>
       </c>
       <c r="I77" t="n" s="0">
-        <v>1.1495265314125381E-13</v>
+        <v>8.908723486493791E-14</v>
       </c>
       <c r="J77" t="n" s="0">
-        <v>5.401101186393556E-12</v>
+        <v>4.163238409583214E-11</v>
       </c>
       <c r="K77" t="n" s="0">
-        <v>1.4624415481730107E-12</v>
+        <v>1.2192489960124512E-10</v>
       </c>
       <c r="L77" t="n" s="0">
-        <v>2.0463738937185622E-12</v>
+        <v>1.992030891860338</v>
       </c>
       <c r="M77" t="n" s="0">
-        <v>5.863292989322194E-13</v>
+        <v>4.5839917277672935E-14</v>
       </c>
       <c r="N77" t="n" s="0">
-        <v>1.3846065027446797E-12</v>
+        <v>1.172075796745E-16</v>
       </c>
       <c r="O77" t="n" s="0">
-        <v>2.6425611402185966E-13</v>
+        <v>3.7776499654257927E-13</v>
       </c>
       <c r="P77" t="n" s="0">
-        <v>8.19231756616101E-11</v>
+        <v>9.371698193978799E-12</v>
       </c>
       <c r="Q77" t="n" s="0">
-        <v>1.1148047956068135E-12</v>
+        <v>8.524885343475041E-11</v>
       </c>
       <c r="R77" t="n" s="0">
-        <v>3.935911749130261E-13</v>
+        <v>1.1750927081173539E-13</v>
       </c>
       <c r="S77" t="n" s="0">
-        <v>1.3860334591120736E-14</v>
+        <v>1.408809696158926E-12</v>
       </c>
       <c r="T77" t="n" s="0">
-        <v>0.9980037482485259</v>
+        <v>1.0160904881573538E-12</v>
       </c>
       <c r="U77" t="n" s="0">
-        <v>4.3102399687569713E-13</v>
+        <v>1.1969147547279718E-12</v>
       </c>
       <c r="V77" t="n" s="0">
-        <v>1.4989811535405185E-14</v>
+        <v>2.3965906291580227E-13</v>
       </c>
       <c r="W77" t="n" s="0">
-        <v>2.3384040358359933E-15</v>
+        <v>2.2518457211409417E-14</v>
       </c>
       <c r="X77" t="n" s="0">
-        <v>6.619404430459196E-11</v>
+        <v>4.1093226882390195E-13</v>
       </c>
       <c r="Y77" t="n" s="0">
-        <v>0.9980037483033825</v>
+        <v>1.1285691672506015E-14</v>
       </c>
       <c r="Z77" t="n" s="0">
-        <v>8.114698230119213E-13</v>
+        <v>2.8059984960255902E-14</v>
       </c>
       <c r="AA77" t="n" s="0">
-        <v>1.9870008178726015E-12</v>
+        <v>1.9920308920275251</v>
       </c>
       <c r="AB77" t="n" s="0">
-        <v>1.9920308918666094</v>
+        <v>1.9920308923602401</v>
       </c>
       <c r="AC77" t="n" s="0">
-        <v>6.135200489668948E-13</v>
+        <v>0.9980037481878556</v>
       </c>
       <c r="AD77" t="n" s="0">
-        <v>5.118542678417032E-16</v>
+        <v>2.5533235454208204E-11</v>
       </c>
       <c r="AE77" t="n" s="0">
-        <v>1.33885427045734E-16</v>
+        <v>1.9920308918831104</v>
       </c>
       <c r="AF77" t="n" s="0">
-        <v>1.2171649253002482E-12</v>
+        <v>2.322450051570617E-16</v>
       </c>
     </row>
     <row r="78">
       <c r="C78" t="n" s="0">
-        <v>3.07793218264258E-4</v>
+        <v>3.074901165435902E-4</v>
       </c>
       <c r="D78" t="n" s="0">
-        <v>3.0833127749291587E-4</v>
+        <v>3.0803143769787876E-4</v>
       </c>
       <c r="E78" t="n" s="0">
-        <v>3.076106049162496E-4</v>
+        <v>3.1083191513504106E-4</v>
       </c>
       <c r="F78" t="n" s="0">
-        <v>3.076007897637868E-4</v>
+        <v>3.0756898153689173E-4</v>
       </c>
       <c r="G78" t="n" s="0">
-        <v>3.169394175623251E-4</v>
+        <v>3.0840661088474947E-4</v>
       </c>
       <c r="H78" t="n" s="0">
-        <v>3.0883549457943267E-4</v>
+        <v>3.0879411484532676E-4</v>
       </c>
       <c r="I78" t="n" s="0">
-        <v>3.1874972722545955E-4</v>
+        <v>3.0842839170032416E-4</v>
       </c>
       <c r="J78" t="n" s="0">
-        <v>3.111371325074917E-4</v>
+        <v>3.079456635146053E-4</v>
       </c>
       <c r="K78" t="n" s="0">
-        <v>3.104334945498647E-4</v>
+        <v>0.001596911074392318</v>
       </c>
       <c r="L78" t="n" s="0">
-        <v>4.362206844003856E-4</v>
+        <v>3.076686410928314E-4</v>
       </c>
       <c r="M78" t="n" s="0">
-        <v>3.075434403996906E-4</v>
+        <v>3.0755410706368076E-4</v>
       </c>
       <c r="N78" t="n" s="0">
-        <v>3.078150624469904E-4</v>
+        <v>3.084704240271979E-4</v>
       </c>
       <c r="O78" t="n" s="0">
-        <v>3.0892592253321555E-4</v>
+        <v>3.080544767278245E-4</v>
       </c>
       <c r="P78" t="n" s="0">
-        <v>3.077761948767346E-4</v>
+        <v>3.084194431453558E-4</v>
       </c>
       <c r="Q78" t="n" s="0">
-        <v>3.080317119718721E-4</v>
+        <v>3.0751377513135416E-4</v>
       </c>
       <c r="R78" t="n" s="0">
-        <v>3.0842158742405105E-4</v>
+        <v>3.0859181875706365E-4</v>
       </c>
       <c r="S78" t="n" s="0">
-        <v>3.075913863683601E-4</v>
+        <v>3.2291888079510065E-4</v>
       </c>
       <c r="T78" t="n" s="0">
-        <v>3.0753337533193895E-4</v>
+        <v>3.075815201459618E-4</v>
       </c>
       <c r="U78" t="n" s="0">
-        <v>3.3595051776932677E-4</v>
+        <v>3.0797848667851377E-4</v>
       </c>
       <c r="V78" t="n" s="0">
-        <v>3.0803653266653634E-4</v>
+        <v>3.0885488094999704E-4</v>
       </c>
       <c r="W78" t="n" s="0">
-        <v>3.6682885831828215E-4</v>
+        <v>4.2624980584425425E-4</v>
       </c>
       <c r="X78" t="n" s="0">
-        <v>3.0751886929149383E-4</v>
+        <v>3.0806435835822106E-4</v>
       </c>
       <c r="Y78" t="n" s="0">
-        <v>3.160571124163886E-4</v>
+        <v>3.07761807599319E-4</v>
       </c>
       <c r="Z78" t="n" s="0">
-        <v>3.075418069417646E-4</v>
+        <v>3.075871348593824E-4</v>
       </c>
       <c r="AA78" t="n" s="0">
-        <v>3.0756556755761016E-4</v>
+        <v>3.0771282914942314E-4</v>
       </c>
       <c r="AB78" t="n" s="0">
-        <v>3.0829612578256227E-4</v>
+        <v>3.346710848240032E-4</v>
       </c>
       <c r="AC78" t="n" s="0">
-        <v>3.279214017934949E-4</v>
+        <v>3.974782006806701E-4</v>
       </c>
       <c r="AD78" t="n" s="0">
-        <v>3.076864484134149E-4</v>
+        <v>3.190462342447608E-4</v>
       </c>
       <c r="AE78" t="n" s="0">
-        <v>3.07964230408171E-4</v>
+        <v>3.0824934060471156E-4</v>
       </c>
       <c r="AF78" t="n" s="0">
-        <v>3.0879157468438785E-4</v>
+        <v>3.07823343300612E-4</v>
       </c>
     </row>
     <row r="79">
       <c r="C79" t="n" s="0">
-        <v>-1.0316283079488318</v>
+        <v>-1.0316284221947887</v>
       </c>
       <c r="D79" t="n" s="0">
-        <v>-1.0316282793395608</v>
+        <v>-1.0316284518536087</v>
       </c>
       <c r="E79" t="n" s="0">
-        <v>-1.0316284490419512</v>
+        <v>-1.0316282718857681</v>
       </c>
       <c r="F79" t="n" s="0">
-        <v>-1.0316284496318773</v>
+        <v>-1.0316283794606664</v>
       </c>
       <c r="G79" t="n" s="0">
-        <v>-1.031628449547973</v>
+        <v>-1.0316284419510138</v>
       </c>
       <c r="H79" t="n" s="0">
-        <v>-1.0316284282278738</v>
+        <v>-1.0316282642202754</v>
       </c>
       <c r="I79" t="n" s="0">
-        <v>-1.0316284272086034</v>
+        <v>-1.0316284193581955</v>
       </c>
       <c r="J79" t="n" s="0">
-        <v>-1.0316283947685407</v>
+        <v>-1.0316284171563772</v>
       </c>
       <c r="K79" t="n" s="0">
-        <v>-1.0316284475401383</v>
+        <v>-1.0316284040510884</v>
       </c>
       <c r="L79" t="n" s="0">
-        <v>-1.0316282906288954</v>
+        <v>-1.0316284206366026</v>
       </c>
       <c r="M79" t="n" s="0">
-        <v>-1.03162799482726</v>
+        <v>-1.031628252339094</v>
       </c>
       <c r="N79" t="n" s="0">
-        <v>-1.0316284089339163</v>
+        <v>-1.031628453447273</v>
       </c>
       <c r="O79" t="n" s="0">
-        <v>-1.0316279601432785</v>
+        <v>-1.031628349709469</v>
       </c>
       <c r="P79" t="n" s="0">
-        <v>-1.0316283570696876</v>
+        <v>-1.0316282978014657</v>
       </c>
       <c r="Q79" t="n" s="0">
-        <v>-1.0316283713570138</v>
+        <v>-1.031628371778927</v>
       </c>
       <c r="R79" t="n" s="0">
-        <v>-1.0316284265425213</v>
+        <v>-1.0316284223901808</v>
       </c>
       <c r="S79" t="n" s="0">
-        <v>-1.031628431608373</v>
+        <v>-1.0316283916597864</v>
       </c>
       <c r="T79" t="n" s="0">
-        <v>-1.0316284260486777</v>
+        <v>-1.031628409725293</v>
       </c>
       <c r="U79" t="n" s="0">
-        <v>-1.0316284267654752</v>
+        <v>-1.0316283775483766</v>
       </c>
       <c r="V79" t="n" s="0">
-        <v>-1.0316283926700398</v>
+        <v>-1.0316284517239367</v>
       </c>
       <c r="W79" t="n" s="0">
-        <v>-1.031628361612169</v>
+        <v>-1.0316283798317405</v>
       </c>
       <c r="X79" t="n" s="0">
-        <v>-1.0316284365508672</v>
+        <v>-1.031628434145176</v>
       </c>
       <c r="Y79" t="n" s="0">
-        <v>-1.0316284357995193</v>
+        <v>-1.0316284175183106</v>
       </c>
       <c r="Z79" t="n" s="0">
-        <v>-1.0316278534229755</v>
+        <v>-1.031628298954467</v>
       </c>
       <c r="AA79" t="n" s="0">
-        <v>-1.031628371267836</v>
+        <v>-1.0316284411844754</v>
       </c>
       <c r="AB79" t="n" s="0">
-        <v>-1.0316281115120858</v>
+        <v>-1.031628431759343</v>
       </c>
       <c r="AC79" t="n" s="0">
-        <v>-1.0316284478234619</v>
+        <v>-1.0316284050259674</v>
       </c>
       <c r="AD79" t="n" s="0">
-        <v>-1.0316284270109353</v>
+        <v>-1.0316284511075509</v>
       </c>
       <c r="AE79" t="n" s="0">
-        <v>-1.0316281378635965</v>
+        <v>-1.031628205337966</v>
       </c>
       <c r="AF79" t="n" s="0">
-        <v>-1.0316283951603535</v>
+        <v>-1.0316283520340654</v>
       </c>
     </row>
     <row r="80">
       <c r="C80" t="n" s="0">
-        <v>0.3978978527019983</v>
+        <v>0.39788973040423414</v>
       </c>
       <c r="D80" t="n" s="0">
-        <v>0.39788741117860127</v>
+        <v>0.39788774975476215</v>
       </c>
       <c r="E80" t="n" s="0">
-        <v>0.39788752543685035</v>
+        <v>0.39788763508533975</v>
       </c>
       <c r="F80" t="n" s="0">
-        <v>0.3978878600644311</v>
+        <v>0.3978914228251984</v>
       </c>
       <c r="G80" t="n" s="0">
-        <v>0.397888920380316</v>
+        <v>0.39788794978438347</v>
       </c>
       <c r="H80" t="n" s="0">
-        <v>0.3978900548317288</v>
+        <v>0.3978878035240534</v>
       </c>
       <c r="I80" t="n" s="0">
-        <v>0.39788779286087994</v>
+        <v>0.39791077484419013</v>
       </c>
       <c r="J80" t="n" s="0">
-        <v>0.3978888280403261</v>
+        <v>0.3978886447713954</v>
       </c>
       <c r="K80" t="n" s="0">
-        <v>0.39788943877130123</v>
+        <v>0.3978875848077337</v>
       </c>
       <c r="L80" t="n" s="0">
-        <v>0.39788771674179735</v>
+        <v>0.39788790252276307</v>
       </c>
       <c r="M80" t="n" s="0">
-        <v>0.3978886279713141</v>
+        <v>0.3978930287984017</v>
       </c>
       <c r="N80" t="n" s="0">
-        <v>0.39788885197497414</v>
+        <v>0.397890326454867</v>
       </c>
       <c r="O80" t="n" s="0">
-        <v>0.3978877190435224</v>
+        <v>0.39788756129094693</v>
       </c>
       <c r="P80" t="n" s="0">
-        <v>0.3978892685651534</v>
+        <v>0.39788965986458</v>
       </c>
       <c r="Q80" t="n" s="0">
-        <v>0.39789064594070567</v>
+        <v>0.3978892762345936</v>
       </c>
       <c r="R80" t="n" s="0">
-        <v>0.39788738118709155</v>
+        <v>0.39788985766027274</v>
       </c>
       <c r="S80" t="n" s="0">
-        <v>0.3978874179780032</v>
+        <v>0.39788759117198147</v>
       </c>
       <c r="T80" t="n" s="0">
-        <v>0.3978911196376025</v>
+        <v>0.3978945131845446</v>
       </c>
       <c r="U80" t="n" s="0">
-        <v>0.39788758788853684</v>
+        <v>0.39788796085696454</v>
       </c>
       <c r="V80" t="n" s="0">
-        <v>0.39788890681030153</v>
+        <v>0.39788869549683703</v>
       </c>
       <c r="W80" t="n" s="0">
-        <v>0.3978884922335162</v>
+        <v>0.3978908248354127</v>
       </c>
       <c r="X80" t="n" s="0">
-        <v>0.3978899620985601</v>
+        <v>0.3978879217808924</v>
       </c>
       <c r="Y80" t="n" s="0">
-        <v>0.39788854800643136</v>
+        <v>0.39788860083844035</v>
       </c>
       <c r="Z80" t="n" s="0">
-        <v>0.3978881751975205</v>
+        <v>0.3978906091771748</v>
       </c>
       <c r="AA80" t="n" s="0">
-        <v>0.39788819371105966</v>
+        <v>0.39788743069936316</v>
       </c>
       <c r="AB80" t="n" s="0">
-        <v>0.39789131862520577</v>
+        <v>0.3978875592778728</v>
       </c>
       <c r="AC80" t="n" s="0">
-        <v>0.3978894501046941</v>
+        <v>0.3978916180438521</v>
       </c>
       <c r="AD80" t="n" s="0">
-        <v>0.3978910911790443</v>
+        <v>0.3978873967290948</v>
       </c>
       <c r="AE80" t="n" s="0">
-        <v>0.39788746683243836</v>
+        <v>0.39789151490476193</v>
       </c>
       <c r="AF80" t="n" s="0">
-        <v>0.3978876136901537</v>
+        <v>0.3978874359613318</v>
       </c>
     </row>
     <row r="81">
       <c r="C81" t="n" s="0">
-        <v>3.000136253397829</v>
+        <v>3.0000647376138274</v>
       </c>
       <c r="D81" t="n" s="0">
-        <v>3.0002904736456455</v>
+        <v>3.0000170108855464</v>
       </c>
       <c r="E81" t="n" s="0">
-        <v>3.000008185921409</v>
+        <v>3.0000053973819982</v>
       </c>
       <c r="F81" t="n" s="0">
-        <v>3.000011859692303</v>
+        <v>3.0002034055701463</v>
       </c>
       <c r="G81" t="n" s="0">
-        <v>3.0000025198905456</v>
+        <v>3.000046999186742</v>
       </c>
       <c r="H81" t="n" s="0">
-        <v>3.000040285337383</v>
+        <v>3.000004232957604</v>
       </c>
       <c r="I81" t="n" s="0">
-        <v>3.0000038956422155</v>
+        <v>3.000038593597653</v>
       </c>
       <c r="J81" t="n" s="0">
-        <v>3.000020469937387</v>
+        <v>3.0000065053108225</v>
       </c>
       <c r="K81" t="n" s="0">
-        <v>3.000046425572341</v>
+        <v>3.00000661008756</v>
       </c>
       <c r="L81" t="n" s="0">
-        <v>3.000032984366768</v>
+        <v>3.0000511465123667</v>
       </c>
       <c r="M81" t="n" s="0">
-        <v>3.0000010443416323</v>
+        <v>3.0000026576736354</v>
       </c>
       <c r="N81" t="n" s="0">
-        <v>3.0000145501817714</v>
+        <v>3.000071096195471</v>
       </c>
       <c r="O81" t="n" s="0">
-        <v>3.0000034409075234</v>
+        <v>3.000002347725947</v>
       </c>
       <c r="P81" t="n" s="0">
-        <v>3.0000084260350777</v>
+        <v>3.0000283499576605</v>
       </c>
       <c r="Q81" t="n" s="0">
-        <v>3.0003989699882463</v>
+        <v>3.000011111814517</v>
       </c>
       <c r="R81" t="n" s="0">
-        <v>3.0000025576693385</v>
+        <v>3.000006538757421</v>
       </c>
       <c r="S81" t="n" s="0">
-        <v>3.000000839593826</v>
+        <v>3.0000032139730655</v>
       </c>
       <c r="T81" t="n" s="0">
-        <v>3.0000731085962085</v>
+        <v>3.000019714254903</v>
       </c>
       <c r="U81" t="n" s="0">
-        <v>3.00000615623541</v>
+        <v>3.0000154676610506</v>
       </c>
       <c r="V81" t="n" s="0">
-        <v>3.0000078036768394</v>
+        <v>3.0000093134576313</v>
       </c>
       <c r="W81" t="n" s="0">
-        <v>3.0000090396438845</v>
+        <v>3.0000157969019745</v>
       </c>
       <c r="X81" t="n" s="0">
-        <v>3.00011282120007</v>
+        <v>3.000033136202853</v>
       </c>
       <c r="Y81" t="n" s="0">
-        <v>3.000013918702219</v>
+        <v>3.0000855451421016</v>
       </c>
       <c r="Z81" t="n" s="0">
-        <v>3.000002463977869</v>
+        <v>3.0000068686402916</v>
       </c>
       <c r="AA81" t="n" s="0">
-        <v>3.0000012647248697</v>
+        <v>3.0000082328996904</v>
       </c>
       <c r="AB81" t="n" s="0">
-        <v>3.0000172926690176</v>
+        <v>3.0000007589187803</v>
       </c>
       <c r="AC81" t="n" s="0">
-        <v>3.000085848725756</v>
+        <v>3.0000625662172227</v>
       </c>
       <c r="AD81" t="n" s="0">
-        <v>3.0000020224830823</v>
+        <v>3.000000395435125</v>
       </c>
       <c r="AE81" t="n" s="0">
-        <v>3.000059770604836</v>
+        <v>3.000013491327966</v>
       </c>
       <c r="AF81" t="n" s="0">
-        <v>3.000057464194572</v>
+        <v>3.0000296940543727</v>
       </c>
     </row>
     <row r="82">
       <c r="C82" t="n" s="0">
-        <v>-3.8626264958655048</v>
+        <v>-3.8621361709925703</v>
       </c>
       <c r="D82" t="n" s="0">
-        <v>-3.8613572352967074</v>
+        <v>-3.8627779368999704</v>
       </c>
       <c r="E82" t="n" s="0">
-        <v>-3.862626107244454</v>
+        <v>-3.8625970111682166</v>
       </c>
       <c r="F82" t="n" s="0">
-        <v>-3.8610638947045075</v>
+        <v>-3.862751405705236</v>
       </c>
       <c r="G82" t="n" s="0">
-        <v>-3.862768301636067</v>
+        <v>-3.862746354310872</v>
       </c>
       <c r="H82" t="n" s="0">
-        <v>-3.862761993318091</v>
+        <v>-3.862737971915535</v>
       </c>
       <c r="I82" t="n" s="0">
-        <v>-3.862679025028885</v>
+        <v>-3.862777498427034</v>
       </c>
       <c r="J82" t="n" s="0">
-        <v>-3.862602695304808</v>
+        <v>-3.862448624894747</v>
       </c>
       <c r="K82" t="n" s="0">
-        <v>-3.862610704971748</v>
+        <v>-3.862672015322707</v>
       </c>
       <c r="L82" t="n" s="0">
-        <v>-3.862779020909939</v>
+        <v>-3.8627741632729826</v>
       </c>
       <c r="M82" t="n" s="0">
-        <v>-3.8627645230268897</v>
+        <v>-3.862343617723087</v>
       </c>
       <c r="N82" t="n" s="0">
-        <v>-3.862547892771567</v>
+        <v>-3.8627817211576616</v>
       </c>
       <c r="O82" t="n" s="0">
-        <v>-3.8625314997546907</v>
+        <v>-3.862778736850408</v>
       </c>
       <c r="P82" t="n" s="0">
-        <v>-3.862585115991818</v>
+        <v>-3.8627756732870946</v>
       </c>
       <c r="Q82" t="n" s="0">
-        <v>-3.8626907754584385</v>
+        <v>-3.86270402724686</v>
       </c>
       <c r="R82" t="n" s="0">
-        <v>-3.862759315086644</v>
+        <v>-3.862779168264189</v>
       </c>
       <c r="S82" t="n" s="0">
-        <v>-3.8627768998406533</v>
+        <v>-3.862718821294182</v>
       </c>
       <c r="T82" t="n" s="0">
-        <v>-3.8626609551611977</v>
+        <v>-3.8621878004169803</v>
       </c>
       <c r="U82" t="n" s="0">
-        <v>-3.862466247816157</v>
+        <v>-3.8623708610478595</v>
       </c>
       <c r="V82" t="n" s="0">
-        <v>-3.86275029602903</v>
+        <v>-3.8625750914726362</v>
       </c>
       <c r="W82" t="n" s="0">
-        <v>-3.8626897641879516</v>
+        <v>-3.862738068911289</v>
       </c>
       <c r="X82" t="n" s="0">
-        <v>-3.862758638950541</v>
+        <v>-3.8626718165299327</v>
       </c>
       <c r="Y82" t="n" s="0">
-        <v>-3.8627698387825724</v>
+        <v>-3.862746964308856</v>
       </c>
       <c r="Z82" t="n" s="0">
-        <v>-3.8626921326749413</v>
+        <v>-3.862191010325296</v>
       </c>
       <c r="AA82" t="n" s="0">
-        <v>-3.8626120569269182</v>
+        <v>-3.8626834588056944</v>
       </c>
       <c r="AB82" t="n" s="0">
-        <v>-3.862745945894356</v>
+        <v>-3.8623621406901973</v>
       </c>
       <c r="AC82" t="n" s="0">
-        <v>-3.862657678595419</v>
+        <v>-3.86275273064762</v>
       </c>
       <c r="AD82" t="n" s="0">
-        <v>-3.862769476638541</v>
+        <v>-3.8627115837808343</v>
       </c>
       <c r="AE82" t="n" s="0">
-        <v>-3.862756558059356</v>
+        <v>-3.8627760070016164</v>
       </c>
       <c r="AF82" t="n" s="0">
-        <v>-3.8620468667615224</v>
+        <v>-3.8627580974792535</v>
       </c>
     </row>
     <row r="83">
       <c r="C83" t="n" s="0">
-        <v>-3.3219546426729654</v>
+        <v>-3.321988377780287</v>
       </c>
       <c r="D83" t="n" s="0">
-        <v>-3.32198016026141</v>
+        <v>-3.3219753605528446</v>
       </c>
       <c r="E83" t="n" s="0">
-        <v>-3.3219864598701196</v>
+        <v>-3.3219925494500817</v>
       </c>
       <c r="F83" t="n" s="0">
-        <v>-3.3219906712062848</v>
+        <v>-3.321966688489147</v>
       </c>
       <c r="G83" t="n" s="0">
-        <v>-3.321986936669252</v>
+        <v>-3.3219836786091803</v>
       </c>
       <c r="H83" t="n" s="0">
-        <v>-3.321976689002787</v>
+        <v>-3.321950945628678</v>
       </c>
       <c r="I83" t="n" s="0">
-        <v>-3.3219462900267382</v>
+        <v>-3.3219772960642557</v>
       </c>
       <c r="J83" t="n" s="0">
-        <v>-3.321944186522288</v>
+        <v>-3.3219424171512753</v>
       </c>
       <c r="K83" t="n" s="0">
-        <v>-3.321945479388929</v>
+        <v>-3.3219558247797907</v>
       </c>
       <c r="L83" t="n" s="0">
-        <v>-3.321991994132544</v>
+        <v>-3.3219831861356517</v>
       </c>
       <c r="M83" t="n" s="0">
-        <v>-3.321975917986641</v>
+        <v>-3.3219538294326214</v>
       </c>
       <c r="N83" t="n" s="0">
-        <v>-3.321980513007058</v>
+        <v>-3.321937091028231</v>
       </c>
       <c r="O83" t="n" s="0">
-        <v>-3.3219644824303565</v>
+        <v>-3.321987447846795</v>
       </c>
       <c r="P83" t="n" s="0">
-        <v>-3.32197075476224</v>
+        <v>-3.3219651774001258</v>
       </c>
       <c r="Q83" t="n" s="0">
-        <v>-3.321931559356777</v>
+        <v>-3.3219674395157353</v>
       </c>
       <c r="R83" t="n" s="0">
-        <v>-3.321974843739886</v>
+        <v>-3.3219630512662297</v>
       </c>
       <c r="S83" t="n" s="0">
-        <v>-3.3219924831741223</v>
+        <v>-3.321983986715303</v>
       </c>
       <c r="T83" t="n" s="0">
-        <v>-3.3219680696881104</v>
+        <v>-3.3219823810674227</v>
       </c>
       <c r="U83" t="n" s="0">
-        <v>-3.321992094339995</v>
+        <v>-3.3219890586051077</v>
       </c>
       <c r="V83" t="n" s="0">
-        <v>-3.3219873129216833</v>
+        <v>-3.321955427054053</v>
       </c>
       <c r="W83" t="n" s="0">
-        <v>-3.3219836283294346</v>
+        <v>-3.321965123635389</v>
       </c>
       <c r="X83" t="n" s="0">
-        <v>-3.3219214432176654</v>
+        <v>-3.321982539912525</v>
       </c>
       <c r="Y83" t="n" s="0">
-        <v>-3.3219832875388957</v>
+        <v>-3.3219845769492906</v>
       </c>
       <c r="Z83" t="n" s="0">
-        <v>-3.321973752689322</v>
+        <v>-3.3219341766563066</v>
       </c>
       <c r="AA83" t="n" s="0">
-        <v>-3.321984361230689</v>
+        <v>-3.321976936916893</v>
       </c>
       <c r="AB83" t="n" s="0">
-        <v>-3.3219234862111375</v>
+        <v>-3.321991267505781</v>
       </c>
       <c r="AC83" t="n" s="0">
-        <v>-3.3219840389481456</v>
+        <v>-3.3219670843074156</v>
       </c>
       <c r="AD83" t="n" s="0">
-        <v>-3.321933127058405</v>
+        <v>-3.321973662331724</v>
       </c>
       <c r="AE83" t="n" s="0">
-        <v>-3.3219676652866594</v>
+        <v>-3.3219863232608797</v>
       </c>
       <c r="AF83" t="n" s="0">
-        <v>-3.3219874067520525</v>
+        <v>-3.321984001483755</v>
       </c>
     </row>
     <row r="84">
       <c r="C84" t="n" s="0">
-        <v>-10.151430121773409</v>
+        <v>-10.152600036771506</v>
       </c>
       <c r="D84" t="n" s="0">
-        <v>-10.151766071609222</v>
+        <v>-10.151524883797514</v>
       </c>
       <c r="E84" t="n" s="0">
-        <v>-10.15296555188321</v>
+        <v>-10.152572215567066</v>
       </c>
       <c r="F84" t="n" s="0">
-        <v>-10.15245111235019</v>
+        <v>-10.151276159354584</v>
       </c>
       <c r="G84" t="n" s="0">
-        <v>-10.15061201464068</v>
+        <v>-10.150551124775005</v>
       </c>
       <c r="H84" t="n" s="0">
-        <v>-10.145811599753904</v>
+        <v>-10.151933984896356</v>
       </c>
       <c r="I84" t="n" s="0">
-        <v>-10.151217179734797</v>
+        <v>-10.150895558115554</v>
       </c>
       <c r="J84" t="n" s="0">
-        <v>-10.152274885871366</v>
+        <v>-10.151769955534927</v>
       </c>
       <c r="K84" t="n" s="0">
-        <v>-10.152569391329061</v>
+        <v>-10.152051370144445</v>
       </c>
       <c r="L84" t="n" s="0">
-        <v>-10.152915827731542</v>
+        <v>-10.151157646651058</v>
       </c>
       <c r="M84" t="n" s="0">
-        <v>-10.15146872535966</v>
+        <v>-10.145277152423432</v>
       </c>
       <c r="N84" t="n" s="0">
-        <v>-10.151622225031302</v>
+        <v>-10.151756551037273</v>
       </c>
       <c r="O84" t="n" s="0">
-        <v>-10.1520322620371</v>
+        <v>-10.1527964697483</v>
       </c>
       <c r="P84" t="n" s="0">
-        <v>-10.151283357264525</v>
+        <v>-10.152272170611413</v>
       </c>
       <c r="Q84" t="n" s="0">
-        <v>-10.152201274783627</v>
+        <v>-10.152811014372768</v>
       </c>
       <c r="R84" t="n" s="0">
-        <v>-10.151803625269103</v>
+        <v>-10.152060178897603</v>
       </c>
       <c r="S84" t="n" s="0">
-        <v>-10.151700345958789</v>
+        <v>-10.152605264429637</v>
       </c>
       <c r="T84" t="n" s="0">
-        <v>-10.152987440604061</v>
+        <v>-10.151877788997039</v>
       </c>
       <c r="U84" t="n" s="0">
-        <v>-10.152827261831083</v>
+        <v>-10.15282640836395</v>
       </c>
       <c r="V84" t="n" s="0">
-        <v>-10.148990600684808</v>
+        <v>-10.152230087248993</v>
       </c>
       <c r="W84" t="n" s="0">
-        <v>-10.152668843761692</v>
+        <v>-5.099024612563444</v>
       </c>
       <c r="X84" t="n" s="0">
-        <v>-10.153038955355179</v>
+        <v>-10.151806439221442</v>
       </c>
       <c r="Y84" t="n" s="0">
-        <v>-10.152401392251695</v>
+        <v>-10.15212913783032</v>
       </c>
       <c r="Z84" t="n" s="0">
-        <v>-10.152492327697377</v>
+        <v>-10.152628345603246</v>
       </c>
       <c r="AA84" t="n" s="0">
-        <v>-10.150687257870997</v>
+        <v>-10.14752399179401</v>
       </c>
       <c r="AB84" t="n" s="0">
-        <v>-10.15189330201634</v>
+        <v>-10.151323467858814</v>
       </c>
       <c r="AC84" t="n" s="0">
-        <v>-10.150993333415927</v>
+        <v>-10.152110152359782</v>
       </c>
       <c r="AD84" t="n" s="0">
-        <v>-10.151817529581596</v>
+        <v>-10.15255840890058</v>
       </c>
       <c r="AE84" t="n" s="0">
-        <v>-10.152304877249591</v>
+        <v>-10.15220417659033</v>
       </c>
       <c r="AF84" t="n" s="0">
-        <v>-10.151019256384103</v>
+        <v>-10.150994352150077</v>
       </c>
     </row>
     <row r="85">
       <c r="C85" t="n" s="0">
-        <v>-10.402136445728587</v>
+        <v>-10.399857230469754</v>
       </c>
       <c r="D85" t="n" s="0">
-        <v>-10.398496870568854</v>
+        <v>-10.397991731606828</v>
       </c>
       <c r="E85" t="n" s="0">
-        <v>-10.40146395284373</v>
+        <v>-10.400457249002704</v>
       </c>
       <c r="F85" t="n" s="0">
-        <v>-10.400219704646997</v>
+        <v>-10.400107738087288</v>
       </c>
       <c r="G85" t="n" s="0">
-        <v>-10.402667717289308</v>
+        <v>-10.40102748141713</v>
       </c>
       <c r="H85" t="n" s="0">
-        <v>-10.399892707458491</v>
+        <v>-10.402522060029334</v>
       </c>
       <c r="I85" t="n" s="0">
-        <v>-10.39914302923322</v>
+        <v>-10.40264479808204</v>
       </c>
       <c r="J85" t="n" s="0">
-        <v>-10.399606527268904</v>
+        <v>-10.398282213984286</v>
       </c>
       <c r="K85" t="n" s="0">
-        <v>-10.401625788627758</v>
+        <v>-10.396620709869973</v>
       </c>
       <c r="L85" t="n" s="0">
-        <v>-10.401163156713697</v>
+        <v>-10.401842371713139</v>
       </c>
       <c r="M85" t="n" s="0">
-        <v>-10.402626298951029</v>
+        <v>-5.123451751619901</v>
       </c>
       <c r="N85" t="n" s="0">
-        <v>-10.401368480485955</v>
+        <v>-10.402613469117385</v>
       </c>
       <c r="O85" t="n" s="0">
-        <v>-10.402736115382698</v>
+        <v>-10.402161612067657</v>
       </c>
       <c r="P85" t="n" s="0">
-        <v>-10.402408070674744</v>
+        <v>-10.397129627937547</v>
       </c>
       <c r="Q85" t="n" s="0">
-        <v>-10.401981416268928</v>
+        <v>-10.401695326647028</v>
       </c>
       <c r="R85" t="n" s="0">
-        <v>-10.398129649981556</v>
+        <v>-10.402812925755779</v>
       </c>
       <c r="S85" t="n" s="0">
-        <v>-10.399946356722998</v>
+        <v>-10.402618403132191</v>
       </c>
       <c r="T85" t="n" s="0">
-        <v>-10.40140019432413</v>
+        <v>-10.401222629148057</v>
       </c>
       <c r="U85" t="n" s="0">
-        <v>-10.400923061133486</v>
+        <v>-10.402765667508312</v>
       </c>
       <c r="V85" t="n" s="0">
-        <v>-10.401043371226251</v>
+        <v>-10.402444506031328</v>
       </c>
       <c r="W85" t="n" s="0">
-        <v>-10.40224995461115</v>
+        <v>-10.401305121761052</v>
       </c>
       <c r="X85" t="n" s="0">
-        <v>-10.400140878712712</v>
+        <v>-10.402619945434154</v>
       </c>
       <c r="Y85" t="n" s="0">
-        <v>-10.401545478334977</v>
+        <v>-10.401292536637737</v>
       </c>
       <c r="Z85" t="n" s="0">
-        <v>-10.401901666645495</v>
+        <v>-10.401800631502823</v>
       </c>
       <c r="AA85" t="n" s="0">
-        <v>-10.400598970933606</v>
+        <v>-10.402509410257341</v>
       </c>
       <c r="AB85" t="n" s="0">
-        <v>-10.402165427191454</v>
+        <v>-10.402254110912647</v>
       </c>
       <c r="AC85" t="n" s="0">
-        <v>-10.400125763623084</v>
+        <v>-10.402674979229362</v>
       </c>
       <c r="AD85" t="n" s="0">
-        <v>-10.400781489227507</v>
+        <v>-10.4010870082656</v>
       </c>
       <c r="AE85" t="n" s="0">
-        <v>-5.12780210427458</v>
+        <v>-5.127884182714614</v>
       </c>
       <c r="AF85" t="n" s="0">
-        <v>-10.399304675243197</v>
+        <v>-10.40202026794173</v>
       </c>
     </row>
     <row r="86">
       <c r="C86" t="n" s="0">
-        <v>-5.172367369727749</v>
+        <v>-10.534667662971675</v>
       </c>
       <c r="D86" t="n" s="0">
-        <v>-10.535757941247624</v>
+        <v>-10.535986163766212</v>
       </c>
       <c r="E86" t="n" s="0">
-        <v>-10.535996971686503</v>
+        <v>-10.536324404905685</v>
       </c>
       <c r="F86" t="n" s="0">
-        <v>-10.531014055433841</v>
+        <v>-10.534137132338575</v>
       </c>
       <c r="G86" t="n" s="0">
-        <v>-10.53535691752018</v>
+        <v>-10.531699191402724</v>
       </c>
       <c r="H86" t="n" s="0">
-        <v>-10.535184070335934</v>
+        <v>-10.536054948297524</v>
       </c>
       <c r="I86" t="n" s="0">
-        <v>-10.535894567418502</v>
+        <v>-10.53468794185962</v>
       </c>
       <c r="J86" t="n" s="0">
-        <v>-10.535554533834988</v>
+        <v>-10.532177245345121</v>
       </c>
       <c r="K86" t="n" s="0">
-        <v>-10.531739129662101</v>
+        <v>-10.535891293141109</v>
       </c>
       <c r="L86" t="n" s="0">
-        <v>-10.536241407168779</v>
+        <v>-10.534011449418326</v>
       </c>
       <c r="M86" t="n" s="0">
-        <v>-10.535882940352334</v>
+        <v>-10.534450319063726</v>
       </c>
       <c r="N86" t="n" s="0">
-        <v>-10.534822266118193</v>
+        <v>-10.535937942046099</v>
       </c>
       <c r="O86" t="n" s="0">
-        <v>-10.535055821061448</v>
+        <v>-10.533676053170538</v>
       </c>
       <c r="P86" t="n" s="0">
-        <v>-10.53493416004627</v>
+        <v>-10.535513061713734</v>
       </c>
       <c r="Q86" t="n" s="0">
-        <v>-10.531113027969385</v>
+        <v>-10.534967677652473</v>
       </c>
       <c r="R86" t="n" s="0">
-        <v>-10.535949771089472</v>
+        <v>-10.536210638743546</v>
       </c>
       <c r="S86" t="n" s="0">
-        <v>-10.533258245203863</v>
+        <v>-10.535469635873577</v>
       </c>
       <c r="T86" t="n" s="0">
-        <v>-10.534785826498425</v>
+        <v>-10.536315377441532</v>
       </c>
       <c r="U86" t="n" s="0">
-        <v>-5.173755041985378</v>
+        <v>-10.534051134612207</v>
       </c>
       <c r="V86" t="n" s="0">
-        <v>-10.53534990022372</v>
+        <v>-10.535956473749042</v>
       </c>
       <c r="W86" t="n" s="0">
-        <v>-10.536095891008175</v>
+        <v>-10.535907978941552</v>
       </c>
       <c r="X86" t="n" s="0">
-        <v>-10.535027348747288</v>
+        <v>-10.535795560646596</v>
       </c>
       <c r="Y86" t="n" s="0">
-        <v>-10.535956551704405</v>
+        <v>-5.174893536205535</v>
       </c>
       <c r="Z86" t="n" s="0">
-        <v>-10.535360650544197</v>
+        <v>-10.536105601416812</v>
       </c>
       <c r="AA86" t="n" s="0">
-        <v>-10.53321981799693</v>
+        <v>-10.53540137263511</v>
       </c>
       <c r="AB86" t="n" s="0">
-        <v>-10.535547176794314</v>
+        <v>-10.53593285700811</v>
       </c>
       <c r="AC86" t="n" s="0">
-        <v>-10.5351807628564</v>
+        <v>-10.535331736733172</v>
       </c>
       <c r="AD86" t="n" s="0">
-        <v>-10.535901484656035</v>
+        <v>-10.534305573417765</v>
       </c>
       <c r="AE86" t="n" s="0">
-        <v>-10.535102837627557</v>
+        <v>-10.533611540361914</v>
       </c>
       <c r="AF86" t="n" s="0">
-        <v>-10.535956630464387</v>
+        <v>-10.535649970940833</v>
       </c>
     </row>
   </sheetData>

--- a/tonghop.xlsx
+++ b/tonghop.xlsx
@@ -13,7 +13,7 @@
 </file>
 
 <file path=xl/sharedStrings.xml><?xml version="1.0" encoding="utf-8"?>
-<sst xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" count="63" uniqueCount="3">
+<sst xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" count="45" uniqueCount="3">
   <si>
     <t>N = 40</t>
   </si>
@@ -86,162 +86,162 @@
     </row>
     <row r="10">
       <c r="B10" t="n" s="0">
-        <v>2.9177517341774225E-42</v>
+        <v>9.81362429068405E-42</v>
       </c>
       <c r="C10" t="n" s="0">
-        <v>7.089653071007392E-42</v>
+        <v>3.361151824300803E-41</v>
       </c>
       <c r="D10" t="n" s="0">
-        <v>2.2131917145449553</v>
+        <v>2.8641251833428423</v>
       </c>
       <c r="E10" t="n" s="0">
-        <v>5.178013628769972</v>
+        <v>3.1449210724492405</v>
       </c>
       <c r="F10" t="n" s="0">
-        <v>1.724454052270313E-31</v>
+        <v>1.6092111552395564E-31</v>
       </c>
       <c r="G10" t="n" s="0">
-        <v>3.490619011033126E-31</v>
+        <v>4.89766532996706E-31</v>
       </c>
     </row>
     <row r="11">
       <c r="B11" t="n" s="0">
-        <v>1.0276298862925235E-24</v>
+        <v>5.004707992415383E-25</v>
       </c>
       <c r="C11" t="n" s="0">
-        <v>3.049141996396935E-24</v>
+        <v>6.724916374361237E-25</v>
       </c>
       <c r="D11" t="n" s="0">
-        <v>1.454504096797602</v>
+        <v>1.4051602951325874</v>
       </c>
       <c r="E11" t="n" s="0">
-        <v>1.7880175461906482</v>
+        <v>1.0968572961696383</v>
       </c>
       <c r="F11" t="n" s="0">
-        <v>7.70012145688017E-19</v>
+        <v>7.905532314668865E-19</v>
       </c>
       <c r="G11" t="n" s="0">
-        <v>7.888619733545883E-19</v>
+        <v>9.61747181270983E-19</v>
       </c>
     </row>
     <row r="12">
       <c r="B12" t="n" s="0">
-        <v>1.8526002261762448E-17</v>
+        <v>2.3886786954333466E-18</v>
       </c>
       <c r="C12" t="n" s="0">
-        <v>9.960138280350122E-17</v>
+        <v>9.205912042312339E-18</v>
       </c>
       <c r="D12" t="n" s="0">
-        <v>224.6661711797245</v>
+        <v>343.2857497536533</v>
       </c>
       <c r="E12" t="n" s="0">
-        <v>250.58130789597507</v>
+        <v>740.1205158352815</v>
       </c>
       <c r="F12" t="n" s="0">
-        <v>1.3671916693888264E-13</v>
+        <v>1.604967706709874E-14</v>
       </c>
       <c r="G12" t="n" s="0">
-        <v>5.595571762905442E-13</v>
+        <v>3.916880700852916E-14</v>
       </c>
     </row>
     <row r="13">
       <c r="B13" t="n" s="0">
-        <v>1.0607411328021336E-13</v>
+        <v>1.6653816980282426E-13</v>
       </c>
       <c r="C13" t="n" s="0">
-        <v>1.2908875993460818E-13</v>
+        <v>2.6674041582009146E-13</v>
       </c>
       <c r="D13" t="n" s="0">
-        <v>3.684960789305568</v>
+        <v>2.5058759148443945</v>
       </c>
       <c r="E13" t="n" s="0">
-        <v>6.762120840002016</v>
+        <v>2.0580071313367982</v>
       </c>
       <c r="F13" t="n" s="0">
-        <v>4.349289616484926E-10</v>
+        <v>5.767338472516947E-10</v>
       </c>
       <c r="G13" t="n" s="0">
-        <v>7.448081397331155E-10</v>
+        <v>1.467425971097447E-9</v>
       </c>
     </row>
     <row r="14">
       <c r="B14" t="n" s="0">
-        <v>6.966797840015383</v>
+        <v>6.896208615852859</v>
       </c>
       <c r="C14" t="n" s="0">
-        <v>0.5363160884258577</v>
+        <v>0.509466027374127</v>
       </c>
       <c r="D14" t="n" s="0">
-        <v>5596.967481243784</v>
+        <v>209.06166785389394</v>
       </c>
       <c r="E14" t="n" s="0">
-        <v>19344.626969838264</v>
+        <v>286.83874804952933</v>
       </c>
       <c r="F14" t="n" s="0">
-        <v>6.241684912162886</v>
+        <v>6.338347546214894</v>
       </c>
       <c r="G14" t="n" s="0">
-        <v>0.25434322500567635</v>
+        <v>0.3218499441345193</v>
       </c>
     </row>
     <row r="15">
       <c r="B15" t="n" s="0">
-        <v>0.008333033692900544</v>
+        <v>3.418591151775146E-6</v>
       </c>
       <c r="C15" t="n" s="0">
-        <v>0.04562781688610472</v>
+        <v>1.3199165755746752E-6</v>
       </c>
       <c r="D15" t="n" s="0">
-        <v>7.491703175796101</v>
+        <v>10.370568107410946</v>
       </c>
       <c r="E15" t="n" s="0">
-        <v>18.333566454128015</v>
+        <v>47.682506013871006</v>
       </c>
       <c r="F15" t="n" s="0">
-        <v>5.002207093377064E-6</v>
+        <v>3.93724834784541E-6</v>
       </c>
       <c r="G15" t="n" s="0">
-        <v>2.948276877432131E-6</v>
+        <v>1.9890598887963447E-6</v>
       </c>
     </row>
     <row r="16">
       <c r="B16" t="n" s="0">
-        <v>0.5394220925013808</v>
+        <v>0.47803884410159375</v>
       </c>
       <c r="C16" t="n" s="0">
-        <v>0.28431630217448756</v>
+        <v>0.30869427416523315</v>
       </c>
       <c r="D16" t="n" s="0">
-        <v>0.029771540100975356</v>
+        <v>0.030332053732468202</v>
       </c>
       <c r="E16" t="n" s="0">
-        <v>0.02834745446404371</v>
+        <v>0.022606531658903792</v>
       </c>
       <c r="F16" t="n" s="0">
-        <v>0.4571970554841536</v>
+        <v>0.4786925609674597</v>
       </c>
       <c r="G16" t="n" s="0">
-        <v>0.2889649034038536</v>
+        <v>0.27954169816224766</v>
       </c>
     </row>
     <row r="17">
       <c r="B17" t="n" s="0">
-        <v>-611.174938030123</v>
+        <v>-659.36114917496</v>
       </c>
       <c r="C17" t="n" s="0">
-        <v>153.73190148520112</v>
+        <v>121.27182389875391</v>
       </c>
       <c r="D17" t="n" s="0">
-        <v>-2893.486413627907</v>
+        <v>-2914.6818154067546</v>
       </c>
       <c r="E17" t="n" s="0">
-        <v>403.1176254836665</v>
+        <v>484.2755654532459</v>
       </c>
       <c r="F17" t="n" s="0">
-        <v>-2556.2319453525074</v>
+        <v>-2581.4978054474764</v>
       </c>
       <c r="G17" t="n" s="0">
-        <v>330.2041947785638</v>
+        <v>351.9133029670419</v>
       </c>
     </row>
     <row r="18">
@@ -252,318 +252,318 @@
         <v>0.0</v>
       </c>
       <c r="D18" t="n" s="0">
-        <v>28.362379246292335</v>
+        <v>31.16537813770562</v>
       </c>
       <c r="E18" t="n" s="0">
-        <v>14.387861409370057</v>
+        <v>14.688846464999498</v>
       </c>
       <c r="F18" t="n" s="0">
-        <v>4.144832625267251E-16</v>
+        <v>0.0</v>
       </c>
       <c r="G18" t="n" s="0">
-        <v>1.7256080763143042E-15</v>
+        <v>0.0</v>
       </c>
     </row>
     <row r="19">
       <c r="B19" t="n" s="0">
-        <v>3.4046839421838135E-15</v>
+        <v>3.641531520770513E-15</v>
       </c>
       <c r="C19" t="n" s="0">
-        <v>1.3466526446473342E-15</v>
+        <v>1.0840344679840707E-15</v>
       </c>
       <c r="D19" t="n" s="0">
-        <v>3.177974736807275</v>
+        <v>3.9126361059709756</v>
       </c>
       <c r="E19" t="n" s="0">
-        <v>2.4807037405367973</v>
+        <v>4.331872900478235</v>
       </c>
       <c r="F19" t="n" s="0">
-        <v>7.431092778157715E-15</v>
+        <v>6.8389738316909644E-15</v>
       </c>
       <c r="G19" t="n" s="0">
-        <v>2.8731395141844268E-15</v>
+        <v>2.1680689359681413E-15</v>
       </c>
     </row>
     <row r="20">
       <c r="B20" t="n" s="0">
-        <v>0.008318953226763244</v>
+        <v>0.009355815899494475</v>
       </c>
       <c r="C20" t="n" s="0">
-        <v>0.010193810432926829</v>
+        <v>0.011048384233869842</v>
       </c>
       <c r="D20" t="n" s="0">
-        <v>0.46424115720296355</v>
+        <v>0.4965105332910325</v>
       </c>
       <c r="E20" t="n" s="0">
-        <v>0.3038035190587179</v>
+        <v>0.34038771568142046</v>
       </c>
       <c r="F20" t="n" s="0">
-        <v>0.01017833001643839</v>
+        <v>0.006917053967802382</v>
       </c>
       <c r="G20" t="n" s="0">
-        <v>0.016075103840624848</v>
+        <v>0.008261169443653437</v>
       </c>
     </row>
     <row r="21">
       <c r="B21" t="n" s="0">
-        <v>0.005339819468094124</v>
+        <v>0.0032629849362122722</v>
       </c>
       <c r="C21" t="n" s="0">
-        <v>0.010449406698155719</v>
+        <v>0.0074173867450130215</v>
       </c>
       <c r="D21" t="n" s="0">
-        <v>1.938606493806445</v>
+        <v>2.1406083253907826</v>
       </c>
       <c r="E21" t="n" s="0">
-        <v>1.778542332717744</v>
+        <v>3.7313099968073598</v>
       </c>
       <c r="F21" t="n" s="0">
-        <v>3.394652849368371E-6</v>
+        <v>6.708935512090463E-4</v>
       </c>
       <c r="G21" t="n" s="0">
-        <v>2.3662041523315276E-6</v>
+        <v>0.0036540691013980772</v>
       </c>
     </row>
     <row r="22">
       <c r="B22" t="n" s="0">
-        <v>0.01617509140956585</v>
+        <v>0.01213327412330909</v>
       </c>
       <c r="C22" t="n" s="0">
-        <v>0.041908587178452486</v>
+        <v>0.048793114068164396</v>
       </c>
       <c r="D22" t="n" s="0">
-        <v>1.7601071735540819</v>
+        <v>0.9549306453024619</v>
       </c>
       <c r="E22" t="n" s="0">
-        <v>3.914136932321208</v>
+        <v>1.949743692679735</v>
       </c>
       <c r="F22" t="n" s="0">
-        <v>2.5504320041164948E-5</v>
+        <v>0.006559240651184046</v>
       </c>
       <c r="G22" t="n" s="0">
-        <v>1.7556825717330505E-5</v>
+        <v>0.025620240626401402</v>
       </c>
     </row>
     <row r="23">
       <c r="B23" t="n" s="0">
-        <v>9.321614363840341</v>
+        <v>7.641006518420377</v>
       </c>
       <c r="C23" t="n" s="0">
-        <v>4.132998401597906</v>
+        <v>4.474501751527129</v>
       </c>
       <c r="D23" t="n" s="0">
-        <v>0.5969512887758069</v>
+        <v>0.9933826609434998</v>
       </c>
       <c r="E23" t="n" s="0">
-        <v>1.0948597398062632</v>
+        <v>1.5414038744592573</v>
       </c>
       <c r="F23" t="n" s="0">
-        <v>0.4980739997587698</v>
+        <v>0.16620140455918517</v>
       </c>
       <c r="G23" t="n" s="0">
-        <v>0.8576429151689016</v>
+        <v>0.4596675827525284</v>
       </c>
     </row>
     <row r="24">
       <c r="B24" t="n" s="0">
-        <v>5.071046864729419E-4</v>
+        <v>4.851439931564325E-4</v>
       </c>
       <c r="C24" t="n" s="0">
-        <v>2.4284193845324406E-4</v>
+        <v>1.281972946418297E-4</v>
       </c>
       <c r="D24" t="n" s="0">
-        <v>0.006646706505048757</v>
+        <v>0.0062047147220433705</v>
       </c>
       <c r="E24" t="n" s="0">
-        <v>0.008401845767439277</v>
+        <v>0.008121308506072109</v>
       </c>
       <c r="F24" t="n" s="0">
-        <v>3.597552966743655E-4</v>
+        <v>3.1691498562194854E-4</v>
       </c>
       <c r="G24" t="n" s="0">
-        <v>2.3518084000811746E-4</v>
+        <v>2.5579917990260454E-5</v>
       </c>
     </row>
     <row r="25">
       <c r="B25" t="n" s="0">
-        <v>-1.0316283776263817</v>
+        <v>-1.031628384747976</v>
       </c>
       <c r="C25" t="n" s="0">
-        <v>8.527769332519992E-8</v>
+        <v>8.169860778140706E-8</v>
       </c>
       <c r="D25" t="n" s="0">
-        <v>-1.0316284534663454</v>
+        <v>-1.0316284534898466</v>
       </c>
       <c r="E25" t="n" s="0">
-        <v>1.288684039502953E-10</v>
+        <v>1.5955510587602435E-13</v>
       </c>
       <c r="F25" t="n" s="0">
-        <v>-1.0316283829263748</v>
+        <v>-1.0316283365958094</v>
       </c>
       <c r="G25" t="n" s="0">
-        <v>6.758898388035616E-8</v>
+        <v>1.6057204559107025E-7</v>
       </c>
     </row>
     <row r="26">
       <c r="B26" t="n" s="0">
-        <v>0.3978884908729379</v>
+        <v>0.3978888189235601</v>
       </c>
       <c r="C26" t="n" s="0">
-        <v>8.880305698560583E-7</v>
+        <v>1.3801924494954916E-6</v>
       </c>
       <c r="D26" t="n" s="0">
-        <v>0.39788735772973877</v>
+        <v>0.397887357729741</v>
       </c>
       <c r="E26" t="n" s="0">
-        <v>2.9257389466589586E-15</v>
+        <v>1.556721547335102E-14</v>
       </c>
       <c r="F26" t="n" s="0">
-        <v>0.3978898860528747</v>
+        <v>0.397889041322802</v>
       </c>
       <c r="G26" t="n" s="0">
-        <v>4.3593914417514265E-6</v>
+        <v>2.0502810458781845E-6</v>
       </c>
     </row>
     <row r="27">
       <c r="B27" t="n" s="0">
-        <v>3.0008907188891665</v>
+        <v>3.0008671462336705</v>
       </c>
       <c r="C27" t="n" s="0">
-        <v>0.0022227405692715066</v>
+        <v>0.0017571963580759482</v>
       </c>
       <c r="D27" t="n" s="0">
-        <v>2.9999999999999125</v>
+        <v>3.0000000077417943</v>
       </c>
       <c r="E27" t="n" s="0">
-        <v>7.42920327257848E-15</v>
+        <v>4.2404003613993165E-8</v>
       </c>
       <c r="F27" t="n" s="0">
-        <v>3.000029031210531</v>
+        <v>3.0000490719185295</v>
       </c>
       <c r="G27" t="n" s="0">
-        <v>4.0487927392878346E-5</v>
+        <v>8.880351707411086E-5</v>
       </c>
     </row>
     <row r="28">
       <c r="B28" t="n" s="0">
-        <v>-3.861220769942824</v>
+        <v>-3.8618432336684925</v>
       </c>
       <c r="C28" t="n" s="0">
-        <v>0.001840863511305315</v>
+        <v>9.767559035457989E-4</v>
       </c>
       <c r="D28" t="n" s="0">
-        <v>-3.8607971066960953</v>
+        <v>-3.8626919722215507</v>
       </c>
       <c r="E28" t="n" s="0">
-        <v>0.009910303284647827</v>
+        <v>2.077993298434464E-4</v>
       </c>
       <c r="F28" t="n" s="0">
-        <v>-3.8626275516717135</v>
+        <v>-3.8625635984229976</v>
       </c>
       <c r="G28" t="n" s="0">
-        <v>2.0234624687636593E-4</v>
+        <v>3.96407251143115E-4</v>
       </c>
     </row>
     <row r="29">
       <c r="B29" t="n" s="0">
-        <v>-3.3219743546827103</v>
+        <v>-3.321974607042488</v>
       </c>
       <c r="C29" t="n" s="0">
-        <v>2.0123054782094338E-5</v>
+        <v>1.875496818488766E-5</v>
       </c>
       <c r="D29" t="n" s="0">
-        <v>-3.25219621624131</v>
+        <v>-3.2095738045716478</v>
       </c>
       <c r="E29" t="n" s="0">
-        <v>0.09235360697808004</v>
+        <v>0.18297645469284413</v>
       </c>
       <c r="F29" t="n" s="0">
-        <v>-3.3219715635844267</v>
+        <v>-3.3219694579474197</v>
       </c>
       <c r="G29" t="n" s="0">
-        <v>1.6468153376083595E-5</v>
+        <v>2.1669514223522357E-5</v>
       </c>
     </row>
     <row r="30">
       <c r="B30" t="n" s="0">
-        <v>-10.151876610777917</v>
+        <v>-10.151685006867076</v>
       </c>
       <c r="C30" t="n" s="0">
-        <v>5.011551331872219E-4</v>
+        <v>0.0010220123114191835</v>
       </c>
       <c r="D30" t="n" s="0">
-        <v>-7.293880151702999</v>
+        <v>-7.376573830628411</v>
       </c>
       <c r="E30" t="n" s="0">
-        <v>2.7872243471395115</v>
+        <v>2.910944917321862</v>
       </c>
       <c r="F30" t="n" s="0">
-        <v>-9.983171636887015</v>
+        <v>-10.151674931702868</v>
       </c>
       <c r="G30" t="n" s="0">
-        <v>0.9224694251014163</v>
+        <v>0.001414336558295026</v>
       </c>
     </row>
     <row r="31">
       <c r="B31" t="n" s="0">
-        <v>-10.1789955375105</v>
+        <v>-10.401579255538703</v>
       </c>
       <c r="C31" t="n" s="0">
-        <v>1.2191196529184254</v>
+        <v>9.304719892030189E-4</v>
       </c>
       <c r="D31" t="n" s="0">
-        <v>-7.334027911838926</v>
+        <v>-7.624843612221154</v>
       </c>
       <c r="E31" t="n" s="0">
-        <v>2.7624552737467964</v>
+        <v>3.114301261693909</v>
       </c>
       <c r="F31" t="n" s="0">
-        <v>-10.049523923262825</v>
+        <v>-10.225186510810968</v>
       </c>
       <c r="G31" t="n" s="0">
-        <v>1.3384536681122108</v>
+        <v>0.9627430213373406</v>
       </c>
     </row>
     <row r="32">
       <c r="B32" t="n" s="0">
-        <v>-10.535124793802646</v>
+        <v>-10.53481049515502</v>
       </c>
       <c r="C32" t="n" s="0">
-        <v>9.97593699718798E-4</v>
+        <v>8.012968584440353E-4</v>
       </c>
       <c r="D32" t="n" s="0">
-        <v>-7.56755310086818</v>
+        <v>-6.278723007996278</v>
       </c>
       <c r="E32" t="n" s="0">
-        <v>3.327355022128981</v>
+        <v>2.7881527111296407</v>
       </c>
       <c r="F32" t="n" s="0">
-        <v>-10.356370715860681</v>
+        <v>-10.177445437232812</v>
       </c>
       <c r="G32" t="n" s="0">
-        <v>0.9786255171131002</v>
+        <v>1.3603432209348878</v>
       </c>
     </row>
     <row r="39">
       <c r="B39" t="n" s="0">
-        <v>5.31674280364282E-10</v>
+        <v>2.8719490663203402E-11</v>
       </c>
       <c r="E39" t="n" s="0">
         <v>2.8719490663203402E-11</v>
       </c>
       <c r="H39" t="n" s="0">
-        <v>5.31674280364282E-10</v>
+        <v>2.8719490663203402E-11</v>
       </c>
     </row>
     <row r="40">
       <c r="B40" t="n" s="0">
-        <v>5.31674280364282E-10</v>
+        <v>2.8719490663203402E-11</v>
       </c>
       <c r="E40" t="n" s="0">
         <v>2.8719490663203402E-11</v>
       </c>
       <c r="H40" t="n" s="0">
-        <v>5.31674280364282E-10</v>
+        <v>2.8719490663203402E-11</v>
       </c>
     </row>
     <row r="41">
@@ -571,7 +571,7 @@
         <v>2.8719490663203402E-11</v>
       </c>
       <c r="E41" t="n" s="0">
-        <v>5.7729863008733963E-11</v>
+        <v>6.373034178451358E-11</v>
       </c>
       <c r="H41" t="n" s="0">
         <v>2.8719490663203402E-11</v>
@@ -590,13 +590,13 @@
     </row>
     <row r="43">
       <c r="B43" t="n" s="0">
-        <v>8.487224956448446E-10</v>
+        <v>5.31674280364282E-10</v>
       </c>
       <c r="E43" t="n" s="0">
-        <v>4.619232489580079E-7</v>
+        <v>6.067192022543983E-6</v>
       </c>
       <c r="H43" t="n" s="0">
-        <v>3.6574283634182565E-9</v>
+        <v>5.840569474989402E-10</v>
       </c>
     </row>
     <row r="44">
@@ -604,26 +604,26 @@
         <v>2.8719490663203402E-11</v>
       </c>
       <c r="E44" t="n" s="0">
-        <v>0.0037585319247780517</v>
+        <v>0.39117045199768496</v>
       </c>
       <c r="H44" t="n" s="0">
-        <v>8.562993904900892E-11</v>
+        <v>2.8719490663203402E-11</v>
       </c>
     </row>
     <row r="45">
       <c r="B45" t="n" s="0">
-        <v>7.03394552480195E-11</v>
+        <v>6.414635193082751E-10</v>
       </c>
       <c r="E45" t="n" s="0">
-        <v>0.26117582460728006</v>
+        <v>0.8941460645782623</v>
       </c>
       <c r="H45" t="n" s="0">
-        <v>4.838863000512779E-10</v>
+        <v>9.444947151237936E-11</v>
       </c>
     </row>
     <row r="46">
       <c r="B46" t="n" s="0">
-        <v>0.0015568790292720205</v>
+        <v>0.0047454249600479975</v>
       </c>
       <c r="E46" t="n" s="0">
         <v>2.8719490663203402E-11</v>
@@ -637,7 +637,7 @@
         <v>2.8719490663203402E-11</v>
       </c>
       <c r="E47" t="n" s="0">
-        <v>0.6573804271100814</v>
+        <v>1.0</v>
       </c>
       <c r="H47" t="n" s="0">
         <v>2.8719490663203402E-11</v>
@@ -645,13 +645,13 @@
     </row>
     <row r="48">
       <c r="B48" t="n" s="0">
-        <v>2.8719490663203402E-11</v>
+        <v>3.643171050266978E-10</v>
       </c>
       <c r="E48" t="n" s="0">
-        <v>8.351995916556194E-8</v>
+        <v>4.275281031924089E-7</v>
       </c>
       <c r="H48" t="n" s="0">
-        <v>2.8719490663203402E-11</v>
+        <v>1.0936695631099071E-10</v>
       </c>
     </row>
     <row r="49">
@@ -659,7 +659,7 @@
         <v>2.8719490663203402E-11</v>
       </c>
       <c r="E49" t="n" s="0">
-        <v>0.7787839689422887</v>
+        <v>0.6897609572758945</v>
       </c>
       <c r="H49" t="n" s="0">
         <v>2.8719490663203402E-11</v>
@@ -667,57 +667,57 @@
     </row>
     <row r="50">
       <c r="B50" t="n" s="0">
-        <v>2.8719490663203402E-11</v>
+        <v>3.8787144759013784E-11</v>
       </c>
       <c r="E50" t="n" s="0">
-        <v>0.5444075540129325</v>
+        <v>0.09775105544859974</v>
       </c>
       <c r="H50" t="n" s="0">
-        <v>5.7729863008733963E-11</v>
+        <v>1.2657957728370648E-10</v>
       </c>
     </row>
     <row r="51">
       <c r="B51" t="n" s="0">
-        <v>2.8719490663203402E-11</v>
+        <v>7.03394552480195E-11</v>
       </c>
       <c r="E51" t="n" s="0">
-        <v>0.08909163442771983</v>
+        <v>0.10078263179832236</v>
       </c>
       <c r="H51" t="n" s="0">
-        <v>3.011893711871355E-10</v>
+        <v>1.8647261589758743E-10</v>
       </c>
     </row>
     <row r="52">
       <c r="B52" t="n" s="0">
-        <v>8.339303300103502E-4</v>
+        <v>0.05099234896566832</v>
       </c>
       <c r="E52" t="n" s="0">
-        <v>3.011893711871355E-10</v>
+        <v>3.8787144759013784E-11</v>
       </c>
       <c r="H52" t="n" s="0">
-        <v>2.260390486287696E-10</v>
+        <v>5.224845695592977E-9</v>
       </c>
     </row>
     <row r="53">
       <c r="B53" t="n" s="0">
-        <v>7.761734689605519E-11</v>
+        <v>2.8719490663203402E-11</v>
       </c>
       <c r="E53" t="n" s="0">
-        <v>1.3690186798427894E-8</v>
+        <v>6.812005340813848E-9</v>
       </c>
       <c r="H53" t="n" s="0">
-        <v>7.761734689605519E-11</v>
+        <v>9.444947151237936E-11</v>
       </c>
     </row>
     <row r="54">
       <c r="B54" t="n" s="0">
-        <v>3.175217248668002E-11</v>
+        <v>2.8719490663203402E-11</v>
       </c>
       <c r="E54" t="n" s="0">
-        <v>0.8130052876119973</v>
+        <v>0.344044940644476</v>
       </c>
       <c r="H54" t="n" s="0">
-        <v>3.175217248668002E-11</v>
+        <v>2.8719490663203402E-11</v>
       </c>
     </row>
     <row r="55">
@@ -725,7 +725,7 @@
         <v>2.8719490663203402E-11</v>
       </c>
       <c r="E55" t="n" s="0">
-        <v>0.4246622046508919</v>
+        <v>0.9293151249146342</v>
       </c>
       <c r="H55" t="n" s="0">
         <v>2.8719490663203402E-11</v>
@@ -736,65 +736,65 @@
         <v>2.8719490663203402E-11</v>
       </c>
       <c r="E56" t="n" s="0">
-        <v>0.8708108045360416</v>
+        <v>0.847587480259332</v>
       </c>
       <c r="H56" t="n" s="0">
-        <v>2.8719490663203402E-11</v>
+        <v>3.8787144759013784E-11</v>
       </c>
     </row>
     <row r="57">
       <c r="B57" t="n" s="0">
-        <v>0.0021038931094179507</v>
+        <v>1.2857816253298126E-4</v>
       </c>
       <c r="E57" t="n" s="0">
-        <v>2.1104831763424417E-7</v>
+        <v>4.58482304215622E-4</v>
       </c>
       <c r="H57" t="n" s="0">
-        <v>3.6599799289507135E-7</v>
+        <v>1.3057305617737233E-7</v>
       </c>
     </row>
     <row r="58">
       <c r="B58" t="n" s="0">
-        <v>0.01729890096036322</v>
+        <v>2.9212595033341424E-4</v>
       </c>
       <c r="E58" t="n" s="0">
-        <v>0.39938939501369475</v>
+        <v>0.47791970420909236</v>
       </c>
       <c r="H58" t="n" s="0">
-        <v>0.014119268503564276</v>
+        <v>2.320278143607131E-4</v>
       </c>
     </row>
     <row r="59">
       <c r="B59" t="n" s="0">
-        <v>0.8130052876119973</v>
+        <v>0.6467245773434842</v>
       </c>
       <c r="E59" t="n" s="0">
-        <v>0.9528424295801989</v>
+        <v>0.6256305639654388</v>
       </c>
       <c r="H59" t="n" s="0">
-        <v>0.6573804271100814</v>
+        <v>0.6467245773434842</v>
       </c>
     </row>
     <row r="60">
       <c r="B60" t="n" s="0">
-        <v>0.5542678363243183</v>
+        <v>0.7227197915710599</v>
       </c>
       <c r="E60" t="n" s="0">
-        <v>0.882465683286275</v>
+        <v>0.03578267558370112</v>
       </c>
       <c r="H60" t="n" s="0">
-        <v>0.48713803171001935</v>
+        <v>0.6256305639654388</v>
       </c>
     </row>
     <row r="61">
       <c r="B61" t="n" s="0">
-        <v>0.7901470561745595</v>
+        <v>0.01009698661285167</v>
       </c>
       <c r="E61" t="n" s="0">
-        <v>0.9646228051136888</v>
+        <v>0.1646090619494488</v>
       </c>
       <c r="H61" t="n" s="0">
-        <v>0.678900536466896</v>
+        <v>0.0019045321644495508</v>
       </c>
     </row>
   </sheetData>
@@ -809,738 +809,738 @@
   <sheetData>
     <row r="6">
       <c r="C6" t="n" s="0">
-        <v>4.0504039776101785E-44</v>
+        <v>1.1512866511916149E-42</v>
       </c>
       <c r="D6" t="n" s="0">
-        <v>1.9692804454414784E-42</v>
+        <v>3.659778158913924E-43</v>
       </c>
       <c r="E6" t="n" s="0">
-        <v>2.3515900997804525E-42</v>
+        <v>7.946245640868671E-41</v>
       </c>
       <c r="F6" t="n" s="0">
-        <v>2.6158838728718237E-44</v>
+        <v>6.299485685850304E-46</v>
       </c>
       <c r="G6" t="n" s="0">
-        <v>2.418797133699933E-44</v>
+        <v>3.809465994540623E-43</v>
       </c>
       <c r="H6" t="n" s="0">
-        <v>4.287890362038066E-43</v>
+        <v>6.344573877187998E-43</v>
       </c>
       <c r="I6" t="n" s="0">
-        <v>6.63313300764729E-44</v>
+        <v>9.46693794063556E-44</v>
       </c>
       <c r="J6" t="n" s="0">
-        <v>1.0215065588534016E-42</v>
+        <v>1.4071248465878353E-41</v>
       </c>
       <c r="K6" t="n" s="0">
-        <v>4.924865117939057E-43</v>
+        <v>1.2385404380668103E-44</v>
       </c>
       <c r="L6" t="n" s="0">
-        <v>1.9935380796085695E-43</v>
+        <v>1.0541687684889608E-43</v>
       </c>
       <c r="M6" t="n" s="0">
-        <v>4.349872829483617E-43</v>
+        <v>4.69598111882626E-43</v>
       </c>
       <c r="N6" t="n" s="0">
-        <v>7.930477840859395E-44</v>
+        <v>3.7383093408321303E-42</v>
       </c>
       <c r="O6" t="n" s="0">
-        <v>3.273965830576057E-44</v>
+        <v>2.1285666098221158E-45</v>
       </c>
       <c r="P6" t="n" s="0">
-        <v>5.8490196986366235E-43</v>
+        <v>6.422692418843085E-43</v>
       </c>
       <c r="Q6" t="n" s="0">
-        <v>2.696354089533025E-43</v>
+        <v>2.546347207928075E-44</v>
       </c>
       <c r="R6" t="n" s="0">
-        <v>1.0177095952537297E-41</v>
+        <v>2.814780039116741E-42</v>
       </c>
       <c r="S6" t="n" s="0">
-        <v>2.363765482193166E-44</v>
+        <v>2.3500563953877646E-43</v>
       </c>
       <c r="T6" t="n" s="0">
-        <v>6.584961293650075E-42</v>
+        <v>1.6003671816840798E-41</v>
       </c>
       <c r="U6" t="n" s="0">
-        <v>1.1667457668638267E-43</v>
+        <v>8.706167098030259E-44</v>
       </c>
       <c r="V6" t="n" s="0">
-        <v>9.457575468889791E-42</v>
+        <v>1.6986382821210618E-40</v>
       </c>
       <c r="W6" t="n" s="0">
-        <v>1.8960450344156734E-43</v>
+        <v>1.3746863069963865E-43</v>
       </c>
       <c r="X6" t="n" s="0">
-        <v>2.3400250285841756E-45</v>
+        <v>3.2317709540765582E-43</v>
       </c>
       <c r="Y6" t="n" s="0">
-        <v>9.766069855634474E-43</v>
+        <v>1.2072692154988953E-43</v>
       </c>
       <c r="Z6" t="n" s="0">
-        <v>4.2538599310127785E-44</v>
+        <v>1.0251847860133533E-42</v>
       </c>
       <c r="AA6" t="n" s="0">
-        <v>2.4105711900022287E-42</v>
+        <v>7.4256939244741E-44</v>
       </c>
       <c r="AB6" t="n" s="0">
-        <v>2.56501847588795E-43</v>
+        <v>3.1964437702650556E-43</v>
       </c>
       <c r="AC6" t="n" s="0">
-        <v>1.1682574895141437E-41</v>
+        <v>2.786817031199663E-43</v>
       </c>
       <c r="AD6" t="n" s="0">
-        <v>3.6345162718959566E-41</v>
+        <v>1.8393276380107418E-42</v>
       </c>
       <c r="AE6" t="n" s="0">
-        <v>6.592246367693923E-43</v>
+        <v>7.424961193947627E-44</v>
       </c>
       <c r="AF6" t="n" s="0">
-        <v>5.857239385001771E-43</v>
+        <v>5.441996761309645E-44</v>
       </c>
     </row>
     <row r="7">
       <c r="C7" t="n" s="0">
-        <v>1.0358863111334551E-25</v>
+        <v>6.408523410791984E-25</v>
       </c>
       <c r="D7" t="n" s="0">
-        <v>1.8837344786191837E-25</v>
+        <v>2.4521819340784446E-25</v>
       </c>
       <c r="E7" t="n" s="0">
-        <v>3.5771009732602587E-25</v>
+        <v>3.290481123478651E-24</v>
       </c>
       <c r="F7" t="n" s="0">
-        <v>1.4753824353899852E-26</v>
+        <v>1.5974972780722214E-25</v>
       </c>
       <c r="G7" t="n" s="0">
-        <v>1.6750814000495968E-23</v>
+        <v>3.301221555074112E-25</v>
       </c>
       <c r="H7" t="n" s="0">
-        <v>1.5407688027576398E-25</v>
+        <v>2.939522674218518E-25</v>
       </c>
       <c r="I7" t="n" s="0">
-        <v>3.4528999480798853E-25</v>
+        <v>1.4845238099003971E-24</v>
       </c>
       <c r="J7" t="n" s="0">
-        <v>1.8856780758407942E-24</v>
+        <v>1.2461290592193092E-24</v>
       </c>
       <c r="K7" t="n" s="0">
-        <v>8.531163591558164E-26</v>
+        <v>5.123519845371257E-26</v>
       </c>
       <c r="L7" t="n" s="0">
-        <v>1.579621913450988E-24</v>
+        <v>1.0271251225778073E-26</v>
       </c>
       <c r="M7" t="n" s="0">
-        <v>1.1430916706189086E-24</v>
+        <v>1.2770288011227483E-25</v>
       </c>
       <c r="N7" t="n" s="0">
-        <v>3.6325483070224905E-26</v>
+        <v>4.223157825099105E-25</v>
       </c>
       <c r="O7" t="n" s="0">
-        <v>3.6293548754551545E-25</v>
+        <v>1.1106250703845529E-25</v>
       </c>
       <c r="P7" t="n" s="0">
-        <v>2.8216619151408644E-26</v>
+        <v>1.0223061814363595E-25</v>
       </c>
       <c r="Q7" t="n" s="0">
-        <v>2.855406248731793E-24</v>
+        <v>4.4051178219545665E-25</v>
       </c>
       <c r="R7" t="n" s="0">
-        <v>1.9749838076493865E-25</v>
+        <v>6.989815679611673E-26</v>
       </c>
       <c r="S7" t="n" s="0">
-        <v>2.1142027146792752E-26</v>
+        <v>6.803260354691194E-26</v>
       </c>
       <c r="T7" t="n" s="0">
-        <v>6.631203190345066E-26</v>
+        <v>1.1365885938613055E-24</v>
       </c>
       <c r="U7" t="n" s="0">
-        <v>5.607824529001428E-25</v>
+        <v>1.696818461088017E-25</v>
       </c>
       <c r="V7" t="n" s="0">
-        <v>1.5463236877873837E-24</v>
+        <v>2.7849037523386906E-25</v>
       </c>
       <c r="W7" t="n" s="0">
-        <v>9.416815615206929E-26</v>
+        <v>5.978614843587686E-26</v>
       </c>
       <c r="X7" t="n" s="0">
-        <v>1.2419807717954459E-24</v>
+        <v>7.792215709505517E-25</v>
       </c>
       <c r="Y7" t="n" s="0">
-        <v>7.298354663534371E-26</v>
+        <v>1.393321063989652E-24</v>
       </c>
       <c r="Z7" t="n" s="0">
-        <v>9.640718681497593E-26</v>
+        <v>1.599804052807417E-25</v>
       </c>
       <c r="AA7" t="n" s="0">
-        <v>4.870188259996254E-26</v>
+        <v>3.574431650831428E-25</v>
       </c>
       <c r="AB7" t="n" s="0">
-        <v>2.6075650757479174E-26</v>
+        <v>1.1382447078228067E-25</v>
       </c>
       <c r="AC7" t="n" s="0">
-        <v>6.07902672492792E-25</v>
+        <v>5.818185159358316E-26</v>
       </c>
       <c r="AD7" t="n" s="0">
-        <v>1.3657754895559114E-25</v>
+        <v>1.692097694295222E-25</v>
       </c>
       <c r="AE7" t="n" s="0">
-        <v>1.8498677871536001E-25</v>
+        <v>5.615099903153665E-25</v>
       </c>
       <c r="AF7" t="n" s="0">
-        <v>3.585980279385654E-26</v>
+        <v>6.82595268337315E-25</v>
       </c>
     </row>
     <row r="8">
       <c r="C8" t="n" s="0">
-        <v>1.0507171292818545E-20</v>
+        <v>4.2119943841899027E-19</v>
       </c>
       <c r="D8" t="n" s="0">
-        <v>3.8372839305341436E-20</v>
+        <v>4.381395850893789E-21</v>
       </c>
       <c r="E8" t="n" s="0">
-        <v>3.3908618872074443E-18</v>
+        <v>6.260116244893611E-20</v>
       </c>
       <c r="F8" t="n" s="0">
-        <v>8.586950133791081E-20</v>
+        <v>4.127908274221612E-19</v>
       </c>
       <c r="G8" t="n" s="0">
-        <v>1.54530155496427E-18</v>
+        <v>4.23880329472124E-20</v>
       </c>
       <c r="H8" t="n" s="0">
-        <v>7.358887828791903E-20</v>
+        <v>2.0135682448613218E-21</v>
       </c>
       <c r="I8" t="n" s="0">
-        <v>8.855137730067429E-22</v>
+        <v>2.3450740046003317E-17</v>
       </c>
       <c r="J8" t="n" s="0">
-        <v>7.7562774621362E-21</v>
+        <v>5.015880020345873E-19</v>
       </c>
       <c r="K8" t="n" s="0">
-        <v>4.968388160853927E-20</v>
+        <v>3.788527377761701E-21</v>
       </c>
       <c r="L8" t="n" s="0">
-        <v>3.347680157939785E-19</v>
+        <v>8.507413310659972E-21</v>
       </c>
       <c r="M8" t="n" s="0">
-        <v>9.327968754670595E-20</v>
+        <v>2.3257499629544677E-22</v>
       </c>
       <c r="N8" t="n" s="0">
-        <v>2.3967035673983163E-21</v>
+        <v>1.9982042119186253E-20</v>
       </c>
       <c r="O8" t="n" s="0">
-        <v>2.387166808790487E-19</v>
+        <v>8.547627136873204E-22</v>
       </c>
       <c r="P8" t="n" s="0">
-        <v>5.9474831564375456E-21</v>
+        <v>4.5585529208248963E-17</v>
       </c>
       <c r="Q8" t="n" s="0">
-        <v>3.2998947300696776E-21</v>
+        <v>9.167255110133983E-21</v>
       </c>
       <c r="R8" t="n" s="0">
-        <v>6.155149174870284E-20</v>
+        <v>5.1852263904429206E-21</v>
       </c>
       <c r="S8" t="n" s="0">
-        <v>5.084700242489853E-19</v>
+        <v>1.3460035491694067E-20</v>
       </c>
       <c r="T8" t="n" s="0">
-        <v>7.187815667020594E-21</v>
+        <v>1.8812898194277958E-19</v>
       </c>
       <c r="U8" t="n" s="0">
-        <v>7.127633678245827E-21</v>
+        <v>3.134810358381362E-22</v>
       </c>
       <c r="V8" t="n" s="0">
-        <v>1.8730704495507578E-20</v>
+        <v>2.0876615500301524E-20</v>
       </c>
       <c r="W8" t="n" s="0">
-        <v>8.033244995729626E-21</v>
+        <v>3.1909963288340687E-25</v>
       </c>
       <c r="X8" t="n" s="0">
-        <v>5.458649932025686E-16</v>
+        <v>4.592637959886433E-19</v>
       </c>
       <c r="Y8" t="n" s="0">
-        <v>3.299639295948034E-20</v>
+        <v>1.898116269190685E-21</v>
       </c>
       <c r="Z8" t="n" s="0">
-        <v>5.511490129604247E-20</v>
+        <v>5.279073167376671E-22</v>
       </c>
       <c r="AA8" t="n" s="0">
-        <v>2.0677081313923373E-20</v>
+        <v>1.255410643761298E-20</v>
       </c>
       <c r="AB8" t="n" s="0">
-        <v>2.3963287714598974E-18</v>
+        <v>1.3762140652270731E-19</v>
       </c>
       <c r="AC8" t="n" s="0">
-        <v>3.1803208660553714E-19</v>
+        <v>1.12986531615161E-19</v>
       </c>
       <c r="AD8" t="n" s="0">
-        <v>8.042124410922859E-22</v>
+        <v>1.6342023743341606E-19</v>
       </c>
       <c r="AE8" t="n" s="0">
-        <v>4.565605863497307E-19</v>
+        <v>2.1636986731404723E-23</v>
       </c>
       <c r="AF8" t="n" s="0">
-        <v>1.422237321317478E-19</v>
+        <v>1.8338207721860253E-20</v>
       </c>
     </row>
     <row r="9">
       <c r="C9" t="n" s="0">
-        <v>6.583634640700722E-14</v>
+        <v>1.5332331759264717E-13</v>
       </c>
       <c r="D9" t="n" s="0">
-        <v>6.340174720230707E-14</v>
+        <v>1.6952656834731834E-13</v>
       </c>
       <c r="E9" t="n" s="0">
-        <v>1.781465975163364E-14</v>
+        <v>7.247656527264659E-14</v>
       </c>
       <c r="F9" t="n" s="0">
-        <v>5.618318246985251E-13</v>
+        <v>1.5359914389456466E-13</v>
       </c>
       <c r="G9" t="n" s="0">
-        <v>1.7160332006956292E-14</v>
+        <v>2.8052180216272812E-14</v>
       </c>
       <c r="H9" t="n" s="0">
-        <v>3.333435575750976E-13</v>
+        <v>5.134837327178973E-14</v>
       </c>
       <c r="I9" t="n" s="0">
-        <v>6.832384127576501E-15</v>
+        <v>6.425974398251122E-14</v>
       </c>
       <c r="J9" t="n" s="0">
-        <v>8.419816585805622E-14</v>
+        <v>1.8979586407189767E-14</v>
       </c>
       <c r="K9" t="n" s="0">
-        <v>2.5657872541708155E-14</v>
+        <v>5.427684796244129E-14</v>
       </c>
       <c r="L9" t="n" s="0">
-        <v>1.0852617194033278E-15</v>
+        <v>1.431568925687446E-13</v>
       </c>
       <c r="M9" t="n" s="0">
-        <v>2.187017722902648E-14</v>
+        <v>1.228946401774097E-13</v>
       </c>
       <c r="N9" t="n" s="0">
-        <v>9.595420516930221E-14</v>
+        <v>4.0967739404460235E-13</v>
       </c>
       <c r="O9" t="n" s="0">
-        <v>2.3160548136649567E-13</v>
+        <v>4.1919833368676395E-14</v>
       </c>
       <c r="P9" t="n" s="0">
-        <v>3.7191530909215886E-14</v>
+        <v>3.142341168807123E-14</v>
       </c>
       <c r="Q9" t="n" s="0">
-        <v>1.9127710564115328E-14</v>
+        <v>5.375595390397804E-14</v>
       </c>
       <c r="R9" t="n" s="0">
-        <v>2.2873039619340626E-13</v>
+        <v>2.4242884433918382E-14</v>
       </c>
       <c r="S9" t="n" s="0">
-        <v>4.987726963995796E-14</v>
+        <v>2.3056759113389285E-13</v>
       </c>
       <c r="T9" t="n" s="0">
-        <v>7.029403325280555E-15</v>
+        <v>7.859115819878838E-14</v>
       </c>
       <c r="U9" t="n" s="0">
-        <v>3.1199464337711383E-13</v>
+        <v>5.748097079830666E-13</v>
       </c>
       <c r="V9" t="n" s="0">
-        <v>8.065928186514006E-14</v>
+        <v>1.0618447131832111E-13</v>
       </c>
       <c r="W9" t="n" s="0">
-        <v>4.8498590074885546E-14</v>
+        <v>8.942460627157211E-14</v>
       </c>
       <c r="X9" t="n" s="0">
-        <v>2.169903984873692E-13</v>
+        <v>1.3880888661962904E-12</v>
       </c>
       <c r="Y9" t="n" s="0">
-        <v>2.2027957955922428E-13</v>
+        <v>3.364500669161378E-14</v>
       </c>
       <c r="Z9" t="n" s="0">
-        <v>9.40545748957236E-14</v>
+        <v>1.0717239297777807E-13</v>
       </c>
       <c r="AA9" t="n" s="0">
-        <v>2.5105695221599392E-15</v>
+        <v>4.5072585843845496E-13</v>
       </c>
       <c r="AB9" t="n" s="0">
-        <v>5.940801424077945E-14</v>
+        <v>9.764949569508154E-14</v>
       </c>
       <c r="AC9" t="n" s="0">
-        <v>4.39450541025149E-15</v>
+        <v>4.313434863833767E-14</v>
       </c>
       <c r="AD9" t="n" s="0">
-        <v>2.065245722682202E-14</v>
+        <v>1.7438716762231163E-13</v>
       </c>
       <c r="AE9" t="n" s="0">
-        <v>1.9918745772903004E-13</v>
+        <v>1.5786482565702117E-14</v>
       </c>
       <c r="AF9" t="n" s="0">
-        <v>5.504499973283005E-14</v>
+        <v>1.3064603220733639E-14</v>
       </c>
     </row>
     <row r="10">
       <c r="C10" t="n" s="0">
-        <v>7.199828480144287</v>
+        <v>7.200134668164904</v>
       </c>
       <c r="D10" t="n" s="0">
-        <v>7.178293242136341</v>
+        <v>7.20628531513611</v>
       </c>
       <c r="E10" t="n" s="0">
-        <v>8.095848013617994</v>
+        <v>7.210018262091892</v>
       </c>
       <c r="F10" t="n" s="0">
-        <v>6.244369359561979</v>
+        <v>6.4688738876273835</v>
       </c>
       <c r="G10" t="n" s="0">
-        <v>6.227583134347169</v>
+        <v>7.220292712285139</v>
       </c>
       <c r="H10" t="n" s="0">
-        <v>8.075693967709409</v>
+        <v>7.227274449823552</v>
       </c>
       <c r="I10" t="n" s="0">
-        <v>7.167094216756297</v>
+        <v>6.267786775189085</v>
       </c>
       <c r="J10" t="n" s="0">
-        <v>7.209206002071522</v>
+        <v>7.204714097492949</v>
       </c>
       <c r="K10" t="n" s="0">
-        <v>7.254340355764442</v>
+        <v>6.265130306517316</v>
       </c>
       <c r="L10" t="n" s="0">
-        <v>7.1940991862738874</v>
+        <v>7.189152298895733</v>
       </c>
       <c r="M10" t="n" s="0">
-        <v>7.207721310446335</v>
+        <v>7.214930617266358</v>
       </c>
       <c r="N10" t="n" s="0">
-        <v>6.21974798795357</v>
+        <v>7.224435541064554</v>
       </c>
       <c r="O10" t="n" s="0">
-        <v>6.239899026276603</v>
+        <v>8.086724697504009</v>
       </c>
       <c r="P10" t="n" s="0">
-        <v>7.204900897090583</v>
+        <v>6.241450162770054</v>
       </c>
       <c r="Q10" t="n" s="0">
-        <v>7.198549435830479</v>
+        <v>6.317284176050533</v>
       </c>
       <c r="R10" t="n" s="0">
-        <v>6.240664582077894</v>
+        <v>7.1997137383742915</v>
       </c>
       <c r="S10" t="n" s="0">
-        <v>7.21662998408571</v>
+        <v>7.195540269809567</v>
       </c>
       <c r="T10" t="n" s="0">
-        <v>6.244776368626668</v>
+        <v>6.242295075528572</v>
       </c>
       <c r="U10" t="n" s="0">
-        <v>7.198499532724648</v>
+        <v>7.213666088179973</v>
       </c>
       <c r="V10" t="n" s="0">
-        <v>7.063521613589119</v>
+        <v>7.22473588727871</v>
       </c>
       <c r="W10" t="n" s="0">
-        <v>6.222269171265593</v>
+        <v>7.223539592542423</v>
       </c>
       <c r="X10" t="n" s="0">
-        <v>7.2151575955444605</v>
+        <v>7.207559959109711</v>
       </c>
       <c r="Y10" t="n" s="0">
-        <v>7.194260876286108</v>
+        <v>6.229911674791709</v>
       </c>
       <c r="Z10" t="n" s="0">
-        <v>7.202143841955615</v>
+        <v>7.230676452083707</v>
       </c>
       <c r="AA10" t="n" s="0">
-        <v>6.248405306147009</v>
+        <v>6.233571316043496</v>
       </c>
       <c r="AB10" t="n" s="0">
-        <v>7.227094834650545</v>
+        <v>6.262172876527679</v>
       </c>
       <c r="AC10" t="n" s="0">
-        <v>7.188449340834771</v>
+        <v>6.215225369653043</v>
       </c>
       <c r="AD10" t="n" s="0">
-        <v>6.2289981738066444</v>
+        <v>7.198391188460727</v>
       </c>
       <c r="AE10" t="n" s="0">
-        <v>7.206402785095885</v>
+        <v>7.20696147449249</v>
       </c>
       <c r="AF10" t="n" s="0">
-        <v>7.189486577789872</v>
+        <v>6.257809544830107</v>
       </c>
     </row>
     <row r="11">
       <c r="C11" t="n" s="0">
-        <v>2.3115288111142375E-6</v>
+        <v>2.7887770699797275E-6</v>
       </c>
       <c r="D11" t="n" s="0">
-        <v>1.3280315410858965E-6</v>
+        <v>3.0657851087110847E-6</v>
       </c>
       <c r="E11" t="n" s="0">
-        <v>1.8885341918134206E-6</v>
+        <v>2.5894522193156633E-6</v>
       </c>
       <c r="F11" t="n" s="0">
-        <v>1.4357425524903834E-6</v>
+        <v>4.94601774384329E-6</v>
       </c>
       <c r="G11" t="n" s="0">
-        <v>1.8288390509651322E-6</v>
+        <v>1.9471732067743365E-6</v>
       </c>
       <c r="H11" t="n" s="0">
-        <v>3.244316617621278E-6</v>
+        <v>2.3180334916301774E-6</v>
       </c>
       <c r="I11" t="n" s="0">
-        <v>2.890669090557664E-6</v>
+        <v>4.8664493568086535E-6</v>
       </c>
       <c r="J11" t="n" s="0">
-        <v>9.619666181742128E-7</v>
+        <v>2.984428025667112E-6</v>
       </c>
       <c r="K11" t="n" s="0">
-        <v>3.5930070481841127E-6</v>
+        <v>1.3654330996433346E-6</v>
       </c>
       <c r="L11" t="n" s="0">
-        <v>3.6829554920587126E-6</v>
+        <v>3.0708967569000083E-6</v>
       </c>
       <c r="M11" t="n" s="0">
-        <v>5.095493974333735E-6</v>
+        <v>1.7880789410553998E-6</v>
       </c>
       <c r="N11" t="n" s="0">
-        <v>2.715199715081345E-6</v>
+        <v>5.628161337019925E-6</v>
       </c>
       <c r="O11" t="n" s="0">
-        <v>1.4928310101591816E-6</v>
+        <v>3.842992602473993E-6</v>
       </c>
       <c r="P11" t="n" s="0">
-        <v>2.9614736812290344E-6</v>
+        <v>6.278186246862216E-7</v>
       </c>
       <c r="Q11" t="n" s="0">
-        <v>1.3815664197875893E-6</v>
+        <v>2.9443943307687736E-6</v>
       </c>
       <c r="R11" t="n" s="0">
-        <v>1.6367317345039681E-6</v>
+        <v>3.705505296296432E-6</v>
       </c>
       <c r="S11" t="n" s="0">
-        <v>2.959383378731379E-6</v>
+        <v>5.542726861850052E-6</v>
       </c>
       <c r="T11" t="n" s="0">
-        <v>2.8791547978992594E-6</v>
+        <v>2.3688432501691568E-6</v>
       </c>
       <c r="U11" t="n" s="0">
-        <v>1.7998559032934556E-6</v>
+        <v>3.7036967958146137E-6</v>
       </c>
       <c r="V11" t="n" s="0">
-        <v>3.3342674697629845E-6</v>
+        <v>3.3154490106543217E-6</v>
       </c>
       <c r="W11" t="n" s="0">
-        <v>2.3090472776901194E-6</v>
+        <v>3.92594874997328E-6</v>
       </c>
       <c r="X11" t="n" s="0">
-        <v>2.1018023814895E-6</v>
+        <v>3.0508031433195078E-6</v>
       </c>
       <c r="Y11" t="n" s="0">
-        <v>3.828034127815628E-6</v>
+        <v>1.2039864630532866E-6</v>
       </c>
       <c r="Z11" t="n" s="0">
-        <v>2.285878185282311E-6</v>
+        <v>3.1867377809681847E-6</v>
       </c>
       <c r="AA11" t="n" s="0">
-        <v>2.861413470392461E-6</v>
+        <v>4.651668067079001E-6</v>
       </c>
       <c r="AB11" t="n" s="0">
-        <v>0.24991641767182274</v>
+        <v>5.318133497344103E-6</v>
       </c>
       <c r="AC11" t="n" s="0">
-        <v>6.583502329466844E-6</v>
+        <v>5.145027429386578E-6</v>
       </c>
       <c r="AD11" t="n" s="0">
-        <v>1.2044946045180324E-6</v>
+        <v>4.152337295184914E-6</v>
       </c>
       <c r="AE11" t="n" s="0">
-        <v>1.463717316106484E-6</v>
+        <v>4.428309005564887E-6</v>
       </c>
       <c r="AF11" t="n" s="0">
-        <v>2.5336764019933183E-6</v>
+        <v>4.084669991318358E-6</v>
       </c>
     </row>
     <row r="12">
       <c r="C12" t="n" s="0">
-        <v>0.36094933964106474</v>
+        <v>0.15509802148168905</v>
       </c>
       <c r="D12" t="n" s="0">
-        <v>0.010353239556894434</v>
+        <v>0.0427332966815838</v>
       </c>
       <c r="E12" t="n" s="0">
-        <v>0.5464953687491122</v>
+        <v>0.6808557367163656</v>
       </c>
       <c r="F12" t="n" s="0">
-        <v>0.09214151590550033</v>
+        <v>0.8629553095411694</v>
       </c>
       <c r="G12" t="n" s="0">
-        <v>0.8484503279205856</v>
+        <v>0.7192294786053531</v>
       </c>
       <c r="H12" t="n" s="0">
-        <v>0.675796579025408</v>
+        <v>0.2288181578809778</v>
       </c>
       <c r="I12" t="n" s="0">
-        <v>0.6662508950290851</v>
+        <v>0.7553306072657874</v>
       </c>
       <c r="J12" t="n" s="0">
-        <v>0.39630753406089275</v>
+        <v>0.2873654843221109</v>
       </c>
       <c r="K12" t="n" s="0">
-        <v>0.7044702029780602</v>
+        <v>0.1796502768168604</v>
       </c>
       <c r="L12" t="n" s="0">
-        <v>0.6068356771274604</v>
+        <v>0.054917876890460696</v>
       </c>
       <c r="M12" t="n" s="0">
-        <v>0.7209478058713163</v>
+        <v>0.6668858633540151</v>
       </c>
       <c r="N12" t="n" s="0">
-        <v>0.2598892623780069</v>
+        <v>0.11786831552592004</v>
       </c>
       <c r="O12" t="n" s="0">
-        <v>0.04622703732288259</v>
+        <v>0.22109455874634787</v>
       </c>
       <c r="P12" t="n" s="0">
-        <v>0.3645918563130879</v>
+        <v>0.24364736946257573</v>
       </c>
       <c r="Q12" t="n" s="0">
-        <v>0.34379165831193376</v>
+        <v>0.26725149884308697</v>
       </c>
       <c r="R12" t="n" s="0">
-        <v>0.8269818860590407</v>
+        <v>0.6323481347430354</v>
       </c>
       <c r="S12" t="n" s="0">
-        <v>0.8475963721720838</v>
+        <v>0.9948919082331452</v>
       </c>
       <c r="T12" t="n" s="0">
-        <v>0.360399242455493</v>
+        <v>0.4608983977005652</v>
       </c>
       <c r="U12" t="n" s="0">
-        <v>0.5098082473810908</v>
+        <v>0.4178788913299069</v>
       </c>
       <c r="V12" t="n" s="0">
-        <v>0.5544960112563373</v>
+        <v>0.8690552332549225</v>
       </c>
       <c r="W12" t="n" s="0">
-        <v>0.9601843382056012</v>
+        <v>0.833553602843077</v>
       </c>
       <c r="X12" t="n" s="0">
-        <v>0.5877599085960742</v>
+        <v>0.09166632710926893</v>
       </c>
       <c r="Y12" t="n" s="0">
-        <v>0.9988782616423314</v>
+        <v>0.7585501459150096</v>
       </c>
       <c r="Z12" t="n" s="0">
-        <v>0.8895433905142158</v>
+        <v>0.5687679171227458</v>
       </c>
       <c r="AA12" t="n" s="0">
-        <v>0.5261280567133026</v>
+        <v>0.20338392371331337</v>
       </c>
       <c r="AB12" t="n" s="0">
-        <v>0.21509320898156797</v>
+        <v>0.23060591281517784</v>
       </c>
       <c r="AC12" t="n" s="0">
-        <v>0.8940516337963816</v>
+        <v>0.9724441793310259</v>
       </c>
       <c r="AD12" t="n" s="0">
-        <v>0.3793633449872676</v>
+        <v>0.616796134236474</v>
       </c>
       <c r="AE12" t="n" s="0">
-        <v>0.14653819397508708</v>
+        <v>0.2824241369880327</v>
       </c>
       <c r="AF12" t="n" s="0">
-        <v>0.8423423781142586</v>
+        <v>0.9241986255778107</v>
       </c>
     </row>
     <row r="13">
       <c r="C13" t="n" s="0">
-        <v>-703.6135931731403</v>
+        <v>-714.275635993808</v>
       </c>
       <c r="D13" t="n" s="0">
-        <v>-712.2158389490218</v>
+        <v>-678.3219598778352</v>
       </c>
       <c r="E13" t="n" s="0">
-        <v>-814.8156253192672</v>
+        <v>-718.3353844200728</v>
       </c>
       <c r="F13" t="n" s="0">
-        <v>-590.3145356030544</v>
+        <v>-639.7266875214359</v>
       </c>
       <c r="G13" t="n" s="0">
-        <v>-678.3262114069846</v>
+        <v>-786.1760943368149</v>
       </c>
       <c r="H13" t="n" s="0">
-        <v>-553.299516406415</v>
+        <v>-511.6062847140629</v>
       </c>
       <c r="I13" t="n" s="0">
-        <v>-463.94311878188887</v>
+        <v>-554.5556213240649</v>
       </c>
       <c r="J13" t="n" s="0">
-        <v>-874.8238767386823</v>
+        <v>-504.5553230560035</v>
       </c>
       <c r="K13" t="n" s="0">
-        <v>-300.2085033900014</v>
+        <v>-813.245628651206</v>
       </c>
       <c r="L13" t="n" s="0">
-        <v>-517.7090027589529</v>
+        <v>-816.894004865823</v>
       </c>
       <c r="M13" t="n" s="0">
-        <v>-333.4905693694159</v>
+        <v>-800.2565299319646</v>
       </c>
       <c r="N13" t="n" s="0">
-        <v>-636.3261712768634</v>
+        <v>-614.3202830589282</v>
       </c>
       <c r="O13" t="n" s="0">
-        <v>-851.606283018068</v>
+        <v>-526.7934663226298</v>
       </c>
       <c r="P13" t="n" s="0">
-        <v>-506.1290742362311</v>
+        <v>-759.7842676088267</v>
       </c>
       <c r="Q13" t="n" s="0">
-        <v>-593.2533956352021</v>
+        <v>-774.3022497559733</v>
       </c>
       <c r="R13" t="n" s="0">
-        <v>-555.7925138651148</v>
+        <v>-659.3760121869213</v>
       </c>
       <c r="S13" t="n" s="0">
-        <v>-576.9563881190031</v>
+        <v>-532.6414623442057</v>
       </c>
       <c r="T13" t="n" s="0">
-        <v>-661.000074487246</v>
+        <v>-716.3580181430056</v>
       </c>
       <c r="U13" t="n" s="0">
-        <v>-800.4298952207176</v>
+        <v>-875.1457670934024</v>
       </c>
       <c r="V13" t="n" s="0">
-        <v>-817.3470981851282</v>
+        <v>-761.302528028229</v>
       </c>
       <c r="W13" t="n" s="0">
-        <v>-534.096289066191</v>
+        <v>-670.051828775846</v>
       </c>
       <c r="X13" t="n" s="0">
-        <v>-437.4927685619014</v>
+        <v>-538.0692931907639</v>
       </c>
       <c r="Y13" t="n" s="0">
-        <v>-497.5028170166676</v>
+        <v>-621.0228621430565</v>
       </c>
       <c r="Z13" t="n" s="0">
-        <v>-357.3139730894207</v>
+        <v>-711.8649436717784</v>
       </c>
       <c r="AA13" t="n" s="0">
-        <v>-764.4481494275005</v>
+        <v>-854.987559199641</v>
       </c>
       <c r="AB13" t="n" s="0">
-        <v>-776.5926768515407</v>
+        <v>-556.5628073946204</v>
       </c>
       <c r="AC13" t="n" s="0">
-        <v>-596.4332686128461</v>
+        <v>-492.6904508029767</v>
       </c>
       <c r="AD13" t="n" s="0">
-        <v>-497.14743154663466</v>
+        <v>-548.7432397248284</v>
       </c>
       <c r="AE13" t="n" s="0">
-        <v>-618.0806360601521</v>
+        <v>-447.44303542544026</v>
       </c>
       <c r="AF13" t="n" s="0">
-        <v>-714.5388447304409</v>
+        <v>-581.4252456846385</v>
       </c>
     </row>
     <row r="14">
@@ -1637,7 +1637,7 @@
     </row>
     <row r="15">
       <c r="C15" t="n" s="0">
-        <v>4.440892098500626E-16</v>
+        <v>3.9968028886505635E-15</v>
       </c>
       <c r="D15" t="n" s="0">
         <v>3.9968028886505635E-15</v>
@@ -1652,7 +1652,7 @@
         <v>3.9968028886505635E-15</v>
       </c>
       <c r="H15" t="n" s="0">
-        <v>3.9968028886505635E-15</v>
+        <v>4.440892098500626E-16</v>
       </c>
       <c r="I15" t="n" s="0">
         <v>3.9968028886505635E-15</v>
@@ -1676,7 +1676,7 @@
         <v>3.9968028886505635E-15</v>
       </c>
       <c r="P15" t="n" s="0">
-        <v>3.9968028886505635E-15</v>
+        <v>4.440892098500626E-16</v>
       </c>
       <c r="Q15" t="n" s="0">
         <v>3.9968028886505635E-15</v>
@@ -1685,7 +1685,7 @@
         <v>3.9968028886505635E-15</v>
       </c>
       <c r="S15" t="n" s="0">
-        <v>4.440892098500626E-16</v>
+        <v>3.9968028886505635E-15</v>
       </c>
       <c r="T15" t="n" s="0">
         <v>3.9968028886505635E-15</v>
@@ -1694,10 +1694,10 @@
         <v>3.9968028886505635E-15</v>
       </c>
       <c r="V15" t="n" s="0">
-        <v>4.440892098500626E-16</v>
+        <v>3.9968028886505635E-15</v>
       </c>
       <c r="W15" t="n" s="0">
-        <v>4.440892098500626E-16</v>
+        <v>3.9968028886505635E-15</v>
       </c>
       <c r="X15" t="n" s="0">
         <v>3.9968028886505635E-15</v>
@@ -1715,10 +1715,10 @@
         <v>3.9968028886505635E-15</v>
       </c>
       <c r="AC15" t="n" s="0">
+        <v>3.9968028886505635E-15</v>
+      </c>
+      <c r="AD15" t="n" s="0">
         <v>4.440892098500626E-16</v>
-      </c>
-      <c r="AD15" t="n" s="0">
-        <v>3.9968028886505635E-15</v>
       </c>
       <c r="AE15" t="n" s="0">
         <v>3.9968028886505635E-15</v>
@@ -1729,88 +1729,88 @@
     </row>
     <row r="16">
       <c r="C16" t="n" s="0">
-        <v>0.020726652218240438</v>
+        <v>0.0100790672155745</v>
       </c>
       <c r="D16" t="n" s="0">
-        <v>0.02751925803702493</v>
+        <v>0.03161738634495015</v>
       </c>
       <c r="E16" t="n" s="0">
         <v>0.0</v>
       </c>
       <c r="F16" t="n" s="0">
-        <v>0.01362438537396371</v>
+        <v>0.019992055064085412</v>
       </c>
       <c r="G16" t="n" s="0">
-        <v>0.027072681983937863</v>
+        <v>0.02187314173810795</v>
       </c>
       <c r="H16" t="n" s="0">
         <v>0.0</v>
       </c>
       <c r="I16" t="n" s="0">
-        <v>0.010016136405594511</v>
+        <v>0.008094795236356589</v>
       </c>
       <c r="J16" t="n" s="0">
         <v>0.0</v>
       </c>
       <c r="K16" t="n" s="0">
-        <v>0.012549619724383732</v>
+        <v>0.0</v>
       </c>
       <c r="L16" t="n" s="0">
         <v>0.0</v>
       </c>
       <c r="M16" t="n" s="0">
-        <v>0.0</v>
+        <v>0.02972271785825631</v>
       </c>
       <c r="N16" t="n" s="0">
-        <v>0.0</v>
+        <v>0.028173026667246637</v>
       </c>
       <c r="O16" t="n" s="0">
-        <v>2.220446049250313E-16</v>
+        <v>0.0</v>
       </c>
       <c r="P16" t="n" s="0">
-        <v>0.018460744276876384</v>
+        <v>0.014140266396380108</v>
       </c>
       <c r="Q16" t="n" s="0">
-        <v>0.012799209742982987</v>
+        <v>0.0</v>
       </c>
       <c r="R16" t="n" s="0">
         <v>0.0</v>
       </c>
       <c r="S16" t="n" s="0">
-        <v>0.0</v>
+        <v>0.012750336875235191</v>
       </c>
       <c r="T16" t="n" s="0">
-        <v>0.027635662511823034</v>
+        <v>0.0</v>
       </c>
       <c r="U16" t="n" s="0">
-        <v>0.017495390751423368</v>
+        <v>0.0</v>
       </c>
       <c r="V16" t="n" s="0">
-        <v>0.00790106043318084</v>
+        <v>0.0</v>
       </c>
       <c r="W16" t="n" s="0">
-        <v>0.007683489472449234</v>
+        <v>0.0</v>
       </c>
       <c r="X16" t="n" s="0">
-        <v>0.0</v>
+        <v>0.013479926680116883</v>
       </c>
       <c r="Y16" t="n" s="0">
-        <v>0.0</v>
+        <v>0.017353502247808295</v>
       </c>
       <c r="Z16" t="n" s="0">
-        <v>0.0</v>
+        <v>0.024695212680549083</v>
       </c>
       <c r="AA16" t="n" s="0">
-        <v>0.030022500082655168</v>
+        <v>0.0</v>
       </c>
       <c r="AB16" t="n" s="0">
-        <v>0.0</v>
+        <v>0.007603698078390342</v>
       </c>
       <c r="AC16" t="n" s="0">
-        <v>0.008289525993616653</v>
+        <v>0.02711506914438111</v>
       </c>
       <c r="AD16" t="n" s="0">
-        <v>0.0077722797947442634</v>
+        <v>0.01398427475739572</v>
       </c>
       <c r="AE16" t="n" s="0">
         <v>0.0</v>
@@ -1821,2332 +1821,2332 @@
     </row>
     <row r="17">
       <c r="C17" t="n" s="0">
-        <v>2.9557310460511897E-6</v>
+        <v>4.673522085748415E-6</v>
       </c>
       <c r="D17" t="n" s="0">
-        <v>0.019698597466991187</v>
+        <v>0.0196652726192565</v>
       </c>
       <c r="E17" t="n" s="0">
-        <v>0.02018879292299204</v>
+        <v>1.328322299024377E-7</v>
       </c>
       <c r="F17" t="n" s="0">
-        <v>1.3932774201946313E-6</v>
+        <v>0.019675637032783716</v>
       </c>
       <c r="G17" t="n" s="0">
-        <v>2.1703094470407125E-6</v>
+        <v>1.6093618807566164E-6</v>
       </c>
       <c r="H17" t="n" s="0">
-        <v>0.019634524132461726</v>
+        <v>4.648731900491025E-6</v>
       </c>
       <c r="I17" t="n" s="0">
-        <v>1.5727450988778138E-6</v>
+        <v>1.0175989845316323E-6</v>
       </c>
       <c r="J17" t="n" s="0">
-        <v>1.7061409515448777E-6</v>
+        <v>1.8188157266903983E-6</v>
       </c>
       <c r="K17" t="n" s="0">
-        <v>1.9214281135900183E-6</v>
+        <v>2.0618393109949283E-6</v>
       </c>
       <c r="L17" t="n" s="0">
-        <v>0.02078206376857101</v>
+        <v>2.5289414063560585E-6</v>
       </c>
       <c r="M17" t="n" s="0">
-        <v>4.377500940528361E-6</v>
+        <v>0.019481498866148934</v>
       </c>
       <c r="N17" t="n" s="0">
-        <v>9.383232952665451E-7</v>
+        <v>5.136985794676421E-6</v>
       </c>
       <c r="O17" t="n" s="0">
-        <v>4.273921323835039E-6</v>
+        <v>1.990878863392706E-6</v>
       </c>
       <c r="P17" t="n" s="0">
-        <v>0.01986900508987571</v>
+        <v>1.226478010960371E-6</v>
       </c>
       <c r="Q17" t="n" s="0">
-        <v>1.144929174300102E-6</v>
+        <v>6.339025039661623E-7</v>
       </c>
       <c r="R17" t="n" s="0">
-        <v>1.4820233215358472E-6</v>
+        <v>2.3189266352466264E-6</v>
       </c>
       <c r="S17" t="n" s="0">
-        <v>9.739789446861028E-7</v>
+        <v>2.5035251423041706E-6</v>
       </c>
       <c r="T17" t="n" s="0">
-        <v>3.0467573307457124E-6</v>
+        <v>2.6446891891321138E-6</v>
       </c>
       <c r="U17" t="n" s="0">
-        <v>1.8078963109303E-6</v>
+        <v>1.5442719128062078E-6</v>
       </c>
       <c r="V17" t="n" s="0">
-        <v>9.942872219973496E-7</v>
+        <v>2.7275770052703342E-6</v>
       </c>
       <c r="W17" t="n" s="0">
-        <v>1.2402427517829695E-6</v>
+        <v>0.020094938069876646</v>
       </c>
       <c r="X17" t="n" s="0">
-        <v>2.13553406101372E-6</v>
+        <v>0.01891386070421684</v>
       </c>
       <c r="Y17" t="n" s="0">
-        <v>3.631960148695182E-6</v>
+        <v>4.5730278032596345E-6</v>
       </c>
       <c r="Z17" t="n" s="0">
-        <v>1.9270362997531673E-6</v>
+        <v>8.675181363955285E-7</v>
       </c>
       <c r="AA17" t="n" s="0">
-        <v>8.956501300815643E-7</v>
+        <v>3.4419576605240482E-6</v>
       </c>
       <c r="AB17" t="n" s="0">
-        <v>8.643115538428187E-7</v>
+        <v>2.049998230001748E-6</v>
       </c>
       <c r="AC17" t="n" s="0">
-        <v>5.828718622155996E-6</v>
+        <v>3.0282479287196425E-6</v>
       </c>
       <c r="AD17" t="n" s="0">
-        <v>0.04037231475852319</v>
+        <v>2.0229870908162568E-6</v>
       </c>
       <c r="AE17" t="n" s="0">
-        <v>0.019600789557589045</v>
+        <v>1.352405907427833E-6</v>
       </c>
       <c r="AF17" t="n" s="0">
-        <v>1.2136423113544147E-6</v>
+        <v>1.785772745161634E-6</v>
       </c>
     </row>
     <row r="18">
       <c r="C18" t="n" s="0">
-        <v>6.644466672456853E-6</v>
+        <v>3.5157157737585633E-6</v>
       </c>
       <c r="D18" t="n" s="0">
-        <v>2.294525418501707E-5</v>
+        <v>1.831840271446833E-5</v>
       </c>
       <c r="E18" t="n" s="0">
-        <v>3.3282223680453965E-5</v>
+        <v>1.3280086564901612E-5</v>
       </c>
       <c r="F18" t="n" s="0">
-        <v>9.29188889166696E-6</v>
+        <v>2.043497248210292E-5</v>
       </c>
       <c r="G18" t="n" s="0">
-        <v>5.225788887273666E-6</v>
+        <v>7.836889699698174E-6</v>
       </c>
       <c r="H18" t="n" s="0">
-        <v>0.1212121432409654</v>
+        <v>6.5280864573522765E-6</v>
       </c>
       <c r="I18" t="n" s="0">
-        <v>4.88820709023335E-6</v>
+        <v>2.3703948497114448E-5</v>
       </c>
       <c r="J18" t="n" s="0">
-        <v>6.342609399993257E-6</v>
+        <v>1.2973920692969038E-5</v>
       </c>
       <c r="K18" t="n" s="0">
-        <v>1.0773619517215121E-5</v>
+        <v>2.453523957198961E-5</v>
       </c>
       <c r="L18" t="n" s="0">
-        <v>1.4644693021460311E-5</v>
+        <v>4.779167367749562E-6</v>
       </c>
       <c r="M18" t="n" s="0">
-        <v>6.188859241629281E-6</v>
+        <v>1.0373015962880913E-5</v>
       </c>
       <c r="N18" t="n" s="0">
-        <v>1.2722027593482557E-5</v>
+        <v>1.6685077931509045E-5</v>
       </c>
       <c r="O18" t="n" s="0">
-        <v>1.216574878824967E-5</v>
+        <v>1.2956772158400787E-5</v>
       </c>
       <c r="P18" t="n" s="0">
-        <v>1.2752183444751122E-5</v>
+        <v>4.676718461671728E-6</v>
       </c>
       <c r="Q18" t="n" s="0">
-        <v>3.60626420965105E-5</v>
+        <v>0.24241516685239675</v>
       </c>
       <c r="R18" t="n" s="0">
-        <v>0.12122336625355137</v>
+        <v>1.1930376394703357E-5</v>
       </c>
       <c r="S18" t="n" s="0">
-        <v>0.12123982134676276</v>
+        <v>1.1759017165401635E-5</v>
       </c>
       <c r="T18" t="n" s="0">
-        <v>9.116663941109733E-6</v>
+        <v>1.472072591430968E-5</v>
       </c>
       <c r="U18" t="n" s="0">
-        <v>1.2018867440556362E-5</v>
+        <v>6.939434982996611E-6</v>
       </c>
       <c r="V18" t="n" s="0">
-        <v>2.550670053128207E-6</v>
+        <v>1.7441705003216536E-5</v>
       </c>
       <c r="W18" t="n" s="0">
-        <v>1.3259153830109285E-5</v>
+        <v>7.133349214198899E-6</v>
       </c>
       <c r="X18" t="n" s="0">
-        <v>8.7605819900575E-6</v>
+        <v>9.718516682225746E-6</v>
       </c>
       <c r="Y18" t="n" s="0">
-        <v>1.5190591558126711E-5</v>
+        <v>1.5290538705658187E-5</v>
       </c>
       <c r="Z18" t="n" s="0">
-        <v>8.471061895056365E-6</v>
+        <v>2.7390873432155334E-5</v>
       </c>
       <c r="AA18" t="n" s="0">
-        <v>4.749108016578851E-6</v>
+        <v>1.7869926853001407E-5</v>
       </c>
       <c r="AB18" t="n" s="0">
-        <v>1.5473172773112036E-5</v>
+        <v>1.6639028462553526E-5</v>
       </c>
       <c r="AC18" t="n" s="0">
-        <v>2.5353921658779823E-5</v>
+        <v>8.738200621334461E-6</v>
       </c>
       <c r="AD18" t="n" s="0">
-        <v>3.5753087259668785E-5</v>
+        <v>7.664311554433788E-6</v>
       </c>
       <c r="AE18" t="n" s="0">
-        <v>0.12122697176664757</v>
+        <v>1.1886139448076338E-5</v>
       </c>
       <c r="AF18" t="n" s="0">
-        <v>5.812586121829314E-6</v>
+        <v>0.12121733668810508</v>
       </c>
     </row>
     <row r="19">
       <c r="C19" t="n" s="0">
-        <v>11.718699111327835</v>
+        <v>9.803897741079606</v>
       </c>
       <c r="D19" t="n" s="0">
+        <v>10.763166845651908</v>
+      </c>
+      <c r="E19" t="n" s="0">
+        <v>10.763166846132064</v>
+      </c>
+      <c r="F19" t="n" s="0">
+        <v>1.992030891891068</v>
+      </c>
+      <c r="G19" t="n" s="0">
+        <v>1.9920308918588832</v>
+      </c>
+      <c r="H19" t="n" s="0">
+        <v>11.718699111328082</v>
+      </c>
+      <c r="I19" t="n" s="0">
+        <v>1.9920324862770211</v>
+      </c>
+      <c r="J19" t="n" s="0">
+        <v>10.763166845903413</v>
+      </c>
+      <c r="K19" t="n" s="0">
+        <v>1.9920308918715115</v>
+      </c>
+      <c r="L19" t="n" s="0">
+        <v>11.718699111327785</v>
+      </c>
+      <c r="M19" t="n" s="0">
+        <v>1.9920308918587886</v>
+      </c>
+      <c r="N19" t="n" s="0">
+        <v>9.803897741018199</v>
+      </c>
+      <c r="O19" t="n" s="0">
+        <v>10.763166846131998</v>
+      </c>
+      <c r="P19" t="n" s="0">
+        <v>11.718699111327831</v>
+      </c>
+      <c r="Q19" t="n" s="0">
+        <v>6.903335554603642</v>
+      </c>
+      <c r="R19" t="n" s="0">
+        <v>11.718699111327831</v>
+      </c>
+      <c r="S19" t="n" s="0">
+        <v>1.992030891913482</v>
+      </c>
+      <c r="T19" t="n" s="0">
+        <v>11.718699111327785</v>
+      </c>
+      <c r="U19" t="n" s="0">
+        <v>1.9920308918690193</v>
+      </c>
+      <c r="V19" t="n" s="0">
+        <v>1.9920309148770095</v>
+      </c>
+      <c r="W19" t="n" s="0">
+        <v>10.763166846131686</v>
+      </c>
+      <c r="X19" t="n" s="0">
+        <v>11.718699111328027</v>
+      </c>
+      <c r="Y19" t="n" s="0">
+        <v>11.718699111327831</v>
+      </c>
+      <c r="Z19" t="n" s="0">
+        <v>11.718699111328029</v>
+      </c>
+      <c r="AA19" t="n" s="0">
         <v>11.718699111328078</v>
       </c>
-      <c r="E19" t="n" s="0">
-        <v>11.718699111328078</v>
-      </c>
-      <c r="F19" t="n" s="0">
-        <v>11.718699111327783</v>
-      </c>
-      <c r="G19" t="n" s="0">
-        <v>11.718699111328077</v>
-      </c>
-      <c r="H19" t="n" s="0">
-        <v>1.9920308918568623</v>
-      </c>
-      <c r="I19" t="n" s="0">
-        <v>11.71869911132808</v>
-      </c>
-      <c r="J19" t="n" s="0">
-        <v>11.718699111327785</v>
-      </c>
-      <c r="K19" t="n" s="0">
+      <c r="AB19" t="n" s="0">
+        <v>1.9920308919703407</v>
+      </c>
+      <c r="AC19" t="n" s="0">
+        <v>9.80389774414984</v>
+      </c>
+      <c r="AD19" t="n" s="0">
+        <v>1.9920308918663472</v>
+      </c>
+      <c r="AE19" t="n" s="0">
         <v>11.718699111327831</v>
       </c>
-      <c r="L19" t="n" s="0">
-        <v>11.718699111328078</v>
-      </c>
-      <c r="M19" t="n" s="0">
-        <v>11.718699111327785</v>
-      </c>
-      <c r="N19" t="n" s="0">
-        <v>11.718699111327835</v>
-      </c>
-      <c r="O19" t="n" s="0">
-        <v>11.718699111328027</v>
-      </c>
-      <c r="P19" t="n" s="0">
-        <v>11.718699111327783</v>
-      </c>
-      <c r="Q19" t="n" s="0">
-        <v>11.718699111327837</v>
-      </c>
-      <c r="R19" t="n" s="0">
-        <v>1.992030891928731</v>
-      </c>
-      <c r="S19" t="n" s="0">
-        <v>1.99203089200362</v>
-      </c>
-      <c r="T19" t="n" s="0">
-        <v>10.76316686492513</v>
-      </c>
-      <c r="U19" t="n" s="0">
-        <v>11.718699111328029</v>
-      </c>
-      <c r="V19" t="n" s="0">
-        <v>10.763166846130746</v>
-      </c>
-      <c r="W19" t="n" s="0">
-        <v>1.9920308921591203</v>
-      </c>
-      <c r="X19" t="n" s="0">
-        <v>11.718699111327785</v>
-      </c>
-      <c r="Y19" t="n" s="0">
-        <v>1.992031555769788</v>
-      </c>
-      <c r="Z19" t="n" s="0">
-        <v>11.718699111328077</v>
-      </c>
-      <c r="AA19" t="n" s="0">
-        <v>11.71869911132803</v>
-      </c>
-      <c r="AB19" t="n" s="0">
-        <v>9.803898069691941</v>
-      </c>
-      <c r="AC19" t="n" s="0">
-        <v>11.718699111328078</v>
-      </c>
-      <c r="AD19" t="n" s="0">
-        <v>11.718699111327787</v>
-      </c>
-      <c r="AE19" t="n" s="0">
-        <v>1.9920308918648941</v>
-      </c>
       <c r="AF19" t="n" s="0">
-        <v>1.9920308923207546</v>
+        <v>1.9920308922763883</v>
       </c>
     </row>
     <row r="20">
       <c r="C20" t="n" s="0">
-        <v>3.308141221756041E-4</v>
+        <v>3.0933547152294953E-4</v>
       </c>
       <c r="D20" t="n" s="0">
-        <v>5.321442580302001E-4</v>
+        <v>6.415111425701822E-4</v>
       </c>
       <c r="E20" t="n" s="0">
-        <v>6.393590219175385E-4</v>
+        <v>4.463092639533402E-4</v>
       </c>
       <c r="F20" t="n" s="0">
-        <v>6.560638283179053E-4</v>
+        <v>5.093820102934946E-4</v>
       </c>
       <c r="G20" t="n" s="0">
-        <v>3.810118813918065E-4</v>
+        <v>3.2542000608071805E-4</v>
       </c>
       <c r="H20" t="n" s="0">
-        <v>3.53200041054643E-4</v>
+        <v>4.4318996150984264E-4</v>
       </c>
       <c r="I20" t="n" s="0">
-        <v>6.115918555343183E-4</v>
+        <v>5.219086080965231E-4</v>
       </c>
       <c r="J20" t="n" s="0">
-        <v>5.622372125219533E-4</v>
+        <v>4.521046303542972E-4</v>
       </c>
       <c r="K20" t="n" s="0">
-        <v>3.140103326669789E-4</v>
+        <v>6.770739715080113E-4</v>
       </c>
       <c r="L20" t="n" s="0">
-        <v>5.298453388181491E-4</v>
+        <v>4.071066026893185E-4</v>
       </c>
       <c r="M20" t="n" s="0">
-        <v>4.648137982993812E-4</v>
+        <v>3.0827740002674147E-4</v>
       </c>
       <c r="N20" t="n" s="0">
-        <v>3.324289725979609E-4</v>
+        <v>5.999489246428031E-4</v>
       </c>
       <c r="O20" t="n" s="0">
-        <v>3.729100131269546E-4</v>
+        <v>6.372126389498986E-4</v>
       </c>
       <c r="P20" t="n" s="0">
-        <v>0.0016136398611190097</v>
+        <v>5.760728446686207E-4</v>
       </c>
       <c r="Q20" t="n" s="0">
-        <v>5.608711199356443E-4</v>
+        <v>4.626747857351084E-4</v>
       </c>
       <c r="R20" t="n" s="0">
-        <v>3.132128108509449E-4</v>
+        <v>5.921852967547031E-4</v>
       </c>
       <c r="S20" t="n" s="0">
-        <v>3.284693862185457E-4</v>
+        <v>6.952901633939257E-4</v>
       </c>
       <c r="T20" t="n" s="0">
-        <v>3.958992036964926E-4</v>
+        <v>4.0945330413257535E-4</v>
       </c>
       <c r="U20" t="n" s="0">
-        <v>6.774000552202004E-4</v>
+        <v>3.115949698758263E-4</v>
       </c>
       <c r="V20" t="n" s="0">
-        <v>6.458742909817348E-4</v>
+        <v>3.3073450073475765E-4</v>
       </c>
       <c r="W20" t="n" s="0">
-        <v>3.6920103609033053E-4</v>
+        <v>5.854941430057244E-4</v>
       </c>
       <c r="X20" t="n" s="0">
-        <v>4.513162936158967E-4</v>
+        <v>3.1048536457629704E-4</v>
       </c>
       <c r="Y20" t="n" s="0">
-        <v>3.152744274430148E-4</v>
+        <v>4.1157224589565634E-4</v>
       </c>
       <c r="Z20" t="n" s="0">
-        <v>4.3119212430924313E-4</v>
+        <v>3.1208164648642496E-4</v>
       </c>
       <c r="AA20" t="n" s="0">
-        <v>3.481650857165793E-4</v>
+        <v>3.4995795962821524E-4</v>
       </c>
       <c r="AB20" t="n" s="0">
-        <v>5.194735290048788E-4</v>
+        <v>6.435324785915229E-4</v>
       </c>
       <c r="AC20" t="n" s="0">
-        <v>4.155164084669077E-4</v>
+        <v>5.983994871919517E-4</v>
       </c>
       <c r="AD20" t="n" s="0">
-        <v>5.444240033677388E-4</v>
+        <v>5.817382051596394E-4</v>
       </c>
       <c r="AE20" t="n" s="0">
-        <v>7.063854957197401E-4</v>
+        <v>5.052276791899124E-4</v>
       </c>
       <c r="AF20" t="n" s="0">
-        <v>4.963947859779636E-4</v>
+        <v>5.990440874739891E-4</v>
       </c>
     </row>
     <row r="21">
       <c r="C21" t="n" s="0">
-        <v>-1.0316284263518218</v>
+        <v>-1.0316281524712292</v>
       </c>
       <c r="D21" t="n" s="0">
-        <v>-1.031628449564669</v>
+        <v>-1.0316284516154384</v>
       </c>
       <c r="E21" t="n" s="0">
-        <v>-1.0316284530619815</v>
+        <v>-1.0316283531374077</v>
       </c>
       <c r="F21" t="n" s="0">
-        <v>-1.0316282242395531</v>
+        <v>-1.03162839400356</v>
       </c>
       <c r="G21" t="n" s="0">
-        <v>-1.0316282419058425</v>
+        <v>-1.031628416544944</v>
       </c>
       <c r="H21" t="n" s="0">
-        <v>-1.0316283949982912</v>
+        <v>-1.0316284397757574</v>
       </c>
       <c r="I21" t="n" s="0">
-        <v>-1.031628443545232</v>
+        <v>-1.0316284497308152</v>
       </c>
       <c r="J21" t="n" s="0">
-        <v>-1.031628433350038</v>
+        <v>-1.0316284398021651</v>
       </c>
       <c r="K21" t="n" s="0">
-        <v>-1.031628392912847</v>
+        <v>-1.0316284440030692</v>
       </c>
       <c r="L21" t="n" s="0">
-        <v>-1.0316281743039102</v>
+        <v>-1.0316284438363237</v>
       </c>
       <c r="M21" t="n" s="0">
-        <v>-1.0316283063421405</v>
+        <v>-1.0316283067228602</v>
       </c>
       <c r="N21" t="n" s="0">
-        <v>-1.0316284452151405</v>
+        <v>-1.0316284010037409</v>
       </c>
       <c r="O21" t="n" s="0">
-        <v>-1.0316284038569263</v>
+        <v>-1.0316282431159054</v>
       </c>
       <c r="P21" t="n" s="0">
-        <v>-1.0316283715940715</v>
+        <v>-1.0316284505806999</v>
       </c>
       <c r="Q21" t="n" s="0">
-        <v>-1.0316284484209182</v>
+        <v>-1.0316284444404993</v>
       </c>
       <c r="R21" t="n" s="0">
-        <v>-1.0316283699116666</v>
+        <v>-1.0316283328917875</v>
       </c>
       <c r="S21" t="n" s="0">
-        <v>-1.0316283581854373</v>
+        <v>-1.0316284487036564</v>
       </c>
       <c r="T21" t="n" s="0">
-        <v>-1.0316282754993538</v>
+        <v>-1.0316281588628557</v>
       </c>
       <c r="U21" t="n" s="0">
-        <v>-1.0316284511115539</v>
+        <v>-1.0316284254155874</v>
       </c>
       <c r="V21" t="n" s="0">
-        <v>-1.0316281599929185</v>
+        <v>-1.0316283173771563</v>
       </c>
       <c r="W21" t="n" s="0">
-        <v>-1.0316284258841704</v>
+        <v>-1.0316284311803863</v>
       </c>
       <c r="X21" t="n" s="0">
-        <v>-1.0316284505444768</v>
+        <v>-1.0316283535547262</v>
       </c>
       <c r="Y21" t="n" s="0">
-        <v>-1.0316284387612487</v>
+        <v>-1.03162841900561</v>
       </c>
       <c r="Z21" t="n" s="0">
-        <v>-1.0316283833432611</v>
+        <v>-1.0316283240508162</v>
       </c>
       <c r="AA21" t="n" s="0">
-        <v>-1.0316284348086204</v>
+        <v>-1.0316284416510793</v>
       </c>
       <c r="AB21" t="n" s="0">
-        <v>-1.0316284378845075</v>
+        <v>-1.0316283976814127</v>
       </c>
       <c r="AC21" t="n" s="0">
-        <v>-1.0316283775795727</v>
+        <v>-1.0316284496993937</v>
       </c>
       <c r="AD21" t="n" s="0">
-        <v>-1.0316283087301998</v>
+        <v>-1.0316283918545435</v>
       </c>
       <c r="AE21" t="n" s="0">
-        <v>-1.0316284306163628</v>
+        <v>-1.0316283935327042</v>
       </c>
       <c r="AF21" t="n" s="0">
-        <v>-1.03162841627472</v>
+        <v>-1.0316284261931459</v>
       </c>
     </row>
     <row r="22">
       <c r="C22" t="n" s="0">
-        <v>0.39788797707428003</v>
+        <v>0.397892139741705</v>
       </c>
       <c r="D22" t="n" s="0">
-        <v>0.3978879351320508</v>
+        <v>0.39788808761432826</v>
       </c>
       <c r="E22" t="n" s="0">
-        <v>0.39789025476846795</v>
+        <v>0.3978876243533005</v>
       </c>
       <c r="F22" t="n" s="0">
-        <v>0.39788757812946507</v>
+        <v>0.3978879101281283</v>
       </c>
       <c r="G22" t="n" s="0">
-        <v>0.39788835425905056</v>
+        <v>0.3978882905200365</v>
       </c>
       <c r="H22" t="n" s="0">
-        <v>0.3978880272458678</v>
+        <v>0.397888134714778</v>
       </c>
       <c r="I22" t="n" s="0">
-        <v>0.39788791504110854</v>
+        <v>0.3978916080838868</v>
       </c>
       <c r="J22" t="n" s="0">
-        <v>0.39788744482496163</v>
+        <v>0.3978907676151522</v>
       </c>
       <c r="K22" t="n" s="0">
-        <v>0.3978876575960193</v>
+        <v>0.39788787777483314</v>
       </c>
       <c r="L22" t="n" s="0">
-        <v>0.39788845029085884</v>
+        <v>0.3978885987906011</v>
       </c>
       <c r="M22" t="n" s="0">
-        <v>0.3978895810163561</v>
+        <v>0.39788761132544437</v>
       </c>
       <c r="N22" t="n" s="0">
-        <v>0.39788805203681754</v>
+        <v>0.39788801869280377</v>
       </c>
       <c r="O22" t="n" s="0">
-        <v>0.3978895915617109</v>
+        <v>0.397888602175378</v>
       </c>
       <c r="P22" t="n" s="0">
-        <v>0.39788800794813106</v>
+        <v>0.39788873688098114</v>
       </c>
       <c r="Q22" t="n" s="0">
-        <v>0.3978895174064281</v>
+        <v>0.397887440126965</v>
       </c>
       <c r="R22" t="n" s="0">
-        <v>0.39788809499527744</v>
+        <v>0.39788901149511346</v>
       </c>
       <c r="S22" t="n" s="0">
-        <v>0.3978893825054577</v>
+        <v>0.39788871672854675</v>
       </c>
       <c r="T22" t="n" s="0">
-        <v>0.3978883736527177</v>
+        <v>0.3978885320006711</v>
       </c>
       <c r="U22" t="n" s="0">
-        <v>0.39788769430320237</v>
+        <v>0.3978896432283783</v>
       </c>
       <c r="V22" t="n" s="0">
-        <v>0.39788847922022974</v>
+        <v>0.3978895805260283</v>
       </c>
       <c r="W22" t="n" s="0">
-        <v>0.3978874429619914</v>
+        <v>0.39788883189384805</v>
       </c>
       <c r="X22" t="n" s="0">
-        <v>0.39788789445121964</v>
+        <v>0.39788758754199804</v>
       </c>
       <c r="Y22" t="n" s="0">
-        <v>0.3978876551044923</v>
+        <v>0.3978875180159829</v>
       </c>
       <c r="Z22" t="n" s="0">
-        <v>0.39788957345994547</v>
+        <v>0.39788785816424443</v>
       </c>
       <c r="AA22" t="n" s="0">
-        <v>0.39789013253149896</v>
+        <v>0.39788890062620474</v>
       </c>
       <c r="AB22" t="n" s="0">
-        <v>0.39788962451630994</v>
+        <v>0.39788740251510646</v>
       </c>
       <c r="AC22" t="n" s="0">
-        <v>0.3978882710115972</v>
+        <v>0.39788883857826285</v>
       </c>
       <c r="AD22" t="n" s="0">
-        <v>0.3978899429494991</v>
+        <v>0.3978907964698486</v>
       </c>
       <c r="AE22" t="n" s="0">
-        <v>0.39788747360025667</v>
+        <v>0.39789219886819716</v>
       </c>
       <c r="AF22" t="n" s="0">
-        <v>0.3978883465928682</v>
+        <v>0.39788770251604966</v>
       </c>
     </row>
     <row r="23">
       <c r="C23" t="n" s="0">
-        <v>3.0000019170254206</v>
+        <v>3.002676646491116</v>
       </c>
       <c r="D23" t="n" s="0">
-        <v>3.0000000728128144</v>
+        <v>3.0000002573336957</v>
       </c>
       <c r="E23" t="n" s="0">
-        <v>3.008483879441659</v>
+        <v>3.0003887013343635</v>
       </c>
       <c r="F23" t="n" s="0">
-        <v>3.0027721500318156</v>
+        <v>3.0000000198155794</v>
       </c>
       <c r="G23" t="n" s="0">
-        <v>3.00041109449307</v>
+        <v>3.0000018902366947</v>
       </c>
       <c r="H23" t="n" s="0">
-        <v>3.000309515362189</v>
+        <v>3.005240854414511</v>
       </c>
       <c r="I23" t="n" s="0">
-        <v>3.000480919367947</v>
+        <v>3.000016392681802</v>
       </c>
       <c r="J23" t="n" s="0">
-        <v>3.0000000845081787</v>
+        <v>3.0000380142692267</v>
       </c>
       <c r="K23" t="n" s="0">
-        <v>3.003855684452125</v>
+        <v>3.0000225058812697</v>
       </c>
       <c r="L23" t="n" s="0">
-        <v>3.0000049622654257</v>
+        <v>3.000002251811419</v>
       </c>
       <c r="M23" t="n" s="0">
-        <v>3.000003845579098</v>
+        <v>3.000000319663611</v>
       </c>
       <c r="N23" t="n" s="0">
-        <v>3.0000000034321674</v>
+        <v>3.000135898109459</v>
       </c>
       <c r="O23" t="n" s="0">
-        <v>3.0000000731718246</v>
+        <v>3.0000008184986546</v>
       </c>
       <c r="P23" t="n" s="0">
-        <v>3.0000000610024093</v>
+        <v>3.0000007979165466</v>
       </c>
       <c r="Q23" t="n" s="0">
-        <v>3.0000001044985174</v>
+        <v>3.0000072685078214</v>
       </c>
       <c r="R23" t="n" s="0">
-        <v>3.0000004565264766</v>
+        <v>3.000000100260824</v>
       </c>
       <c r="S23" t="n" s="0">
-        <v>3.0000000974457253</v>
+        <v>3.000053498806209</v>
       </c>
       <c r="T23" t="n" s="0">
-        <v>3.000001550476281</v>
+        <v>3.000033892524381</v>
       </c>
       <c r="U23" t="n" s="0">
-        <v>3.0000213266005558</v>
+        <v>3.000002381865118</v>
       </c>
       <c r="V23" t="n" s="0">
-        <v>3.0011758719829937</v>
+        <v>3.0000180058160826</v>
       </c>
       <c r="W23" t="n" s="0">
-        <v>3.0000968902262373</v>
+        <v>3.0000003713508994</v>
       </c>
       <c r="X23" t="n" s="0">
-        <v>3.0000665179015806</v>
+        <v>3.0000048491782114</v>
       </c>
       <c r="Y23" t="n" s="0">
-        <v>3.0000205604788004</v>
+        <v>3.0000000177741777</v>
       </c>
       <c r="Z23" t="n" s="0">
-        <v>3.0000197934825574</v>
+        <v>3.001026732753191</v>
       </c>
       <c r="AA23" t="n" s="0">
-        <v>3.0005392143699203</v>
+        <v>3.0000173212501746</v>
       </c>
       <c r="AB23" t="n" s="0">
-        <v>3.0000542560430645</v>
+        <v>3.000003337885849</v>
       </c>
       <c r="AC23" t="n" s="0">
-        <v>3.000000018247829</v>
+        <v>3.0044425668763886</v>
       </c>
       <c r="AD23" t="n" s="0">
-        <v>3.0000018595574156</v>
+        <v>3.004430211480351</v>
       </c>
       <c r="AE23" t="n" s="0">
-        <v>3.000010515819072</v>
+        <v>3.005861759302792</v>
       </c>
       <c r="AF23" t="n" s="0">
-        <v>3.0083882700718054</v>
+        <v>3.001586702919677</v>
       </c>
     </row>
     <row r="24">
       <c r="C24" t="n" s="0">
-        <v>-3.8593640134645737</v>
+        <v>-3.8599912632246225</v>
       </c>
       <c r="D24" t="n" s="0">
-        <v>-3.8616773549351793</v>
+        <v>-3.8627605384351575</v>
       </c>
       <c r="E24" t="n" s="0">
-        <v>-3.8624231236412885</v>
+        <v>-3.8615997973033025</v>
       </c>
       <c r="F24" t="n" s="0">
-        <v>-3.8594495545449186</v>
+        <v>-3.861620017075684</v>
       </c>
       <c r="G24" t="n" s="0">
-        <v>-3.8627611313777557</v>
+        <v>-3.8621186396429943</v>
       </c>
       <c r="H24" t="n" s="0">
-        <v>-3.8617736611966738</v>
+        <v>-3.862599879196451</v>
       </c>
       <c r="I24" t="n" s="0">
-        <v>-3.8625889232438295</v>
+        <v>-3.8620575344800177</v>
       </c>
       <c r="J24" t="n" s="0">
-        <v>-3.862772675524142</v>
+        <v>-3.862745093111545</v>
       </c>
       <c r="K24" t="n" s="0">
-        <v>-3.8619898375375956</v>
+        <v>-3.862742583847763</v>
       </c>
       <c r="L24" t="n" s="0">
-        <v>-3.862305249092522</v>
+        <v>-3.86133862557974</v>
       </c>
       <c r="M24" t="n" s="0">
-        <v>-3.8573715354102758</v>
+        <v>-3.861761265463778</v>
       </c>
       <c r="N24" t="n" s="0">
-        <v>-3.861684205164668</v>
+        <v>-3.86176727191338</v>
       </c>
       <c r="O24" t="n" s="0">
-        <v>-3.8540511177254473</v>
+        <v>-3.8625216830082914</v>
       </c>
       <c r="P24" t="n" s="0">
-        <v>-3.8625040190730093</v>
+        <v>-3.8588608179304114</v>
       </c>
       <c r="Q24" t="n" s="0">
-        <v>-3.8620355540075018</v>
+        <v>-3.8624996138293355</v>
       </c>
       <c r="R24" t="n" s="0">
-        <v>-3.862620813804444</v>
+        <v>-3.862581715876788</v>
       </c>
       <c r="S24" t="n" s="0">
-        <v>-3.861827057559541</v>
+        <v>-3.8623296712999813</v>
       </c>
       <c r="T24" t="n" s="0">
-        <v>-3.8602581743424396</v>
+        <v>-3.8626821436762473</v>
       </c>
       <c r="U24" t="n" s="0">
-        <v>-3.860612437170033</v>
+        <v>-3.8623636284917344</v>
       </c>
       <c r="V24" t="n" s="0">
-        <v>-3.860847534849916</v>
+        <v>-3.8613621454467357</v>
       </c>
       <c r="W24" t="n" s="0">
-        <v>-3.8614949889606134</v>
+        <v>-3.8614599701594976</v>
       </c>
       <c r="X24" t="n" s="0">
-        <v>-3.861820495968553</v>
+        <v>-3.8627730007926036</v>
       </c>
       <c r="Y24" t="n" s="0">
-        <v>-3.8618583332163654</v>
+        <v>-3.8607953761703615</v>
       </c>
       <c r="Z24" t="n" s="0">
-        <v>-3.8623986630919145</v>
+        <v>-3.8627809017663113</v>
       </c>
       <c r="AA24" t="n" s="0">
-        <v>-3.860210149700899</v>
+        <v>-3.8627764888615155</v>
       </c>
       <c r="AB24" t="n" s="0">
-        <v>-3.861311041577796</v>
+        <v>-3.8610817332245264</v>
       </c>
       <c r="AC24" t="n" s="0">
-        <v>-3.862537486330038</v>
+        <v>-3.8619175009461983</v>
       </c>
       <c r="AD24" t="n" s="0">
-        <v>-3.859936186146784</v>
+        <v>-3.8608598602947315</v>
       </c>
       <c r="AE24" t="n" s="0">
-        <v>-3.8626685235346856</v>
+        <v>-3.862472022179446</v>
       </c>
       <c r="AF24" t="n" s="0">
-        <v>-3.8614692560913584</v>
+        <v>-3.860076226825624</v>
       </c>
     </row>
     <row r="25">
       <c r="C25" t="n" s="0">
-        <v>-3.3219737939660945</v>
+        <v>-3.3219715684412883</v>
       </c>
       <c r="D25" t="n" s="0">
-        <v>-3.321947751958625</v>
+        <v>-3.321901551865567</v>
       </c>
       <c r="E25" t="n" s="0">
-        <v>-3.3218881422658053</v>
+        <v>-3.3219798923276693</v>
       </c>
       <c r="F25" t="n" s="0">
-        <v>-3.321980887696234</v>
+        <v>-3.321979973634273</v>
       </c>
       <c r="G25" t="n" s="0">
-        <v>-3.321985586249143</v>
+        <v>-3.321978613771237</v>
       </c>
       <c r="H25" t="n" s="0">
-        <v>-3.3219799021582754</v>
+        <v>-3.3219770663733446</v>
       </c>
       <c r="I25" t="n" s="0">
-        <v>-3.3219603886498836</v>
+        <v>-3.321987030891525</v>
       </c>
       <c r="J25" t="n" s="0">
-        <v>-3.3219785106239414</v>
+        <v>-3.3219422016083673</v>
       </c>
       <c r="K25" t="n" s="0">
-        <v>-3.3219584822044164</v>
+        <v>-3.3219861376672495</v>
       </c>
       <c r="L25" t="n" s="0">
-        <v>-3.321983474654059</v>
+        <v>-3.3219792011395315</v>
       </c>
       <c r="M25" t="n" s="0">
-        <v>-3.3219874233894475</v>
+        <v>-3.3219912488618606</v>
       </c>
       <c r="N25" t="n" s="0">
-        <v>-3.3219833213953014</v>
+        <v>-3.321967624051529</v>
       </c>
       <c r="O25" t="n" s="0">
-        <v>-3.3219860486804604</v>
+        <v>-3.3219599319364046</v>
       </c>
       <c r="P25" t="n" s="0">
-        <v>-3.321984773975808</v>
+        <v>-3.321984846931347</v>
       </c>
       <c r="Q25" t="n" s="0">
-        <v>-3.321981969690482</v>
+        <v>-3.3219572194560705</v>
       </c>
       <c r="R25" t="n" s="0">
-        <v>-3.3219905413928927</v>
+        <v>-3.3219771452363664</v>
       </c>
       <c r="S25" t="n" s="0">
-        <v>-3.3219822547779243</v>
+        <v>-3.3219730743064635</v>
       </c>
       <c r="T25" t="n" s="0">
-        <v>-3.3219768811260626</v>
+        <v>-3.3219763444198693</v>
       </c>
       <c r="U25" t="n" s="0">
-        <v>-3.3219508258588077</v>
+        <v>-3.3219894074372434</v>
       </c>
       <c r="V25" t="n" s="0">
-        <v>-3.321989654655154</v>
+        <v>-3.321978285324742</v>
       </c>
       <c r="W25" t="n" s="0">
-        <v>-3.321993692738126</v>
+        <v>-3.3219637594837947</v>
       </c>
       <c r="X25" t="n" s="0">
-        <v>-3.3219752838225136</v>
+        <v>-3.321984104212151</v>
       </c>
       <c r="Y25" t="n" s="0">
-        <v>-3.321988538860228</v>
+        <v>-3.321987001890665</v>
       </c>
       <c r="Z25" t="n" s="0">
-        <v>-3.3219719438998268</v>
+        <v>-3.3219818637642278</v>
       </c>
       <c r="AA25" t="n" s="0">
-        <v>-3.3219643351186017</v>
+        <v>-3.3219877679525167</v>
       </c>
       <c r="AB25" t="n" s="0">
-        <v>-3.3219667701292854</v>
+        <v>-3.321991188815615</v>
       </c>
       <c r="AC25" t="n" s="0">
-        <v>-3.3219881713778006</v>
+        <v>-3.3219805719219035</v>
       </c>
       <c r="AD25" t="n" s="0">
-        <v>-3.3219800071159633</v>
+        <v>-3.3219943412231734</v>
       </c>
       <c r="AE25" t="n" s="0">
-        <v>-3.3219652330236706</v>
+        <v>-3.3219454174371084</v>
       </c>
       <c r="AF25" t="n" s="0">
-        <v>-3.321986049026484</v>
+        <v>-3.3219838288915526</v>
       </c>
     </row>
     <row r="26">
       <c r="C26" t="n" s="0">
-        <v>-10.1526262138922</v>
+        <v>-10.150706562895612</v>
       </c>
       <c r="D26" t="n" s="0">
-        <v>-10.15117747284005</v>
+        <v>-10.15177488535799</v>
       </c>
       <c r="E26" t="n" s="0">
-        <v>-10.151120609869785</v>
+        <v>-10.152234647889276</v>
       </c>
       <c r="F26" t="n" s="0">
-        <v>-10.15201690506811</v>
+        <v>-10.151457826811214</v>
       </c>
       <c r="G26" t="n" s="0">
-        <v>-10.151645158273977</v>
+        <v>-10.152220093401468</v>
       </c>
       <c r="H26" t="n" s="0">
-        <v>-10.15131214348625</v>
+        <v>-10.15115441072535</v>
       </c>
       <c r="I26" t="n" s="0">
-        <v>-10.152938297711597</v>
+        <v>-10.152348412519284</v>
       </c>
       <c r="J26" t="n" s="0">
-        <v>-10.151088194288002</v>
+        <v>-10.152590954255478</v>
       </c>
       <c r="K26" t="n" s="0">
-        <v>-10.152154131639634</v>
+        <v>-10.151897974406236</v>
       </c>
       <c r="L26" t="n" s="0">
-        <v>-10.152088258124785</v>
+        <v>-10.152089510697893</v>
       </c>
       <c r="M26" t="n" s="0">
-        <v>-10.151313121913095</v>
+        <v>-10.150859442987688</v>
       </c>
       <c r="N26" t="n" s="0">
-        <v>-10.152276640553406</v>
+        <v>-10.152732378359076</v>
       </c>
       <c r="O26" t="n" s="0">
-        <v>-10.15213685919788</v>
+        <v>-10.152405096537429</v>
       </c>
       <c r="P26" t="n" s="0">
-        <v>-10.152100185464343</v>
+        <v>-10.151167359849584</v>
       </c>
       <c r="Q26" t="n" s="0">
-        <v>-10.151560423681339</v>
+        <v>-10.152145345189313</v>
       </c>
       <c r="R26" t="n" s="0">
-        <v>-10.151299391841254</v>
+        <v>-10.15149196112672</v>
       </c>
       <c r="S26" t="n" s="0">
-        <v>-10.15257212813111</v>
+        <v>-10.147839747493627</v>
       </c>
       <c r="T26" t="n" s="0">
-        <v>-10.151462088551373</v>
+        <v>-10.15309543781159</v>
       </c>
       <c r="U26" t="n" s="0">
-        <v>-10.151535980121976</v>
+        <v>-10.151577258710407</v>
       </c>
       <c r="V26" t="n" s="0">
-        <v>-10.152128194830048</v>
+        <v>-10.150968404759725</v>
       </c>
       <c r="W26" t="n" s="0">
-        <v>-10.151815518103286</v>
+        <v>-10.152418285001454</v>
       </c>
       <c r="X26" t="n" s="0">
-        <v>-10.15212835970336</v>
+        <v>-10.15197092853605</v>
       </c>
       <c r="Y26" t="n" s="0">
-        <v>-10.152118120906396</v>
+        <v>-10.151658569370289</v>
       </c>
       <c r="Z26" t="n" s="0">
-        <v>-10.151279765615916</v>
+        <v>-10.15152856495055</v>
       </c>
       <c r="AA26" t="n" s="0">
-        <v>-10.151421337060661</v>
+        <v>-10.15264407224326</v>
       </c>
       <c r="AB26" t="n" s="0">
-        <v>-10.152400615468192</v>
+        <v>-10.150468283133415</v>
       </c>
       <c r="AC26" t="n" s="0">
-        <v>-10.151978070065324</v>
+        <v>-10.152672023671602</v>
       </c>
       <c r="AD26" t="n" s="0">
-        <v>-10.152603685328955</v>
+        <v>-10.152562115579649</v>
       </c>
       <c r="AE26" t="n" s="0">
-        <v>-10.152035673845264</v>
+        <v>-10.15160764166226</v>
       </c>
       <c r="AF26" t="n" s="0">
-        <v>-10.151964777759874</v>
+        <v>-10.150262010078793</v>
       </c>
     </row>
     <row r="27">
       <c r="C27" t="n" s="0">
-        <v>-10.400556045790152</v>
+        <v>-10.401256625330095</v>
       </c>
       <c r="D27" t="n" s="0">
-        <v>-10.401025497046854</v>
+        <v>-10.401293221906187</v>
       </c>
       <c r="E27" t="n" s="0">
-        <v>-10.402159561445702</v>
+        <v>-10.402209486673796</v>
       </c>
       <c r="F27" t="n" s="0">
-        <v>-10.402272804636388</v>
+        <v>-10.402143015373907</v>
       </c>
       <c r="G27" t="n" s="0">
-        <v>-10.401924242841808</v>
+        <v>-10.402429352107713</v>
       </c>
       <c r="H27" t="n" s="0">
-        <v>-10.400881089661452</v>
+        <v>-10.401392811008924</v>
       </c>
       <c r="I27" t="n" s="0">
-        <v>-10.401306463905605</v>
+        <v>-10.402108164050963</v>
       </c>
       <c r="J27" t="n" s="0">
-        <v>-10.402689398056083</v>
+        <v>-10.401757651264953</v>
       </c>
       <c r="K27" t="n" s="0">
-        <v>-10.401060454396541</v>
+        <v>-10.401945776760995</v>
       </c>
       <c r="L27" t="n" s="0">
-        <v>-10.400701954064482</v>
+        <v>-10.402330392010978</v>
       </c>
       <c r="M27" t="n" s="0">
-        <v>-10.401931368690338</v>
+        <v>-10.400535993507702</v>
       </c>
       <c r="N27" t="n" s="0">
-        <v>-10.400922583492777</v>
+        <v>-10.40169653483259</v>
       </c>
       <c r="O27" t="n" s="0">
-        <v>-10.40257771201838</v>
+        <v>-10.399961296782067</v>
       </c>
       <c r="P27" t="n" s="0">
-        <v>-10.401850022776998</v>
+        <v>-10.400953473737221</v>
       </c>
       <c r="Q27" t="n" s="0">
-        <v>-3.7241832444079055</v>
+        <v>-10.402334168250674</v>
       </c>
       <c r="R27" t="n" s="0">
-        <v>-10.402227309141644</v>
+        <v>-10.401335590133577</v>
       </c>
       <c r="S27" t="n" s="0">
-        <v>-10.399792817640932</v>
+        <v>-10.40214810054117</v>
       </c>
       <c r="T27" t="n" s="0">
-        <v>-10.40031064397445</v>
+        <v>-10.402338216697919</v>
       </c>
       <c r="U27" t="n" s="0">
-        <v>-10.40175245551955</v>
+        <v>-10.401145574155002</v>
       </c>
       <c r="V27" t="n" s="0">
-        <v>-10.401271901935367</v>
+        <v>-10.402523583189208</v>
       </c>
       <c r="W27" t="n" s="0">
-        <v>-10.401872186656528</v>
+        <v>-10.4024203135367</v>
       </c>
       <c r="X27" t="n" s="0">
-        <v>-10.402127845368526</v>
+        <v>-10.400676281216153</v>
       </c>
       <c r="Y27" t="n" s="0">
-        <v>-10.401883894274924</v>
+        <v>-10.402695430399875</v>
       </c>
       <c r="Z27" t="n" s="0">
-        <v>-10.402241448083327</v>
+        <v>-10.40179722947111</v>
       </c>
       <c r="AA27" t="n" s="0">
-        <v>-10.402726014626172</v>
+        <v>-10.402018399789476</v>
       </c>
       <c r="AB27" t="n" s="0">
-        <v>-10.401604721294873</v>
+        <v>-10.401603957764138</v>
       </c>
       <c r="AC27" t="n" s="0">
-        <v>-10.402113078487414</v>
+        <v>-10.3987720358565</v>
       </c>
       <c r="AD27" t="n" s="0">
-        <v>-10.401689689195987</v>
+        <v>-10.4017874751531</v>
       </c>
       <c r="AE27" t="n" s="0">
-        <v>-10.402078786133657</v>
+        <v>-10.399502087489758</v>
       </c>
       <c r="AF27" t="n" s="0">
-        <v>-10.40013088975027</v>
+        <v>-10.402265427168574</v>
       </c>
     </row>
     <row r="28">
       <c r="C28" t="n" s="0">
-        <v>-10.53133439222762</v>
+        <v>-10.534827889708426</v>
       </c>
       <c r="D28" t="n" s="0">
-        <v>-10.535413083747844</v>
+        <v>-10.53468919438118</v>
       </c>
       <c r="E28" t="n" s="0">
-        <v>-10.53541989249725</v>
+        <v>-10.534091274778795</v>
       </c>
       <c r="F28" t="n" s="0">
-        <v>-10.535576211300125</v>
+        <v>-10.535421897875958</v>
       </c>
       <c r="G28" t="n" s="0">
-        <v>-10.535766233574419</v>
+        <v>-10.53500433245413</v>
       </c>
       <c r="H28" t="n" s="0">
-        <v>-10.53532632691462</v>
+        <v>-10.534932399681125</v>
       </c>
       <c r="I28" t="n" s="0">
-        <v>-10.534881536656833</v>
+        <v>-10.535217178692006</v>
       </c>
       <c r="J28" t="n" s="0">
-        <v>-10.535570523492105</v>
+        <v>-10.535703865107013</v>
       </c>
       <c r="K28" t="n" s="0">
-        <v>-10.53494918930863</v>
+        <v>-10.536048775384389</v>
       </c>
       <c r="L28" t="n" s="0">
-        <v>-10.533925372476903</v>
+        <v>-10.534903590880244</v>
       </c>
       <c r="M28" t="n" s="0">
-        <v>-10.534954569678082</v>
+        <v>-10.534530942774067</v>
       </c>
       <c r="N28" t="n" s="0">
-        <v>-10.535089193764628</v>
+        <v>-10.535529576056012</v>
       </c>
       <c r="O28" t="n" s="0">
-        <v>-10.536273680360013</v>
+        <v>-10.53568104075203</v>
       </c>
       <c r="P28" t="n" s="0">
-        <v>-10.53619188868565</v>
+        <v>-10.532563566381068</v>
       </c>
       <c r="Q28" t="n" s="0">
-        <v>-10.533506514341704</v>
+        <v>-10.535749260436017</v>
       </c>
       <c r="R28" t="n" s="0">
-        <v>-10.535844429438862</v>
+        <v>-10.536119655968072</v>
       </c>
       <c r="S28" t="n" s="0">
-        <v>-10.535554105961575</v>
+        <v>-10.533325613910334</v>
       </c>
       <c r="T28" t="n" s="0">
-        <v>-10.534207102750823</v>
+        <v>-10.535749346079891</v>
       </c>
       <c r="U28" t="n" s="0">
-        <v>-10.535601444732906</v>
+        <v>-10.53422138451843</v>
       </c>
       <c r="V28" t="n" s="0">
-        <v>-10.534433371785273</v>
+        <v>-10.53484195355643</v>
       </c>
       <c r="W28" t="n" s="0">
-        <v>-10.536024747845241</v>
+        <v>-10.534523288620832</v>
       </c>
       <c r="X28" t="n" s="0">
-        <v>-10.535577580542494</v>
+        <v>-10.533672314074893</v>
       </c>
       <c r="Y28" t="n" s="0">
-        <v>-10.535122204398512</v>
+        <v>-10.534964687148284</v>
       </c>
       <c r="Z28" t="n" s="0">
-        <v>-10.536031805846932</v>
+        <v>-10.534104029509932</v>
       </c>
       <c r="AA28" t="n" s="0">
-        <v>-10.535089577519503</v>
+        <v>-10.534514480364923</v>
       </c>
       <c r="AB28" t="n" s="0">
-        <v>-10.53616714483023</v>
+        <v>-10.535044792003285</v>
       </c>
       <c r="AC28" t="n" s="0">
-        <v>-10.533980200770332</v>
+        <v>-10.534762113455658</v>
       </c>
       <c r="AD28" t="n" s="0">
-        <v>-10.535137710827412</v>
+        <v>-10.534180405624943</v>
       </c>
       <c r="AE28" t="n" s="0">
-        <v>-10.53508133809258</v>
+        <v>-10.5350563862544</v>
       </c>
       <c r="AF28" t="n" s="0">
-        <v>-10.535712439710247</v>
+        <v>-10.534339618217839</v>
       </c>
     </row>
     <row r="35">
       <c r="C35" t="n" s="0">
-        <v>0.0</v>
+        <v>1.8119914151376761</v>
       </c>
       <c r="D35" t="n" s="0">
-        <v>0.599046796331471</v>
+        <v>5.849112079866011</v>
       </c>
       <c r="E35" t="n" s="0">
-        <v>0.00978130564227977</v>
+        <v>5.482430521603653</v>
       </c>
       <c r="F35" t="n" s="0">
-        <v>7.646489833955252</v>
+        <v>0.42913581877718676</v>
       </c>
       <c r="G35" t="n" s="0">
-        <v>0.2318665090100453</v>
+        <v>3.749511322299803</v>
       </c>
       <c r="H35" t="n" s="0">
-        <v>0.06796564290922934</v>
+        <v>0.722587244035823</v>
       </c>
       <c r="I35" t="n" s="0">
-        <v>0.024991160586661544</v>
+        <v>3.6368380567485064</v>
       </c>
       <c r="J35" t="n" s="0">
-        <v>8.177981816669291E-5</v>
+        <v>1.1381998970751939</v>
       </c>
       <c r="K35" t="n" s="0">
-        <v>1.052850184661432</v>
+        <v>0.48716269097717096</v>
       </c>
       <c r="L35" t="n" s="0">
-        <v>0.37300010159121016</v>
+        <v>7.753800726865793E-4</v>
       </c>
       <c r="M35" t="n" s="0">
-        <v>1.4904713756353192</v>
+        <v>5.115356601468488</v>
       </c>
       <c r="N35" t="n" s="0">
-        <v>0.42707079383026914</v>
+        <v>0.24064579582154905</v>
       </c>
       <c r="O35" t="n" s="0">
-        <v>15.645441095047138</v>
+        <v>5.1705109622855</v>
       </c>
       <c r="P35" t="n" s="0">
-        <v>23.781608225713427</v>
+        <v>0.10230178659637545</v>
       </c>
       <c r="Q35" t="n" s="0">
-        <v>0.00829438213521632</v>
+        <v>1.0727260869907676E-4</v>
       </c>
       <c r="R35" t="n" s="0">
-        <v>0.32397576017389806</v>
+        <v>0.07293652269658243</v>
       </c>
       <c r="S35" t="n" s="0">
-        <v>0.6733308745567371</v>
+        <v>11.394931764962164</v>
       </c>
       <c r="T35" t="n" s="0">
-        <v>4.85993872499944</v>
+        <v>3.487220958269776</v>
       </c>
       <c r="U35" t="n" s="0">
-        <v>0.2342583492235334</v>
+        <v>8.298877534810796</v>
       </c>
       <c r="V35" t="n" s="0">
-        <v>0.014674935054912438</v>
+        <v>0.759788211049591</v>
       </c>
       <c r="W35" t="n" s="0">
-        <v>0.024884126257188447</v>
+        <v>0.8417082723258668</v>
       </c>
       <c r="X35" t="n" s="0">
-        <v>0.03299565342098555</v>
+        <v>0.14167889844023004</v>
       </c>
       <c r="Y35" t="n" s="0">
-        <v>0.011583523233529893</v>
+        <v>4.2889866588012255</v>
       </c>
       <c r="Z35" t="n" s="0">
-        <v>4.60746383687426</v>
+        <v>0.3694382556846705</v>
       </c>
       <c r="AA35" t="n" s="0">
-        <v>0.44534581321194155</v>
+        <v>2.682242152553594</v>
       </c>
       <c r="AB35" t="n" s="0">
-        <v>2.1530059436054687</v>
+        <v>10.629155739026423</v>
       </c>
       <c r="AC35" t="n" s="0">
-        <v>0.10006109897424735</v>
+        <v>4.835845083090114</v>
       </c>
       <c r="AD35" t="n" s="0">
-        <v>0.14801576550285947</v>
+        <v>2.4459240271080183</v>
       </c>
       <c r="AE35" t="n" s="0">
-        <v>0.3244748778641354</v>
+        <v>0.1263999116186898</v>
       </c>
       <c r="AF35" t="n" s="0">
-        <v>1.082782966528391</v>
+        <v>1.6119546644731821</v>
       </c>
     </row>
     <row r="36">
       <c r="C36" t="n" s="0">
-        <v>0.8357682652491949</v>
+        <v>0.027282833613965978</v>
       </c>
       <c r="D36" t="n" s="0">
-        <v>2.566120989277514</v>
+        <v>0.27435058396029244</v>
       </c>
       <c r="E36" t="n" s="0">
-        <v>0.6275093441524688</v>
+        <v>1.063983847377874</v>
       </c>
       <c r="F36" t="n" s="0">
-        <v>0.0</v>
+        <v>1.9986929968454008</v>
       </c>
       <c r="G36" t="n" s="0">
-        <v>1.2932576382088121</v>
+        <v>4.55035506573416</v>
       </c>
       <c r="H36" t="n" s="0">
-        <v>0.01047537647584968</v>
+        <v>2.6192941794166558</v>
       </c>
       <c r="I36" t="n" s="0">
-        <v>1.6048030099762196</v>
+        <v>0.18884576599968372</v>
       </c>
       <c r="J36" t="n" s="0">
-        <v>1.2542702986308696</v>
+        <v>1.1037710110741423</v>
       </c>
       <c r="K36" t="n" s="0">
-        <v>0.681228467269563</v>
+        <v>0.724103549861323</v>
       </c>
       <c r="L36" t="n" s="0">
-        <v>1.555193864337885</v>
+        <v>0.4206969800007777</v>
       </c>
       <c r="M36" t="n" s="0">
-        <v>1.6043803902322382</v>
+        <v>0.5068383293433583</v>
       </c>
       <c r="N36" t="n" s="0">
-        <v>0.07808562631292383</v>
+        <v>2.139199670676419</v>
       </c>
       <c r="O36" t="n" s="0">
-        <v>0.6100397442430031</v>
+        <v>1.506039140544649</v>
       </c>
       <c r="P36" t="n" s="0">
-        <v>0.5125159791246228</v>
+        <v>2.1778148123188545</v>
       </c>
       <c r="Q36" t="n" s="0">
-        <v>0.4107275323874584</v>
+        <v>1.3582593297412908</v>
       </c>
       <c r="R36" t="n" s="0">
-        <v>0.8170788470128869</v>
+        <v>0.24590503917192183</v>
       </c>
       <c r="S36" t="n" s="0">
-        <v>1.2226204830050882</v>
+        <v>1.1600903227068455</v>
       </c>
       <c r="T36" t="n" s="0">
-        <v>2.0833718045512937</v>
+        <v>2.6412054081242413</v>
       </c>
       <c r="U36" t="n" s="0">
-        <v>1.302230439017739</v>
+        <v>0.24822253942845815</v>
       </c>
       <c r="V36" t="n" s="0">
-        <v>2.6282859531953613</v>
+        <v>1.1101318294310203</v>
       </c>
       <c r="W36" t="n" s="0">
-        <v>1.5041682962559997</v>
+        <v>0.40596314884491946</v>
       </c>
       <c r="X36" t="n" s="0">
-        <v>9.744732634166164</v>
+        <v>2.196868673344203</v>
       </c>
       <c r="Y36" t="n" s="0">
-        <v>3.2785737058786917</v>
+        <v>0.5535661497468093</v>
       </c>
       <c r="Z36" t="n" s="0">
-        <v>0.21643705091532772</v>
+        <v>1.1996879138386005</v>
       </c>
       <c r="AA36" t="n" s="0">
-        <v>0.71344309200947</v>
+        <v>0.12181878943113209</v>
       </c>
       <c r="AB36" t="n" s="0">
-        <v>0.1705331787891404</v>
+        <v>3.413611687794298</v>
       </c>
       <c r="AC36" t="n" s="0">
-        <v>0.3156805355837304</v>
+        <v>1.5120710080190132</v>
       </c>
       <c r="AD36" t="n" s="0">
-        <v>2.53644240615696</v>
+        <v>1.7355508895186162</v>
       </c>
       <c r="AE36" t="n" s="0">
-        <v>1.3793924432658142</v>
+        <v>2.6718960789407937</v>
       </c>
       <c r="AF36" t="n" s="0">
-        <v>2.077755508245765</v>
+        <v>2.278691279127908</v>
       </c>
     </row>
     <row r="37">
       <c r="C37" t="n" s="0">
-        <v>61.73028596214628</v>
+        <v>42.77898225455749</v>
       </c>
       <c r="D37" t="n" s="0">
-        <v>537.4863791514063</v>
+        <v>470.416208668403</v>
       </c>
       <c r="E37" t="n" s="0">
-        <v>19.941320850087454</v>
+        <v>4.860407406624084</v>
       </c>
       <c r="F37" t="n" s="0">
-        <v>13.834038123150407</v>
+        <v>14.911680786735193</v>
       </c>
       <c r="G37" t="n" s="0">
-        <v>798.8396478811235</v>
+        <v>362.9755629223475</v>
       </c>
       <c r="H37" t="n" s="0">
-        <v>4.275661187551887</v>
+        <v>76.915811500264</v>
       </c>
       <c r="I37" t="n" s="0">
-        <v>18.1527890990586</v>
+        <v>124.06735919964808</v>
       </c>
       <c r="J37" t="n" s="0">
-        <v>447.2051880949384</v>
+        <v>81.52522063058281</v>
       </c>
       <c r="K37" t="n" s="0">
-        <v>30.11640436863266</v>
+        <v>122.8702941398679</v>
       </c>
       <c r="L37" t="n" s="0">
-        <v>372.8669861723456</v>
+        <v>66.98663888541181</v>
       </c>
       <c r="M37" t="n" s="0">
-        <v>187.54502974195526</v>
+        <v>1.8972255279363015</v>
       </c>
       <c r="N37" t="n" s="0">
-        <v>134.77195863258837</v>
+        <v>76.8363385308887</v>
       </c>
       <c r="O37" t="n" s="0">
-        <v>791.0392821121773</v>
+        <v>100.54219990087994</v>
       </c>
       <c r="P37" t="n" s="0">
-        <v>679.8856797900952</v>
+        <v>86.57954115356573</v>
       </c>
       <c r="Q37" t="n" s="0">
-        <v>170.77301581489843</v>
+        <v>486.28481265077033</v>
       </c>
       <c r="R37" t="n" s="0">
-        <v>6.828568112280416</v>
+        <v>198.60718760729694</v>
       </c>
       <c r="S37" t="n" s="0">
-        <v>157.47610546954797</v>
+        <v>197.0110733107607</v>
       </c>
       <c r="T37" t="n" s="0">
-        <v>13.569582473110513</v>
+        <v>192.2833308387801</v>
       </c>
       <c r="U37" t="n" s="0">
-        <v>16.432068982755048</v>
+        <v>53.60996309317056</v>
       </c>
       <c r="V37" t="n" s="0">
-        <v>61.071302242352786</v>
+        <v>317.8289793768126</v>
       </c>
       <c r="W37" t="n" s="0">
-        <v>148.15155005301443</v>
+        <v>822.270894899805</v>
       </c>
       <c r="X37" t="n" s="0">
-        <v>427.161126082574</v>
+        <v>392.66665791749614</v>
       </c>
       <c r="Y37" t="n" s="0">
-        <v>21.798343249137698</v>
+        <v>137.68595561008843</v>
       </c>
       <c r="Z37" t="n" s="0">
-        <v>92.34848660872609</v>
+        <v>4009.0887651270637</v>
       </c>
       <c r="AA37" t="n" s="0">
-        <v>22.381715673956506</v>
+        <v>1176.9373614225997</v>
       </c>
       <c r="AB37" t="n" s="0">
-        <v>413.0863151161313</v>
+        <v>65.1433184319396</v>
       </c>
       <c r="AC37" t="n" s="0">
-        <v>61.97530048272989</v>
+        <v>73.8073907297289</v>
       </c>
       <c r="AD37" t="n" s="0">
-        <v>571.4356049457781</v>
+        <v>22.758380390386172</v>
       </c>
       <c r="AE37" t="n" s="0">
-        <v>80.20381612616528</v>
+        <v>50.25912250071536</v>
       </c>
       <c r="AF37" t="n" s="0">
-        <v>377.60158279131923</v>
+        <v>468.16582719447456</v>
       </c>
     </row>
     <row r="38">
       <c r="C38" t="n" s="0">
-        <v>0.10866210376565849</v>
+        <v>1.8212642710331381</v>
       </c>
       <c r="D38" t="n" s="0">
-        <v>1.7993099195251303</v>
+        <v>2.979316308296124</v>
       </c>
       <c r="E38" t="n" s="0">
-        <v>0.2483646362420102</v>
+        <v>0.7896143905193138</v>
       </c>
       <c r="F38" t="n" s="0">
-        <v>3.169250218482064</v>
+        <v>2.3853534358711626</v>
       </c>
       <c r="G38" t="n" s="0">
-        <v>0.9162773124838972</v>
+        <v>0.8356635673532827</v>
       </c>
       <c r="H38" t="n" s="0">
-        <v>3.684919868908623</v>
+        <v>1.0071718034553925</v>
       </c>
       <c r="I38" t="n" s="0">
-        <v>2.384374445696592</v>
+        <v>3.365714176445589</v>
       </c>
       <c r="J38" t="n" s="0">
-        <v>0.8609565373486494</v>
+        <v>1.2730619583659541</v>
       </c>
       <c r="K38" t="n" s="0">
-        <v>0.5396180120326644</v>
+        <v>0.5575889348771903</v>
       </c>
       <c r="L38" t="n" s="0">
-        <v>0.9836328043932974</v>
+        <v>1.4736406521041305</v>
       </c>
       <c r="M38" t="n" s="0">
-        <v>1.113411593264128</v>
+        <v>4.970696651433543</v>
       </c>
       <c r="N38" t="n" s="0">
-        <v>1.6617760948223723</v>
+        <v>1.8315071838923558</v>
       </c>
       <c r="O38" t="n" s="0">
-        <v>3.80373765331139</v>
+        <v>7.5362362273344425</v>
       </c>
       <c r="P38" t="n" s="0">
-        <v>1.9030837105902585</v>
+        <v>6.484705953014411</v>
       </c>
       <c r="Q38" t="n" s="0">
-        <v>5.712329538085621</v>
+        <v>0.15675283961232409</v>
       </c>
       <c r="R38" t="n" s="0">
-        <v>3.0380578043697244</v>
+        <v>2.761590590116682</v>
       </c>
       <c r="S38" t="n" s="0">
-        <v>0.6490164145196993</v>
+        <v>4.931535568138743</v>
       </c>
       <c r="T38" t="n" s="0">
-        <v>3.694553106251484</v>
+        <v>2.6913771989915327</v>
       </c>
       <c r="U38" t="n" s="0">
-        <v>1.7847417059878141</v>
+        <v>1.189389977337882</v>
       </c>
       <c r="V38" t="n" s="0">
-        <v>0.5294911676595127</v>
+        <v>1.0803318165901605</v>
       </c>
       <c r="W38" t="n" s="0">
-        <v>37.41324711601858</v>
+        <v>0.3078985148134037</v>
       </c>
       <c r="X38" t="n" s="0">
-        <v>1.2931056369834355</v>
+        <v>0.40314649691969334</v>
       </c>
       <c r="Y38" t="n" s="0">
-        <v>3.5654770919377436</v>
+        <v>2.6179587382740936</v>
       </c>
       <c r="Z38" t="n" s="0">
-        <v>3.558000302695369</v>
+        <v>1.3056215654176346</v>
       </c>
       <c r="AA38" t="n" s="0">
-        <v>3.7987736534639116</v>
+        <v>4.313301628750901</v>
       </c>
       <c r="AB38" t="n" s="0">
-        <v>3.1692415961224474</v>
+        <v>3.9749590022256513</v>
       </c>
       <c r="AC38" t="n" s="0">
-        <v>12.185699745920306</v>
+        <v>2.024294206438504</v>
       </c>
       <c r="AD38" t="n" s="0">
-        <v>2.428823194587413</v>
+        <v>1.097165117434997</v>
       </c>
       <c r="AE38" t="n" s="0">
-        <v>1.7920048939158182</v>
+        <v>7.483504349249286</v>
       </c>
       <c r="AF38" t="n" s="0">
-        <v>2.7588857997814427</v>
+        <v>1.5259143210243329</v>
       </c>
     </row>
     <row r="39">
       <c r="C39" t="n" s="0">
-        <v>433.9234461630173</v>
+        <v>79.06253131030226</v>
       </c>
       <c r="D39" t="n" s="0">
-        <v>71.69892176131893</v>
+        <v>4.4741133242530635</v>
       </c>
       <c r="E39" t="n" s="0">
-        <v>591.2233114829548</v>
+        <v>14.058925774332824</v>
       </c>
       <c r="F39" t="n" s="0">
-        <v>1003.4344626681235</v>
+        <v>72.19697748334768</v>
       </c>
       <c r="G39" t="n" s="0">
-        <v>177.667113461112</v>
+        <v>8.101347554850301</v>
       </c>
       <c r="H39" t="n" s="0">
-        <v>355.65880140621886</v>
+        <v>340.4519732305905</v>
       </c>
       <c r="I39" t="n" s="0">
-        <v>3541.7477623187315</v>
+        <v>330.21270075227045</v>
       </c>
       <c r="J39" t="n" s="0">
-        <v>39.279959402645</v>
+        <v>359.2877236511052</v>
       </c>
       <c r="K39" t="n" s="0">
-        <v>408.82321269688373</v>
+        <v>1155.368742178981</v>
       </c>
       <c r="L39" t="n" s="0">
-        <v>354.7183423316107</v>
+        <v>851.2501406379349</v>
       </c>
       <c r="M39" t="n" s="0">
-        <v>337.4448504797361</v>
+        <v>58.212937393263516</v>
       </c>
       <c r="N39" t="n" s="0">
-        <v>60143.46849373258</v>
+        <v>77.4064187224125</v>
       </c>
       <c r="O39" t="n" s="0">
-        <v>15.381024620830406</v>
+        <v>9.082471877459563</v>
       </c>
       <c r="P39" t="n" s="0">
-        <v>17.660221946580908</v>
+        <v>94.96143039117995</v>
       </c>
       <c r="Q39" t="n" s="0">
-        <v>82.3548722183325</v>
+        <v>80.82885667500582</v>
       </c>
       <c r="R39" t="n" s="0">
-        <v>195.37379189330278</v>
+        <v>10.420000859256763</v>
       </c>
       <c r="S39" t="n" s="0">
-        <v>7343.73233279091</v>
+        <v>9.476901581659597</v>
       </c>
       <c r="T39" t="n" s="0">
-        <v>14.250576571896497</v>
+        <v>282.68935493603357</v>
       </c>
       <c r="U39" t="n" s="0">
-        <v>75.78486515071278</v>
+        <v>75.78232445613126</v>
       </c>
       <c r="V39" t="n" s="0">
-        <v>6.332077572344925</v>
+        <v>98.06240785480173</v>
       </c>
       <c r="W39" t="n" s="0">
-        <v>137.27130563613593</v>
+        <v>97.11667667370638</v>
       </c>
       <c r="X39" t="n" s="0">
-        <v>776.5809185171751</v>
+        <v>8.063578487891371</v>
       </c>
       <c r="Y39" t="n" s="0">
-        <v>114.19922555627778</v>
+        <v>119.09129684211145</v>
       </c>
       <c r="Z39" t="n" s="0">
-        <v>5.592432351206208</v>
+        <v>158.48503837084735</v>
       </c>
       <c r="AA39" t="n" s="0">
-        <v>41.414140868594345</v>
+        <v>8.753951418203604</v>
       </c>
       <c r="AB39" t="n" s="0">
-        <v>77.40669513701924</v>
+        <v>588.0402950688994</v>
       </c>
       <c r="AC39" t="n" s="0">
-        <v>90024.07783901035</v>
+        <v>129.4292384499682</v>
       </c>
       <c r="AD39" t="n" s="0">
-        <v>719.2676950344169</v>
+        <v>136.3100804200691</v>
       </c>
       <c r="AE39" t="n" s="0">
-        <v>8.991504312951449</v>
+        <v>828.6513733367648</v>
       </c>
       <c r="AF39" t="n" s="0">
-        <v>794.2642402195604</v>
+        <v>186.52022590318413</v>
       </c>
     </row>
     <row r="40">
       <c r="C40" t="n" s="0">
-        <v>0.001050459211524898</v>
+        <v>0.05076310545294178</v>
       </c>
       <c r="D40" t="n" s="0">
-        <v>0.12129018642788494</v>
+        <v>0.020005070145156064</v>
       </c>
       <c r="E40" t="n" s="0">
-        <v>6.835766286770169</v>
+        <v>0.009770925284742032</v>
       </c>
       <c r="F40" t="n" s="0">
-        <v>0.1282302560403405</v>
+        <v>0.5332294410751098</v>
       </c>
       <c r="G40" t="n" s="0">
-        <v>92.72472183053817</v>
+        <v>2.9221016251844274</v>
       </c>
       <c r="H40" t="n" s="0">
-        <v>0.8185556518096406</v>
+        <v>1.0320823836559698</v>
       </c>
       <c r="I40" t="n" s="0">
-        <v>6.457891117457592</v>
+        <v>0.14844233589175207</v>
       </c>
       <c r="J40" t="n" s="0">
-        <v>0.46927362815507273</v>
+        <v>0.5165033996828803</v>
       </c>
       <c r="K40" t="n" s="0">
-        <v>3.2567263133952125</v>
+        <v>0.5046099498725239</v>
       </c>
       <c r="L40" t="n" s="0">
-        <v>0.006066181323125096</v>
+        <v>0.007159310015644808</v>
       </c>
       <c r="M40" t="n" s="0">
-        <v>19.74532865397739</v>
+        <v>0.27274942928730084</v>
       </c>
       <c r="N40" t="n" s="0">
-        <v>0.009125362051576168</v>
+        <v>2.1171148092620893</v>
       </c>
       <c r="O40" t="n" s="0">
-        <v>0.00854631821173381</v>
+        <v>0.006458784329743774</v>
       </c>
       <c r="P40" t="n" s="0">
-        <v>2.3615982482400444</v>
+        <v>0.0191135122447228</v>
       </c>
       <c r="Q40" t="n" s="0">
-        <v>0.04769630075074054</v>
+        <v>3.8292001874606083E-4</v>
       </c>
       <c r="R40" t="n" s="0">
-        <v>1.165157616025273E-4</v>
+        <v>0.6042899588198243</v>
       </c>
       <c r="S40" t="n" s="0">
-        <v>7.317989225141959</v>
+        <v>6.500371789995288</v>
       </c>
       <c r="T40" t="n" s="0">
-        <v>38.657335492269894</v>
+        <v>0.7743777221208556</v>
       </c>
       <c r="U40" t="n" s="0">
-        <v>0.5851978410147505</v>
+        <v>0.01444978603041229</v>
       </c>
       <c r="V40" t="n" s="0">
-        <v>0.026222549259227724</v>
+        <v>0.8900985067537196</v>
       </c>
       <c r="W40" t="n" s="0">
-        <v>2.1463104036983593</v>
+        <v>0.128560372101217</v>
       </c>
       <c r="X40" t="n" s="0">
-        <v>0.04508835502217038</v>
+        <v>0.05357235106694243</v>
       </c>
       <c r="Y40" t="n" s="0">
-        <v>2.379080017264442</v>
+        <v>0.058103915225405756</v>
       </c>
       <c r="Z40" t="n" s="0">
-        <v>0.06112556691724906</v>
+        <v>2.096008487554586</v>
       </c>
       <c r="AA40" t="n" s="0">
-        <v>5.709265332594632</v>
+        <v>0.13237013111525786</v>
       </c>
       <c r="AB40" t="n" s="0">
-        <v>1.194933692346662</v>
+        <v>14.306761883113362</v>
       </c>
       <c r="AC40" t="n" s="0">
-        <v>2.9511258716391997</v>
+        <v>1.4530769759473183</v>
       </c>
       <c r="AD40" t="n" s="0">
-        <v>2.5886626601442804</v>
+        <v>262.1068563409714</v>
       </c>
       <c r="AE40" t="n" s="0">
-        <v>26.995217231056753</v>
+        <v>0.008559017713537384</v>
       </c>
       <c r="AF40" t="n" s="0">
-        <v>1.1015577253916207</v>
+        <v>13.829098982395506</v>
       </c>
     </row>
     <row r="41">
       <c r="C41" t="n" s="0">
-        <v>0.02287513860022234</v>
+        <v>0.0031596088252383984</v>
       </c>
       <c r="D41" t="n" s="0">
-        <v>0.012247070896703197</v>
+        <v>0.052815404786779346</v>
       </c>
       <c r="E41" t="n" s="0">
-        <v>0.044669108447092876</v>
+        <v>0.053440790225830107</v>
       </c>
       <c r="F41" t="n" s="0">
-        <v>0.024247886894749018</v>
+        <v>0.009808480377992292</v>
       </c>
       <c r="G41" t="n" s="0">
-        <v>0.12960985304533448</v>
+        <v>0.016286787534050006</v>
       </c>
       <c r="H41" t="n" s="0">
-        <v>0.008685402516252157</v>
+        <v>0.0488977990534668</v>
       </c>
       <c r="I41" t="n" s="0">
-        <v>0.01835054596930677</v>
+        <v>0.020732320251191677</v>
       </c>
       <c r="J41" t="n" s="0">
-        <v>0.0897872258948621</v>
+        <v>0.05440105372951403</v>
       </c>
       <c r="K41" t="n" s="0">
-        <v>0.02063860858825806</v>
+        <v>0.022736645530088414</v>
       </c>
       <c r="L41" t="n" s="0">
-        <v>0.01290681233021936</v>
+        <v>0.02184578773280025</v>
       </c>
       <c r="M41" t="n" s="0">
-        <v>0.0251964759300237</v>
+        <v>0.10615217188602993</v>
       </c>
       <c r="N41" t="n" s="0">
-        <v>0.006592149709161664</v>
+        <v>0.027097729313866264</v>
       </c>
       <c r="O41" t="n" s="0">
-        <v>0.028623697836319385</v>
+        <v>0.018593047709798697</v>
       </c>
       <c r="P41" t="n" s="0">
-        <v>0.08158440741291516</v>
+        <v>0.05501009590954649</v>
       </c>
       <c r="Q41" t="n" s="0">
-        <v>0.030652866545217584</v>
+        <v>0.005140794677313993</v>
       </c>
       <c r="R41" t="n" s="0">
-        <v>0.002753705655429602</v>
+        <v>0.029285934588903835</v>
       </c>
       <c r="S41" t="n" s="0">
-        <v>0.015304857415657213</v>
+        <v>0.01926185448977063</v>
       </c>
       <c r="T41" t="n" s="0">
-        <v>0.005438263975530283</v>
+        <v>0.011392116931507767</v>
       </c>
       <c r="U41" t="n" s="0">
-        <v>0.03203082580591533</v>
+        <v>0.039535790904041204</v>
       </c>
       <c r="V41" t="n" s="0">
-        <v>0.050814398304587644</v>
+        <v>0.00685010893538043</v>
       </c>
       <c r="W41" t="n" s="0">
-        <v>0.035044323716539934</v>
+        <v>0.031112787230613486</v>
       </c>
       <c r="X41" t="n" s="0">
-        <v>0.0421258139096476</v>
+        <v>0.03801592820488249</v>
       </c>
       <c r="Y41" t="n" s="0">
-        <v>0.0020257820548093405</v>
+        <v>0.022547546167688042</v>
       </c>
       <c r="Z41" t="n" s="0">
-        <v>0.00953065355039209</v>
+        <v>0.014703271031465294</v>
       </c>
       <c r="AA41" t="n" s="0">
-        <v>0.010473190411627722</v>
+        <v>0.0286058246797449</v>
       </c>
       <c r="AB41" t="n" s="0">
-        <v>0.01868995328722091</v>
+        <v>0.007337294780555152</v>
       </c>
       <c r="AC41" t="n" s="0">
-        <v>0.05245742627720575</v>
+        <v>0.05195147574029538</v>
       </c>
       <c r="AD41" t="n" s="0">
-        <v>0.028973808880591964</v>
+        <v>0.030792793958226032</v>
       </c>
       <c r="AE41" t="n" s="0">
-        <v>0.024814143274558078</v>
+        <v>0.05998195209269402</v>
       </c>
       <c r="AF41" t="n" s="0">
-        <v>0.006001805892909054</v>
+        <v>0.0024684146947708124</v>
       </c>
     </row>
     <row r="42">
       <c r="C42" t="n" s="0">
-        <v>-2465.762957239392</v>
+        <v>-3400.5394465826776</v>
       </c>
       <c r="D42" t="n" s="0">
-        <v>-3654.699989605351</v>
+        <v>-2639.71603080197</v>
       </c>
       <c r="E42" t="n" s="0">
-        <v>-3055.970635066969</v>
+        <v>-3417.41104847686</v>
       </c>
       <c r="F42" t="n" s="0">
-        <v>-3234.8486530975806</v>
+        <v>-3655.322295972883</v>
       </c>
       <c r="G42" t="n" s="0">
-        <v>-2191.4510458839995</v>
+        <v>-3773.432798291795</v>
       </c>
       <c r="H42" t="n" s="0">
-        <v>-3169.3853879880553</v>
+        <v>-2842.9629687376823</v>
       </c>
       <c r="I42" t="n" s="0">
-        <v>-3022.9754771774838</v>
+        <v>-2456.6015876184065</v>
       </c>
       <c r="J42" t="n" s="0">
-        <v>-3080.500991696796</v>
+        <v>-2276.9701442520586</v>
       </c>
       <c r="K42" t="n" s="0">
-        <v>-2566.581594385449</v>
+        <v>-2744.7448302524385</v>
       </c>
       <c r="L42" t="n" s="0">
-        <v>-2190.836332009986</v>
+        <v>-2874.849364542817</v>
       </c>
       <c r="M42" t="n" s="0">
-        <v>-2821.6878666341604</v>
+        <v>-3257.309001395397</v>
       </c>
       <c r="N42" t="n" s="0">
-        <v>-3180.998550296456</v>
+        <v>-3723.091338249856</v>
       </c>
       <c r="O42" t="n" s="0">
-        <v>-2724.5244221530515</v>
+        <v>-2439.9747084731393</v>
       </c>
       <c r="P42" t="n" s="0">
-        <v>-2879.4218838464526</v>
+        <v>-2543.3108993651617</v>
       </c>
       <c r="Q42" t="n" s="0">
-        <v>-2488.7200016003676</v>
+        <v>-2547.510948725861</v>
       </c>
       <c r="R42" t="n" s="0">
-        <v>-3047.2420810892736</v>
+        <v>-2861.8630937145517</v>
       </c>
       <c r="S42" t="n" s="0">
-        <v>-3704.385070979473</v>
+        <v>-3896.962519971217</v>
       </c>
       <c r="T42" t="n" s="0">
-        <v>-3215.016964956191</v>
+        <v>-2800.1539340254044</v>
       </c>
       <c r="U42" t="n" s="0">
-        <v>-2930.716289386485</v>
+        <v>-2189.980112413031</v>
       </c>
       <c r="V42" t="n" s="0">
-        <v>-2961.394126892737</v>
+        <v>-2942.8381845288427</v>
       </c>
       <c r="W42" t="n" s="0">
-        <v>-2353.5627059860335</v>
+        <v>-3159.9062174291666</v>
       </c>
       <c r="X42" t="n" s="0">
-        <v>-2521.19984062389</v>
+        <v>-2704.855949772581</v>
       </c>
       <c r="Y42" t="n" s="0">
-        <v>-2681.729597115605</v>
+        <v>-2363.346312734541</v>
       </c>
       <c r="Z42" t="n" s="0">
-        <v>-2709.0448378535307</v>
+        <v>-2729.434090129888</v>
       </c>
       <c r="AA42" t="n" s="0">
-        <v>-2683.3576985918066</v>
+        <v>-2065.722543789698</v>
       </c>
       <c r="AB42" t="n" s="0">
-        <v>-3185.7802933545936</v>
+        <v>-2794.7673018388236</v>
       </c>
       <c r="AC42" t="n" s="0">
-        <v>-3000.8882578231537</v>
+        <v>-3357.7238607033114</v>
       </c>
       <c r="AD42" t="n" s="0">
-        <v>-2448.14356973517</v>
+        <v>-3099.042159222895</v>
       </c>
       <c r="AE42" t="n" s="0">
-        <v>-2924.4205792433986</v>
+        <v>-3178.539928799371</v>
       </c>
       <c r="AF42" t="n" s="0">
-        <v>-3709.3447065243045</v>
+        <v>-2701.570841390323</v>
       </c>
     </row>
     <row r="43">
       <c r="C43" t="n" s="0">
-        <v>54.811141062345015</v>
+        <v>41.660131466104474</v>
       </c>
       <c r="D43" t="n" s="0">
-        <v>24.197786714821575</v>
+        <v>24.90682468480422</v>
       </c>
       <c r="E43" t="n" s="0">
-        <v>17.027882998081445</v>
+        <v>9.968923730894058</v>
       </c>
       <c r="F43" t="n" s="0">
-        <v>62.04518925047246</v>
+        <v>39.02296470025024</v>
       </c>
       <c r="G43" t="n" s="0">
-        <v>34.49915925014152</v>
+        <v>12.033066056314185</v>
       </c>
       <c r="H43" t="n" s="0">
-        <v>22.83208575583484</v>
+        <v>12.23649930230616</v>
       </c>
       <c r="I43" t="n" s="0">
-        <v>40.95311630217947</v>
+        <v>40.87057054698889</v>
       </c>
       <c r="J43" t="n" s="0">
-        <v>11.958657200425993</v>
+        <v>22.698418967704818</v>
       </c>
       <c r="K43" t="n" s="0">
-        <v>16.352081997152972</v>
+        <v>8.098326002754987</v>
       </c>
       <c r="L43" t="n" s="0">
-        <v>13.807049135382709</v>
+        <v>61.72743496288193</v>
       </c>
       <c r="M43" t="n" s="0">
-        <v>35.85234373297179</v>
+        <v>27.906995381934856</v>
       </c>
       <c r="N43" t="n" s="0">
-        <v>42.78346897933184</v>
+        <v>40.62945692132716</v>
       </c>
       <c r="O43" t="n" s="0">
-        <v>34.07902691690832</v>
+        <v>41.92772635085915</v>
       </c>
       <c r="P43" t="n" s="0">
-        <v>33.61017856274533</v>
+        <v>33.71744649632683</v>
       </c>
       <c r="Q43" t="n" s="0">
-        <v>29.848758077847414</v>
+        <v>66.34125021414864</v>
       </c>
       <c r="R43" t="n" s="0">
-        <v>46.763241050883295</v>
+        <v>29.84911263125025</v>
       </c>
       <c r="S43" t="n" s="0">
-        <v>27.867810116843437</v>
+        <v>35.84837489633697</v>
       </c>
       <c r="T43" t="n" s="0">
-        <v>22.494758046020905</v>
+        <v>24.326862416163152</v>
       </c>
       <c r="U43" t="n" s="0">
-        <v>8.50473583045927</v>
+        <v>47.31422939843995</v>
       </c>
       <c r="V43" t="n" s="0">
-        <v>22.902477761179036</v>
+        <v>30.172701969383958</v>
       </c>
       <c r="W43" t="n" s="0">
-        <v>31.0862736577823</v>
+        <v>41.97090860986784</v>
       </c>
       <c r="X43" t="n" s="0">
-        <v>16.08430714718896</v>
+        <v>19.078331103137277</v>
       </c>
       <c r="Y43" t="n" s="0">
-        <v>36.44672089773354</v>
+        <v>26.53688614896366</v>
       </c>
       <c r="Z43" t="n" s="0">
-        <v>24.9016119437648</v>
+        <v>11.115124043957929</v>
       </c>
       <c r="AA43" t="n" s="0">
-        <v>6.898297724218139</v>
+        <v>41.97326944677569</v>
       </c>
       <c r="AB43" t="n" s="0">
-        <v>52.84974986266727</v>
+        <v>30.8911917694427</v>
       </c>
       <c r="AC43" t="n" s="0">
-        <v>10.68049643519734</v>
+        <v>34.826054447922374</v>
       </c>
       <c r="AD43" t="n" s="0">
-        <v>12.87422917507559</v>
+        <v>37.44863858672088</v>
       </c>
       <c r="AE43" t="n" s="0">
-        <v>17.958966524568694</v>
+        <v>6.895407914457698</v>
       </c>
       <c r="AF43" t="n" s="0">
-        <v>37.89977527854439</v>
+        <v>32.96821496274761</v>
       </c>
     </row>
     <row r="44">
       <c r="C44" t="n" s="0">
-        <v>9.023728233818922</v>
+        <v>1.6470393649636645</v>
       </c>
       <c r="D44" t="n" s="0">
-        <v>2.3527356410854527</v>
+        <v>2.317045654857314</v>
       </c>
       <c r="E44" t="n" s="0">
-        <v>3.9960850736601903</v>
+        <v>8.788716181028093</v>
       </c>
       <c r="F44" t="n" s="0">
-        <v>3.048011141367138</v>
+        <v>1.3342910747095726</v>
       </c>
       <c r="G44" t="n" s="0">
-        <v>2.0572684574132976</v>
+        <v>0.006141212494921167</v>
       </c>
       <c r="H44" t="n" s="0">
-        <v>1.6708069110622046</v>
+        <v>2.5993817756050572</v>
       </c>
       <c r="I44" t="n" s="0">
-        <v>1.2294159193973084</v>
+        <v>19.21274289485431</v>
       </c>
       <c r="J44" t="n" s="0">
-        <v>6.889232773420309</v>
+        <v>4.651180341162956</v>
       </c>
       <c r="K44" t="n" s="0">
-        <v>8.908026388847265</v>
+        <v>3.026948643201312</v>
       </c>
       <c r="L44" t="n" s="0">
-        <v>2.317038897321581</v>
+        <v>3.7817046175693467</v>
       </c>
       <c r="M44" t="n" s="0">
-        <v>3.736114337110678</v>
+        <v>18.101143205494555</v>
       </c>
       <c r="N44" t="n" s="0">
-        <v>3.4961725091155356</v>
+        <v>2.329314449037988</v>
       </c>
       <c r="O44" t="n" s="0">
-        <v>3.6125402581870536</v>
+        <v>3.1776932663428004</v>
       </c>
       <c r="P44" t="n" s="0">
-        <v>1.6473382161974226</v>
+        <v>2.815794849336261</v>
       </c>
       <c r="Q44" t="n" s="0">
-        <v>1.737361271162055</v>
+        <v>1.7425057949275744</v>
       </c>
       <c r="R44" t="n" s="0">
-        <v>1.346846960122225</v>
+        <v>3.9968028886505635E-15</v>
       </c>
       <c r="S44" t="n" s="0">
-        <v>1.7076857739691715</v>
+        <v>3.1855924438303522</v>
       </c>
       <c r="T44" t="n" s="0">
-        <v>2.3187761144026493</v>
+        <v>4.192039103278034</v>
       </c>
       <c r="U44" t="n" s="0">
-        <v>1.1633614361660283</v>
+        <v>3.246805878398036</v>
       </c>
       <c r="V44" t="n" s="0">
-        <v>2.655048036993574</v>
+        <v>2.920505959055188</v>
       </c>
       <c r="W44" t="n" s="0">
-        <v>1.3692729795530885</v>
+        <v>2.407759973776852</v>
       </c>
       <c r="X44" t="n" s="0">
-        <v>2.3168693485541856</v>
+        <v>2.923501628725156</v>
       </c>
       <c r="Y44" t="n" s="0">
-        <v>1.155691968323414</v>
+        <v>2.5800294866239075</v>
       </c>
       <c r="Z44" t="n" s="0">
-        <v>3.6379052395191107</v>
+        <v>4.575010559620992</v>
       </c>
       <c r="AA44" t="n" s="0">
-        <v>2.5812967159539153</v>
+        <v>2.6174218304029933</v>
       </c>
       <c r="AB44" t="n" s="0">
-        <v>1.7266971825714674</v>
+        <v>4.0536614596227025</v>
       </c>
       <c r="AC44" t="n" s="0">
-        <v>0.0182078775404233</v>
+        <v>2.361388501291661</v>
       </c>
       <c r="AD44" t="n" s="0">
-        <v>2.823593185231584</v>
+        <v>4.080342925744905</v>
       </c>
       <c r="AE44" t="n" s="0">
-        <v>4.557186375940695</v>
+        <v>2.6434431873673465</v>
       </c>
       <c r="AF44" t="n" s="0">
-        <v>10.238926880210292</v>
+        <v>0.05993691580539151</v>
       </c>
     </row>
     <row r="45">
       <c r="C45" t="n" s="0">
-        <v>0.2925089419475809</v>
+        <v>0.3595773686880295</v>
       </c>
       <c r="D45" t="n" s="0">
-        <v>0.4141374989229759</v>
+        <v>0.7094030790173335</v>
       </c>
       <c r="E45" t="n" s="0">
-        <v>0.406730676320484</v>
+        <v>0.5334145399906959</v>
       </c>
       <c r="F45" t="n" s="0">
-        <v>0.3486485692145842</v>
+        <v>0.2613097500831165</v>
       </c>
       <c r="G45" t="n" s="0">
-        <v>0.17448308824629655</v>
+        <v>0.22425960052369465</v>
       </c>
       <c r="H45" t="n" s="0">
-        <v>0.19265524554493474</v>
+        <v>0.36254268130001543</v>
       </c>
       <c r="I45" t="n" s="0">
-        <v>0.6567655388294871</v>
+        <v>0.3300149789493778</v>
       </c>
       <c r="J45" t="n" s="0">
-        <v>0.17661546132796457</v>
+        <v>0.5187671104053216</v>
       </c>
       <c r="K45" t="n" s="0">
-        <v>0.6837337737756088</v>
+        <v>0.44223617905341495</v>
       </c>
       <c r="L45" t="n" s="0">
-        <v>0.2529479238567378</v>
+        <v>0.36396115071241264</v>
       </c>
       <c r="M45" t="n" s="0">
-        <v>1.0450634482479162</v>
+        <v>0.6564221115415798</v>
       </c>
       <c r="N45" t="n" s="0">
-        <v>0.6340303221781517</v>
+        <v>0.563193387080481</v>
       </c>
       <c r="O45" t="n" s="0">
-        <v>0.5297366594567389</v>
+        <v>0.38446107292460696</v>
       </c>
       <c r="P45" t="n" s="0">
-        <v>0.2656939132259182</v>
+        <v>0.34150709057707385</v>
       </c>
       <c r="Q45" t="n" s="0">
-        <v>0.11811368611773254</v>
+        <v>0.26419783677440845</v>
       </c>
       <c r="R45" t="n" s="0">
-        <v>0.19206465918400295</v>
+        <v>0.4179288717786396</v>
       </c>
       <c r="S45" t="n" s="0">
-        <v>0.23561330760683052</v>
+        <v>0.9449499103210425</v>
       </c>
       <c r="T45" t="n" s="0">
-        <v>1.2372451059816516</v>
+        <v>0.6454131793717893</v>
       </c>
       <c r="U45" t="n" s="0">
-        <v>0.7399361278961335</v>
+        <v>2.050217326465447</v>
       </c>
       <c r="V45" t="n" s="0">
-        <v>0.2982395444767091</v>
+        <v>0.08071326183421212</v>
       </c>
       <c r="W45" t="n" s="0">
-        <v>0.23727547971426632</v>
+        <v>0.467609876373666</v>
       </c>
       <c r="X45" t="n" s="0">
-        <v>0.41754417301221836</v>
+        <v>0.40517949854512647</v>
       </c>
       <c r="Y45" t="n" s="0">
-        <v>1.0778436847686232</v>
+        <v>0.49421718153475414</v>
       </c>
       <c r="Z45" t="n" s="0">
-        <v>0.3862459565624943</v>
+        <v>0.6276658942662326</v>
       </c>
       <c r="AA45" t="n" s="0">
-        <v>0.3907228108505455</v>
+        <v>0.3597007587208465</v>
       </c>
       <c r="AB45" t="n" s="0">
-        <v>0.5253169928396422</v>
+        <v>0.39105909494687374</v>
       </c>
       <c r="AC45" t="n" s="0">
-        <v>1.0801666055816659</v>
+        <v>0.35531027686758265</v>
       </c>
       <c r="AD45" t="n" s="0">
-        <v>0.3026466744666695</v>
+        <v>0.3983981654163977</v>
       </c>
       <c r="AE45" t="n" s="0">
-        <v>0.3186481962614439</v>
+        <v>0.27785507655402897</v>
       </c>
       <c r="AF45" t="n" s="0">
-        <v>0.2958606496728938</v>
+        <v>0.6638296881127735</v>
       </c>
     </row>
     <row r="46">
       <c r="C46" t="n" s="0">
-        <v>5.836055122443988</v>
+        <v>0.001041477484511747</v>
       </c>
       <c r="D46" t="n" s="0">
-        <v>0.614863656021513</v>
+        <v>0.8569523583102052</v>
       </c>
       <c r="E46" t="n" s="0">
-        <v>1.4962692846978802</v>
+        <v>2.205877883377533</v>
       </c>
       <c r="F46" t="n" s="0">
-        <v>0.634891463422877</v>
+        <v>1.9693031798319356</v>
       </c>
       <c r="G46" t="n" s="0">
-        <v>0.7573423306312483</v>
+        <v>1.123888024641742</v>
       </c>
       <c r="H46" t="n" s="0">
-        <v>1.5231978621021849</v>
+        <v>1.0633352071584914</v>
       </c>
       <c r="I46" t="n" s="0">
-        <v>1.3402230423011396</v>
+        <v>1.739130151885821</v>
       </c>
       <c r="J46" t="n" s="0">
-        <v>0.7110841524483761</v>
+        <v>0.7512991711227345</v>
       </c>
       <c r="K46" t="n" s="0">
-        <v>6.490974571564942</v>
+        <v>1.8123856141471189</v>
       </c>
       <c r="L46" t="n" s="0">
-        <v>0.30537161068248303</v>
+        <v>1.062972878912544</v>
       </c>
       <c r="M46" t="n" s="0">
-        <v>1.7744868020145843</v>
+        <v>0.012206814599742839</v>
       </c>
       <c r="N46" t="n" s="0">
-        <v>2.396713443756705</v>
+        <v>1.1131308810694582</v>
       </c>
       <c r="O46" t="n" s="0">
-        <v>0.010954925084602522</v>
+        <v>1.3727137153879667</v>
       </c>
       <c r="P46" t="n" s="0">
-        <v>1.251940657119002</v>
+        <v>1.0083136696695432</v>
       </c>
       <c r="Q46" t="n" s="0">
-        <v>0.0476435038935348</v>
+        <v>0.57482589434681</v>
       </c>
       <c r="R46" t="n" s="0">
-        <v>1.93093721253417</v>
+        <v>5.152747410342707</v>
       </c>
       <c r="S46" t="n" s="0">
-        <v>0.42897069144961053</v>
+        <v>1.519529273158568</v>
       </c>
       <c r="T46" t="n" s="0">
-        <v>1.0695537176881893</v>
+        <v>2.541732918451719</v>
       </c>
       <c r="U46" t="n" s="0">
-        <v>2.7589164185658883</v>
+        <v>21.001061469285055</v>
       </c>
       <c r="V46" t="n" s="0">
-        <v>0.8093976493264152</v>
+        <v>1.6614275856739247</v>
       </c>
       <c r="W46" t="n" s="0">
-        <v>3.090976683025377</v>
+        <v>0.004351012459193942</v>
       </c>
       <c r="X46" t="n" s="0">
-        <v>2.2213781731343714</v>
+        <v>4.219518402877624</v>
       </c>
       <c r="Y46" t="n" s="0">
-        <v>3.1508310002690623</v>
+        <v>1.3236724785510905</v>
       </c>
       <c r="Z46" t="n" s="0">
-        <v>1.9631092787728686</v>
+        <v>1.543366971228465</v>
       </c>
       <c r="AA46" t="n" s="0">
-        <v>1.269096246210232</v>
+        <v>1.7073480229280746</v>
       </c>
       <c r="AB46" t="n" s="0">
-        <v>1.4328160310886822</v>
+        <v>1.9131695454967825</v>
       </c>
       <c r="AC46" t="n" s="0">
-        <v>5.319524080982067</v>
+        <v>0.5892330635394297</v>
       </c>
       <c r="AD46" t="n" s="0">
-        <v>0.40779863709038966</v>
+        <v>1.9070061904852795</v>
       </c>
       <c r="AE46" t="n" s="0">
-        <v>5.847515609218215</v>
+        <v>0.18166563593473328</v>
       </c>
       <c r="AF46" t="n" s="0">
-        <v>1.2653609566527522</v>
+        <v>2.285042859364684</v>
       </c>
     </row>
     <row r="47">
       <c r="C47" t="n" s="0">
-        <v>0.07739629202930588</v>
+        <v>0.4610599679286793</v>
       </c>
       <c r="D47" t="n" s="0">
-        <v>0.3424520748050811</v>
+        <v>0.27878924399501337</v>
       </c>
       <c r="E47" t="n" s="0">
-        <v>0.17828293603916726</v>
+        <v>0.06950705889138062</v>
       </c>
       <c r="F47" t="n" s="0">
-        <v>0.022939523282029074</v>
+        <v>0.4693522961212546</v>
       </c>
       <c r="G47" t="n" s="0">
-        <v>10.729055617045855</v>
+        <v>0.5840781589480227</v>
       </c>
       <c r="H47" t="n" s="0">
-        <v>2.629386418414438</v>
+        <v>0.36031359890351755</v>
       </c>
       <c r="I47" t="n" s="0">
-        <v>1.232905726261702</v>
+        <v>0.22650670329369713</v>
       </c>
       <c r="J47" t="n" s="0">
-        <v>0.41509136608903746</v>
+        <v>0.14805511722433848</v>
       </c>
       <c r="K47" t="n" s="0">
-        <v>0.8514432057223215</v>
+        <v>0.005738880721319307</v>
       </c>
       <c r="L47" t="n" s="0">
-        <v>3.0285805049172465</v>
+        <v>0.10128426476859227</v>
       </c>
       <c r="M47" t="n" s="0">
-        <v>0.1864344692854678</v>
+        <v>0.1421877460101488</v>
       </c>
       <c r="N47" t="n" s="0">
-        <v>0.17909874970720263</v>
+        <v>0.6776086663705474</v>
       </c>
       <c r="O47" t="n" s="0">
-        <v>0.26790247539875583</v>
+        <v>10.666983196137238</v>
       </c>
       <c r="P47" t="n" s="0">
-        <v>0.5641947554363578</v>
+        <v>2.670874941585639</v>
       </c>
       <c r="Q47" t="n" s="0">
-        <v>0.2273248221305237</v>
+        <v>1.5291953072649855</v>
       </c>
       <c r="R47" t="n" s="0">
-        <v>0.11926905355128753</v>
+        <v>1.127194981472643</v>
       </c>
       <c r="S47" t="n" s="0">
-        <v>17.278281934449243</v>
+        <v>1.3093684167842685</v>
       </c>
       <c r="T47" t="n" s="0">
-        <v>0.050712926450155564</v>
+        <v>0.7533727284052238</v>
       </c>
       <c r="U47" t="n" s="0">
-        <v>0.3425625557994661</v>
+        <v>0.07328040417741635</v>
       </c>
       <c r="V47" t="n" s="0">
-        <v>0.12022119114682364</v>
+        <v>0.20358947179144737</v>
       </c>
       <c r="W47" t="n" s="0">
-        <v>0.6533763236746334</v>
+        <v>2.026529478224478</v>
       </c>
       <c r="X47" t="n" s="0">
-        <v>10.04361694885449</v>
+        <v>1.5891907092500914</v>
       </c>
       <c r="Y47" t="n" s="0">
-        <v>1.5156895814500893</v>
+        <v>0.31614777268982563</v>
       </c>
       <c r="Z47" t="n" s="0">
-        <v>0.14483212692959743</v>
+        <v>0.8879490208449039</v>
       </c>
       <c r="AA47" t="n" s="0">
-        <v>0.23637538746049352</v>
+        <v>0.16586161206304084</v>
       </c>
       <c r="AB47" t="n" s="0">
-        <v>0.18017687354846892</v>
+        <v>0.1644539095702059</v>
       </c>
       <c r="AC47" t="n" s="0">
-        <v>0.04504735942664176</v>
+        <v>0.10775262111788769</v>
       </c>
       <c r="AD47" t="n" s="0">
-        <v>0.13902770577328954</v>
+        <v>1.2523076843809866</v>
       </c>
       <c r="AE47" t="n" s="0">
-        <v>0.3694228394034191</v>
+        <v>0.11918892377947743</v>
       </c>
       <c r="AF47" t="n" s="0">
-        <v>0.6321134621398654</v>
+        <v>0.16019647635759088</v>
       </c>
     </row>
     <row r="48">
       <c r="C48" t="n" s="0">
-        <v>0.0</v>
+        <v>1.9920308918556293</v>
       </c>
       <c r="D48" t="n" s="0">
+        <v>1.9920308918556306</v>
+      </c>
+      <c r="E48" t="n" s="0">
+        <v>2.9821051755564376</v>
+      </c>
+      <c r="F48" t="n" s="0">
+        <v>0.0</v>
+      </c>
+      <c r="G48" t="n" s="0">
+        <v>0.0</v>
+      </c>
+      <c r="H48" t="n" s="0">
+        <v>0.0</v>
+      </c>
+      <c r="I48" t="n" s="0">
         <v>0.998003748179203</v>
       </c>
-      <c r="E48" t="n" s="0">
-        <v>0.9980037481792028</v>
-      </c>
-      <c r="F48" t="n" s="0">
-        <v>3.4649682406289974E-55</v>
-      </c>
-      <c r="G48" t="n" s="0">
-        <v>1.2868893973670072E-85</v>
-      </c>
-      <c r="H48" t="n" s="0">
+      <c r="J48" t="n" s="0">
+        <v>0.998003748179203</v>
+      </c>
+      <c r="K48" t="n" s="0">
         <v>1.9920308918556306</v>
       </c>
-      <c r="I48" t="n" s="0">
-        <v>0.9980037481792026</v>
-      </c>
-      <c r="J48" t="n" s="0">
-        <v>8.211056237818357E-67</v>
-      </c>
-      <c r="K48" t="n" s="0">
-        <v>0.0</v>
-      </c>
       <c r="L48" t="n" s="0">
         <v>0.0</v>
       </c>
@@ -4154,31 +4154,31 @@
         <v>0.0</v>
       </c>
       <c r="N48" t="n" s="0">
-        <v>1.28471022234132E-53</v>
+        <v>0.0</v>
       </c>
       <c r="O48" t="n" s="0">
-        <v>0.0</v>
+        <v>3.968251517879963</v>
       </c>
       <c r="P48" t="n" s="0">
-        <v>3.968251535733217</v>
+        <v>1.3069970442008667E-85</v>
       </c>
       <c r="Q48" t="n" s="0">
-        <v>0.998003748179203</v>
+        <v>3.968251517880211</v>
       </c>
       <c r="R48" t="n" s="0">
-        <v>2.9821051755564363</v>
+        <v>9.381423706805483E-83</v>
       </c>
       <c r="S48" t="n" s="0">
-        <v>0.0</v>
+        <v>4.950489035327462</v>
       </c>
       <c r="T48" t="n" s="0">
-        <v>0.0</v>
+        <v>7.636743513971997E-76</v>
       </c>
       <c r="U48" t="n" s="0">
-        <v>0.0</v>
+        <v>1.9920308918556615</v>
       </c>
       <c r="V48" t="n" s="0">
-        <v>2.510486614325891E-77</v>
+        <v>0.0</v>
       </c>
       <c r="W48" t="n" s="0">
         <v>0.0</v>
@@ -4193,19 +4193,19 @@
         <v>0.0</v>
       </c>
       <c r="AA48" t="n" s="0">
-        <v>2.0107646833859488E-87</v>
+        <v>1.4658474541883567E-84</v>
       </c>
       <c r="AB48" t="n" s="0">
-        <v>2.982105175556438</v>
+        <v>3.1082489271148415E-78</v>
       </c>
       <c r="AC48" t="n" s="0">
-        <v>0.0</v>
+        <v>3.968251517879963</v>
       </c>
       <c r="AD48" t="n" s="0">
         <v>0.0</v>
       </c>
       <c r="AE48" t="n" s="0">
-        <v>1.9920308918556746</v>
+        <v>0.0</v>
       </c>
       <c r="AF48" t="n" s="0">
         <v>0.0</v>
@@ -4213,108 +4213,108 @@
     </row>
     <row r="49">
       <c r="C49" t="n" s="0">
-        <v>0.0023264483551068667</v>
+        <v>0.0014939647641664404</v>
       </c>
       <c r="D49" t="n" s="0">
-        <v>0.0015143076432277342</v>
+        <v>8.260403479432983E-4</v>
       </c>
       <c r="E49" t="n" s="0">
-        <v>0.0016556336799688153</v>
+        <v>7.832968608021464E-4</v>
       </c>
       <c r="F49" t="n" s="0">
-        <v>0.02036358706686035</v>
+        <v>0.02036333934816068</v>
       </c>
       <c r="G49" t="n" s="0">
-        <v>0.001655371334718708</v>
+        <v>0.020363339348068495</v>
       </c>
       <c r="H49" t="n" s="0">
-        <v>0.00606921456989451</v>
+        <v>9.13333045654494E-4</v>
       </c>
       <c r="I49" t="n" s="0">
-        <v>0.020363339348068495</v>
+        <v>0.0018878181559469393</v>
       </c>
       <c r="J49" t="n" s="0">
-        <v>9.158012202565507E-4</v>
+        <v>0.0016553715148082515</v>
       </c>
       <c r="K49" t="n" s="0">
-        <v>0.00148865923536384</v>
+        <v>0.0012425622639537295</v>
       </c>
       <c r="L49" t="n" s="0">
-        <v>0.0016553752096103058</v>
+        <v>0.020363339348119135</v>
       </c>
       <c r="M49" t="n" s="0">
-        <v>0.020363339498435808</v>
+        <v>0.0014791897390482463</v>
       </c>
       <c r="N49" t="n" s="0">
-        <v>7.897922706148673E-4</v>
+        <v>8.149138054327766E-4</v>
       </c>
       <c r="O49" t="n" s="0">
-        <v>0.0014886592353638393</v>
+        <v>0.002251949318339088</v>
       </c>
       <c r="P49" t="n" s="0">
-        <v>0.020363339348068495</v>
+        <v>0.020363340148017894</v>
       </c>
       <c r="Q49" t="n" s="0">
-        <v>0.00165542987494791</v>
+        <v>8.022327526269968E-4</v>
       </c>
       <c r="R49" t="n" s="0">
-        <v>0.019516530567148818</v>
+        <v>0.0013751222012800316</v>
       </c>
       <c r="S49" t="n" s="0">
-        <v>0.02036338648689962</v>
+        <v>0.0014887148976191493</v>
       </c>
       <c r="T49" t="n" s="0">
-        <v>7.846800988823895E-4</v>
+        <v>9.439393546162079E-4</v>
       </c>
       <c r="U49" t="n" s="0">
-        <v>0.0022519493183390878</v>
+        <v>0.0016553713347187107</v>
       </c>
       <c r="V49" t="n" s="0">
-        <v>7.83001020923254E-4</v>
+        <v>0.001488659235363839</v>
       </c>
       <c r="W49" t="n" s="0">
-        <v>8.318411134808196E-4</v>
+        <v>5.611232109582008E-4</v>
       </c>
       <c r="X49" t="n" s="0">
-        <v>0.001655754332286074</v>
+        <v>0.0016553723170428052</v>
       </c>
       <c r="Y49" t="n" s="0">
-        <v>0.020363341306371747</v>
+        <v>0.007389886878663718</v>
       </c>
       <c r="Z49" t="n" s="0">
-        <v>0.001758902818078667</v>
+        <v>0.0016553790596360158</v>
       </c>
       <c r="AA49" t="n" s="0">
-        <v>7.864156670159089E-4</v>
+        <v>0.02036669552096372</v>
       </c>
       <c r="AB49" t="n" s="0">
-        <v>0.0022519493183390886</v>
+        <v>0.02036337359002775</v>
       </c>
       <c r="AC49" t="n" s="0">
-        <v>0.0016553713347187118</v>
+        <v>0.0016559766084041645</v>
       </c>
       <c r="AD49" t="n" s="0">
-        <v>0.0011295759081899927</v>
+        <v>0.008333703114662368</v>
       </c>
       <c r="AE49" t="n" s="0">
-        <v>0.002236858622181302</v>
+        <v>0.020363376014597645</v>
       </c>
       <c r="AF49" t="n" s="0">
-        <v>0.020363339348100196</v>
+        <v>0.0012407175616581613</v>
       </c>
     </row>
     <row r="50">
       <c r="C50" t="n" s="0">
+        <v>-1.0316284534898776</v>
+      </c>
+      <c r="D50" t="n" s="0">
         <v>-1.0316284534898779</v>
       </c>
-      <c r="D50" t="n" s="0">
+      <c r="E50" t="n" s="0">
+        <v>-1.0316284534898779</v>
+      </c>
+      <c r="F50" t="n" s="0">
         <v>-1.0316284534898776</v>
-      </c>
-      <c r="E50" t="n" s="0">
-        <v>-1.0316284534898776</v>
-      </c>
-      <c r="F50" t="n" s="0">
-        <v>-1.0316284534898779</v>
       </c>
       <c r="G50" t="n" s="0">
         <v>-1.0316284534898776</v>
@@ -4323,22 +4323,22 @@
         <v>-1.0316284534898776</v>
       </c>
       <c r="I50" t="n" s="0">
-        <v>-1.0316284534898776</v>
+        <v>-1.0316284534898779</v>
       </c>
       <c r="J50" t="n" s="0">
         <v>-1.0316284534898776</v>
       </c>
       <c r="K50" t="n" s="0">
+        <v>-1.0316284534898776</v>
+      </c>
+      <c r="L50" t="n" s="0">
         <v>-1.0316284534898779</v>
-      </c>
-      <c r="L50" t="n" s="0">
-        <v>-1.0316284534898776</v>
       </c>
       <c r="M50" t="n" s="0">
         <v>-1.0316284534898776</v>
       </c>
       <c r="N50" t="n" s="0">
-        <v>-1.031628453489764</v>
+        <v>-1.0316284534898776</v>
       </c>
       <c r="O50" t="n" s="0">
         <v>-1.0316284534898776</v>
@@ -4347,28 +4347,28 @@
         <v>-1.0316284534898776</v>
       </c>
       <c r="Q50" t="n" s="0">
-        <v>-1.0316284534898776</v>
+        <v>-1.031628453489835</v>
       </c>
       <c r="R50" t="n" s="0">
         <v>-1.0316284534898776</v>
       </c>
       <c r="S50" t="n" s="0">
-        <v>-1.0316284534898776</v>
+        <v>-1.0316284534898768</v>
       </c>
       <c r="T50" t="n" s="0">
-        <v>-1.0316284534898779</v>
+        <v>-1.0316284534890032</v>
       </c>
       <c r="U50" t="n" s="0">
         <v>-1.0316284534898779</v>
       </c>
       <c r="V50" t="n" s="0">
-        <v>-1.0316284534898776</v>
+        <v>-1.0316284534898779</v>
       </c>
       <c r="W50" t="n" s="0">
-        <v>-1.0316284534898776</v>
+        <v>-1.0316284534898779</v>
       </c>
       <c r="X50" t="n" s="0">
-        <v>-1.0316284534898779</v>
+        <v>-1.0316284534898743</v>
       </c>
       <c r="Y50" t="n" s="0">
         <v>-1.0316284534898779</v>
@@ -4377,22 +4377,22 @@
         <v>-1.0316284534898776</v>
       </c>
       <c r="AA50" t="n" s="0">
+        <v>-1.0316284534898779</v>
+      </c>
+      <c r="AB50" t="n" s="0">
         <v>-1.0316284534898776</v>
       </c>
-      <c r="AB50" t="n" s="0">
-        <v>-1.0316284534898779</v>
-      </c>
       <c r="AC50" t="n" s="0">
-        <v>-1.0316284527840325</v>
+        <v>-1.0316284534898776</v>
       </c>
       <c r="AD50" t="n" s="0">
         <v>-1.0316284534898776</v>
       </c>
       <c r="AE50" t="n" s="0">
+        <v>-1.0316284534898779</v>
+      </c>
+      <c r="AF50" t="n" s="0">
         <v>-1.0316284534898776</v>
-      </c>
-      <c r="AF50" t="n" s="0">
-        <v>-1.0316284534898779</v>
       </c>
     </row>
     <row r="51">
@@ -4406,7 +4406,7 @@
         <v>0.39788735772973816</v>
       </c>
       <c r="F51" t="n" s="0">
-        <v>0.39788735772975414</v>
+        <v>0.39788735772973816</v>
       </c>
       <c r="G51" t="n" s="0">
         <v>0.39788735772973816</v>
@@ -4475,10 +4475,10 @@
         <v>0.39788735772973816</v>
       </c>
       <c r="AC51" t="n" s="0">
+        <v>0.3978873577298234</v>
+      </c>
+      <c r="AD51" t="n" s="0">
         <v>0.39788735772973816</v>
-      </c>
-      <c r="AD51" t="n" s="0">
-        <v>0.39788735772973993</v>
       </c>
       <c r="AE51" t="n" s="0">
         <v>0.39788735772973816</v>
@@ -4492,1287 +4492,1287 @@
         <v>2.999999999999904</v>
       </c>
       <c r="D52" t="n" s="0">
+        <v>2.999999999999911</v>
+      </c>
+      <c r="E52" t="n" s="0">
+        <v>2.999999999999912</v>
+      </c>
+      <c r="F52" t="n" s="0">
+        <v>2.999999999999906</v>
+      </c>
+      <c r="G52" t="n" s="0">
+        <v>2.999999999999912</v>
+      </c>
+      <c r="H52" t="n" s="0">
         <v>2.9999999999999045</v>
       </c>
-      <c r="E52" t="n" s="0">
+      <c r="I52" t="n" s="0">
         <v>2.9999999999999116</v>
       </c>
-      <c r="F52" t="n" s="0">
-        <v>2.999999999999924</v>
-      </c>
-      <c r="G52" t="n" s="0">
-        <v>2.9999999999999116</v>
-      </c>
-      <c r="H52" t="n" s="0">
-        <v>2.999999999999908</v>
-      </c>
-      <c r="I52" t="n" s="0">
-        <v>2.999999999999916</v>
-      </c>
       <c r="J52" t="n" s="0">
-        <v>2.9999999999999054</v>
+        <v>2.999999999999904</v>
       </c>
       <c r="K52" t="n" s="0">
-        <v>2.999999999999904</v>
+        <v>2.999999999999907</v>
       </c>
       <c r="L52" t="n" s="0">
-        <v>2.999999999999904</v>
+        <v>2.9999999999999205</v>
       </c>
       <c r="M52" t="n" s="0">
-        <v>2.9999999999999303</v>
+        <v>3.0000000000000355</v>
       </c>
       <c r="N52" t="n" s="0">
-        <v>2.9999999999999067</v>
+        <v>2.999999999999911</v>
       </c>
       <c r="O52" t="n" s="0">
-        <v>2.9999999999999196</v>
+        <v>2.999999999999906</v>
       </c>
       <c r="P52" t="n" s="0">
-        <v>2.999999999999906</v>
+        <v>2.9999999999999205</v>
       </c>
       <c r="Q52" t="n" s="0">
-        <v>2.9999999999999156</v>
+        <v>2.9999999999999107</v>
       </c>
       <c r="R52" t="n" s="0">
-        <v>2.99999999999993</v>
+        <v>2.999999999999935</v>
       </c>
       <c r="S52" t="n" s="0">
         <v>2.999999999999911</v>
       </c>
       <c r="T52" t="n" s="0">
+        <v>2.999999999999911</v>
+      </c>
+      <c r="U52" t="n" s="0">
+        <v>3.0000002322562107</v>
+      </c>
+      <c r="V52" t="n" s="0">
+        <v>2.999999999999904</v>
+      </c>
+      <c r="W52" t="n" s="0">
+        <v>2.999999999999925</v>
+      </c>
+      <c r="X52" t="n" s="0">
         <v>2.9999999999999045</v>
       </c>
-      <c r="U52" t="n" s="0">
-        <v>2.999999999999912</v>
-      </c>
-      <c r="V52" t="n" s="0">
-        <v>2.9999999999999245</v>
-      </c>
-      <c r="W52" t="n" s="0">
-        <v>2.9999999999999054</v>
-      </c>
-      <c r="X52" t="n" s="0">
-        <v>2.9999999999999085</v>
-      </c>
       <c r="Y52" t="n" s="0">
-        <v>2.999999999999911</v>
+        <v>2.9999999999999303</v>
       </c>
       <c r="Z52" t="n" s="0">
-        <v>2.9999999999999116</v>
+        <v>2.9999999999999147</v>
       </c>
       <c r="AA52" t="n" s="0">
-        <v>2.999999999999913</v>
+        <v>2.9999999999999045</v>
       </c>
       <c r="AB52" t="n" s="0">
-        <v>2.999999999999913</v>
+        <v>2.999999999999907</v>
       </c>
       <c r="AC52" t="n" s="0">
-        <v>2.999999999999904</v>
+        <v>2.999999999999906</v>
       </c>
       <c r="AD52" t="n" s="0">
-        <v>2.999999999999913</v>
+        <v>2.9999999999999547</v>
       </c>
       <c r="AE52" t="n" s="0">
         <v>2.9999999999999116</v>
       </c>
       <c r="AF52" t="n" s="0">
-        <v>2.9999999999999116</v>
+        <v>2.9999999999999143</v>
       </c>
     </row>
     <row r="53">
       <c r="C53" t="n" s="0">
-        <v>-3.8627821477948068</v>
+        <v>-3.8627670637238163</v>
       </c>
       <c r="D53" t="n" s="0">
-        <v>-3.8627385662637157</v>
+        <v>-3.862561576149235</v>
       </c>
       <c r="E53" t="n" s="0">
-        <v>-3.862691569231342</v>
+        <v>-3.862747837965121</v>
       </c>
       <c r="F53" t="n" s="0">
-        <v>-3.8627588408953786</v>
+        <v>-3.8619958434843187</v>
       </c>
       <c r="G53" t="n" s="0">
-        <v>-3.86278214696114</v>
+        <v>-3.862782147820756</v>
       </c>
       <c r="H53" t="n" s="0">
-        <v>-3.8627821477804223</v>
+        <v>-3.8627820919419684</v>
       </c>
       <c r="I53" t="n" s="0">
-        <v>-3.8627714445264854</v>
+        <v>-3.8627819007806545</v>
       </c>
       <c r="J53" t="n" s="0">
-        <v>-3.862782098334168</v>
+        <v>-3.8627785252606173</v>
       </c>
       <c r="K53" t="n" s="0">
-        <v>-3.8627819700933426</v>
+        <v>-3.8627485560405406</v>
       </c>
       <c r="L53" t="n" s="0">
-        <v>-3.8626632095092717</v>
+        <v>-3.862339600132734</v>
       </c>
       <c r="M53" t="n" s="0">
-        <v>-3.862782147816266</v>
+        <v>-3.862782147820754</v>
       </c>
       <c r="N53" t="n" s="0">
-        <v>-3.862782147820733</v>
+        <v>-3.862706789210379</v>
       </c>
       <c r="O53" t="n" s="0">
-        <v>-3.8627821440069363</v>
+        <v>-3.8627821475369233</v>
       </c>
       <c r="P53" t="n" s="0">
-        <v>-3.862782147634218</v>
+        <v>-3.8627821413815795</v>
       </c>
       <c r="Q53" t="n" s="0">
-        <v>-3.861392165351954</v>
+        <v>-3.8627821478207545</v>
       </c>
       <c r="R53" t="n" s="0">
-        <v>-3.86155502401643</v>
+        <v>-3.862780477753253</v>
       </c>
       <c r="S53" t="n" s="0">
-        <v>-3.8083862455324575</v>
+        <v>-3.8627810711911224</v>
       </c>
       <c r="T53" t="n" s="0">
-        <v>-3.862782147820752</v>
+        <v>-3.8627783258189385</v>
       </c>
       <c r="U53" t="n" s="0">
-        <v>-3.8627802718156437</v>
+        <v>-3.8627083970510316</v>
       </c>
       <c r="V53" t="n" s="0">
-        <v>-3.8626274580602087</v>
+        <v>-3.862782137875915</v>
       </c>
       <c r="W53" t="n" s="0">
-        <v>-3.8627227896208756</v>
+        <v>-3.862782147820506</v>
       </c>
       <c r="X53" t="n" s="0">
-        <v>-3.862762468405114</v>
+        <v>-3.862782147820756</v>
       </c>
       <c r="Y53" t="n" s="0">
-        <v>-3.862773300350014</v>
+        <v>-3.8627821426208717</v>
       </c>
       <c r="Z53" t="n" s="0">
-        <v>-3.8627821478207554</v>
+        <v>-3.862035139742507</v>
       </c>
       <c r="AA53" t="n" s="0">
-        <v>-3.8627797022116903</v>
+        <v>-3.8625342121047312</v>
       </c>
       <c r="AB53" t="n" s="0">
-        <v>-3.8627821478202717</v>
+        <v>-3.8627821465802143</v>
       </c>
       <c r="AC53" t="n" s="0">
-        <v>-3.8627821478207554</v>
+        <v>-3.862782147820547</v>
       </c>
       <c r="AD53" t="n" s="0">
-        <v>-3.86278214780729</v>
+        <v>-3.8627671732637587</v>
       </c>
       <c r="AE53" t="n" s="0">
-        <v>-3.8627821478200284</v>
+        <v>-3.862778948784634</v>
       </c>
       <c r="AF53" t="n" s="0">
-        <v>-3.8607781599404065</v>
+        <v>-3.862782033327571</v>
       </c>
     </row>
     <row r="54">
       <c r="C54" t="n" s="0">
-        <v>-3.1797885992271495</v>
+        <v>-3.321994491533448</v>
       </c>
       <c r="D54" t="n" s="0">
-        <v>-3.3219943434001995</v>
+        <v>-3.1917863210592206</v>
       </c>
       <c r="E54" t="n" s="0">
-        <v>-3.099196274023126</v>
+        <v>-3.165316005208565</v>
       </c>
       <c r="F54" t="n" s="0">
-        <v>-3.3192981599341964</v>
+        <v>-3.2011470831699964</v>
       </c>
       <c r="G54" t="n" s="0">
-        <v>-3.321995171584125</v>
+        <v>-2.867248866995874</v>
       </c>
       <c r="H54" t="n" s="0">
-        <v>-3.3219951705318054</v>
+        <v>-3.3219951032310178</v>
       </c>
       <c r="I54" t="n" s="0">
-        <v>-3.1884002735641634</v>
+        <v>-3.3219950203301454</v>
       </c>
       <c r="J54" t="n" s="0">
-        <v>-3.3218521982369453</v>
+        <v>-3.101090910983492</v>
       </c>
       <c r="K54" t="n" s="0">
-        <v>-3.321995049305353</v>
+        <v>-3.321983374072152</v>
       </c>
       <c r="L54" t="n" s="0">
-        <v>-3.196905606443115</v>
+        <v>-3.32199202715313</v>
       </c>
       <c r="M54" t="n" s="0">
-        <v>-3.3219950125284465</v>
+        <v>-2.3978807046674113</v>
       </c>
       <c r="N54" t="n" s="0">
-        <v>-3.3219891112471753</v>
+        <v>-3.1737454931387425</v>
       </c>
       <c r="O54" t="n" s="0">
-        <v>-2.9519900529634833</v>
+        <v>-3.315361454815753</v>
       </c>
       <c r="P54" t="n" s="0">
-        <v>-3.1652894409572743</v>
+        <v>-3.3219311617049607</v>
       </c>
       <c r="Q54" t="n" s="0">
-        <v>-3.199277690829759</v>
+        <v>-3.1723891879009325</v>
       </c>
       <c r="R54" t="n" s="0">
-        <v>-3.32102790990015</v>
+        <v>-3.320244064635806</v>
       </c>
       <c r="S54" t="n" s="0">
-        <v>-3.3219515052887947</v>
+        <v>-3.2023309473281127</v>
       </c>
       <c r="T54" t="n" s="0">
-        <v>-3.321994819632543</v>
+        <v>-3.1739542736366713</v>
       </c>
       <c r="U54" t="n" s="0">
-        <v>-3.318788457890237</v>
+        <v>-3.3216629596890774</v>
       </c>
       <c r="V54" t="n" s="0">
-        <v>-3.1921828376035988</v>
+        <v>-3.1943137121881504</v>
       </c>
       <c r="W54" t="n" s="0">
-        <v>-3.1901835659529043</v>
+        <v>-3.3219937217881106</v>
       </c>
       <c r="X54" t="n" s="0">
-        <v>-3.3219943765464572</v>
+        <v>-3.1996954058949973</v>
       </c>
       <c r="Y54" t="n" s="0">
-        <v>-3.1676240119089503</v>
+        <v>-3.193634616274213</v>
       </c>
       <c r="Z54" t="n" s="0">
-        <v>-3.1468862546054863</v>
+        <v>-3.1695065775785825</v>
       </c>
       <c r="AA54" t="n" s="0">
-        <v>-3.201524270371916</v>
+        <v>-3.3183213495518644</v>
       </c>
       <c r="AB54" t="n" s="0">
-        <v>-3.3218993110122517</v>
+        <v>-3.3219460303650523</v>
       </c>
       <c r="AC54" t="n" s="0">
-        <v>-3.321979700415459</v>
+        <v>-3.3219951715639593</v>
       </c>
       <c r="AD54" t="n" s="0">
-        <v>-3.321755896209236</v>
+        <v>-3.32156542946268</v>
       </c>
       <c r="AE54" t="n" s="0">
-        <v>-3.321995171569946</v>
+        <v>-3.189682026108412</v>
       </c>
       <c r="AF54" t="n" s="0">
-        <v>-3.2201362435550296</v>
+        <v>-3.1985106451188945</v>
       </c>
     </row>
     <row r="55">
       <c r="C55" t="n" s="0">
-        <v>-5.10077214028838</v>
+        <v>-10.153199679058227</v>
       </c>
       <c r="D55" t="n" s="0">
+        <v>-5.100770168193738</v>
+      </c>
+      <c r="E55" t="n" s="0">
+        <v>-10.153199679058229</v>
+      </c>
+      <c r="F55" t="n" s="0">
+        <v>-10.153199679058227</v>
+      </c>
+      <c r="G55" t="n" s="0">
+        <v>-10.153017883236569</v>
+      </c>
+      <c r="H55" t="n" s="0">
+        <v>-10.153199508009594</v>
+      </c>
+      <c r="I55" t="n" s="0">
+        <v>-5.1007721400594335</v>
+      </c>
+      <c r="J55" t="n" s="0">
+        <v>-10.14307315026306</v>
+      </c>
+      <c r="K55" t="n" s="0">
+        <v>-10.153199679058227</v>
+      </c>
+      <c r="L55" t="n" s="0">
+        <v>-2.630470255425536</v>
+      </c>
+      <c r="M55" t="n" s="0">
+        <v>-10.153199679058215</v>
+      </c>
+      <c r="N55" t="n" s="0">
+        <v>-5.055197728932868</v>
+      </c>
+      <c r="O55" t="n" s="0">
+        <v>-5.100772140331135</v>
+      </c>
+      <c r="P55" t="n" s="0">
+        <v>-5.100772140331753</v>
+      </c>
+      <c r="Q55" t="n" s="0">
+        <v>-10.153199679058226</v>
+      </c>
+      <c r="R55" t="n" s="0">
+        <v>-10.153199679058227</v>
+      </c>
+      <c r="S55" t="n" s="0">
+        <v>-10.153199675852708</v>
+      </c>
+      <c r="T55" t="n" s="0">
+        <v>-10.153199564336857</v>
+      </c>
+      <c r="U55" t="n" s="0">
+        <v>-10.15319967905767</v>
+      </c>
+      <c r="V55" t="n" s="0">
+        <v>-5.100772139515442</v>
+      </c>
+      <c r="W55" t="n" s="0">
+        <v>-10.153199550533506</v>
+      </c>
+      <c r="X55" t="n" s="0">
+        <v>-10.153199679056925</v>
+      </c>
+      <c r="Y55" t="n" s="0">
+        <v>-5.100772140331988</v>
+      </c>
+      <c r="Z55" t="n" s="0">
         <v>-5.100772140331986</v>
       </c>
-      <c r="E55" t="n" s="0">
-        <v>-10.153055686708933</v>
-      </c>
-      <c r="F55" t="n" s="0">
-        <v>-10.153199679058229</v>
-      </c>
-      <c r="G55" t="n" s="0">
-        <v>-10.153199678897414</v>
-      </c>
-      <c r="H55" t="n" s="0">
-        <v>-5.100772140331986</v>
-      </c>
-      <c r="I55" t="n" s="0">
-        <v>-5.100772140328711</v>
-      </c>
-      <c r="J55" t="n" s="0">
-        <v>-10.153199672158268</v>
-      </c>
-      <c r="K55" t="n" s="0">
+      <c r="AA55" t="n" s="0">
+        <v>-5.100772136346834</v>
+      </c>
+      <c r="AB55" t="n" s="0">
+        <v>-2.6304716684108937</v>
+      </c>
+      <c r="AC55" t="n" s="0">
         <v>-5.100772140331988</v>
       </c>
-      <c r="L55" t="n" s="0">
-        <v>-10.153199679048083</v>
-      </c>
-      <c r="M55" t="n" s="0">
-        <v>-5.10077201546755</v>
-      </c>
-      <c r="N55" t="n" s="0">
-        <v>-5.100772136266641</v>
-      </c>
-      <c r="O55" t="n" s="0">
-        <v>-10.153199631566398</v>
-      </c>
-      <c r="P55" t="n" s="0">
-        <v>-5.100772140331987</v>
-      </c>
-      <c r="Q55" t="n" s="0">
-        <v>-5.10077206636211</v>
-      </c>
-      <c r="R55" t="n" s="0">
-        <v>-10.153199679058217</v>
-      </c>
-      <c r="S55" t="n" s="0">
-        <v>-10.153199679058229</v>
-      </c>
-      <c r="T55" t="n" s="0">
-        <v>-2.6304716684108937</v>
-      </c>
-      <c r="U55" t="n" s="0">
-        <v>-5.100772133605136</v>
-      </c>
-      <c r="V55" t="n" s="0">
+      <c r="AD55" t="n" s="0">
+        <v>-2.63047166841038</v>
+      </c>
+      <c r="AE55" t="n" s="0">
         <v>-5.100772140331988</v>
       </c>
-      <c r="W55" t="n" s="0">
-        <v>-10.153199679058226</v>
-      </c>
-      <c r="X55" t="n" s="0">
-        <v>-10.153199678586075</v>
-      </c>
-      <c r="Y55" t="n" s="0">
-        <v>-10.153199679058227</v>
-      </c>
-      <c r="Z55" t="n" s="0">
-        <v>-5.100772140331587</v>
-      </c>
-      <c r="AA55" t="n" s="0">
-        <v>-2.6304716683151286</v>
-      </c>
-      <c r="AB55" t="n" s="0">
-        <v>-5.100772140291469</v>
-      </c>
-      <c r="AC55" t="n" s="0">
-        <v>-10.153199679058227</v>
-      </c>
-      <c r="AD55" t="n" s="0">
-        <v>-5.100772140331473</v>
-      </c>
-      <c r="AE55" t="n" s="0">
-        <v>-10.153199679058229</v>
-      </c>
       <c r="AF55" t="n" s="0">
-        <v>-10.153199679058229</v>
+        <v>-5.055197727811798</v>
       </c>
     </row>
     <row r="56">
       <c r="C56" t="n" s="0">
-        <v>-10.402916445645069</v>
+        <v>-5.128822755876281</v>
       </c>
       <c r="D56" t="n" s="0">
-        <v>-10.402940566818664</v>
+        <v>-10.40294056681866</v>
       </c>
       <c r="E56" t="n" s="0">
-        <v>-5.12882279696545</v>
+        <v>-3.7243003465069995</v>
       </c>
       <c r="F56" t="n" s="0">
-        <v>-5.1288227928618095</v>
+        <v>-10.351972508578482</v>
       </c>
       <c r="G56" t="n" s="0">
-        <v>-10.40294056546987</v>
+        <v>-10.402940566809805</v>
       </c>
       <c r="H56" t="n" s="0">
-        <v>-5.1288227969654026</v>
+        <v>-2.7658953371529833</v>
       </c>
       <c r="I56" t="n" s="0">
-        <v>-5.0876702231854045</v>
+        <v>-10.402940566818662</v>
       </c>
       <c r="J56" t="n" s="0">
+        <v>-5.128822082190909</v>
+      </c>
+      <c r="K56" t="n" s="0">
+        <v>-10.402453711224899</v>
+      </c>
+      <c r="L56" t="n" s="0">
+        <v>-5.128822796965454</v>
+      </c>
+      <c r="M56" t="n" s="0">
         <v>-5.128822796965456</v>
       </c>
-      <c r="K56" t="n" s="0">
+      <c r="N56" t="n" s="0">
+        <v>-10.372538477949115</v>
+      </c>
+      <c r="O56" t="n" s="0">
+        <v>-10.402940566818662</v>
+      </c>
+      <c r="P56" t="n" s="0">
+        <v>-5.12882032894864</v>
+      </c>
+      <c r="Q56" t="n" s="0">
+        <v>-1.837592927360792</v>
+      </c>
+      <c r="R56" t="n" s="0">
+        <v>-10.40294056681866</v>
+      </c>
+      <c r="S56" t="n" s="0">
+        <v>-2.765468352698561</v>
+      </c>
+      <c r="T56" t="n" s="0">
+        <v>-10.40294056052227</v>
+      </c>
+      <c r="U56" t="n" s="0">
+        <v>-10.402900198764383</v>
+      </c>
+      <c r="V56" t="n" s="0">
+        <v>-5.128822796965416</v>
+      </c>
+      <c r="W56" t="n" s="0">
+        <v>-10.40294056659746</v>
+      </c>
+      <c r="X56" t="n" s="0">
+        <v>-5.12783857682306</v>
+      </c>
+      <c r="Y56" t="n" s="0">
+        <v>-10.402940566818666</v>
+      </c>
+      <c r="Z56" t="n" s="0">
+        <v>-5.128822796965434</v>
+      </c>
+      <c r="AA56" t="n" s="0">
+        <v>-10.40294056659042</v>
+      </c>
+      <c r="AB56" t="n" s="0">
+        <v>-10.402940566625729</v>
+      </c>
+      <c r="AC56" t="n" s="0">
         <v>-5.128822796965455</v>
       </c>
-      <c r="L56" t="n" s="0">
-        <v>-5.128800450609823</v>
-      </c>
-      <c r="M56" t="n" s="0">
-        <v>-10.402940482956405</v>
-      </c>
-      <c r="N56" t="n" s="0">
-        <v>-5.128822796965455</v>
-      </c>
-      <c r="O56" t="n" s="0">
-        <v>-5.1288227969652445</v>
-      </c>
-      <c r="P56" t="n" s="0">
-        <v>-10.402905985087811</v>
-      </c>
-      <c r="Q56" t="n" s="0">
+      <c r="AD56" t="n" s="0">
+        <v>-5.128822787825472</v>
+      </c>
+      <c r="AE56" t="n" s="0">
+        <v>-10.402599761849178</v>
+      </c>
+      <c r="AF56" t="n" s="0">
         <v>-10.40294056681866</v>
-      </c>
-      <c r="R56" t="n" s="0">
-        <v>-10.40294056681716</v>
-      </c>
-      <c r="S56" t="n" s="0">
-        <v>-2.7658973277790255</v>
-      </c>
-      <c r="T56" t="n" s="0">
-        <v>-10.402940424371582</v>
-      </c>
-      <c r="U56" t="n" s="0">
-        <v>-5.12609135614498</v>
-      </c>
-      <c r="V56" t="n" s="0">
-        <v>-10.402940566818659</v>
-      </c>
-      <c r="W56" t="n" s="0">
-        <v>-10.40294056681816</v>
-      </c>
-      <c r="X56" t="n" s="0">
-        <v>-5.128822493912207</v>
-      </c>
-      <c r="Y56" t="n" s="0">
-        <v>-5.128822796965445</v>
-      </c>
-      <c r="Z56" t="n" s="0">
-        <v>-10.402454168639242</v>
-      </c>
-      <c r="AA56" t="n" s="0">
-        <v>-5.128822796965455</v>
-      </c>
-      <c r="AB56" t="n" s="0">
-        <v>-5.128822701518603</v>
-      </c>
-      <c r="AC56" t="n" s="0">
-        <v>-5.128822796861512</v>
-      </c>
-      <c r="AD56" t="n" s="0">
-        <v>-10.402940566772143</v>
-      </c>
-      <c r="AE56" t="n" s="0">
-        <v>-10.402940566818664</v>
-      </c>
-      <c r="AF56" t="n" s="0">
-        <v>-5.128822796718973</v>
       </c>
     </row>
     <row r="57">
       <c r="C57" t="n" s="0">
-        <v>-10.536409816692048</v>
+        <v>-1.6765531443344086</v>
       </c>
       <c r="D57" t="n" s="0">
-        <v>-5.175646741647882</v>
+        <v>-5.175646739650303</v>
       </c>
       <c r="E57" t="n" s="0">
-        <v>-9.969476039730315</v>
+        <v>-5.17564674164788</v>
       </c>
       <c r="F57" t="n" s="0">
-        <v>-2.8066189799828054</v>
+        <v>-10.536409816692032</v>
       </c>
       <c r="G57" t="n" s="0">
-        <v>-5.175646741647881</v>
+        <v>-5.175646741647884</v>
       </c>
       <c r="H57" t="n" s="0">
-        <v>-5.128480786627355</v>
+        <v>-5.175646740742729</v>
       </c>
       <c r="I57" t="n" s="0">
-        <v>-2.341319178979983</v>
+        <v>-5.1756467416463305</v>
       </c>
       <c r="J57" t="n" s="0">
-        <v>-5.136351319679044</v>
+        <v>-5.175646737888616</v>
       </c>
       <c r="K57" t="n" s="0">
-        <v>-3.8354268032089385</v>
+        <v>-10.53640981651506</v>
       </c>
       <c r="L57" t="n" s="0">
-        <v>-1.8594803012174992</v>
+        <v>-5.1756467416478795</v>
       </c>
       <c r="M57" t="n" s="0">
-        <v>-1.676553243486734</v>
+        <v>-10.536409816692043</v>
       </c>
       <c r="N57" t="n" s="0">
-        <v>-10.53640981669135</v>
+        <v>-5.175646741647879</v>
       </c>
       <c r="O57" t="n" s="0">
-        <v>-10.536409816692034</v>
+        <v>-10.536259658999457</v>
       </c>
       <c r="P57" t="n" s="0">
+        <v>-2.4273352000741277</v>
+      </c>
+      <c r="Q57" t="n" s="0">
         <v>-10.536409816692046</v>
       </c>
-      <c r="Q57" t="n" s="0">
-        <v>-10.536409815078715</v>
-      </c>
       <c r="R57" t="n" s="0">
+        <v>-1.6765532502392722</v>
+      </c>
+      <c r="S57" t="n" s="0">
+        <v>-5.175645553208794</v>
+      </c>
+      <c r="T57" t="n" s="0">
         <v>-5.175646741647883</v>
       </c>
-      <c r="S57" t="n" s="0">
-        <v>-5.175644154652529</v>
-      </c>
-      <c r="T57" t="n" s="0">
-        <v>-10.536409816692046</v>
-      </c>
       <c r="U57" t="n" s="0">
-        <v>-10.536409816646858</v>
+        <v>-10.536409803827654</v>
       </c>
       <c r="V57" t="n" s="0">
-        <v>-10.536409816692046</v>
+        <v>-5.175646741644656</v>
       </c>
       <c r="W57" t="n" s="0">
-        <v>-10.536409742504631</v>
+        <v>-5.175646083162655</v>
       </c>
       <c r="X57" t="n" s="0">
-        <v>-5.1756467416477925</v>
+        <v>-10.536409816692045</v>
       </c>
       <c r="Y57" t="n" s="0">
-        <v>-5.1756467399927795</v>
+        <v>-5.128480786627454</v>
       </c>
       <c r="Z57" t="n" s="0">
-        <v>-10.533625705698581</v>
+        <v>-5.175646741626435</v>
       </c>
       <c r="AA57" t="n" s="0">
-        <v>-10.536409816690808</v>
+        <v>-5.175646741580516</v>
       </c>
       <c r="AB57" t="n" s="0">
-        <v>-10.536409787720968</v>
+        <v>-5.175646741647883</v>
       </c>
       <c r="AC57" t="n" s="0">
-        <v>-10.53640973074645</v>
+        <v>-5.175646741490748</v>
       </c>
       <c r="AD57" t="n" s="0">
-        <v>-5.17564670233168</v>
+        <v>-5.175646741647883</v>
       </c>
       <c r="AE57" t="n" s="0">
-        <v>-10.536409816692045</v>
+        <v>-5.175646741647871</v>
       </c>
       <c r="AF57" t="n" s="0">
-        <v>-10.536408677633691</v>
+        <v>-10.53640981667794</v>
       </c>
     </row>
     <row r="64">
       <c r="C64" t="n" s="0">
-        <v>8.763988796181985E-34</v>
+        <v>1.9547832386329982E-33</v>
       </c>
       <c r="D64" t="n" s="0">
-        <v>4.153745084038235E-32</v>
+        <v>7.672480897738633E-33</v>
       </c>
       <c r="E64" t="n" s="0">
-        <v>3.697320326895416E-34</v>
+        <v>2.0434759254824222E-31</v>
       </c>
       <c r="F64" t="n" s="0">
-        <v>1.1073057165195085E-31</v>
+        <v>4.625519954636297E-33</v>
       </c>
       <c r="G64" t="n" s="0">
-        <v>1.3011654676306686E-31</v>
+        <v>2.1068031514466566E-31</v>
       </c>
       <c r="H64" t="n" s="0">
-        <v>1.679823904399776E-32</v>
+        <v>8.995356353958908E-32</v>
       </c>
       <c r="I64" t="n" s="0">
-        <v>1.8457393646530886E-33</v>
+        <v>1.147376273865607E-32</v>
       </c>
       <c r="J64" t="n" s="0">
-        <v>1.0473769380095707E-33</v>
+        <v>2.103979526017725E-33</v>
       </c>
       <c r="K64" t="n" s="0">
-        <v>4.374416355402399E-34</v>
+        <v>1.3975662176819205E-31</v>
       </c>
       <c r="L64" t="n" s="0">
-        <v>1.205787798394549E-33</v>
+        <v>1.339475085047795E-32</v>
       </c>
       <c r="M64" t="n" s="0">
-        <v>1.3343859655474314E-32</v>
+        <v>1.033934704502039E-31</v>
       </c>
       <c r="N64" t="n" s="0">
-        <v>2.883587969374623E-34</v>
+        <v>3.945779333576391E-31</v>
       </c>
       <c r="O64" t="n" s="0">
-        <v>6.859983933276548E-31</v>
+        <v>1.3312699866277665E-33</v>
       </c>
       <c r="P64" t="n" s="0">
-        <v>2.5885366957525653E-31</v>
+        <v>7.719811162559364E-32</v>
       </c>
       <c r="Q64" t="n" s="0">
-        <v>1.2973976309232055E-33</v>
+        <v>2.0217866892376491E-35</v>
       </c>
       <c r="R64" t="n" s="0">
-        <v>2.056131289035809E-32</v>
+        <v>2.1430431589045436E-32</v>
       </c>
       <c r="S64" t="n" s="0">
-        <v>4.238577188634274E-31</v>
+        <v>1.1489315906642853E-33</v>
       </c>
       <c r="T64" t="n" s="0">
-        <v>5.401607389656318E-31</v>
+        <v>3.295135730605171E-31</v>
       </c>
       <c r="U64" t="n" s="0">
-        <v>1.5162712406517708E-33</v>
+        <v>1.2918662091955492E-34</v>
       </c>
       <c r="V64" t="n" s="0">
-        <v>8.781754412609867E-33</v>
+        <v>1.0481208978892162E-31</v>
       </c>
       <c r="W64" t="n" s="0">
-        <v>5.2787231205129715E-33</v>
+        <v>8.755186644001901E-32</v>
       </c>
       <c r="X64" t="n" s="0">
-        <v>1.6370979326033515E-30</v>
+        <v>5.721523273715327E-33</v>
       </c>
       <c r="Y64" t="n" s="0">
-        <v>2.729038269292107E-33</v>
+        <v>4.159065913512035E-34</v>
       </c>
       <c r="Z64" t="n" s="0">
-        <v>3.984325550104111E-32</v>
+        <v>2.691299879909689E-30</v>
       </c>
       <c r="AA64" t="n" s="0">
-        <v>3.0450830694800747E-32</v>
+        <v>2.848208889203442E-34</v>
       </c>
       <c r="AB64" t="n" s="0">
-        <v>6.1861529495238355E-31</v>
+        <v>2.1995651972464952E-32</v>
       </c>
       <c r="AC64" t="n" s="0">
-        <v>1.6952904162496764E-33</v>
+        <v>2.723201719667837E-33</v>
       </c>
       <c r="AD64" t="n" s="0">
-        <v>3.99092457720591E-34</v>
+        <v>1.0716121292004376E-32</v>
       </c>
       <c r="AE64" t="n" s="0">
-        <v>5.649786237991872E-31</v>
+        <v>2.738916582921087E-31</v>
       </c>
       <c r="AF64" t="n" s="0">
-        <v>1.2649314689171253E-32</v>
+        <v>1.3514249194854957E-32</v>
       </c>
     </row>
     <row r="65">
       <c r="C65" t="n" s="0">
-        <v>2.1256670549092138E-19</v>
+        <v>6.260783473750237E-20</v>
       </c>
       <c r="D65" t="n" s="0">
-        <v>1.7765865148063064E-19</v>
+        <v>9.748413423480769E-19</v>
       </c>
       <c r="E65" t="n" s="0">
-        <v>1.0641888536011075E-18</v>
+        <v>1.859033942604992E-18</v>
       </c>
       <c r="F65" t="n" s="0">
-        <v>9.453764315660267E-19</v>
+        <v>2.2536474051957354E-19</v>
       </c>
       <c r="G65" t="n" s="0">
-        <v>2.7316893712100016E-19</v>
+        <v>1.0495076198156626E-18</v>
       </c>
       <c r="H65" t="n" s="0">
-        <v>1.1832530597170412E-18</v>
+        <v>3.39574528138087E-19</v>
       </c>
       <c r="I65" t="n" s="0">
-        <v>5.353942999543195E-19</v>
+        <v>3.19095580471405E-19</v>
       </c>
       <c r="J65" t="n" s="0">
-        <v>2.235516783301948E-18</v>
+        <v>2.256287591113569E-19</v>
       </c>
       <c r="K65" t="n" s="0">
-        <v>3.8709706765613204E-19</v>
+        <v>5.020674665553766E-20</v>
       </c>
       <c r="L65" t="n" s="0">
-        <v>9.124252575995654E-20</v>
+        <v>1.2907151328502272E-19</v>
       </c>
       <c r="M65" t="n" s="0">
-        <v>1.524458114255416E-19</v>
+        <v>7.727193611817127E-19</v>
       </c>
       <c r="N65" t="n" s="0">
-        <v>6.717798972801967E-19</v>
+        <v>1.4069148156356643E-18</v>
       </c>
       <c r="O65" t="n" s="0">
-        <v>1.175292137602021E-18</v>
+        <v>2.8834703850440393E-19</v>
       </c>
       <c r="P65" t="n" s="0">
-        <v>1.779490838117816E-18</v>
+        <v>4.5470270044332883E-20</v>
       </c>
       <c r="Q65" t="n" s="0">
-        <v>5.879129382388592E-19</v>
+        <v>8.079898322239498E-19</v>
       </c>
       <c r="R65" t="n" s="0">
-        <v>6.009195124335802E-19</v>
+        <v>5.002691056074781E-19</v>
       </c>
       <c r="S65" t="n" s="0">
-        <v>6.419958821153185E-19</v>
+        <v>2.1085397028979353E-18</v>
       </c>
       <c r="T65" t="n" s="0">
-        <v>1.9662592477139895E-19</v>
+        <v>1.900588839728742E-19</v>
       </c>
       <c r="U65" t="n" s="0">
-        <v>2.3366588515585193E-18</v>
+        <v>5.172050977389888E-19</v>
       </c>
       <c r="V65" t="n" s="0">
-        <v>5.103496904430391E-19</v>
+        <v>3.366754722761261E-19</v>
       </c>
       <c r="W65" t="n" s="0">
-        <v>4.330825112301131E-19</v>
+        <v>1.2957925137221514E-18</v>
       </c>
       <c r="X65" t="n" s="0">
-        <v>1.070596583565699E-18</v>
+        <v>3.940524195736618E-19</v>
       </c>
       <c r="Y65" t="n" s="0">
-        <v>7.33176286134247E-20</v>
+        <v>1.894720779624233E-18</v>
       </c>
       <c r="Z65" t="n" s="0">
-        <v>4.847888427054088E-20</v>
+        <v>4.873322233979167E-18</v>
       </c>
       <c r="AA65" t="n" s="0">
-        <v>1.4289728598763873E-18</v>
+        <v>1.0685163988616257E-18</v>
       </c>
       <c r="AB65" t="n" s="0">
-        <v>3.3433181233634676E-18</v>
+        <v>4.0065626670215554E-19</v>
       </c>
       <c r="AC65" t="n" s="0">
-        <v>3.4491592914725325E-19</v>
+        <v>6.773799109222352E-19</v>
       </c>
       <c r="AD65" t="n" s="0">
-        <v>2.4845068162249387E-20</v>
+        <v>3.6072636530167765E-19</v>
       </c>
       <c r="AE65" t="n" s="0">
-        <v>4.719079872352424E-19</v>
+        <v>4.756990839106409E-19</v>
       </c>
       <c r="AF65" t="n" s="0">
-        <v>1.0199399554075498E-19</v>
+        <v>6.660878363836243E-20</v>
       </c>
     </row>
     <row r="66">
       <c r="C66" t="n" s="0">
-        <v>6.605871869081475E-16</v>
+        <v>8.413387202230722E-17</v>
       </c>
       <c r="D66" t="n" s="0">
-        <v>1.5233729799095401E-15</v>
+        <v>5.743559928517712E-16</v>
       </c>
       <c r="E66" t="n" s="0">
-        <v>5.273939528773727E-15</v>
+        <v>4.4371882965236996E-16</v>
       </c>
       <c r="F66" t="n" s="0">
-        <v>3.0531959027709513E-12</v>
+        <v>5.512896129360393E-17</v>
       </c>
       <c r="G66" t="n" s="0">
-        <v>9.09785907601232E-15</v>
+        <v>5.689237163388572E-14</v>
       </c>
       <c r="H66" t="n" s="0">
-        <v>1.4653225388152454E-14</v>
+        <v>4.8882712773328706E-15</v>
       </c>
       <c r="I66" t="n" s="0">
-        <v>6.764093820792378E-16</v>
+        <v>2.8763652123554433E-16</v>
       </c>
       <c r="J66" t="n" s="0">
-        <v>1.7240412699590133E-17</v>
+        <v>8.601001163770052E-16</v>
       </c>
       <c r="K66" t="n" s="0">
-        <v>1.8688527991982387E-17</v>
+        <v>6.627114757786712E-17</v>
       </c>
       <c r="L66" t="n" s="0">
-        <v>1.3835808790361687E-13</v>
+        <v>1.1200812572975936E-17</v>
       </c>
       <c r="M66" t="n" s="0">
-        <v>8.06733874974235E-15</v>
+        <v>1.2038970029163439E-14</v>
       </c>
       <c r="N66" t="n" s="0">
-        <v>2.940602176417468E-15</v>
+        <v>6.678383917928748E-19</v>
       </c>
       <c r="O66" t="n" s="0">
-        <v>2.111231794786704E-15</v>
+        <v>1.8494971580272636E-14</v>
       </c>
       <c r="P66" t="n" s="0">
-        <v>1.5029004466269316E-17</v>
+        <v>1.8999782415444736E-18</v>
       </c>
       <c r="Q66" t="n" s="0">
-        <v>4.821257008796502E-13</v>
+        <v>1.999446229693308E-15</v>
       </c>
       <c r="R66" t="n" s="0">
-        <v>1.5196637830245524E-16</v>
+        <v>5.875614306882267E-14</v>
       </c>
       <c r="S66" t="n" s="0">
-        <v>1.8458908389425497E-15</v>
+        <v>2.8466505699954717E-15</v>
       </c>
       <c r="T66" t="n" s="0">
-        <v>3.776818274856867E-15</v>
+        <v>2.699584067986841E-16</v>
       </c>
       <c r="U66" t="n" s="0">
-        <v>1.037498912992873E-15</v>
+        <v>3.822086984332358E-14</v>
       </c>
       <c r="V66" t="n" s="0">
-        <v>2.415003033458549E-14</v>
+        <v>5.230350404635776E-14</v>
       </c>
       <c r="W66" t="n" s="0">
-        <v>1.472566667888571E-15</v>
+        <v>1.79696577910641E-16</v>
       </c>
       <c r="X66" t="n" s="0">
-        <v>3.7934415197499395E-14</v>
+        <v>3.0044215718256826E-15</v>
       </c>
       <c r="Y66" t="n" s="0">
-        <v>4.703059639605322E-17</v>
+        <v>2.606167833476891E-15</v>
       </c>
       <c r="Z66" t="n" s="0">
-        <v>3.0670538983975326E-16</v>
+        <v>1.6518783003915401E-15</v>
       </c>
       <c r="AA66" t="n" s="0">
-        <v>2.775769866515891E-16</v>
+        <v>8.558847014002995E-16</v>
       </c>
       <c r="AB66" t="n" s="0">
-        <v>2.512107254209058E-13</v>
+        <v>2.1058279314077454E-14</v>
       </c>
       <c r="AC66" t="n" s="0">
-        <v>3.52401806487338E-14</v>
+        <v>9.342021541206105E-17</v>
       </c>
       <c r="AD66" t="n" s="0">
-        <v>1.051775942367773E-15</v>
+        <v>2.087725847726022E-15</v>
       </c>
       <c r="AE66" t="n" s="0">
-        <v>1.914385857344756E-14</v>
+        <v>2.008540502564816E-13</v>
       </c>
       <c r="AF66" t="n" s="0">
-        <v>5.1927522409122405E-15</v>
+        <v>2.5166383971595266E-18</v>
       </c>
     </row>
     <row r="67">
       <c r="C67" t="n" s="0">
-        <v>1.0297029464855945E-10</v>
+        <v>1.012376182298066E-10</v>
       </c>
       <c r="D67" t="n" s="0">
-        <v>6.273479836713235E-10</v>
+        <v>2.4877829471526623E-10</v>
       </c>
       <c r="E67" t="n" s="0">
-        <v>2.347010471590065E-11</v>
+        <v>1.6957661292895193E-10</v>
       </c>
       <c r="F67" t="n" s="0">
-        <v>7.719861016709201E-11</v>
+        <v>1.2642050704227589E-10</v>
       </c>
       <c r="G67" t="n" s="0">
-        <v>3.2599281307612436E-10</v>
+        <v>4.851455556436258E-11</v>
       </c>
       <c r="H67" t="n" s="0">
-        <v>3.5575530384441424E-11</v>
+        <v>1.021667959281206E-9</v>
       </c>
       <c r="I67" t="n" s="0">
-        <v>2.0023706557877836E-10</v>
+        <v>1.6161260484472044E-10</v>
       </c>
       <c r="J67" t="n" s="0">
-        <v>1.3269620226702663E-10</v>
+        <v>1.0289750659624268E-10</v>
       </c>
       <c r="K67" t="n" s="0">
-        <v>7.272759673127675E-11</v>
+        <v>5.559860221282965E-11</v>
       </c>
       <c r="L67" t="n" s="0">
-        <v>4.396227098752599E-11</v>
+        <v>5.102412164122879E-11</v>
       </c>
       <c r="M67" t="n" s="0">
-        <v>1.4297647250365349E-10</v>
+        <v>1.3029885068553798E-10</v>
       </c>
       <c r="N67" t="n" s="0">
-        <v>6.612306661771048E-12</v>
+        <v>2.9080946909323217E-10</v>
       </c>
       <c r="O67" t="n" s="0">
-        <v>8.303779291082136E-11</v>
+        <v>3.331495773248434E-10</v>
       </c>
       <c r="P67" t="n" s="0">
-        <v>3.662866656893887E-12</v>
+        <v>1.7904837460643213E-10</v>
       </c>
       <c r="Q67" t="n" s="0">
-        <v>4.4882760417908055E-11</v>
+        <v>3.167973653160629E-10</v>
       </c>
       <c r="R67" t="n" s="0">
-        <v>2.4792980090813934E-10</v>
+        <v>3.2883793100412443E-9</v>
       </c>
       <c r="S67" t="n" s="0">
-        <v>8.7854167583728E-12</v>
+        <v>4.4603955734978326E-11</v>
       </c>
       <c r="T67" t="n" s="0">
-        <v>1.950905662059684E-9</v>
+        <v>3.102216730997892E-10</v>
       </c>
       <c r="U67" t="n" s="0">
-        <v>2.9400253643455644E-11</v>
+        <v>6.170369882675207E-11</v>
       </c>
       <c r="V67" t="n" s="0">
-        <v>2.7249349990417708E-9</v>
+        <v>4.4122915340712445E-11</v>
       </c>
       <c r="W67" t="n" s="0">
-        <v>1.872055841168387E-11</v>
+        <v>1.1868551144557483E-10</v>
       </c>
       <c r="X67" t="n" s="0">
-        <v>1.450444055070745E-9</v>
+        <v>6.294332756980983E-10</v>
       </c>
       <c r="Y67" t="n" s="0">
-        <v>1.4228001098038216E-10</v>
+        <v>4.5233148510797584E-10</v>
       </c>
       <c r="Z67" t="n" s="0">
-        <v>4.458730473440449E-10</v>
+        <v>1.8055546593847875E-11</v>
       </c>
       <c r="AA67" t="n" s="0">
-        <v>2.9373858809898793E-10</v>
+        <v>1.0744264068342586E-11</v>
       </c>
       <c r="AB67" t="n" s="0">
-        <v>2.4178262967830265E-9</v>
+        <v>1.0650121224814473E-9</v>
       </c>
       <c r="AC67" t="n" s="0">
-        <v>2.596180507431259E-11</v>
+        <v>1.439917575934183E-10</v>
       </c>
       <c r="AD67" t="n" s="0">
-        <v>1.262739638876668E-9</v>
+        <v>8.215855905591292E-11</v>
       </c>
       <c r="AE67" t="n" s="0">
-        <v>4.9279101964510076E-11</v>
+        <v>6.781847283734148E-11</v>
       </c>
       <c r="AF67" t="n" s="0">
-        <v>5.569894305990182E-11</v>
+        <v>7.627320849542405E-9</v>
       </c>
     </row>
     <row r="68">
       <c r="C68" t="n" s="0">
-        <v>5.972490757223117</v>
+        <v>6.956621000725626</v>
       </c>
       <c r="D68" t="n" s="0">
-        <v>6.035823665923131</v>
+        <v>6.032367302058626</v>
       </c>
       <c r="E68" t="n" s="0">
-        <v>6.21295469651251</v>
+        <v>6.197427856838467</v>
       </c>
       <c r="F68" t="n" s="0">
-        <v>6.175235160864254</v>
+        <v>6.760856109170982</v>
       </c>
       <c r="G68" t="n" s="0">
-        <v>6.257438131142494</v>
+        <v>6.190978617893232</v>
       </c>
       <c r="H68" t="n" s="0">
-        <v>6.253294415016616</v>
+        <v>6.161623629909407</v>
       </c>
       <c r="I68" t="n" s="0">
-        <v>5.917046983415501</v>
+        <v>6.153061535598918</v>
       </c>
       <c r="J68" t="n" s="0">
-        <v>6.867567593299828</v>
+        <v>6.183664926035569</v>
       </c>
       <c r="K68" t="n" s="0">
-        <v>6.249510346951591</v>
+        <v>6.165708691510874</v>
       </c>
       <c r="L68" t="n" s="0">
-        <v>6.023155962006175</v>
+        <v>6.357624703151166</v>
       </c>
       <c r="M68" t="n" s="0">
-        <v>6.821959165540954</v>
+        <v>6.186860873444127</v>
       </c>
       <c r="N68" t="n" s="0">
-        <v>6.174306239850099</v>
+        <v>7.166459949492329</v>
       </c>
       <c r="O68" t="n" s="0">
-        <v>6.2700704748567695</v>
+        <v>6.007538973390566</v>
       </c>
       <c r="P68" t="n" s="0">
-        <v>6.610865429530984</v>
+        <v>6.152567603096639</v>
       </c>
       <c r="Q68" t="n" s="0">
-        <v>5.920187539116461</v>
+        <v>5.9689303060962775</v>
       </c>
       <c r="R68" t="n" s="0">
-        <v>6.271305271117733</v>
+        <v>6.248975946318273</v>
       </c>
       <c r="S68" t="n" s="0">
-        <v>5.987916463560315</v>
+        <v>6.021740697371023</v>
       </c>
       <c r="T68" t="n" s="0">
-        <v>6.412311664800362</v>
+        <v>6.295819247032284</v>
       </c>
       <c r="U68" t="n" s="0">
-        <v>6.244837095283026</v>
+        <v>6.403356981920837</v>
       </c>
       <c r="V68" t="n" s="0">
-        <v>6.176545877227348</v>
+        <v>6.327072766873629</v>
       </c>
       <c r="W68" t="n" s="0">
-        <v>6.898462613175606</v>
+        <v>6.21787515029751</v>
       </c>
       <c r="X68" t="n" s="0">
-        <v>6.176994010887304</v>
+        <v>6.708336537130506</v>
       </c>
       <c r="Y68" t="n" s="0">
-        <v>6.318370474673859</v>
+        <v>6.216140747069076</v>
       </c>
       <c r="Z68" t="n" s="0">
-        <v>6.06112876549133</v>
+        <v>6.4059665735101134</v>
       </c>
       <c r="AA68" t="n" s="0">
-        <v>6.176507003789937</v>
+        <v>7.2040557664612574</v>
       </c>
       <c r="AB68" t="n" s="0">
-        <v>6.182706894297343</v>
+        <v>6.030663103084268</v>
       </c>
       <c r="AC68" t="n" s="0">
-        <v>6.223261401502346</v>
+        <v>6.200044934041963</v>
       </c>
       <c r="AD68" t="n" s="0">
-        <v>6.091453348035877</v>
+        <v>6.263462246866745</v>
       </c>
       <c r="AE68" t="n" s="0">
-        <v>6.1662706345897496</v>
+        <v>6.525027959447121</v>
       </c>
       <c r="AF68" t="n" s="0">
-        <v>6.1005692852039335</v>
+        <v>6.439595650609437</v>
       </c>
     </row>
     <row r="69">
       <c r="C69" t="n" s="0">
-        <v>1.6652540288193454E-6</v>
+        <v>3.4382437008949755E-6</v>
       </c>
       <c r="D69" t="n" s="0">
-        <v>2.5054705267079E-6</v>
+        <v>6.965772758922193E-7</v>
       </c>
       <c r="E69" t="n" s="0">
-        <v>4.877258872508315E-6</v>
+        <v>9.804884350205041E-6</v>
       </c>
       <c r="F69" t="n" s="0">
-        <v>1.2701699536279117E-5</v>
+        <v>3.5419238789237317E-6</v>
       </c>
       <c r="G69" t="n" s="0">
-        <v>4.8833133990093965E-6</v>
+        <v>7.926561506957271E-7</v>
       </c>
       <c r="H69" t="n" s="0">
-        <v>8.34602869267099E-6</v>
+        <v>3.549747652955448E-6</v>
       </c>
       <c r="I69" t="n" s="0">
-        <v>9.269239799107704E-6</v>
+        <v>2.201111477197821E-6</v>
       </c>
       <c r="J69" t="n" s="0">
-        <v>1.3688909470819348E-6</v>
+        <v>1.6884491738928765E-6</v>
       </c>
       <c r="K69" t="n" s="0">
-        <v>6.178384498468126E-6</v>
+        <v>2.581963802018477E-6</v>
       </c>
       <c r="L69" t="n" s="0">
-        <v>4.0421453153446255E-6</v>
+        <v>2.4843621015405543E-6</v>
       </c>
       <c r="M69" t="n" s="0">
-        <v>5.662549183384847E-6</v>
+        <v>4.187773911542959E-6</v>
       </c>
       <c r="N69" t="n" s="0">
-        <v>4.710034587222907E-6</v>
+        <v>4.873130049394541E-6</v>
       </c>
       <c r="O69" t="n" s="0">
-        <v>8.689597224053006E-6</v>
+        <v>3.7946084494161436E-6</v>
       </c>
       <c r="P69" t="n" s="0">
-        <v>6.4815552461844545E-6</v>
+        <v>3.292478783143573E-6</v>
       </c>
       <c r="Q69" t="n" s="0">
-        <v>9.970439084543108E-7</v>
+        <v>5.623580743419473E-6</v>
       </c>
       <c r="R69" t="n" s="0">
-        <v>1.9732474717388477E-6</v>
+        <v>1.8383693565516423E-6</v>
       </c>
       <c r="S69" t="n" s="0">
-        <v>5.242849371328457E-6</v>
+        <v>5.881635076028808E-6</v>
       </c>
       <c r="T69" t="n" s="0">
-        <v>7.110232049614823E-6</v>
+        <v>7.102617839162842E-6</v>
       </c>
       <c r="U69" t="n" s="0">
-        <v>7.759505703669881E-6</v>
+        <v>3.189302590411667E-6</v>
       </c>
       <c r="V69" t="n" s="0">
-        <v>1.945093569762954E-6</v>
+        <v>3.5954698564452243E-6</v>
       </c>
       <c r="W69" t="n" s="0">
-        <v>5.583692865596999E-6</v>
+        <v>4.1191068847893314E-6</v>
       </c>
       <c r="X69" t="n" s="0">
-        <v>1.0200419723108373E-6</v>
+        <v>4.181190339323333E-6</v>
       </c>
       <c r="Y69" t="n" s="0">
-        <v>1.415498711954016E-6</v>
+        <v>3.309806516964938E-6</v>
       </c>
       <c r="Z69" t="n" s="0">
-        <v>5.298549260077198E-6</v>
+        <v>5.574844517743944E-6</v>
       </c>
       <c r="AA69" t="n" s="0">
-        <v>5.2143048967666675E-6</v>
+        <v>7.794061757183208E-6</v>
       </c>
       <c r="AB69" t="n" s="0">
-        <v>4.144308886302696E-6</v>
+        <v>2.8423188795809734E-6</v>
       </c>
       <c r="AC69" t="n" s="0">
-        <v>4.373415923514594E-6</v>
+        <v>4.614485264069328E-6</v>
       </c>
       <c r="AD69" t="n" s="0">
-        <v>5.346041832089397E-6</v>
+        <v>2.161821056882673E-6</v>
       </c>
       <c r="AE69" t="n" s="0">
-        <v>1.3703768642999792E-6</v>
+        <v>5.056570340733584E-6</v>
       </c>
       <c r="AF69" t="n" s="0">
-        <v>9.89058765698755E-6</v>
+        <v>4.3043586583572645E-6</v>
       </c>
     </row>
     <row r="70">
       <c r="C70" t="n" s="0">
-        <v>0.49361724008535174</v>
+        <v>0.00326936393348934</v>
       </c>
       <c r="D70" t="n" s="0">
-        <v>0.23119958185905684</v>
+        <v>0.3283573919297923</v>
       </c>
       <c r="E70" t="n" s="0">
-        <v>0.7243154095819372</v>
+        <v>0.57472520304253</v>
       </c>
       <c r="F70" t="n" s="0">
-        <v>0.0833503413351532</v>
+        <v>0.675070954451504</v>
       </c>
       <c r="G70" t="n" s="0">
-        <v>0.6814880855121221</v>
+        <v>0.34555356081636934</v>
       </c>
       <c r="H70" t="n" s="0">
-        <v>0.06206982161201906</v>
+        <v>0.6090866866810533</v>
       </c>
       <c r="I70" t="n" s="0">
-        <v>0.5491036961730011</v>
+        <v>0.0552247714610991</v>
       </c>
       <c r="J70" t="n" s="0">
-        <v>0.25858412040544365</v>
+        <v>0.7105125651969265</v>
       </c>
       <c r="K70" t="n" s="0">
-        <v>0.5939119855841909</v>
+        <v>0.807800983005445</v>
       </c>
       <c r="L70" t="n" s="0">
-        <v>0.23064994629114782</v>
+        <v>0.7001765616470174</v>
       </c>
       <c r="M70" t="n" s="0">
-        <v>0.2502972080446277</v>
+        <v>0.12363853729571601</v>
       </c>
       <c r="N70" t="n" s="0">
-        <v>0.3554623573350111</v>
+        <v>0.19695912343132477</v>
       </c>
       <c r="O70" t="n" s="0">
-        <v>0.7572872255397355</v>
+        <v>0.42754542886681385</v>
       </c>
       <c r="P70" t="n" s="0">
-        <v>0.9052724369145781</v>
+        <v>0.3640744629131099</v>
       </c>
       <c r="Q70" t="n" s="0">
-        <v>0.8966974786299078</v>
+        <v>0.2882103727196576</v>
       </c>
       <c r="R70" t="n" s="0">
-        <v>0.9434391852450936</v>
+        <v>0.6414490385755139</v>
       </c>
       <c r="S70" t="n" s="0">
-        <v>0.23440183585271404</v>
+        <v>0.8127498221725864</v>
       </c>
       <c r="T70" t="n" s="0">
-        <v>0.24164841128516698</v>
+        <v>0.703381742939249</v>
       </c>
       <c r="U70" t="n" s="0">
-        <v>0.10269475070953533</v>
+        <v>0.2608272078118308</v>
       </c>
       <c r="V70" t="n" s="0">
-        <v>0.5681810268724953</v>
+        <v>0.20585146471215493</v>
       </c>
       <c r="W70" t="n" s="0">
-        <v>0.34532053853223793</v>
+        <v>0.09442931512276209</v>
       </c>
       <c r="X70" t="n" s="0">
-        <v>0.6655772447371753</v>
+        <v>0.6562962627318067</v>
       </c>
       <c r="Y70" t="n" s="0">
-        <v>0.1660878934347118</v>
+        <v>0.5952783379028763</v>
       </c>
       <c r="Z70" t="n" s="0">
-        <v>0.834429317428629</v>
+        <v>0.8810845702626036</v>
       </c>
       <c r="AA70" t="n" s="0">
-        <v>0.21569348804482105</v>
+        <v>0.8680237968103507</v>
       </c>
       <c r="AB70" t="n" s="0">
-        <v>0.0788896116598316</v>
+        <v>0.3321743934683849</v>
       </c>
       <c r="AC70" t="n" s="0">
-        <v>0.1673168478482005</v>
+        <v>0.8131786679209794</v>
       </c>
       <c r="AD70" t="n" s="0">
-        <v>0.9357508446278751</v>
+        <v>0.09845702803685198</v>
       </c>
       <c r="AE70" t="n" s="0">
-        <v>0.6059361801716852</v>
+        <v>0.30562675340020423</v>
       </c>
       <c r="AF70" t="n" s="0">
-        <v>0.537237553171153</v>
+        <v>0.8817624597637904</v>
       </c>
     </row>
     <row r="71">
       <c r="C71" t="n" s="0">
-        <v>-2799.604516017596</v>
+        <v>-2844.73467994208</v>
       </c>
       <c r="D71" t="n" s="0">
-        <v>-3222.258822918483</v>
+        <v>-2523.0090519669375</v>
       </c>
       <c r="E71" t="n" s="0">
-        <v>-2257.900252698954</v>
+        <v>-2379.4551409629917</v>
       </c>
       <c r="F71" t="n" s="0">
-        <v>-2794.8317846812297</v>
+        <v>-2569.447479526034</v>
       </c>
       <c r="G71" t="n" s="0">
-        <v>-2548.3960453371283</v>
+        <v>-2924.732704168538</v>
       </c>
       <c r="H71" t="n" s="0">
-        <v>-2694.326390742937</v>
+        <v>-2409.622445718276</v>
       </c>
       <c r="I71" t="n" s="0">
-        <v>-2147.845513350392</v>
+        <v>-2767.8228233301616</v>
       </c>
       <c r="J71" t="n" s="0">
-        <v>-2649.989985248471</v>
+        <v>-1990.342719904669</v>
       </c>
       <c r="K71" t="n" s="0">
-        <v>-2347.4867435165875</v>
+        <v>-2353.592662309257</v>
       </c>
       <c r="L71" t="n" s="0">
-        <v>-2923.950851492366</v>
+        <v>-2278.4391992785113</v>
       </c>
       <c r="M71" t="n" s="0">
-        <v>-2584.2760878237927</v>
+        <v>-2688.741624362242</v>
       </c>
       <c r="N71" t="n" s="0">
-        <v>-2491.135977384899</v>
+        <v>-2748.596402649481</v>
       </c>
       <c r="O71" t="n" s="0">
-        <v>-2865.5738835182647</v>
+        <v>-2312.5210255311276</v>
       </c>
       <c r="P71" t="n" s="0">
-        <v>-2472.3375721237294</v>
+        <v>-2307.385293602286</v>
       </c>
       <c r="Q71" t="n" s="0">
-        <v>-1988.8889725850524</v>
+        <v>-2889.0454956675553</v>
       </c>
       <c r="R71" t="n" s="0">
-        <v>-2725.413716503979</v>
+        <v>-2530.806732150868</v>
       </c>
       <c r="S71" t="n" s="0">
-        <v>-2344.476798119548</v>
+        <v>-2570.415807118396</v>
       </c>
       <c r="T71" t="n" s="0">
-        <v>-1880.0181354981937</v>
+        <v>-2059.4977460550645</v>
       </c>
       <c r="U71" t="n" s="0">
-        <v>-2728.691965672894</v>
+        <v>-2097.203971988346</v>
       </c>
       <c r="V71" t="n" s="0">
-        <v>-3143.1533021187215</v>
+        <v>-3617.211778729505</v>
       </c>
       <c r="W71" t="n" s="0">
-        <v>-2432.5662924331127</v>
+        <v>-3163.26426566516</v>
       </c>
       <c r="X71" t="n" s="0">
-        <v>-2116.8388913068693</v>
+        <v>-2699.4741058602804</v>
       </c>
       <c r="Y71" t="n" s="0">
-        <v>-2370.0498726836668</v>
+        <v>-2630.123788025565</v>
       </c>
       <c r="Z71" t="n" s="0">
-        <v>-2617.7451043781484</v>
+        <v>-2570.468013421885</v>
       </c>
       <c r="AA71" t="n" s="0">
-        <v>-2317.8755706086463</v>
+        <v>-2629.955344284673</v>
       </c>
       <c r="AB71" t="n" s="0">
-        <v>-2957.708743200958</v>
+        <v>-2214.884610511246</v>
       </c>
       <c r="AC71" t="n" s="0">
-        <v>-2459.558002829079</v>
+        <v>-3202.1435361721833</v>
       </c>
       <c r="AD71" t="n" s="0">
-        <v>-2999.8987870472247</v>
+        <v>-2567.9222085668503</v>
       </c>
       <c r="AE71" t="n" s="0">
-        <v>-2193.9134212775634</v>
+        <v>-2333.6813671869745</v>
       </c>
       <c r="AF71" t="n" s="0">
-        <v>-2610.246357456742</v>
+        <v>-2570.3921387671285</v>
       </c>
     </row>
     <row r="72">
@@ -5840,7 +5840,7 @@
         <v>0.0</v>
       </c>
       <c r="X72" t="n" s="0">
-        <v>8.881784197001252E-15</v>
+        <v>0.0</v>
       </c>
       <c r="Y72" t="n" s="0">
         <v>0.0</v>
@@ -5855,7 +5855,7 @@
         <v>0.0</v>
       </c>
       <c r="AC72" t="n" s="0">
-        <v>3.552713678800501E-15</v>
+        <v>0.0</v>
       </c>
       <c r="AD72" t="n" s="0">
         <v>0.0</v>
@@ -5869,13 +5869,13 @@
     </row>
     <row r="73">
       <c r="C73" t="n" s="0">
-        <v>1.4654943925052066E-14</v>
+        <v>7.549516567451064E-15</v>
       </c>
       <c r="D73" t="n" s="0">
-        <v>7.549516567451064E-15</v>
+        <v>3.9968028886505635E-15</v>
       </c>
       <c r="E73" t="n" s="0">
-        <v>7.549516567451064E-15</v>
+        <v>3.9968028886505635E-15</v>
       </c>
       <c r="F73" t="n" s="0">
         <v>7.549516567451064E-15</v>
@@ -5893,19 +5893,19 @@
         <v>3.9968028886505635E-15</v>
       </c>
       <c r="K73" t="n" s="0">
-        <v>3.9968028886505635E-15</v>
+        <v>7.549516567451064E-15</v>
       </c>
       <c r="L73" t="n" s="0">
-        <v>1.4654943925052066E-14</v>
+        <v>7.549516567451064E-15</v>
       </c>
       <c r="M73" t="n" s="0">
         <v>7.549516567451064E-15</v>
       </c>
       <c r="N73" t="n" s="0">
+        <v>7.549516567451064E-15</v>
+      </c>
+      <c r="O73" t="n" s="0">
         <v>3.9968028886505635E-15</v>
-      </c>
-      <c r="O73" t="n" s="0">
-        <v>7.549516567451064E-15</v>
       </c>
       <c r="P73" t="n" s="0">
         <v>7.549516567451064E-15</v>
@@ -5917,19 +5917,19 @@
         <v>7.549516567451064E-15</v>
       </c>
       <c r="S73" t="n" s="0">
-        <v>3.9968028886505635E-15</v>
+        <v>7.549516567451064E-15</v>
       </c>
       <c r="T73" t="n" s="0">
-        <v>7.549516567451064E-15</v>
+        <v>1.4654943925052066E-14</v>
       </c>
       <c r="U73" t="n" s="0">
         <v>7.549516567451064E-15</v>
       </c>
       <c r="V73" t="n" s="0">
-        <v>1.4654943925052066E-14</v>
+        <v>7.549516567451064E-15</v>
       </c>
       <c r="W73" t="n" s="0">
-        <v>7.549516567451064E-15</v>
+        <v>3.9968028886505635E-15</v>
       </c>
       <c r="X73" t="n" s="0">
         <v>7.549516567451064E-15</v>
@@ -5944,10 +5944,10 @@
         <v>3.9968028886505635E-15</v>
       </c>
       <c r="AB73" t="n" s="0">
+        <v>7.549516567451064E-15</v>
+      </c>
+      <c r="AC73" t="n" s="0">
         <v>3.9968028886505635E-15</v>
-      </c>
-      <c r="AC73" t="n" s="0">
-        <v>7.549516567451064E-15</v>
       </c>
       <c r="AD73" t="n" s="0">
         <v>3.9968028886505635E-15</v>
@@ -5961,1198 +5961,1198 @@
     </row>
     <row r="74">
       <c r="C74" t="n" s="0">
-        <v>0.027901849723153904</v>
+        <v>0.0</v>
       </c>
       <c r="D74" t="n" s="0">
-        <v>0.04196380768383379</v>
+        <v>0.0189594192708602</v>
       </c>
       <c r="E74" t="n" s="0">
         <v>0.0</v>
       </c>
       <c r="F74" t="n" s="0">
-        <v>0.0</v>
+        <v>0.01365059970233895</v>
       </c>
       <c r="G74" t="n" s="0">
         <v>0.0</v>
       </c>
       <c r="H74" t="n" s="0">
-        <v>0.029785760395028227</v>
+        <v>0.010211468549043312</v>
       </c>
       <c r="I74" t="n" s="0">
-        <v>0.010152690321530988</v>
+        <v>0.0</v>
       </c>
       <c r="J74" t="n" s="0">
-        <v>0.011241508641993359</v>
+        <v>0.02533369487877235</v>
       </c>
       <c r="K74" t="n" s="0">
-        <v>0.0</v>
+        <v>0.02005563575445979</v>
       </c>
       <c r="L74" t="n" s="0">
         <v>0.0</v>
       </c>
       <c r="M74" t="n" s="0">
-        <v>0.0</v>
+        <v>0.009933130232577025</v>
       </c>
       <c r="N74" t="n" s="0">
-        <v>0.0</v>
+        <v>0.01867457355486235</v>
       </c>
       <c r="O74" t="n" s="0">
         <v>0.0</v>
       </c>
       <c r="P74" t="n" s="0">
-        <v>0.010336092660694018</v>
+        <v>0.01617661406739057</v>
       </c>
       <c r="Q74" t="n" s="0">
-        <v>0.0</v>
+        <v>0.010869963458771448</v>
       </c>
       <c r="R74" t="n" s="0">
         <v>0.0</v>
       </c>
       <c r="S74" t="n" s="0">
-        <v>0.020439302846542162</v>
+        <v>0.0</v>
       </c>
       <c r="T74" t="n" s="0">
-        <v>0.0</v>
+        <v>0.013181450234297731</v>
       </c>
       <c r="U74" t="n" s="0">
-        <v>0.016845918918379277</v>
+        <v>0.0</v>
       </c>
       <c r="V74" t="n" s="0">
-        <v>0.01494827974538282</v>
+        <v>0.008031111785411937</v>
       </c>
       <c r="W74" t="n" s="0">
-        <v>0.06541142105440789</v>
+        <v>0.0</v>
       </c>
       <c r="X74" t="n" s="0">
-        <v>0.03311401803400238</v>
+        <v>0.0</v>
       </c>
       <c r="Y74" t="n" s="0">
-        <v>0.02320925046820288</v>
+        <v>0.015293007172346162</v>
       </c>
       <c r="Z74" t="n" s="0">
         <v>0.0</v>
       </c>
       <c r="AA74" t="n" s="0">
-        <v>0.0</v>
+        <v>0.008435008650882203</v>
       </c>
       <c r="AB74" t="n" s="0">
         <v>0.0</v>
       </c>
       <c r="AC74" t="n" s="0">
-        <v>0.0</v>
+        <v>2.098370477376932E-9</v>
       </c>
       <c r="AD74" t="n" s="0">
-        <v>0.0</v>
+        <v>0.018705936317057748</v>
       </c>
       <c r="AE74" t="n" s="0">
         <v>0.0</v>
       </c>
       <c r="AF74" t="n" s="0">
-        <v>0.0</v>
+        <v>3.306629192678656E-9</v>
       </c>
     </row>
     <row r="75">
       <c r="C75" t="n" s="0">
-        <v>5.1629622095320764E-6</v>
+        <v>9.974523988458447E-6</v>
       </c>
       <c r="D75" t="n" s="0">
-        <v>4.637371689388956E-6</v>
+        <v>3.871455442072983E-6</v>
       </c>
       <c r="E75" t="n" s="0">
-        <v>2.806561798325501E-6</v>
+        <v>2.6659122408747285E-6</v>
       </c>
       <c r="F75" t="n" s="0">
-        <v>5.3120120685525216E-6</v>
+        <v>4.407265178486857E-6</v>
       </c>
       <c r="G75" t="n" s="0">
-        <v>3.833184601927087E-6</v>
+        <v>2.467128090456288E-6</v>
       </c>
       <c r="H75" t="n" s="0">
-        <v>1.5378254166562356E-6</v>
+        <v>0.020017912642242584</v>
       </c>
       <c r="I75" t="n" s="0">
-        <v>2.937812619431583E-6</v>
+        <v>2.444332794637157E-6</v>
       </c>
       <c r="J75" t="n" s="0">
-        <v>2.0898442622597686E-6</v>
+        <v>9.98964236462778E-7</v>
       </c>
       <c r="K75" t="n" s="0">
-        <v>1.8349337678748169E-6</v>
+        <v>6.522844119493085E-6</v>
       </c>
       <c r="L75" t="n" s="0">
-        <v>1.228143741085414E-5</v>
+        <v>5.7866547236599685E-6</v>
       </c>
       <c r="M75" t="n" s="0">
-        <v>7.296907159831298E-6</v>
+        <v>2.784323622455724E-6</v>
       </c>
       <c r="N75" t="n" s="0">
-        <v>5.198701418705507E-6</v>
+        <v>4.843769132858631E-6</v>
       </c>
       <c r="O75" t="n" s="0">
-        <v>5.694503817652004E-6</v>
+        <v>2.7166201204644456E-6</v>
       </c>
       <c r="P75" t="n" s="0">
-        <v>2.990848076756763E-6</v>
+        <v>1.5969843241208625E-6</v>
       </c>
       <c r="Q75" t="n" s="0">
-        <v>1.3196191371169635E-6</v>
+        <v>1.5580819236065342E-6</v>
       </c>
       <c r="R75" t="n" s="0">
-        <v>2.408894451513555E-6</v>
+        <v>2.9771229916757204E-6</v>
       </c>
       <c r="S75" t="n" s="0">
-        <v>1.2550789513651805E-6</v>
+        <v>3.533588138483098E-6</v>
       </c>
       <c r="T75" t="n" s="0">
-        <v>4.139165381950328E-6</v>
+        <v>3.0245408659295614E-6</v>
       </c>
       <c r="U75" t="n" s="0">
-        <v>1.9458005484899454E-6</v>
+        <v>3.6469556724051178E-6</v>
       </c>
       <c r="V75" t="n" s="0">
-        <v>2.5252902691799246E-6</v>
+        <v>3.0078965231739067E-6</v>
       </c>
       <c r="W75" t="n" s="0">
-        <v>6.2339542752055E-6</v>
+        <v>3.2138193183982135E-6</v>
       </c>
       <c r="X75" t="n" s="0">
-        <v>2.524596270198845E-6</v>
+        <v>8.399679933253745E-6</v>
       </c>
       <c r="Y75" t="n" s="0">
-        <v>2.7700864404094277E-6</v>
+        <v>1.6025073685844266E-6</v>
       </c>
       <c r="Z75" t="n" s="0">
-        <v>2.1345091954759335E-6</v>
+        <v>3.651268932466505E-6</v>
       </c>
       <c r="AA75" t="n" s="0">
-        <v>2.989333434967027E-6</v>
+        <v>5.336982700289437E-6</v>
       </c>
       <c r="AB75" t="n" s="0">
-        <v>5.22586897209993E-7</v>
+        <v>2.160872040237843E-6</v>
       </c>
       <c r="AC75" t="n" s="0">
-        <v>1.5039162885429497E-6</v>
+        <v>3.2817710646216325E-6</v>
       </c>
       <c r="AD75" t="n" s="0">
-        <v>1.3409591861132002E-6</v>
+        <v>4.756072639647077E-6</v>
       </c>
       <c r="AE75" t="n" s="0">
-        <v>2.572138634013269E-6</v>
+        <v>1.8440201242631257E-6</v>
       </c>
       <c r="AF75" t="n" s="0">
-        <v>2.038749801550831E-6</v>
+        <v>5.817935777259954E-6</v>
       </c>
     </row>
     <row r="76">
       <c r="C76" t="n" s="0">
-        <v>2.797346590404133E-5</v>
+        <v>4.764580250041706E-6</v>
       </c>
       <c r="D76" t="n" s="0">
-        <v>2.6540169652957434E-5</v>
+        <v>5.0705023676392535E-5</v>
       </c>
       <c r="E76" t="n" s="0">
-        <v>3.551282365138881E-5</v>
+        <v>8.197805187797311E-6</v>
       </c>
       <c r="F76" t="n" s="0">
-        <v>8.371503047686528E-6</v>
+        <v>1.3568697083054673E-5</v>
       </c>
       <c r="G76" t="n" s="0">
-        <v>4.0178469877253916E-6</v>
+        <v>2.982926473757277E-5</v>
       </c>
       <c r="H76" t="n" s="0">
-        <v>1.6017235167062367E-5</v>
+        <v>1.1986112525534541E-5</v>
       </c>
       <c r="I76" t="n" s="0">
-        <v>2.445853207835664E-5</v>
+        <v>2.556424475943466E-5</v>
       </c>
       <c r="J76" t="n" s="0">
-        <v>3.548543167862494E-5</v>
+        <v>2.5506222214352902E-5</v>
       </c>
       <c r="K76" t="n" s="0">
-        <v>3.679136128380357E-5</v>
+        <v>2.265071523702333E-5</v>
       </c>
       <c r="L76" t="n" s="0">
-        <v>8.923931916863672E-6</v>
+        <v>5.216460800755741E-6</v>
       </c>
       <c r="M76" t="n" s="0">
-        <v>4.304670821217214E-5</v>
+        <v>6.478836926661508E-6</v>
       </c>
       <c r="N76" t="n" s="0">
-        <v>2.2369467612302343E-5</v>
+        <v>1.9570824079485617E-5</v>
       </c>
       <c r="O76" t="n" s="0">
-        <v>1.541070064543011E-5</v>
+        <v>2.8836446815952564E-5</v>
       </c>
       <c r="P76" t="n" s="0">
-        <v>1.657440245644384E-5</v>
+        <v>1.0654233808023476E-5</v>
       </c>
       <c r="Q76" t="n" s="0">
-        <v>7.738550911930053E-6</v>
+        <v>0.12123934611531165</v>
       </c>
       <c r="R76" t="n" s="0">
-        <v>3.419178014533661E-5</v>
+        <v>1.4848948916041815E-5</v>
       </c>
       <c r="S76" t="n" s="0">
-        <v>9.634492726020915E-6</v>
+        <v>1.9665524956278936E-5</v>
       </c>
       <c r="T76" t="n" s="0">
-        <v>4.734166799109536E-5</v>
+        <v>1.8016488645983958E-5</v>
       </c>
       <c r="U76" t="n" s="0">
-        <v>4.564076453553192E-5</v>
+        <v>0.07501481191067072</v>
       </c>
       <c r="V76" t="n" s="0">
-        <v>1.7126600539032445E-5</v>
+        <v>1.0816518853211548E-5</v>
       </c>
       <c r="W76" t="n" s="0">
-        <v>3.289514052300408E-6</v>
+        <v>3.6936455162657016E-5</v>
       </c>
       <c r="X76" t="n" s="0">
-        <v>3.8121994573135346E-5</v>
+        <v>1.764922653989902E-5</v>
       </c>
       <c r="Y76" t="n" s="0">
-        <v>1.3890211334446663E-5</v>
+        <v>3.412131963898443E-5</v>
       </c>
       <c r="Z76" t="n" s="0">
-        <v>7.682899457979357E-5</v>
+        <v>2.729991911499032E-5</v>
       </c>
       <c r="AA76" t="n" s="0">
-        <v>3.1821772928043815E-6</v>
+        <v>8.319405440827058E-6</v>
       </c>
       <c r="AB76" t="n" s="0">
-        <v>5.912072374543425E-5</v>
+        <v>4.389258895037289E-6</v>
       </c>
       <c r="AC76" t="n" s="0">
-        <v>3.438328350736418E-5</v>
+        <v>2.5856029462198202E-5</v>
       </c>
       <c r="AD76" t="n" s="0">
-        <v>1.1728111258434957E-5</v>
+        <v>7.285249674239618E-6</v>
       </c>
       <c r="AE76" t="n" s="0">
-        <v>2.4173754085668346E-5</v>
+        <v>2.4964755617103576E-5</v>
       </c>
       <c r="AF76" t="n" s="0">
-        <v>1.7243399661760017E-5</v>
+        <v>9.362940519484369E-6</v>
       </c>
     </row>
     <row r="77">
       <c r="C77" t="n" s="0">
-        <v>4.626103501988173E-16</v>
+        <v>1.377438118583247E-15</v>
       </c>
       <c r="D77" t="n" s="0">
-        <v>9.138223178565083E-15</v>
+        <v>8.637874235572762E-13</v>
       </c>
       <c r="E77" t="n" s="0">
-        <v>1.992030891954196</v>
+        <v>0.9980037481892611</v>
       </c>
       <c r="F77" t="n" s="0">
-        <v>2.3876518653707124E-13</v>
+        <v>2.0734670850869773E-13</v>
       </c>
       <c r="G77" t="n" s="0">
-        <v>1.992030891934186</v>
+        <v>7.219929354718862E-13</v>
       </c>
       <c r="H77" t="n" s="0">
-        <v>1.992030892266717</v>
+        <v>4.176619584185763E-15</v>
       </c>
       <c r="I77" t="n" s="0">
-        <v>8.908723486493791E-14</v>
+        <v>1.1495265314125381E-13</v>
       </c>
       <c r="J77" t="n" s="0">
-        <v>4.163238409583214E-11</v>
+        <v>5.401101186393556E-12</v>
       </c>
       <c r="K77" t="n" s="0">
-        <v>1.2192489960124512E-10</v>
+        <v>1.4624415481730107E-12</v>
       </c>
       <c r="L77" t="n" s="0">
-        <v>1.992030891860338</v>
+        <v>2.0463738937185622E-12</v>
       </c>
       <c r="M77" t="n" s="0">
-        <v>4.5839917277672935E-14</v>
+        <v>5.863292989322194E-13</v>
       </c>
       <c r="N77" t="n" s="0">
-        <v>1.172075796745E-16</v>
+        <v>1.3846065027446797E-12</v>
       </c>
       <c r="O77" t="n" s="0">
-        <v>3.7776499654257927E-13</v>
+        <v>2.6425611402185966E-13</v>
       </c>
       <c r="P77" t="n" s="0">
-        <v>9.371698193978799E-12</v>
+        <v>8.19231756616101E-11</v>
       </c>
       <c r="Q77" t="n" s="0">
-        <v>8.524885343475041E-11</v>
+        <v>1.1148047956068135E-12</v>
       </c>
       <c r="R77" t="n" s="0">
-        <v>1.1750927081173539E-13</v>
+        <v>3.935911749130261E-13</v>
       </c>
       <c r="S77" t="n" s="0">
-        <v>1.408809696158926E-12</v>
+        <v>1.3860334591120736E-14</v>
       </c>
       <c r="T77" t="n" s="0">
-        <v>1.0160904881573538E-12</v>
+        <v>0.9980037482485259</v>
       </c>
       <c r="U77" t="n" s="0">
-        <v>1.1969147547279718E-12</v>
+        <v>4.3102399687569713E-13</v>
       </c>
       <c r="V77" t="n" s="0">
-        <v>2.3965906291580227E-13</v>
+        <v>1.4989811535405185E-14</v>
       </c>
       <c r="W77" t="n" s="0">
-        <v>2.2518457211409417E-14</v>
+        <v>2.3384040358359933E-15</v>
       </c>
       <c r="X77" t="n" s="0">
-        <v>4.1093226882390195E-13</v>
+        <v>6.619404430459196E-11</v>
       </c>
       <c r="Y77" t="n" s="0">
-        <v>1.1285691672506015E-14</v>
+        <v>0.9980037483033825</v>
       </c>
       <c r="Z77" t="n" s="0">
-        <v>2.8059984960255902E-14</v>
+        <v>8.114698230119213E-13</v>
       </c>
       <c r="AA77" t="n" s="0">
-        <v>1.9920308920275251</v>
+        <v>1.9870008178726015E-12</v>
       </c>
       <c r="AB77" t="n" s="0">
-        <v>1.9920308923602401</v>
+        <v>1.9920308918666094</v>
       </c>
       <c r="AC77" t="n" s="0">
-        <v>0.9980037481878556</v>
+        <v>6.135200489668948E-13</v>
       </c>
       <c r="AD77" t="n" s="0">
-        <v>2.5533235454208204E-11</v>
+        <v>5.118542678417032E-16</v>
       </c>
       <c r="AE77" t="n" s="0">
-        <v>1.9920308918831104</v>
+        <v>1.33885427045734E-16</v>
       </c>
       <c r="AF77" t="n" s="0">
-        <v>2.322450051570617E-16</v>
+        <v>1.2171649253002482E-12</v>
       </c>
     </row>
     <row r="78">
       <c r="C78" t="n" s="0">
-        <v>3.074901165435902E-4</v>
+        <v>3.07793218264258E-4</v>
       </c>
       <c r="D78" t="n" s="0">
-        <v>3.0803143769787876E-4</v>
+        <v>3.0833127749291587E-4</v>
       </c>
       <c r="E78" t="n" s="0">
-        <v>3.1083191513504106E-4</v>
+        <v>3.076106049162496E-4</v>
       </c>
       <c r="F78" t="n" s="0">
-        <v>3.0756898153689173E-4</v>
+        <v>3.076007897637868E-4</v>
       </c>
       <c r="G78" t="n" s="0">
-        <v>3.0840661088474947E-4</v>
+        <v>3.169394175623251E-4</v>
       </c>
       <c r="H78" t="n" s="0">
-        <v>3.0879411484532676E-4</v>
+        <v>3.0883549457943267E-4</v>
       </c>
       <c r="I78" t="n" s="0">
-        <v>3.0842839170032416E-4</v>
+        <v>3.1874972722545955E-4</v>
       </c>
       <c r="J78" t="n" s="0">
-        <v>3.079456635146053E-4</v>
+        <v>3.111371325074917E-4</v>
       </c>
       <c r="K78" t="n" s="0">
-        <v>0.001596911074392318</v>
+        <v>3.104334945498647E-4</v>
       </c>
       <c r="L78" t="n" s="0">
-        <v>3.076686410928314E-4</v>
+        <v>4.362206844003856E-4</v>
       </c>
       <c r="M78" t="n" s="0">
-        <v>3.0755410706368076E-4</v>
+        <v>3.075434403996906E-4</v>
       </c>
       <c r="N78" t="n" s="0">
-        <v>3.084704240271979E-4</v>
+        <v>3.078150624469904E-4</v>
       </c>
       <c r="O78" t="n" s="0">
-        <v>3.080544767278245E-4</v>
+        <v>3.0892592253321555E-4</v>
       </c>
       <c r="P78" t="n" s="0">
-        <v>3.084194431453558E-4</v>
+        <v>3.077761948767346E-4</v>
       </c>
       <c r="Q78" t="n" s="0">
-        <v>3.0751377513135416E-4</v>
+        <v>3.080317119718721E-4</v>
       </c>
       <c r="R78" t="n" s="0">
-        <v>3.0859181875706365E-4</v>
+        <v>3.0842158742405105E-4</v>
       </c>
       <c r="S78" t="n" s="0">
-        <v>3.2291888079510065E-4</v>
+        <v>3.075913863683601E-4</v>
       </c>
       <c r="T78" t="n" s="0">
-        <v>3.075815201459618E-4</v>
+        <v>3.0753337533193895E-4</v>
       </c>
       <c r="U78" t="n" s="0">
-        <v>3.0797848667851377E-4</v>
+        <v>3.3595051776932677E-4</v>
       </c>
       <c r="V78" t="n" s="0">
-        <v>3.0885488094999704E-4</v>
+        <v>3.0803653266653634E-4</v>
       </c>
       <c r="W78" t="n" s="0">
-        <v>4.2624980584425425E-4</v>
+        <v>3.6682885831828215E-4</v>
       </c>
       <c r="X78" t="n" s="0">
-        <v>3.0806435835822106E-4</v>
+        <v>3.0751886929149383E-4</v>
       </c>
       <c r="Y78" t="n" s="0">
-        <v>3.07761807599319E-4</v>
+        <v>3.160571124163886E-4</v>
       </c>
       <c r="Z78" t="n" s="0">
-        <v>3.075871348593824E-4</v>
+        <v>3.075418069417646E-4</v>
       </c>
       <c r="AA78" t="n" s="0">
-        <v>3.0771282914942314E-4</v>
+        <v>3.0756556755761016E-4</v>
       </c>
       <c r="AB78" t="n" s="0">
-        <v>3.346710848240032E-4</v>
+        <v>3.0829612578256227E-4</v>
       </c>
       <c r="AC78" t="n" s="0">
-        <v>3.974782006806701E-4</v>
+        <v>3.279214017934949E-4</v>
       </c>
       <c r="AD78" t="n" s="0">
-        <v>3.190462342447608E-4</v>
+        <v>3.076864484134149E-4</v>
       </c>
       <c r="AE78" t="n" s="0">
-        <v>3.0824934060471156E-4</v>
+        <v>3.07964230408171E-4</v>
       </c>
       <c r="AF78" t="n" s="0">
-        <v>3.07823343300612E-4</v>
+        <v>3.0879157468438785E-4</v>
       </c>
     </row>
     <row r="79">
       <c r="C79" t="n" s="0">
-        <v>-1.0316284221947887</v>
+        <v>-1.0316283079488318</v>
       </c>
       <c r="D79" t="n" s="0">
-        <v>-1.0316284518536087</v>
+        <v>-1.0316282793395608</v>
       </c>
       <c r="E79" t="n" s="0">
-        <v>-1.0316282718857681</v>
+        <v>-1.0316284490419512</v>
       </c>
       <c r="F79" t="n" s="0">
-        <v>-1.0316283794606664</v>
+        <v>-1.0316284496318773</v>
       </c>
       <c r="G79" t="n" s="0">
-        <v>-1.0316284419510138</v>
+        <v>-1.031628449547973</v>
       </c>
       <c r="H79" t="n" s="0">
-        <v>-1.0316282642202754</v>
+        <v>-1.0316284282278738</v>
       </c>
       <c r="I79" t="n" s="0">
-        <v>-1.0316284193581955</v>
+        <v>-1.0316284272086034</v>
       </c>
       <c r="J79" t="n" s="0">
-        <v>-1.0316284171563772</v>
+        <v>-1.0316283947685407</v>
       </c>
       <c r="K79" t="n" s="0">
-        <v>-1.0316284040510884</v>
+        <v>-1.0316284475401383</v>
       </c>
       <c r="L79" t="n" s="0">
-        <v>-1.0316284206366026</v>
+        <v>-1.0316282906288954</v>
       </c>
       <c r="M79" t="n" s="0">
-        <v>-1.031628252339094</v>
+        <v>-1.03162799482726</v>
       </c>
       <c r="N79" t="n" s="0">
-        <v>-1.031628453447273</v>
+        <v>-1.0316284089339163</v>
       </c>
       <c r="O79" t="n" s="0">
-        <v>-1.031628349709469</v>
+        <v>-1.0316279601432785</v>
       </c>
       <c r="P79" t="n" s="0">
-        <v>-1.0316282978014657</v>
+        <v>-1.0316283570696876</v>
       </c>
       <c r="Q79" t="n" s="0">
-        <v>-1.031628371778927</v>
+        <v>-1.0316283713570138</v>
       </c>
       <c r="R79" t="n" s="0">
-        <v>-1.0316284223901808</v>
+        <v>-1.0316284265425213</v>
       </c>
       <c r="S79" t="n" s="0">
-        <v>-1.0316283916597864</v>
+        <v>-1.031628431608373</v>
       </c>
       <c r="T79" t="n" s="0">
-        <v>-1.031628409725293</v>
+        <v>-1.0316284260486777</v>
       </c>
       <c r="U79" t="n" s="0">
-        <v>-1.0316283775483766</v>
+        <v>-1.0316284267654752</v>
       </c>
       <c r="V79" t="n" s="0">
-        <v>-1.0316284517239367</v>
+        <v>-1.0316283926700398</v>
       </c>
       <c r="W79" t="n" s="0">
-        <v>-1.0316283798317405</v>
+        <v>-1.031628361612169</v>
       </c>
       <c r="X79" t="n" s="0">
-        <v>-1.031628434145176</v>
+        <v>-1.0316284365508672</v>
       </c>
       <c r="Y79" t="n" s="0">
-        <v>-1.0316284175183106</v>
+        <v>-1.0316284357995193</v>
       </c>
       <c r="Z79" t="n" s="0">
-        <v>-1.031628298954467</v>
+        <v>-1.0316278534229755</v>
       </c>
       <c r="AA79" t="n" s="0">
-        <v>-1.0316284411844754</v>
+        <v>-1.031628371267836</v>
       </c>
       <c r="AB79" t="n" s="0">
-        <v>-1.031628431759343</v>
+        <v>-1.0316281115120858</v>
       </c>
       <c r="AC79" t="n" s="0">
-        <v>-1.0316284050259674</v>
+        <v>-1.0316284478234619</v>
       </c>
       <c r="AD79" t="n" s="0">
-        <v>-1.0316284511075509</v>
+        <v>-1.0316284270109353</v>
       </c>
       <c r="AE79" t="n" s="0">
-        <v>-1.031628205337966</v>
+        <v>-1.0316281378635965</v>
       </c>
       <c r="AF79" t="n" s="0">
-        <v>-1.0316283520340654</v>
+        <v>-1.0316283951603535</v>
       </c>
     </row>
     <row r="80">
       <c r="C80" t="n" s="0">
-        <v>0.39788973040423414</v>
+        <v>0.3978978527019983</v>
       </c>
       <c r="D80" t="n" s="0">
-        <v>0.39788774975476215</v>
+        <v>0.39788741117860127</v>
       </c>
       <c r="E80" t="n" s="0">
-        <v>0.39788763508533975</v>
+        <v>0.39788752543685035</v>
       </c>
       <c r="F80" t="n" s="0">
-        <v>0.3978914228251984</v>
+        <v>0.3978878600644311</v>
       </c>
       <c r="G80" t="n" s="0">
-        <v>0.39788794978438347</v>
+        <v>0.397888920380316</v>
       </c>
       <c r="H80" t="n" s="0">
-        <v>0.3978878035240534</v>
+        <v>0.3978900548317288</v>
       </c>
       <c r="I80" t="n" s="0">
-        <v>0.39791077484419013</v>
+        <v>0.39788779286087994</v>
       </c>
       <c r="J80" t="n" s="0">
-        <v>0.3978886447713954</v>
+        <v>0.3978888280403261</v>
       </c>
       <c r="K80" t="n" s="0">
-        <v>0.3978875848077337</v>
+        <v>0.39788943877130123</v>
       </c>
       <c r="L80" t="n" s="0">
-        <v>0.39788790252276307</v>
+        <v>0.39788771674179735</v>
       </c>
       <c r="M80" t="n" s="0">
-        <v>0.3978930287984017</v>
+        <v>0.3978886279713141</v>
       </c>
       <c r="N80" t="n" s="0">
-        <v>0.397890326454867</v>
+        <v>0.39788885197497414</v>
       </c>
       <c r="O80" t="n" s="0">
-        <v>0.39788756129094693</v>
+        <v>0.3978877190435224</v>
       </c>
       <c r="P80" t="n" s="0">
-        <v>0.39788965986458</v>
+        <v>0.3978892685651534</v>
       </c>
       <c r="Q80" t="n" s="0">
-        <v>0.3978892762345936</v>
+        <v>0.39789064594070567</v>
       </c>
       <c r="R80" t="n" s="0">
-        <v>0.39788985766027274</v>
+        <v>0.39788738118709155</v>
       </c>
       <c r="S80" t="n" s="0">
-        <v>0.39788759117198147</v>
+        <v>0.3978874179780032</v>
       </c>
       <c r="T80" t="n" s="0">
-        <v>0.3978945131845446</v>
+        <v>0.3978911196376025</v>
       </c>
       <c r="U80" t="n" s="0">
-        <v>0.39788796085696454</v>
+        <v>0.39788758788853684</v>
       </c>
       <c r="V80" t="n" s="0">
-        <v>0.39788869549683703</v>
+        <v>0.39788890681030153</v>
       </c>
       <c r="W80" t="n" s="0">
-        <v>0.3978908248354127</v>
+        <v>0.3978884922335162</v>
       </c>
       <c r="X80" t="n" s="0">
-        <v>0.3978879217808924</v>
+        <v>0.3978899620985601</v>
       </c>
       <c r="Y80" t="n" s="0">
-        <v>0.39788860083844035</v>
+        <v>0.39788854800643136</v>
       </c>
       <c r="Z80" t="n" s="0">
-        <v>0.3978906091771748</v>
+        <v>0.3978881751975205</v>
       </c>
       <c r="AA80" t="n" s="0">
-        <v>0.39788743069936316</v>
+        <v>0.39788819371105966</v>
       </c>
       <c r="AB80" t="n" s="0">
-        <v>0.3978875592778728</v>
+        <v>0.39789131862520577</v>
       </c>
       <c r="AC80" t="n" s="0">
-        <v>0.3978916180438521</v>
+        <v>0.3978894501046941</v>
       </c>
       <c r="AD80" t="n" s="0">
-        <v>0.3978873967290948</v>
+        <v>0.3978910911790443</v>
       </c>
       <c r="AE80" t="n" s="0">
-        <v>0.39789151490476193</v>
+        <v>0.39788746683243836</v>
       </c>
       <c r="AF80" t="n" s="0">
-        <v>0.3978874359613318</v>
+        <v>0.3978876136901537</v>
       </c>
     </row>
     <row r="81">
       <c r="C81" t="n" s="0">
-        <v>3.0000647376138274</v>
+        <v>3.000136253397829</v>
       </c>
       <c r="D81" t="n" s="0">
-        <v>3.0000170108855464</v>
+        <v>3.0002904736456455</v>
       </c>
       <c r="E81" t="n" s="0">
-        <v>3.0000053973819982</v>
+        <v>3.000008185921409</v>
       </c>
       <c r="F81" t="n" s="0">
-        <v>3.0002034055701463</v>
+        <v>3.000011859692303</v>
       </c>
       <c r="G81" t="n" s="0">
-        <v>3.000046999186742</v>
+        <v>3.0000025198905456</v>
       </c>
       <c r="H81" t="n" s="0">
-        <v>3.000004232957604</v>
+        <v>3.000040285337383</v>
       </c>
       <c r="I81" t="n" s="0">
-        <v>3.000038593597653</v>
+        <v>3.0000038956422155</v>
       </c>
       <c r="J81" t="n" s="0">
-        <v>3.0000065053108225</v>
+        <v>3.000020469937387</v>
       </c>
       <c r="K81" t="n" s="0">
-        <v>3.00000661008756</v>
+        <v>3.000046425572341</v>
       </c>
       <c r="L81" t="n" s="0">
-        <v>3.0000511465123667</v>
+        <v>3.000032984366768</v>
       </c>
       <c r="M81" t="n" s="0">
-        <v>3.0000026576736354</v>
+        <v>3.0000010443416323</v>
       </c>
       <c r="N81" t="n" s="0">
-        <v>3.000071096195471</v>
+        <v>3.0000145501817714</v>
       </c>
       <c r="O81" t="n" s="0">
-        <v>3.000002347725947</v>
+        <v>3.0000034409075234</v>
       </c>
       <c r="P81" t="n" s="0">
-        <v>3.0000283499576605</v>
+        <v>3.0000084260350777</v>
       </c>
       <c r="Q81" t="n" s="0">
-        <v>3.000011111814517</v>
+        <v>3.0003989699882463</v>
       </c>
       <c r="R81" t="n" s="0">
-        <v>3.000006538757421</v>
+        <v>3.0000025576693385</v>
       </c>
       <c r="S81" t="n" s="0">
-        <v>3.0000032139730655</v>
+        <v>3.000000839593826</v>
       </c>
       <c r="T81" t="n" s="0">
-        <v>3.000019714254903</v>
+        <v>3.0000731085962085</v>
       </c>
       <c r="U81" t="n" s="0">
-        <v>3.0000154676610506</v>
+        <v>3.00000615623541</v>
       </c>
       <c r="V81" t="n" s="0">
-        <v>3.0000093134576313</v>
+        <v>3.0000078036768394</v>
       </c>
       <c r="W81" t="n" s="0">
-        <v>3.0000157969019745</v>
+        <v>3.0000090396438845</v>
       </c>
       <c r="X81" t="n" s="0">
-        <v>3.000033136202853</v>
+        <v>3.00011282120007</v>
       </c>
       <c r="Y81" t="n" s="0">
-        <v>3.0000855451421016</v>
+        <v>3.000013918702219</v>
       </c>
       <c r="Z81" t="n" s="0">
-        <v>3.0000068686402916</v>
+        <v>3.000002463977869</v>
       </c>
       <c r="AA81" t="n" s="0">
-        <v>3.0000082328996904</v>
+        <v>3.0000012647248697</v>
       </c>
       <c r="AB81" t="n" s="0">
-        <v>3.0000007589187803</v>
+        <v>3.0000172926690176</v>
       </c>
       <c r="AC81" t="n" s="0">
-        <v>3.0000625662172227</v>
+        <v>3.000085848725756</v>
       </c>
       <c r="AD81" t="n" s="0">
-        <v>3.000000395435125</v>
+        <v>3.0000020224830823</v>
       </c>
       <c r="AE81" t="n" s="0">
-        <v>3.000013491327966</v>
+        <v>3.000059770604836</v>
       </c>
       <c r="AF81" t="n" s="0">
-        <v>3.0000296940543727</v>
+        <v>3.000057464194572</v>
       </c>
     </row>
     <row r="82">
       <c r="C82" t="n" s="0">
-        <v>-3.8621361709925703</v>
+        <v>-3.8626264958655048</v>
       </c>
       <c r="D82" t="n" s="0">
-        <v>-3.8627779368999704</v>
+        <v>-3.8613572352967074</v>
       </c>
       <c r="E82" t="n" s="0">
-        <v>-3.8625970111682166</v>
+        <v>-3.862626107244454</v>
       </c>
       <c r="F82" t="n" s="0">
-        <v>-3.862751405705236</v>
+        <v>-3.8610638947045075</v>
       </c>
       <c r="G82" t="n" s="0">
-        <v>-3.862746354310872</v>
+        <v>-3.862768301636067</v>
       </c>
       <c r="H82" t="n" s="0">
-        <v>-3.862737971915535</v>
+        <v>-3.862761993318091</v>
       </c>
       <c r="I82" t="n" s="0">
-        <v>-3.862777498427034</v>
+        <v>-3.862679025028885</v>
       </c>
       <c r="J82" t="n" s="0">
-        <v>-3.862448624894747</v>
+        <v>-3.862602695304808</v>
       </c>
       <c r="K82" t="n" s="0">
-        <v>-3.862672015322707</v>
+        <v>-3.862610704971748</v>
       </c>
       <c r="L82" t="n" s="0">
-        <v>-3.8627741632729826</v>
+        <v>-3.862779020909939</v>
       </c>
       <c r="M82" t="n" s="0">
-        <v>-3.862343617723087</v>
+        <v>-3.8627645230268897</v>
       </c>
       <c r="N82" t="n" s="0">
-        <v>-3.8627817211576616</v>
+        <v>-3.862547892771567</v>
       </c>
       <c r="O82" t="n" s="0">
-        <v>-3.862778736850408</v>
+        <v>-3.8625314997546907</v>
       </c>
       <c r="P82" t="n" s="0">
-        <v>-3.8627756732870946</v>
+        <v>-3.862585115991818</v>
       </c>
       <c r="Q82" t="n" s="0">
-        <v>-3.86270402724686</v>
+        <v>-3.8626907754584385</v>
       </c>
       <c r="R82" t="n" s="0">
-        <v>-3.862779168264189</v>
+        <v>-3.862759315086644</v>
       </c>
       <c r="S82" t="n" s="0">
-        <v>-3.862718821294182</v>
+        <v>-3.8627768998406533</v>
       </c>
       <c r="T82" t="n" s="0">
-        <v>-3.8621878004169803</v>
+        <v>-3.8626609551611977</v>
       </c>
       <c r="U82" t="n" s="0">
-        <v>-3.8623708610478595</v>
+        <v>-3.862466247816157</v>
       </c>
       <c r="V82" t="n" s="0">
-        <v>-3.8625750914726362</v>
+        <v>-3.86275029602903</v>
       </c>
       <c r="W82" t="n" s="0">
-        <v>-3.862738068911289</v>
+        <v>-3.8626897641879516</v>
       </c>
       <c r="X82" t="n" s="0">
-        <v>-3.8626718165299327</v>
+        <v>-3.862758638950541</v>
       </c>
       <c r="Y82" t="n" s="0">
-        <v>-3.862746964308856</v>
+        <v>-3.8627698387825724</v>
       </c>
       <c r="Z82" t="n" s="0">
-        <v>-3.862191010325296</v>
+        <v>-3.8626921326749413</v>
       </c>
       <c r="AA82" t="n" s="0">
-        <v>-3.8626834588056944</v>
+        <v>-3.8626120569269182</v>
       </c>
       <c r="AB82" t="n" s="0">
-        <v>-3.8623621406901973</v>
+        <v>-3.862745945894356</v>
       </c>
       <c r="AC82" t="n" s="0">
-        <v>-3.86275273064762</v>
+        <v>-3.862657678595419</v>
       </c>
       <c r="AD82" t="n" s="0">
-        <v>-3.8627115837808343</v>
+        <v>-3.862769476638541</v>
       </c>
       <c r="AE82" t="n" s="0">
-        <v>-3.8627760070016164</v>
+        <v>-3.862756558059356</v>
       </c>
       <c r="AF82" t="n" s="0">
-        <v>-3.8627580974792535</v>
+        <v>-3.8620468667615224</v>
       </c>
     </row>
     <row r="83">
       <c r="C83" t="n" s="0">
-        <v>-3.321988377780287</v>
+        <v>-3.3219546426729654</v>
       </c>
       <c r="D83" t="n" s="0">
-        <v>-3.3219753605528446</v>
+        <v>-3.32198016026141</v>
       </c>
       <c r="E83" t="n" s="0">
-        <v>-3.3219925494500817</v>
+        <v>-3.3219864598701196</v>
       </c>
       <c r="F83" t="n" s="0">
-        <v>-3.321966688489147</v>
+        <v>-3.3219906712062848</v>
       </c>
       <c r="G83" t="n" s="0">
-        <v>-3.3219836786091803</v>
+        <v>-3.321986936669252</v>
       </c>
       <c r="H83" t="n" s="0">
-        <v>-3.321950945628678</v>
+        <v>-3.321976689002787</v>
       </c>
       <c r="I83" t="n" s="0">
-        <v>-3.3219772960642557</v>
+        <v>-3.3219462900267382</v>
       </c>
       <c r="J83" t="n" s="0">
-        <v>-3.3219424171512753</v>
+        <v>-3.321944186522288</v>
       </c>
       <c r="K83" t="n" s="0">
-        <v>-3.3219558247797907</v>
+        <v>-3.321945479388929</v>
       </c>
       <c r="L83" t="n" s="0">
-        <v>-3.3219831861356517</v>
+        <v>-3.321991994132544</v>
       </c>
       <c r="M83" t="n" s="0">
-        <v>-3.3219538294326214</v>
+        <v>-3.321975917986641</v>
       </c>
       <c r="N83" t="n" s="0">
-        <v>-3.321937091028231</v>
+        <v>-3.321980513007058</v>
       </c>
       <c r="O83" t="n" s="0">
-        <v>-3.321987447846795</v>
+        <v>-3.3219644824303565</v>
       </c>
       <c r="P83" t="n" s="0">
-        <v>-3.3219651774001258</v>
+        <v>-3.32197075476224</v>
       </c>
       <c r="Q83" t="n" s="0">
-        <v>-3.3219674395157353</v>
+        <v>-3.321931559356777</v>
       </c>
       <c r="R83" t="n" s="0">
-        <v>-3.3219630512662297</v>
+        <v>-3.321974843739886</v>
       </c>
       <c r="S83" t="n" s="0">
-        <v>-3.321983986715303</v>
+        <v>-3.3219924831741223</v>
       </c>
       <c r="T83" t="n" s="0">
-        <v>-3.3219823810674227</v>
+        <v>-3.3219680696881104</v>
       </c>
       <c r="U83" t="n" s="0">
-        <v>-3.3219890586051077</v>
+        <v>-3.321992094339995</v>
       </c>
       <c r="V83" t="n" s="0">
-        <v>-3.321955427054053</v>
+        <v>-3.3219873129216833</v>
       </c>
       <c r="W83" t="n" s="0">
-        <v>-3.321965123635389</v>
+        <v>-3.3219836283294346</v>
       </c>
       <c r="X83" t="n" s="0">
-        <v>-3.321982539912525</v>
+        <v>-3.3219214432176654</v>
       </c>
       <c r="Y83" t="n" s="0">
-        <v>-3.3219845769492906</v>
+        <v>-3.3219832875388957</v>
       </c>
       <c r="Z83" t="n" s="0">
-        <v>-3.3219341766563066</v>
+        <v>-3.321973752689322</v>
       </c>
       <c r="AA83" t="n" s="0">
-        <v>-3.321976936916893</v>
+        <v>-3.321984361230689</v>
       </c>
       <c r="AB83" t="n" s="0">
-        <v>-3.321991267505781</v>
+        <v>-3.3219234862111375</v>
       </c>
       <c r="AC83" t="n" s="0">
-        <v>-3.3219670843074156</v>
+        <v>-3.3219840389481456</v>
       </c>
       <c r="AD83" t="n" s="0">
-        <v>-3.321973662331724</v>
+        <v>-3.321933127058405</v>
       </c>
       <c r="AE83" t="n" s="0">
-        <v>-3.3219863232608797</v>
+        <v>-3.3219676652866594</v>
       </c>
       <c r="AF83" t="n" s="0">
-        <v>-3.321984001483755</v>
+        <v>-3.3219874067520525</v>
       </c>
     </row>
     <row r="84">
       <c r="C84" t="n" s="0">
-        <v>-10.152600036771506</v>
+        <v>-10.151430121773409</v>
       </c>
       <c r="D84" t="n" s="0">
-        <v>-10.151524883797514</v>
+        <v>-10.151766071609222</v>
       </c>
       <c r="E84" t="n" s="0">
-        <v>-10.152572215567066</v>
+        <v>-10.15296555188321</v>
       </c>
       <c r="F84" t="n" s="0">
-        <v>-10.151276159354584</v>
+        <v>-10.15245111235019</v>
       </c>
       <c r="G84" t="n" s="0">
-        <v>-10.150551124775005</v>
+        <v>-10.15061201464068</v>
       </c>
       <c r="H84" t="n" s="0">
-        <v>-10.151933984896356</v>
+        <v>-10.145811599753904</v>
       </c>
       <c r="I84" t="n" s="0">
-        <v>-10.150895558115554</v>
+        <v>-10.151217179734797</v>
       </c>
       <c r="J84" t="n" s="0">
-        <v>-10.151769955534927</v>
+        <v>-10.152274885871366</v>
       </c>
       <c r="K84" t="n" s="0">
-        <v>-10.152051370144445</v>
+        <v>-10.152569391329061</v>
       </c>
       <c r="L84" t="n" s="0">
-        <v>-10.151157646651058</v>
+        <v>-10.152915827731542</v>
       </c>
       <c r="M84" t="n" s="0">
-        <v>-10.145277152423432</v>
+        <v>-10.15146872535966</v>
       </c>
       <c r="N84" t="n" s="0">
-        <v>-10.151756551037273</v>
+        <v>-10.151622225031302</v>
       </c>
       <c r="O84" t="n" s="0">
-        <v>-10.1527964697483</v>
+        <v>-10.1520322620371</v>
       </c>
       <c r="P84" t="n" s="0">
-        <v>-10.152272170611413</v>
+        <v>-10.151283357264525</v>
       </c>
       <c r="Q84" t="n" s="0">
-        <v>-10.152811014372768</v>
+        <v>-10.152201274783627</v>
       </c>
       <c r="R84" t="n" s="0">
-        <v>-10.152060178897603</v>
+        <v>-10.151803625269103</v>
       </c>
       <c r="S84" t="n" s="0">
-        <v>-10.152605264429637</v>
+        <v>-10.151700345958789</v>
       </c>
       <c r="T84" t="n" s="0">
-        <v>-10.151877788997039</v>
+        <v>-10.152987440604061</v>
       </c>
       <c r="U84" t="n" s="0">
-        <v>-10.15282640836395</v>
+        <v>-10.152827261831083</v>
       </c>
       <c r="V84" t="n" s="0">
-        <v>-10.152230087248993</v>
+        <v>-10.148990600684808</v>
       </c>
       <c r="W84" t="n" s="0">
-        <v>-5.099024612563444</v>
+        <v>-10.152668843761692</v>
       </c>
       <c r="X84" t="n" s="0">
-        <v>-10.151806439221442</v>
+        <v>-10.153038955355179</v>
       </c>
       <c r="Y84" t="n" s="0">
-        <v>-10.15212913783032</v>
+        <v>-10.152401392251695</v>
       </c>
       <c r="Z84" t="n" s="0">
-        <v>-10.152628345603246</v>
+        <v>-10.152492327697377</v>
       </c>
       <c r="AA84" t="n" s="0">
-        <v>-10.14752399179401</v>
+        <v>-10.150687257870997</v>
       </c>
       <c r="AB84" t="n" s="0">
-        <v>-10.151323467858814</v>
+        <v>-10.15189330201634</v>
       </c>
       <c r="AC84" t="n" s="0">
-        <v>-10.152110152359782</v>
+        <v>-10.150993333415927</v>
       </c>
       <c r="AD84" t="n" s="0">
-        <v>-10.15255840890058</v>
+        <v>-10.151817529581596</v>
       </c>
       <c r="AE84" t="n" s="0">
-        <v>-10.15220417659033</v>
+        <v>-10.152304877249591</v>
       </c>
       <c r="AF84" t="n" s="0">
-        <v>-10.150994352150077</v>
+        <v>-10.151019256384103</v>
       </c>
     </row>
     <row r="85">
       <c r="C85" t="n" s="0">
-        <v>-10.399857230469754</v>
+        <v>-10.402136445728587</v>
       </c>
       <c r="D85" t="n" s="0">
-        <v>-10.397991731606828</v>
+        <v>-10.398496870568854</v>
       </c>
       <c r="E85" t="n" s="0">
-        <v>-10.400457249002704</v>
+        <v>-10.40146395284373</v>
       </c>
       <c r="F85" t="n" s="0">
-        <v>-10.400107738087288</v>
+        <v>-10.400219704646997</v>
       </c>
       <c r="G85" t="n" s="0">
-        <v>-10.40102748141713</v>
+        <v>-10.402667717289308</v>
       </c>
       <c r="H85" t="n" s="0">
-        <v>-10.402522060029334</v>
+        <v>-10.399892707458491</v>
       </c>
       <c r="I85" t="n" s="0">
-        <v>-10.40264479808204</v>
+        <v>-10.39914302923322</v>
       </c>
       <c r="J85" t="n" s="0">
-        <v>-10.398282213984286</v>
+        <v>-10.399606527268904</v>
       </c>
       <c r="K85" t="n" s="0">
-        <v>-10.396620709869973</v>
+        <v>-10.401625788627758</v>
       </c>
       <c r="L85" t="n" s="0">
-        <v>-10.401842371713139</v>
+        <v>-10.401163156713697</v>
       </c>
       <c r="M85" t="n" s="0">
-        <v>-5.123451751619901</v>
+        <v>-10.402626298951029</v>
       </c>
       <c r="N85" t="n" s="0">
-        <v>-10.402613469117385</v>
+        <v>-10.401368480485955</v>
       </c>
       <c r="O85" t="n" s="0">
-        <v>-10.402161612067657</v>
+        <v>-10.402736115382698</v>
       </c>
       <c r="P85" t="n" s="0">
-        <v>-10.397129627937547</v>
+        <v>-10.402408070674744</v>
       </c>
       <c r="Q85" t="n" s="0">
-        <v>-10.401695326647028</v>
+        <v>-10.401981416268928</v>
       </c>
       <c r="R85" t="n" s="0">
-        <v>-10.402812925755779</v>
+        <v>-10.398129649981556</v>
       </c>
       <c r="S85" t="n" s="0">
-        <v>-10.402618403132191</v>
+        <v>-10.399946356722998</v>
       </c>
       <c r="T85" t="n" s="0">
-        <v>-10.401222629148057</v>
+        <v>-10.40140019432413</v>
       </c>
       <c r="U85" t="n" s="0">
-        <v>-10.402765667508312</v>
+        <v>-10.400923061133486</v>
       </c>
       <c r="V85" t="n" s="0">
-        <v>-10.402444506031328</v>
+        <v>-10.401043371226251</v>
       </c>
       <c r="W85" t="n" s="0">
-        <v>-10.401305121761052</v>
+        <v>-10.40224995461115</v>
       </c>
       <c r="X85" t="n" s="0">
-        <v>-10.402619945434154</v>
+        <v>-10.400140878712712</v>
       </c>
       <c r="Y85" t="n" s="0">
-        <v>-10.401292536637737</v>
+        <v>-10.401545478334977</v>
       </c>
       <c r="Z85" t="n" s="0">
-        <v>-10.401800631502823</v>
+        <v>-10.401901666645495</v>
       </c>
       <c r="AA85" t="n" s="0">
-        <v>-10.402509410257341</v>
+        <v>-10.400598970933606</v>
       </c>
       <c r="AB85" t="n" s="0">
-        <v>-10.402254110912647</v>
+        <v>-10.402165427191454</v>
       </c>
       <c r="AC85" t="n" s="0">
-        <v>-10.402674979229362</v>
+        <v>-10.400125763623084</v>
       </c>
       <c r="AD85" t="n" s="0">
-        <v>-10.4010870082656</v>
+        <v>-10.400781489227507</v>
       </c>
       <c r="AE85" t="n" s="0">
-        <v>-5.127884182714614</v>
+        <v>-5.12780210427458</v>
       </c>
       <c r="AF85" t="n" s="0">
-        <v>-10.40202026794173</v>
+        <v>-10.399304675243197</v>
       </c>
     </row>
     <row r="86">
       <c r="C86" t="n" s="0">
-        <v>-10.534667662971675</v>
+        <v>-5.172367369727749</v>
       </c>
       <c r="D86" t="n" s="0">
-        <v>-10.535986163766212</v>
+        <v>-10.535757941247624</v>
       </c>
       <c r="E86" t="n" s="0">
-        <v>-10.536324404905685</v>
+        <v>-10.535996971686503</v>
       </c>
       <c r="F86" t="n" s="0">
-        <v>-10.534137132338575</v>
+        <v>-10.531014055433841</v>
       </c>
       <c r="G86" t="n" s="0">
-        <v>-10.531699191402724</v>
+        <v>-10.53535691752018</v>
       </c>
       <c r="H86" t="n" s="0">
-        <v>-10.536054948297524</v>
+        <v>-10.535184070335934</v>
       </c>
       <c r="I86" t="n" s="0">
-        <v>-10.53468794185962</v>
+        <v>-10.535894567418502</v>
       </c>
       <c r="J86" t="n" s="0">
-        <v>-10.532177245345121</v>
+        <v>-10.535554533834988</v>
       </c>
       <c r="K86" t="n" s="0">
-        <v>-10.535891293141109</v>
+        <v>-10.531739129662101</v>
       </c>
       <c r="L86" t="n" s="0">
-        <v>-10.534011449418326</v>
+        <v>-10.536241407168779</v>
       </c>
       <c r="M86" t="n" s="0">
-        <v>-10.534450319063726</v>
+        <v>-10.535882940352334</v>
       </c>
       <c r="N86" t="n" s="0">
-        <v>-10.535937942046099</v>
+        <v>-10.534822266118193</v>
       </c>
       <c r="O86" t="n" s="0">
-        <v>-10.533676053170538</v>
+        <v>-10.535055821061448</v>
       </c>
       <c r="P86" t="n" s="0">
-        <v>-10.535513061713734</v>
+        <v>-10.53493416004627</v>
       </c>
       <c r="Q86" t="n" s="0">
-        <v>-10.534967677652473</v>
+        <v>-10.531113027969385</v>
       </c>
       <c r="R86" t="n" s="0">
-        <v>-10.536210638743546</v>
+        <v>-10.535949771089472</v>
       </c>
       <c r="S86" t="n" s="0">
-        <v>-10.535469635873577</v>
+        <v>-10.533258245203863</v>
       </c>
       <c r="T86" t="n" s="0">
-        <v>-10.536315377441532</v>
+        <v>-10.534785826498425</v>
       </c>
       <c r="U86" t="n" s="0">
-        <v>-10.534051134612207</v>
+        <v>-5.173755041985378</v>
       </c>
       <c r="V86" t="n" s="0">
-        <v>-10.535956473749042</v>
+        <v>-10.53534990022372</v>
       </c>
       <c r="W86" t="n" s="0">
-        <v>-10.535907978941552</v>
+        <v>-10.536095891008175</v>
       </c>
       <c r="X86" t="n" s="0">
-        <v>-10.535795560646596</v>
+        <v>-10.535027348747288</v>
       </c>
       <c r="Y86" t="n" s="0">
-        <v>-5.174893536205535</v>
+        <v>-10.535956551704405</v>
       </c>
       <c r="Z86" t="n" s="0">
-        <v>-10.536105601416812</v>
+        <v>-10.535360650544197</v>
       </c>
       <c r="AA86" t="n" s="0">
-        <v>-10.53540137263511</v>
+        <v>-10.53321981799693</v>
       </c>
       <c r="AB86" t="n" s="0">
-        <v>-10.53593285700811</v>
+        <v>-10.535547176794314</v>
       </c>
       <c r="AC86" t="n" s="0">
-        <v>-10.535331736733172</v>
+        <v>-10.5351807628564</v>
       </c>
       <c r="AD86" t="n" s="0">
-        <v>-10.534305573417765</v>
+        <v>-10.535901484656035</v>
       </c>
       <c r="AE86" t="n" s="0">
-        <v>-10.533611540361914</v>
+        <v>-10.535102837627557</v>
       </c>
       <c r="AF86" t="n" s="0">
-        <v>-10.535649970940833</v>
+        <v>-10.535956630464387</v>
       </c>
     </row>
   </sheetData>
